--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B083968-A506-4140-9CE1-E249DB8920EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BED0DFEE-367F-4E92-9C10-E4C88A1BD3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="28800" windowHeight="11295" xr2:uid="{0E31E147-4E30-43D8-BA3A-4F46A6E577A5}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="28800" windowHeight="11295" xr2:uid="{57221A63-0445-4D81-A640-CA5D9D8D6192}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -2201,8 +2201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33B50ED-4873-4DAF-A854-DE816F729AE8}">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DDFC2ED-1F33-4B0B-8FC7-E1D84169068B}">
   <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -16465,8 +16464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C02E35AE-8652-4992-81CC-614822808880}">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A1055A-FBB8-45A5-A8E6-D8A5E2A11D84}">
   <dimension ref="A1:J410"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BED0DFEE-367F-4E92-9C10-E4C88A1BD3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13D8985F-45EA-4C2E-A5B9-4F7075A370A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="28800" windowHeight="11295" xr2:uid="{57221A63-0445-4D81-A640-CA5D9D8D6192}"/>
+    <workbookView xWindow="3180" yWindow="960" windowWidth="28800" windowHeight="11295" xr2:uid="{19E1BBB0-DC4C-4774-A6C7-81C368F39362}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -2201,7 +2201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DDFC2ED-1F33-4B0B-8FC7-E1D84169068B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF450AFD-A21E-4812-ADAB-54724B3D4D01}">
   <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -16464,7 +16464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A1055A-FBB8-45A5-A8E6-D8A5E2A11D84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA804C6-5811-40DC-A4A3-C34262A8354C}">
   <dimension ref="A1:J410"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13D8985F-45EA-4C2E-A5B9-4F7075A370A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D6EBA2A-96F4-471E-A030-E21A90A1F3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="960" windowWidth="28800" windowHeight="11295" xr2:uid="{19E1BBB0-DC4C-4774-A6C7-81C368F39362}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{6A530734-1423-4229-84C6-E0E8AC0E0AC5}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4863" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4891" uniqueCount="592">
   <si>
     <t>날짜</t>
   </si>
@@ -2201,7 +2201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF450AFD-A21E-4812-ADAB-54724B3D4D01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE6036C-661A-4286-963D-6B5BAE8484CC}">
   <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -8441,13 +8441,13 @@
         <v>260</v>
       </c>
       <c r="G112">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H112">
         <v>0</v>
       </c>
       <c r="I112">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -8456,16 +8456,16 @@
         <v>178</v>
       </c>
       <c r="L112">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M112">
         <v>0</v>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P112" t="s">
         <v>16</v>
@@ -8553,13 +8553,13 @@
         <v>270</v>
       </c>
       <c r="G114">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -8568,16 +8568,16 @@
         <v>178</v>
       </c>
       <c r="L114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M114">
         <v>0</v>
       </c>
       <c r="N114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P114" t="s">
         <v>16</v>
@@ -9673,13 +9673,13 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -9688,16 +9688,16 @@
         <v>178</v>
       </c>
       <c r="L134">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M134">
         <v>6</v>
       </c>
       <c r="N134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O134">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P134" t="s">
         <v>16</v>
@@ -11857,13 +11857,13 @@
         <v>240</v>
       </c>
       <c r="G173">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H173">
         <v>0</v>
       </c>
       <c r="I173">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -11872,16 +11872,16 @@
         <v>178</v>
       </c>
       <c r="L173">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M173">
         <v>0</v>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O173">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P173" t="s">
         <v>16</v>
@@ -12361,13 +12361,13 @@
         <v>235</v>
       </c>
       <c r="G182">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H182">
         <v>0</v>
       </c>
       <c r="I182">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -12376,16 +12376,16 @@
         <v>178</v>
       </c>
       <c r="L182">
+        <v>5</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>3</v>
+      </c>
+      <c r="O182">
         <v>4</v>
-      </c>
-      <c r="M182">
-        <v>1</v>
-      </c>
-      <c r="N182">
-        <v>2</v>
-      </c>
-      <c r="O182">
-        <v>3</v>
       </c>
       <c r="P182" t="s">
         <v>16</v>
@@ -12585,13 +12585,13 @@
         <v>255</v>
       </c>
       <c r="G186">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H186">
         <v>0</v>
       </c>
       <c r="I186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -12600,16 +12600,16 @@
         <v>178</v>
       </c>
       <c r="L186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M186">
         <v>0</v>
       </c>
       <c r="N186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P186" t="s">
         <v>16</v>
@@ -16464,8 +16464,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA804C6-5811-40DC-A4A3-C34262A8354C}">
-  <dimension ref="A1:J410"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D206C9F4-AD80-4982-BFB7-01580D76919C}">
+  <dimension ref="A1:J417"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -29585,6 +29585,146 @@
         <v>1</v>
       </c>
       <c r="J410" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A411" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B411" t="s">
+        <v>52</v>
+      </c>
+      <c r="E411" t="s">
+        <v>53</v>
+      </c>
+      <c r="F411" t="s">
+        <v>94</v>
+      </c>
+      <c r="I411">
+        <v>1</v>
+      </c>
+      <c r="J411" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A412" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B412" t="s">
+        <v>61</v>
+      </c>
+      <c r="E412" t="s">
+        <v>53</v>
+      </c>
+      <c r="F412" t="s">
+        <v>94</v>
+      </c>
+      <c r="I412">
+        <v>1</v>
+      </c>
+      <c r="J412" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A413" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B413" t="s">
+        <v>27</v>
+      </c>
+      <c r="E413" t="s">
+        <v>53</v>
+      </c>
+      <c r="F413" t="s">
+        <v>94</v>
+      </c>
+      <c r="I413">
+        <v>1</v>
+      </c>
+      <c r="J413" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A414" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B414" t="s">
+        <v>107</v>
+      </c>
+      <c r="E414" t="s">
+        <v>130</v>
+      </c>
+      <c r="F414" t="s">
+        <v>131</v>
+      </c>
+      <c r="I414">
+        <v>1</v>
+      </c>
+      <c r="J414" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A415" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B415" t="s">
+        <v>26</v>
+      </c>
+      <c r="E415" t="s">
+        <v>100</v>
+      </c>
+      <c r="F415" t="s">
+        <v>94</v>
+      </c>
+      <c r="I415">
+        <v>1</v>
+      </c>
+      <c r="J415" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A416" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B416" t="s">
+        <v>160</v>
+      </c>
+      <c r="E416" t="s">
+        <v>100</v>
+      </c>
+      <c r="F416" t="s">
+        <v>94</v>
+      </c>
+      <c r="I416">
+        <v>1</v>
+      </c>
+      <c r="J416" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A417" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B417" t="s">
+        <v>26</v>
+      </c>
+      <c r="E417" t="s">
+        <v>100</v>
+      </c>
+      <c r="F417" t="s">
+        <v>94</v>
+      </c>
+      <c r="I417">
+        <v>1</v>
+      </c>
+      <c r="J417" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D6EBA2A-96F4-471E-A030-E21A90A1F3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B52D5915-654C-4557-B3E8-675FBED9857B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{6A530734-1423-4229-84C6-E0E8AC0E0AC5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{A026C6F0-B722-4E5E-8C2E-9852D804BFC6}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4891" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4912" uniqueCount="592">
   <si>
     <t>날짜</t>
   </si>
@@ -2201,7 +2201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE6036C-661A-4286-963D-6B5BAE8484CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FBFE95-82B5-4084-97F9-13572F9B571F}">
   <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -16464,7 +16464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D206C9F4-AD80-4982-BFB7-01580D76919C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407C3041-C9BB-4CD8-A81E-DEF1395761BD}">
   <dimension ref="A1:J417"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -29595,11 +29595,23 @@
       <c r="B411" t="s">
         <v>52</v>
       </c>
+      <c r="C411" t="s">
+        <v>24</v>
+      </c>
+      <c r="D411" t="s">
+        <v>38</v>
+      </c>
       <c r="E411" t="s">
         <v>53</v>
       </c>
       <c r="F411" t="s">
         <v>94</v>
+      </c>
+      <c r="G411">
+        <v>260</v>
+      </c>
+      <c r="H411" t="s">
+        <v>15</v>
       </c>
       <c r="I411">
         <v>1</v>
@@ -29615,11 +29627,23 @@
       <c r="B412" t="s">
         <v>61</v>
       </c>
+      <c r="C412" t="s">
+        <v>18</v>
+      </c>
+      <c r="D412" t="s">
+        <v>21</v>
+      </c>
       <c r="E412" t="s">
         <v>53</v>
       </c>
       <c r="F412" t="s">
         <v>94</v>
+      </c>
+      <c r="G412">
+        <v>245</v>
+      </c>
+      <c r="H412" t="s">
+        <v>22</v>
       </c>
       <c r="I412">
         <v>1</v>
@@ -29635,11 +29659,23 @@
       <c r="B413" t="s">
         <v>27</v>
       </c>
+      <c r="C413" t="s">
+        <v>24</v>
+      </c>
+      <c r="D413" t="s">
+        <v>25</v>
+      </c>
       <c r="E413" t="s">
         <v>53</v>
       </c>
       <c r="F413" t="s">
         <v>94</v>
+      </c>
+      <c r="G413">
+        <v>235</v>
+      </c>
+      <c r="H413" t="s">
+        <v>22</v>
       </c>
       <c r="I413">
         <v>1</v>
@@ -29655,11 +29691,23 @@
       <c r="B414" t="s">
         <v>107</v>
       </c>
+      <c r="C414" t="s">
+        <v>24</v>
+      </c>
+      <c r="D414" t="s">
+        <v>38</v>
+      </c>
       <c r="E414" t="s">
         <v>130</v>
       </c>
       <c r="F414" t="s">
         <v>131</v>
+      </c>
+      <c r="G414">
+        <v>270</v>
+      </c>
+      <c r="H414" t="s">
+        <v>15</v>
       </c>
       <c r="I414">
         <v>1</v>
@@ -29675,11 +29723,23 @@
       <c r="B415" t="s">
         <v>26</v>
       </c>
+      <c r="C415" t="s">
+        <v>24</v>
+      </c>
+      <c r="D415" t="s">
+        <v>25</v>
+      </c>
       <c r="E415" t="s">
         <v>100</v>
       </c>
       <c r="F415" t="s">
         <v>94</v>
+      </c>
+      <c r="G415">
+        <v>240</v>
+      </c>
+      <c r="H415" t="s">
+        <v>22</v>
       </c>
       <c r="I415">
         <v>1</v>
@@ -29695,11 +29755,23 @@
       <c r="B416" t="s">
         <v>160</v>
       </c>
+      <c r="C416" t="s">
+        <v>24</v>
+      </c>
+      <c r="D416" t="s">
+        <v>25</v>
+      </c>
       <c r="E416" t="s">
         <v>100</v>
       </c>
       <c r="F416" t="s">
         <v>94</v>
+      </c>
+      <c r="G416">
+        <v>255</v>
+      </c>
+      <c r="H416" t="s">
+        <v>22</v>
       </c>
       <c r="I416">
         <v>1</v>
@@ -29715,11 +29787,23 @@
       <c r="B417" t="s">
         <v>26</v>
       </c>
+      <c r="C417" t="s">
+        <v>24</v>
+      </c>
+      <c r="D417" t="s">
+        <v>25</v>
+      </c>
       <c r="E417" t="s">
         <v>100</v>
       </c>
       <c r="F417" t="s">
         <v>94</v>
+      </c>
+      <c r="G417">
+        <v>240</v>
+      </c>
+      <c r="H417" t="s">
+        <v>22</v>
       </c>
       <c r="I417">
         <v>1</v>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B52D5915-654C-4557-B3E8-675FBED9857B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{208505F7-E8C1-44D8-98F6-0AD3A0EA4AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{A026C6F0-B722-4E5E-8C2E-9852D804BFC6}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{7A7B5A73-668C-4486-8F7B-BAA1C87E2B61}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4912" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5087" uniqueCount="594">
   <si>
     <t>날짜</t>
   </si>
@@ -537,6 +537,33 @@
     <t>DPM644-APCO275</t>
   </si>
   <si>
+    <t>BJW1179-BKSL245</t>
+  </si>
+  <si>
+    <t>BJW1179-GDWH240</t>
+  </si>
+  <si>
+    <t>S-20R-GYGG</t>
+  </si>
+  <si>
+    <t>아이두젠카페24</t>
+  </si>
+  <si>
+    <t>S-20R-GYGC</t>
+  </si>
+  <si>
+    <t>스토어팜/바오지</t>
+  </si>
+  <si>
+    <t>BJW1179-GDWH245</t>
+  </si>
+  <si>
+    <t>BJW1179-GY235</t>
+  </si>
+  <si>
+    <t>S-10HA-MAGC</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1302,9 +1329,6 @@
     <t>BJW1179BKSL 바오지 여성 데일리화 블랙실버 240</t>
   </si>
   <si>
-    <t>BJW1179-BKSL245</t>
-  </si>
-  <si>
     <t>BJW1179BKSL 바오지 여성 데일리화 블랙실버 245</t>
   </si>
   <si>
@@ -1320,15 +1344,9 @@
     <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/7d0830bae29f3498109786ad117520e8.jpg</t>
   </si>
   <si>
-    <t>BJW1179-GDWH240</t>
-  </si>
-  <si>
     <t>BJW1179GDWH 바오지 여성 데일리화 골드화이트 240</t>
   </si>
   <si>
-    <t>BJW1179-GDWH245</t>
-  </si>
-  <si>
     <t>BJW1179GDWH 바오지 여성 데일리화 골드화이트 245</t>
   </si>
   <si>
@@ -1344,9 +1362,6 @@
     <t>BJW1179GDWH 바오지 여성 데일리화 골드화이트 255</t>
   </si>
   <si>
-    <t>BJW1179-GY235</t>
-  </si>
-  <si>
     <t>BJW1179GY 바오지 여성 데일리화 그레이 235</t>
   </si>
   <si>
@@ -1785,9 +1800,6 @@
     <t>S-10HA-GYGC</t>
   </si>
   <si>
-    <t>S-10HA-MAGC</t>
-  </si>
-  <si>
     <t>S-10HA-MAGG</t>
   </si>
   <si>
@@ -1804,12 +1816,6 @@
   </si>
   <si>
     <t>S-10RA-MAGG</t>
-  </si>
-  <si>
-    <t>S-20R-GYGC</t>
-  </si>
-  <si>
-    <t>S-20R-GYGG</t>
   </si>
   <si>
     <t>R-10F-BRMB</t>
@@ -2201,7 +2207,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FBFE95-82B5-4084-97F9-13572F9B571F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F10E01A-D154-44D1-B22C-609E19AC1C89}">
   <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2210,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2225,40 +2231,40 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="I1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="K1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="M1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="N1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="O1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="R1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -2266,7 +2272,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2293,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2302,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>4</v>
@@ -2311,7 +2317,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2322,7 +2328,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2349,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -2358,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>3</v>
@@ -2367,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2378,7 +2384,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2405,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2414,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>4</v>
@@ -2423,7 +2429,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2434,7 +2440,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2461,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2470,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>2</v>
@@ -2479,7 +2485,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2490,7 +2496,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2517,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2526,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>2</v>
@@ -2535,7 +2541,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2546,7 +2552,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2573,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2582,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>4</v>
@@ -2591,7 +2597,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2602,7 +2608,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2629,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2638,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>2</v>
@@ -2647,7 +2653,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2658,7 +2664,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2685,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2694,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>4</v>
@@ -2703,7 +2709,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2714,7 +2720,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2741,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2750,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>2</v>
@@ -2759,7 +2765,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2770,7 +2776,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2797,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2806,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>2</v>
@@ -2815,7 +2821,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2823,16 +2829,16 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D12" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2853,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2879,16 +2885,16 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D13" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -2909,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2935,16 +2941,16 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D14" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -2965,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2991,16 +2997,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C15" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D15" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3021,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3047,16 +3053,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" t="s">
         <v>201</v>
       </c>
-      <c r="C16" t="s">
-        <v>192</v>
-      </c>
       <c r="D16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3077,7 +3083,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3103,16 +3109,16 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" t="s">
         <v>202</v>
-      </c>
-      <c r="B17" t="s">
-        <v>203</v>
-      </c>
-      <c r="C17" t="s">
-        <v>192</v>
-      </c>
-      <c r="D17" t="s">
-        <v>193</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3133,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3159,16 +3165,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C18" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D18" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3189,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3215,16 +3221,16 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C19" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D19" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3245,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3271,16 +3277,16 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3301,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3327,16 +3333,16 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C21" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D21" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3357,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3383,16 +3389,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D22" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3413,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3439,16 +3445,16 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C23" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D23" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3469,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3495,16 +3501,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C24" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3525,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3551,16 +3557,16 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D25" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3581,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3607,16 +3613,16 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C26" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D26" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3637,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3663,16 +3669,16 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C27" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D27" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3693,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3719,16 +3725,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D28" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3749,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -3775,16 +3781,16 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B29" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C29" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D29" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3805,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3831,16 +3837,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B30" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D30" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3861,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -3887,16 +3893,16 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B31" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C31" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D31" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3917,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -3943,16 +3949,16 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B32" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D32" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3973,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -3999,16 +4005,16 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D33" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4029,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4055,16 +4061,16 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B34" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C34" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D34" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4085,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4111,16 +4117,16 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B35" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C35" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D35" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4141,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4167,16 +4173,16 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C36" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D36" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4197,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4223,16 +4229,16 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>252</v>
+      </c>
+      <c r="B37" t="s">
+        <v>253</v>
+      </c>
+      <c r="C37" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" t="s">
         <v>243</v>
-      </c>
-      <c r="B37" t="s">
-        <v>244</v>
-      </c>
-      <c r="C37" t="s">
-        <v>192</v>
-      </c>
-      <c r="D37" t="s">
-        <v>234</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4253,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4279,16 +4285,16 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B38" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C38" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D38" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4309,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4335,16 +4341,16 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B39" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C39" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D39" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4365,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4391,16 +4397,16 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B40" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C40" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D40" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4421,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4447,16 +4453,16 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B41" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D41" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4477,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4503,16 +4509,16 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B42" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D42" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4533,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4559,16 +4565,16 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="B43" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C43" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D43" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4589,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4615,16 +4621,16 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B44" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C44" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D44" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4645,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4671,16 +4677,16 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B45" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C45" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D45" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4701,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4727,16 +4733,16 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B46" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="C46" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D46" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4757,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -4783,16 +4789,16 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B47" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="C47" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D47" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4813,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -4839,16 +4845,16 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B48" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C48" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D48" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4869,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4895,16 +4901,16 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B49" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C49" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D49" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4925,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -4951,16 +4957,16 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C50" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D50" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4981,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5007,16 +5013,16 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B51" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C51" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D51" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5037,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5063,16 +5069,16 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B52" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C52" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D52" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5093,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5119,16 +5125,16 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B53" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C53" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D53" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5149,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5175,16 +5181,16 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B54" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C54" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D54" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5205,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5231,16 +5237,16 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B55" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C55" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D55" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5261,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5287,16 +5293,16 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B56" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C56" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D56" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5317,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5343,16 +5349,16 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>293</v>
+      </c>
+      <c r="B57" t="s">
+        <v>294</v>
+      </c>
+      <c r="C57" t="s">
+        <v>201</v>
+      </c>
+      <c r="D57" t="s">
         <v>284</v>
-      </c>
-      <c r="B57" t="s">
-        <v>285</v>
-      </c>
-      <c r="C57" t="s">
-        <v>192</v>
-      </c>
-      <c r="D57" t="s">
-        <v>275</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5373,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5399,16 +5405,16 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B58" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C58" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D58" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5429,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5455,16 +5461,16 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B59" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C59" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D59" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5485,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5511,16 +5517,16 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B60" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C60" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D60" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5541,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5567,16 +5573,16 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B61" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C61" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D61" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -5597,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -5623,16 +5629,16 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B62" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C62" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D62" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5653,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -5679,16 +5685,16 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B63" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C63" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D63" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5709,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -5735,16 +5741,16 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B64" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C64" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D64" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5765,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -5791,16 +5797,16 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B65" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C65" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D65" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5821,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5847,16 +5853,16 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B66" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C66" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D66" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5877,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -5906,7 +5912,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -5933,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -5942,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="N67">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O67">
         <v>4</v>
@@ -5951,7 +5957,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -5962,7 +5968,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -5989,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -5998,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O68">
         <v>2</v>
@@ -6007,7 +6013,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6018,7 +6024,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6045,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L69">
         <v>4</v>
@@ -6054,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O69">
         <v>4</v>
@@ -6063,7 +6069,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6074,7 +6080,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6101,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6110,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70">
         <v>2</v>
@@ -6119,7 +6125,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6130,7 +6136,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6157,7 +6163,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6166,7 +6172,7 @@
         <v>0</v>
       </c>
       <c r="N71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71">
         <v>2</v>
@@ -6175,7 +6181,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6183,10 +6189,10 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B72" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6213,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6231,7 +6237,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6242,7 +6248,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6269,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6287,7 +6293,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6295,10 +6301,10 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B74" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6325,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -6343,7 +6349,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6351,10 +6357,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B75" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6381,7 +6387,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -6399,7 +6405,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6407,10 +6413,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B76" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6437,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6455,7 +6461,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6463,10 +6469,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B77" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -6493,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -6511,7 +6517,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -6519,10 +6525,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B78" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -6549,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -6567,7 +6573,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -6575,10 +6581,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B79" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -6605,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -6623,7 +6629,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -6634,7 +6640,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -6661,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -6679,7 +6685,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -6687,10 +6693,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B81" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -6717,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -6735,7 +6741,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -6743,10 +6749,10 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B82" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -6773,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6791,7 +6797,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -6799,10 +6805,10 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B83" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -6829,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -6847,7 +6853,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -6855,10 +6861,10 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B84" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -6885,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -6903,7 +6909,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -6911,10 +6917,10 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B85" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -6941,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -6959,7 +6965,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -6967,10 +6973,10 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B86" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -6997,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7015,7 +7021,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7023,10 +7029,10 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B87" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7053,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7071,7 +7077,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7082,7 +7088,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7109,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -7127,7 +7133,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7135,10 +7141,10 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B89" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7165,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -7183,7 +7189,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7194,7 +7200,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7221,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -7239,7 +7245,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7247,10 +7253,10 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B91" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7277,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7295,7 +7301,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7303,10 +7309,10 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B92" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7333,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7351,7 +7357,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7362,7 +7368,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -7389,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -7407,7 +7413,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -7415,10 +7421,10 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B94" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -7445,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -7463,7 +7469,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -7471,10 +7477,10 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B95" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -7501,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -7519,7 +7525,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -7527,10 +7533,10 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B96" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -7557,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -7575,7 +7581,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -7583,10 +7589,10 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B97" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -7613,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -7631,7 +7637,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -7642,7 +7648,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -7669,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L98">
         <v>3</v>
@@ -7687,7 +7693,7 @@
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -7698,7 +7704,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -7725,7 +7731,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L99">
         <v>1</v>
@@ -7743,7 +7749,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -7754,7 +7760,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -7781,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L100">
         <v>1</v>
@@ -7799,7 +7805,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -7807,10 +7813,10 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B101" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -7837,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -7855,7 +7861,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -7863,10 +7869,10 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B102" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -7893,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -7911,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -7919,10 +7925,10 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B103" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -7949,7 +7955,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -7967,7 +7973,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -7978,7 +7984,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8005,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8023,7 +8029,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8031,10 +8037,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B105" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8061,7 +8067,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8079,7 +8085,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8090,7 +8096,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8117,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8135,7 +8141,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8143,10 +8149,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B107" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8173,7 +8179,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8191,7 +8197,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8202,7 +8208,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8229,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8247,7 +8253,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8258,7 +8264,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -8285,7 +8291,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -8303,7 +8309,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -8311,10 +8317,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B110" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -8341,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -8359,7 +8365,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -8367,10 +8373,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B111" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -8397,7 +8403,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -8415,7 +8421,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -8426,7 +8432,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -8453,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -8471,7 +8477,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -8482,7 +8488,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -8509,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L113">
         <v>5</v>
@@ -8527,7 +8533,7 @@
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -8538,7 +8544,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -8553,37 +8559,37 @@
         <v>270</v>
       </c>
       <c r="G114">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L114">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M114">
         <v>0</v>
       </c>
       <c r="N114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O114">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P114" t="s">
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -8594,7 +8600,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -8609,37 +8615,37 @@
         <v>275</v>
       </c>
       <c r="G115">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H115">
         <v>0</v>
       </c>
       <c r="I115">
+        <v>3</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115" t="s">
+        <v>187</v>
+      </c>
+      <c r="L115">
+        <v>4</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
         <v>2</v>
       </c>
-      <c r="J115">
-        <v>0</v>
-      </c>
-      <c r="K115" t="s">
-        <v>178</v>
-      </c>
-      <c r="L115">
+      <c r="O115">
         <v>3</v>
       </c>
-      <c r="M115">
-        <v>1</v>
-      </c>
-      <c r="N115">
-        <v>1</v>
-      </c>
-      <c r="O115">
-        <v>2</v>
-      </c>
       <c r="P115" t="s">
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -8650,7 +8656,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -8677,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L116">
         <v>3</v>
@@ -8695,7 +8701,7 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -8706,7 +8712,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -8733,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -8751,7 +8757,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -8762,7 +8768,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -8789,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -8807,7 +8813,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -8815,10 +8821,10 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B119" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -8845,7 +8851,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -8863,7 +8869,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -8874,7 +8880,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -8901,7 +8907,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -8919,7 +8925,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -8930,7 +8936,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -8957,7 +8963,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -8975,7 +8981,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -8986,7 +8992,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9013,7 +9019,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L122">
         <v>4</v>
@@ -9031,7 +9037,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9042,7 +9048,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9069,7 +9075,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -9087,7 +9093,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9098,7 +9104,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9125,7 +9131,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -9143,7 +9149,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9154,7 +9160,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9181,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -9199,7 +9205,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -9210,7 +9216,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -9237,7 +9243,7 @@
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -9255,7 +9261,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -9266,7 +9272,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -9293,7 +9299,7 @@
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L127">
         <v>7</v>
@@ -9311,7 +9317,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -9322,7 +9328,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -9349,7 +9355,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -9367,7 +9373,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -9378,7 +9384,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -9405,7 +9411,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L129">
         <v>7</v>
@@ -9423,7 +9429,7 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -9434,7 +9440,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -9461,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -9479,7 +9485,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -9490,7 +9496,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -9517,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -9535,7 +9541,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -9546,7 +9552,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -9573,7 +9579,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L132">
         <v>17</v>
@@ -9591,7 +9597,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -9602,7 +9608,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -9629,7 +9635,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L133">
         <v>10</v>
@@ -9647,7 +9653,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -9658,7 +9664,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -9685,7 +9691,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L134">
         <v>13</v>
@@ -9703,7 +9709,7 @@
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -9714,7 +9720,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -9741,7 +9747,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -9759,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -9770,7 +9776,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -9797,7 +9803,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -9806,7 +9812,7 @@
         <v>1</v>
       </c>
       <c r="N136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O136">
         <v>4</v>
@@ -9815,7 +9821,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -9826,7 +9832,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -9841,37 +9847,37 @@
         <v>235</v>
       </c>
       <c r="G137">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H137">
         <v>0</v>
       </c>
       <c r="I137">
+        <v>3</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137" t="s">
+        <v>187</v>
+      </c>
+      <c r="L137">
+        <v>3</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
         <v>2</v>
       </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137" t="s">
-        <v>178</v>
-      </c>
-      <c r="L137">
-        <v>2</v>
-      </c>
-      <c r="M137">
-        <v>0</v>
-      </c>
-      <c r="N137">
-        <v>1</v>
-      </c>
       <c r="O137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P137" t="s">
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -9882,7 +9888,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -9909,7 +9915,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L138">
         <v>2</v>
@@ -9927,7 +9933,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -9935,10 +9941,10 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>420</v>
+        <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -9953,37 +9959,37 @@
         <v>245</v>
       </c>
       <c r="G139">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H139">
         <v>0</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P139" t="s">
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -9994,7 +10000,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10021,7 +10027,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L140">
         <v>2</v>
@@ -10039,7 +10045,7 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10050,7 +10056,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10065,37 +10071,37 @@
         <v>255</v>
       </c>
       <c r="G141">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H141">
         <v>0</v>
       </c>
       <c r="I141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M141">
         <v>0</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P141" t="s">
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -10106,7 +10112,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -10133,7 +10139,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -10151,7 +10157,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -10159,10 +10165,10 @@
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>426</v>
+        <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -10177,37 +10183,37 @@
         <v>240</v>
       </c>
       <c r="G143">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
       <c r="I143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P143" t="s">
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -10215,10 +10221,10 @@
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>428</v>
+        <v>171</v>
       </c>
       <c r="B144" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -10233,37 +10239,37 @@
         <v>245</v>
       </c>
       <c r="G144">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H144">
         <v>0</v>
       </c>
       <c r="I144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144">
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144">
         <v>0</v>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P144" t="s">
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -10271,10 +10277,10 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B145" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -10301,7 +10307,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -10319,7 +10325,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -10327,10 +10333,10 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B146" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -10357,7 +10363,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -10375,7 +10381,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -10383,10 +10389,10 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>434</v>
+        <v>172</v>
       </c>
       <c r="B147" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -10401,37 +10407,37 @@
         <v>235</v>
       </c>
       <c r="G147">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M147">
         <v>0</v>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P147" t="s">
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -10442,7 +10448,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -10457,37 +10463,37 @@
         <v>240</v>
       </c>
       <c r="G148">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148">
+        <v>6</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148" t="s">
+        <v>187</v>
+      </c>
+      <c r="L148">
+        <v>6</v>
+      </c>
+      <c r="M148">
+        <v>1</v>
+      </c>
+      <c r="N148">
         <v>4</v>
       </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148" t="s">
-        <v>178</v>
-      </c>
-      <c r="L148">
-        <v>4</v>
-      </c>
-      <c r="M148">
-        <v>0</v>
-      </c>
-      <c r="N148">
-        <v>2</v>
-      </c>
       <c r="O148">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P148" t="s">
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -10498,7 +10504,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -10525,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -10543,7 +10549,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -10554,7 +10560,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -10581,7 +10587,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -10599,7 +10605,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -10610,7 +10616,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -10637,7 +10643,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -10655,7 +10661,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -10663,16 +10669,16 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B152" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C152" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D152" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -10693,7 +10699,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -10719,16 +10725,16 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B153" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C153" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D153" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -10749,7 +10755,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -10775,16 +10781,16 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B154" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C154" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D154" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -10805,7 +10811,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -10831,16 +10837,16 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>453</v>
+      </c>
+      <c r="B155" t="s">
+        <v>454</v>
+      </c>
+      <c r="C155" t="s">
+        <v>201</v>
+      </c>
+      <c r="D155" t="s">
         <v>448</v>
-      </c>
-      <c r="B155" t="s">
-        <v>449</v>
-      </c>
-      <c r="C155" t="s">
-        <v>192</v>
-      </c>
-      <c r="D155" t="s">
-        <v>443</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -10861,7 +10867,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -10887,16 +10893,16 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B156" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C156" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D156" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -10917,7 +10923,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -10943,16 +10949,16 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B157" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C157" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D157" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -10973,7 +10979,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -10999,16 +11005,16 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B158" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C158" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D158" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -11029,7 +11035,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -11055,16 +11061,16 @@
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B159" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C159" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D159" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -11085,7 +11091,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -11111,16 +11117,16 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B160" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C160" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D160" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -11141,7 +11147,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -11167,16 +11173,16 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B161" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C161" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D161" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -11197,7 +11203,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -11223,16 +11229,16 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B162" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C162" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D162" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -11253,7 +11259,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -11279,16 +11285,16 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B163" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C163" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D163" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -11309,7 +11315,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -11335,16 +11341,16 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B164" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C164" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D164" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -11365,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -11391,16 +11397,16 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B165" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C165" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D165" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -11421,7 +11427,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -11447,16 +11453,16 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B166" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C166" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D166" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -11477,7 +11483,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -11503,16 +11509,16 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B167" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C167" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D167" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -11533,7 +11539,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -11559,16 +11565,16 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B168" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C168" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D168" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -11589,7 +11595,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -11615,16 +11621,16 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B169" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C169" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D169" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -11645,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -11671,16 +11677,16 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B170" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C170" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D170" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -11701,7 +11707,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -11727,16 +11733,16 @@
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B171" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C171" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D171" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -11757,7 +11763,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -11786,7 +11792,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -11813,7 +11819,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -11831,7 +11837,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -11842,7 +11848,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -11857,37 +11863,37 @@
         <v>240</v>
       </c>
       <c r="G173">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H173">
         <v>0</v>
       </c>
       <c r="I173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J173">
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L173">
+        <v>6</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>3</v>
+      </c>
+      <c r="O173">
         <v>5</v>
       </c>
-      <c r="M173">
-        <v>0</v>
-      </c>
-      <c r="N173">
-        <v>2</v>
-      </c>
-      <c r="O173">
-        <v>4</v>
-      </c>
       <c r="P173" t="s">
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -11898,7 +11904,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -11925,7 +11931,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L174">
         <v>4</v>
@@ -11943,7 +11949,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -11954,7 +11960,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -11981,7 +11987,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -11999,7 +12005,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -12010,7 +12016,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -12037,7 +12043,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -12055,7 +12061,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -12066,7 +12072,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -12093,7 +12099,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -12111,7 +12117,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -12122,7 +12128,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -12149,7 +12155,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -12167,7 +12173,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -12175,10 +12181,10 @@
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B179" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -12205,7 +12211,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -12223,7 +12229,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -12234,7 +12240,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -12261,7 +12267,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L180">
         <v>2</v>
@@ -12279,7 +12285,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -12287,10 +12293,10 @@
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B181" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -12317,7 +12323,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -12335,7 +12341,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -12346,7 +12352,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -12373,7 +12379,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L182">
         <v>5</v>
@@ -12391,7 +12397,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -12402,7 +12408,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -12429,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L183">
         <v>4</v>
@@ -12438,7 +12444,7 @@
         <v>2</v>
       </c>
       <c r="N183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O183">
         <v>3</v>
@@ -12447,7 +12453,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -12458,7 +12464,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -12485,7 +12491,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -12503,7 +12509,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -12514,7 +12520,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -12541,7 +12547,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L185">
         <v>3</v>
@@ -12559,7 +12565,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -12570,7 +12576,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -12597,7 +12603,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -12615,7 +12621,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -12626,7 +12632,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -12641,37 +12647,37 @@
         <v>235</v>
       </c>
       <c r="G187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H187">
         <v>0</v>
       </c>
       <c r="I187">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J187">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K187" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L187">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M187">
         <v>3</v>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O187">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P187" t="s">
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -12682,7 +12688,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -12709,7 +12715,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -12727,7 +12733,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -12738,7 +12744,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -12765,7 +12771,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -12783,7 +12789,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -12794,7 +12800,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -12821,7 +12827,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L190">
         <v>7</v>
@@ -12839,7 +12845,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -12847,10 +12853,10 @@
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B191" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -12877,7 +12883,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -12895,7 +12901,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -12906,7 +12912,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -12933,7 +12939,7 @@
         <v>7</v>
       </c>
       <c r="K192" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L192">
         <v>12</v>
@@ -12951,7 +12957,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -12962,7 +12968,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -12989,7 +12995,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L193">
         <v>21</v>
@@ -12998,7 +13004,7 @@
         <v>17</v>
       </c>
       <c r="N193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O193">
         <v>21</v>
@@ -13007,7 +13013,7 @@
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -13018,7 +13024,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -13045,7 +13051,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L194">
         <v>20</v>
@@ -13054,7 +13060,7 @@
         <v>14</v>
       </c>
       <c r="N194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O194">
         <v>18</v>
@@ -13063,7 +13069,7 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -13074,7 +13080,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -13101,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -13119,7 +13125,7 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -13130,7 +13136,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -13145,37 +13151,37 @@
         <v>255</v>
       </c>
       <c r="G196">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H196">
         <v>0</v>
       </c>
       <c r="I196">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J196">
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L196">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M196">
         <v>7</v>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O196">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P196" t="s">
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -13183,10 +13189,10 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B197" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -13213,7 +13219,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -13231,7 +13237,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -13242,7 +13248,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -13269,7 +13275,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -13287,7 +13293,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -13298,7 +13304,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -13325,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -13343,7 +13349,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -13351,10 +13357,10 @@
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B200" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -13381,7 +13387,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -13399,7 +13405,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -13410,7 +13416,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -13437,7 +13443,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -13455,7 +13461,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -13463,10 +13469,10 @@
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B202" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -13493,7 +13499,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -13511,7 +13517,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -13522,7 +13528,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -13549,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -13567,7 +13573,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -13575,10 +13581,10 @@
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B204" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -13605,7 +13611,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -13623,7 +13629,7 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -13634,7 +13640,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -13661,7 +13667,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -13679,7 +13685,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -13687,10 +13693,10 @@
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B206" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -13717,7 +13723,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -13735,7 +13741,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -13743,10 +13749,10 @@
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B207" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -13773,7 +13779,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -13791,7 +13797,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -13799,10 +13805,10 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B208" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -13829,7 +13835,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L208">
         <v>0</v>
@@ -13847,7 +13853,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -13855,10 +13861,10 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B209" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -13885,7 +13891,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -13903,7 +13909,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -13911,10 +13917,10 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B210" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -13941,7 +13947,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -13959,7 +13965,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -13967,10 +13973,10 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B211" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -13997,7 +14003,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -14015,7 +14021,7 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -14023,10 +14029,10 @@
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B212" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -14053,7 +14059,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -14071,7 +14077,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -14079,10 +14085,10 @@
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B213" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -14109,7 +14115,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -14127,7 +14133,7 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -14138,7 +14144,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -14165,7 +14171,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -14183,7 +14189,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -14194,7 +14200,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -14221,7 +14227,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -14239,7 +14245,7 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -14247,10 +14253,10 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B216" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -14277,7 +14283,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -14295,7 +14301,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -14306,7 +14312,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -14333,7 +14339,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L217">
         <v>6</v>
@@ -14351,7 +14357,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -14362,7 +14368,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -14389,7 +14395,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L218">
         <v>3</v>
@@ -14407,7 +14413,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -14418,7 +14424,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -14445,7 +14451,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L219">
         <v>3</v>
@@ -14463,7 +14469,7 @@
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -14474,7 +14480,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -14489,37 +14495,37 @@
         <v>250</v>
       </c>
       <c r="G220">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H220">
         <v>0</v>
       </c>
       <c r="I220">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J220">
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L220">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M220">
         <v>2</v>
       </c>
       <c r="N220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O220">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P220" t="s">
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -14527,10 +14533,10 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B221" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -14557,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -14575,7 +14581,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -14586,7 +14592,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -14613,7 +14619,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -14631,7 +14637,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -14642,7 +14648,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -14657,22 +14663,22 @@
         <v>240</v>
       </c>
       <c r="G223">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H223">
         <v>0</v>
       </c>
       <c r="I223">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J223">
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L223">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M223">
         <v>8</v>
@@ -14681,13 +14687,13 @@
         <v>2</v>
       </c>
       <c r="O223">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P223" t="s">
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -14698,7 +14704,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -14713,37 +14719,37 @@
         <v>245</v>
       </c>
       <c r="G224">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H224">
         <v>0</v>
       </c>
       <c r="I224">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J224">
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L224">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M224">
         <v>5</v>
       </c>
       <c r="N224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O224">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P224" t="s">
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -14754,7 +14760,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -14781,7 +14787,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L225">
         <v>6</v>
@@ -14799,7 +14805,7 @@
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -14810,7 +14816,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -14837,7 +14843,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -14846,7 +14852,7 @@
         <v>1</v>
       </c>
       <c r="N226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O226">
         <v>3</v>
@@ -14855,7 +14861,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -14866,7 +14872,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -14881,37 +14887,37 @@
         <v>235</v>
       </c>
       <c r="G227">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J227">
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L227">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M227">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N227">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O227">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P227" t="s">
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -14922,7 +14928,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -14937,37 +14943,37 @@
         <v>240</v>
       </c>
       <c r="G228">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J228">
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L228">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M228">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N228">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O228">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P228" t="s">
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -14978,7 +14984,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -14993,37 +14999,37 @@
         <v>245</v>
       </c>
       <c r="G229">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H229">
         <v>0</v>
       </c>
       <c r="I229">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J229">
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L229">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M229">
         <v>8</v>
       </c>
       <c r="N229">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O229">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P229" t="s">
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -15034,7 +15040,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -15061,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -15079,7 +15085,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -15090,7 +15096,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -15117,7 +15123,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -15135,7 +15141,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -15170,7 +15176,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -15190,10 +15196,10 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B233" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C233" t="s">
         <v>120</v>
@@ -15217,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -15237,10 +15243,10 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B234" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -15264,7 +15270,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -15284,10 +15290,10 @@
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B235" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C235" t="s">
         <v>120</v>
@@ -15311,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -15331,10 +15337,10 @@
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B236" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C236" t="s">
         <v>120</v>
@@ -15358,7 +15364,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -15405,7 +15411,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -15425,10 +15431,10 @@
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B238" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -15452,7 +15458,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -15472,10 +15478,10 @@
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B239" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -15499,7 +15505,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -15519,10 +15525,10 @@
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B240" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C240" t="s">
         <v>120</v>
@@ -15546,7 +15552,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -15593,7 +15599,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -15613,10 +15619,10 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B242" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C242" t="s">
         <v>120</v>
@@ -15640,7 +15646,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -15660,10 +15666,10 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B243" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C243" t="s">
         <v>120</v>
@@ -15687,7 +15693,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -15707,10 +15713,10 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B244" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -15734,7 +15740,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -15769,7 +15775,7 @@
         <v>122</v>
       </c>
       <c r="G245">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -15781,19 +15787,19 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M245">
         <v>0</v>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P245" t="s">
         <v>13</v>
@@ -15801,10 +15807,10 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>581</v>
+        <v>173</v>
       </c>
       <c r="B246" t="s">
-        <v>581</v>
+        <v>173</v>
       </c>
       <c r="C246" t="s">
         <v>120</v>
@@ -15816,7 +15822,7 @@
         <v>122</v>
       </c>
       <c r="G246">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -15828,19 +15834,19 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M246">
         <v>0</v>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P246" t="s">
         <v>13</v>
@@ -15848,10 +15854,10 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B247" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C247" t="s">
         <v>120</v>
@@ -15875,7 +15881,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -15895,16 +15901,16 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B248" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
       </c>
       <c r="D248" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E248" t="s">
         <v>122</v>
@@ -15922,7 +15928,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -15942,16 +15948,16 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B249" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C249" t="s">
         <v>120</v>
       </c>
       <c r="D249" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E249" t="s">
         <v>122</v>
@@ -15969,7 +15975,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -15989,16 +15995,16 @@
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B250" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
       </c>
       <c r="D250" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E250" t="s">
         <v>122</v>
@@ -16016,7 +16022,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -16036,16 +16042,16 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B251" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
       </c>
       <c r="D251" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E251" t="s">
         <v>122</v>
@@ -16063,7 +16069,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -16083,10 +16089,10 @@
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>588</v>
+        <v>169</v>
       </c>
       <c r="B252" t="s">
-        <v>588</v>
+        <v>169</v>
       </c>
       <c r="C252" t="s">
         <v>120</v>
@@ -16098,7 +16104,7 @@
         <v>122</v>
       </c>
       <c r="G252">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -16110,19 +16116,19 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M252">
         <v>0</v>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P252" t="s">
         <v>13</v>
@@ -16130,10 +16136,10 @@
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>589</v>
+        <v>167</v>
       </c>
       <c r="B253" t="s">
-        <v>589</v>
+        <v>167</v>
       </c>
       <c r="C253" t="s">
         <v>120</v>
@@ -16145,7 +16151,7 @@
         <v>122</v>
       </c>
       <c r="G253">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -16157,19 +16163,19 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M253">
         <v>0</v>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P253" t="s">
         <v>13</v>
@@ -16204,7 +16210,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -16251,7 +16257,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -16298,7 +16304,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L256">
         <v>2</v>
@@ -16318,10 +16324,10 @@
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B257" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C257" t="s">
         <v>120</v>
@@ -16345,7 +16351,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -16392,7 +16398,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L258">
         <v>2</v>
@@ -16412,10 +16418,10 @@
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B259" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C259" t="s">
         <v>120</v>
@@ -16439,7 +16445,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -16464,8 +16470,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407C3041-C9BB-4CD8-A81E-DEF1395761BD}">
-  <dimension ref="A1:J417"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF9974C-273C-41B0-BCD1-2FDE2F3A5AA0}">
+  <dimension ref="A1:J442"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -29810,6 +29816,806 @@
       </c>
       <c r="J417" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A418" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B418" t="s">
+        <v>165</v>
+      </c>
+      <c r="C418" t="s">
+        <v>18</v>
+      </c>
+      <c r="D418" t="s">
+        <v>90</v>
+      </c>
+      <c r="E418" t="s">
+        <v>100</v>
+      </c>
+      <c r="F418" t="s">
+        <v>66</v>
+      </c>
+      <c r="G418">
+        <v>245</v>
+      </c>
+      <c r="H418" t="s">
+        <v>22</v>
+      </c>
+      <c r="I418">
+        <v>1</v>
+      </c>
+      <c r="J418" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A419" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B419" t="s">
+        <v>112</v>
+      </c>
+      <c r="C419" t="s">
+        <v>18</v>
+      </c>
+      <c r="D419" t="s">
+        <v>90</v>
+      </c>
+      <c r="E419" t="s">
+        <v>100</v>
+      </c>
+      <c r="F419" t="s">
+        <v>66</v>
+      </c>
+      <c r="G419">
+        <v>240</v>
+      </c>
+      <c r="H419" t="s">
+        <v>22</v>
+      </c>
+      <c r="I419">
+        <v>1</v>
+      </c>
+      <c r="J419" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A420" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B420" t="s">
+        <v>70</v>
+      </c>
+      <c r="C420" t="s">
+        <v>24</v>
+      </c>
+      <c r="D420" t="s">
+        <v>49</v>
+      </c>
+      <c r="E420" t="s">
+        <v>100</v>
+      </c>
+      <c r="F420" t="s">
+        <v>66</v>
+      </c>
+      <c r="G420">
+        <v>235</v>
+      </c>
+      <c r="H420" t="s">
+        <v>22</v>
+      </c>
+      <c r="I420">
+        <v>1</v>
+      </c>
+      <c r="J420" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A421" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B421" t="s">
+        <v>76</v>
+      </c>
+      <c r="C421" t="s">
+        <v>24</v>
+      </c>
+      <c r="D421" t="s">
+        <v>49</v>
+      </c>
+      <c r="E421" t="s">
+        <v>100</v>
+      </c>
+      <c r="F421" t="s">
+        <v>66</v>
+      </c>
+      <c r="G421">
+        <v>240</v>
+      </c>
+      <c r="H421" t="s">
+        <v>22</v>
+      </c>
+      <c r="I421">
+        <v>1</v>
+      </c>
+      <c r="J421" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A422" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B422" t="s">
+        <v>166</v>
+      </c>
+      <c r="C422" t="s">
+        <v>18</v>
+      </c>
+      <c r="D422" t="s">
+        <v>90</v>
+      </c>
+      <c r="E422" t="s">
+        <v>100</v>
+      </c>
+      <c r="F422" t="s">
+        <v>66</v>
+      </c>
+      <c r="G422">
+        <v>240</v>
+      </c>
+      <c r="H422" t="s">
+        <v>22</v>
+      </c>
+      <c r="I422">
+        <v>1</v>
+      </c>
+      <c r="J422" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A423" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B423" t="s">
+        <v>50</v>
+      </c>
+      <c r="C423" t="s">
+        <v>24</v>
+      </c>
+      <c r="D423" t="s">
+        <v>49</v>
+      </c>
+      <c r="E423" t="s">
+        <v>53</v>
+      </c>
+      <c r="F423" t="s">
+        <v>94</v>
+      </c>
+      <c r="G423">
+        <v>245</v>
+      </c>
+      <c r="H423" t="s">
+        <v>22</v>
+      </c>
+      <c r="I423">
+        <v>1</v>
+      </c>
+      <c r="J423" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A424" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B424" t="s">
+        <v>112</v>
+      </c>
+      <c r="C424" t="s">
+        <v>18</v>
+      </c>
+      <c r="D424" t="s">
+        <v>90</v>
+      </c>
+      <c r="E424" t="s">
+        <v>53</v>
+      </c>
+      <c r="F424" t="s">
+        <v>94</v>
+      </c>
+      <c r="G424">
+        <v>240</v>
+      </c>
+      <c r="H424" t="s">
+        <v>22</v>
+      </c>
+      <c r="I424">
+        <v>1</v>
+      </c>
+      <c r="J424" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A425" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B425" t="s">
+        <v>167</v>
+      </c>
+      <c r="C425" t="s">
+        <v>120</v>
+      </c>
+      <c r="D425" t="s">
+        <v>121</v>
+      </c>
+      <c r="E425" t="s">
+        <v>168</v>
+      </c>
+      <c r="F425" t="s">
+        <v>94</v>
+      </c>
+      <c r="G425">
+        <v>0</v>
+      </c>
+      <c r="H425" t="s">
+        <v>122</v>
+      </c>
+      <c r="I425">
+        <v>1</v>
+      </c>
+      <c r="J425" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A426" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B426" t="s">
+        <v>169</v>
+      </c>
+      <c r="C426" t="s">
+        <v>120</v>
+      </c>
+      <c r="D426" t="s">
+        <v>121</v>
+      </c>
+      <c r="E426" t="s">
+        <v>168</v>
+      </c>
+      <c r="F426" t="s">
+        <v>94</v>
+      </c>
+      <c r="G426">
+        <v>0</v>
+      </c>
+      <c r="H426" t="s">
+        <v>122</v>
+      </c>
+      <c r="I426">
+        <v>1</v>
+      </c>
+      <c r="J426" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A427" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B427" t="s">
+        <v>86</v>
+      </c>
+      <c r="C427" t="s">
+        <v>24</v>
+      </c>
+      <c r="D427" t="s">
+        <v>49</v>
+      </c>
+      <c r="E427" t="s">
+        <v>170</v>
+      </c>
+      <c r="F427" t="s">
+        <v>94</v>
+      </c>
+      <c r="G427">
+        <v>240</v>
+      </c>
+      <c r="H427" t="s">
+        <v>22</v>
+      </c>
+      <c r="I427">
+        <v>1</v>
+      </c>
+      <c r="J427" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A428" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B428" t="s">
+        <v>65</v>
+      </c>
+      <c r="C428" t="s">
+        <v>24</v>
+      </c>
+      <c r="D428" t="s">
+        <v>40</v>
+      </c>
+      <c r="E428" t="s">
+        <v>170</v>
+      </c>
+      <c r="F428" t="s">
+        <v>94</v>
+      </c>
+      <c r="G428">
+        <v>255</v>
+      </c>
+      <c r="H428" t="s">
+        <v>22</v>
+      </c>
+      <c r="I428">
+        <v>1</v>
+      </c>
+      <c r="J428" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A429" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B429" t="s">
+        <v>26</v>
+      </c>
+      <c r="C429" t="s">
+        <v>24</v>
+      </c>
+      <c r="D429" t="s">
+        <v>25</v>
+      </c>
+      <c r="E429" t="s">
+        <v>170</v>
+      </c>
+      <c r="F429" t="s">
+        <v>94</v>
+      </c>
+      <c r="G429">
+        <v>240</v>
+      </c>
+      <c r="H429" t="s">
+        <v>22</v>
+      </c>
+      <c r="I429">
+        <v>1</v>
+      </c>
+      <c r="J429" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A430" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B430" t="s">
+        <v>162</v>
+      </c>
+      <c r="C430" t="s">
+        <v>18</v>
+      </c>
+      <c r="D430" t="s">
+        <v>90</v>
+      </c>
+      <c r="E430" t="s">
+        <v>170</v>
+      </c>
+      <c r="F430" t="s">
+        <v>94</v>
+      </c>
+      <c r="G430">
+        <v>255</v>
+      </c>
+      <c r="H430" t="s">
+        <v>22</v>
+      </c>
+      <c r="I430">
+        <v>1</v>
+      </c>
+      <c r="J430" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A431" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B431" t="s">
+        <v>107</v>
+      </c>
+      <c r="C431" t="s">
+        <v>24</v>
+      </c>
+      <c r="D431" t="s">
+        <v>38</v>
+      </c>
+      <c r="E431" t="s">
+        <v>170</v>
+      </c>
+      <c r="F431" t="s">
+        <v>94</v>
+      </c>
+      <c r="G431">
+        <v>270</v>
+      </c>
+      <c r="H431" t="s">
+        <v>15</v>
+      </c>
+      <c r="I431">
+        <v>1</v>
+      </c>
+      <c r="J431" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A432" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B432" t="s">
+        <v>50</v>
+      </c>
+      <c r="C432" t="s">
+        <v>24</v>
+      </c>
+      <c r="D432" t="s">
+        <v>49</v>
+      </c>
+      <c r="E432" t="s">
+        <v>170</v>
+      </c>
+      <c r="F432" t="s">
+        <v>94</v>
+      </c>
+      <c r="G432">
+        <v>245</v>
+      </c>
+      <c r="H432" t="s">
+        <v>22</v>
+      </c>
+      <c r="I432">
+        <v>1</v>
+      </c>
+      <c r="J432" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A433" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B433" t="s">
+        <v>48</v>
+      </c>
+      <c r="C433" t="s">
+        <v>24</v>
+      </c>
+      <c r="D433" t="s">
+        <v>49</v>
+      </c>
+      <c r="E433" t="s">
+        <v>170</v>
+      </c>
+      <c r="F433" t="s">
+        <v>94</v>
+      </c>
+      <c r="G433">
+        <v>245</v>
+      </c>
+      <c r="H433" t="s">
+        <v>22</v>
+      </c>
+      <c r="I433">
+        <v>1</v>
+      </c>
+      <c r="J433" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A434" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B434" t="s">
+        <v>58</v>
+      </c>
+      <c r="C434" t="s">
+        <v>24</v>
+      </c>
+      <c r="D434" t="s">
+        <v>38</v>
+      </c>
+      <c r="E434" t="s">
+        <v>170</v>
+      </c>
+      <c r="F434" t="s">
+        <v>94</v>
+      </c>
+      <c r="G434">
+        <v>275</v>
+      </c>
+      <c r="H434" t="s">
+        <v>15</v>
+      </c>
+      <c r="I434">
+        <v>1</v>
+      </c>
+      <c r="J434" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A435" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B435" t="s">
+        <v>76</v>
+      </c>
+      <c r="C435" t="s">
+        <v>24</v>
+      </c>
+      <c r="D435" t="s">
+        <v>49</v>
+      </c>
+      <c r="E435" t="s">
+        <v>170</v>
+      </c>
+      <c r="F435" t="s">
+        <v>94</v>
+      </c>
+      <c r="G435">
+        <v>240</v>
+      </c>
+      <c r="H435" t="s">
+        <v>22</v>
+      </c>
+      <c r="I435">
+        <v>1</v>
+      </c>
+      <c r="J435" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A436" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B436" t="s">
+        <v>98</v>
+      </c>
+      <c r="C436" t="s">
+        <v>24</v>
+      </c>
+      <c r="D436" t="s">
+        <v>49</v>
+      </c>
+      <c r="E436" t="s">
+        <v>170</v>
+      </c>
+      <c r="F436" t="s">
+        <v>94</v>
+      </c>
+      <c r="G436">
+        <v>250</v>
+      </c>
+      <c r="H436" t="s">
+        <v>22</v>
+      </c>
+      <c r="I436">
+        <v>1</v>
+      </c>
+      <c r="J436" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A437" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B437" t="s">
+        <v>171</v>
+      </c>
+      <c r="C437" t="s">
+        <v>18</v>
+      </c>
+      <c r="D437" t="s">
+        <v>90</v>
+      </c>
+      <c r="E437" t="s">
+        <v>170</v>
+      </c>
+      <c r="F437" t="s">
+        <v>94</v>
+      </c>
+      <c r="G437">
+        <v>245</v>
+      </c>
+      <c r="H437" t="s">
+        <v>22</v>
+      </c>
+      <c r="I437">
+        <v>1</v>
+      </c>
+      <c r="J437" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A438" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B438" t="s">
+        <v>89</v>
+      </c>
+      <c r="C438" t="s">
+        <v>18</v>
+      </c>
+      <c r="D438" t="s">
+        <v>90</v>
+      </c>
+      <c r="E438" t="s">
+        <v>170</v>
+      </c>
+      <c r="F438" t="s">
+        <v>94</v>
+      </c>
+      <c r="G438">
+        <v>235</v>
+      </c>
+      <c r="H438" t="s">
+        <v>22</v>
+      </c>
+      <c r="I438">
+        <v>1</v>
+      </c>
+      <c r="J438" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A439" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B439" t="s">
+        <v>172</v>
+      </c>
+      <c r="C439" t="s">
+        <v>18</v>
+      </c>
+      <c r="D439" t="s">
+        <v>90</v>
+      </c>
+      <c r="E439" t="s">
+        <v>170</v>
+      </c>
+      <c r="F439" t="s">
+        <v>94</v>
+      </c>
+      <c r="G439">
+        <v>235</v>
+      </c>
+      <c r="H439" t="s">
+        <v>22</v>
+      </c>
+      <c r="I439">
+        <v>1</v>
+      </c>
+      <c r="J439" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A440" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B440" t="s">
+        <v>39</v>
+      </c>
+      <c r="C440" t="s">
+        <v>24</v>
+      </c>
+      <c r="D440" t="s">
+        <v>40</v>
+      </c>
+      <c r="E440" t="s">
+        <v>170</v>
+      </c>
+      <c r="F440" t="s">
+        <v>94</v>
+      </c>
+      <c r="G440">
+        <v>235</v>
+      </c>
+      <c r="H440" t="s">
+        <v>22</v>
+      </c>
+      <c r="I440">
+        <v>1</v>
+      </c>
+      <c r="J440" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A441" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B441" t="s">
+        <v>123</v>
+      </c>
+      <c r="C441" t="s">
+        <v>120</v>
+      </c>
+      <c r="D441" t="s">
+        <v>124</v>
+      </c>
+      <c r="E441" t="s">
+        <v>133</v>
+      </c>
+      <c r="F441" t="s">
+        <v>94</v>
+      </c>
+      <c r="G441">
+        <v>0</v>
+      </c>
+      <c r="H441" t="s">
+        <v>122</v>
+      </c>
+      <c r="I441">
+        <v>1</v>
+      </c>
+      <c r="J441" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A442" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B442" t="s">
+        <v>173</v>
+      </c>
+      <c r="C442" t="s">
+        <v>120</v>
+      </c>
+      <c r="D442" t="s">
+        <v>124</v>
+      </c>
+      <c r="E442" t="s">
+        <v>133</v>
+      </c>
+      <c r="F442" t="s">
+        <v>94</v>
+      </c>
+      <c r="G442">
+        <v>0</v>
+      </c>
+      <c r="H442" t="s">
+        <v>122</v>
+      </c>
+      <c r="I442">
+        <v>1</v>
+      </c>
+      <c r="J442" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{208505F7-E8C1-44D8-98F6-0AD3A0EA4AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85B20BDA-1A27-4A8B-B3B5-72805F6A757D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{7A7B5A73-668C-4486-8F7B-BAA1C87E2B61}"/>
+    <workbookView xWindow="4455" yWindow="3720" windowWidth="28800" windowHeight="11295" xr2:uid="{005915E2-9709-49F3-9306-D81B9857AEA7}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -2207,7 +2207,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F10E01A-D154-44D1-B22C-609E19AC1C89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{899AE51B-0D16-4107-B006-0C76B1E71F1B}">
   <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -16470,7 +16470,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF9974C-273C-41B0-BCD1-2FDE2F3A5AA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4BC72F-6E7C-4D95-9B4B-D7CE6C96B6C9}">
   <dimension ref="A1:J442"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8814168B-5140-4504-B391-73897D32DA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21308665-CA65-4A46-ABDB-823CD77DEB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{3396BC6D-1795-453B-BB58-54DF10F2ACB2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{E2CA3A7E-BAA0-4864-A0E2-91E0C4DC6C4B}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5246" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5274" uniqueCount="792">
   <si>
     <t>날짜</t>
   </si>
@@ -561,6 +561,9 @@
     <t>S-10HA-MAGC</t>
   </si>
   <si>
+    <t>X-10H-GYGG</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -2362,9 +2365,6 @@
   </si>
   <si>
     <t>U-ECW304-132541</t>
-  </si>
-  <si>
-    <t>X-10H-GYGG</t>
   </si>
   <si>
     <t>X-10H-MAGC</t>
@@ -2801,8 +2801,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DDDDEF6-EEA7-4169-AAD4-49F85ECA411A}">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9313D139-1E2E-4D88-8CC6-8BC3FA81237D}">
   <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2811,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2826,40 +2825,40 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -2867,7 +2866,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2894,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2912,7 +2911,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2923,7 +2922,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2950,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -2968,7 +2967,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2979,7 +2978,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -3006,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -3024,7 +3023,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -3035,7 +3034,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -3062,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -3080,7 +3079,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -3091,7 +3090,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -3118,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -3136,7 +3135,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -3147,7 +3146,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -3174,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -3192,7 +3191,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -3203,7 +3202,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -3230,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -3248,7 +3247,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -3259,7 +3258,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -3286,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -3304,7 +3303,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3315,7 +3314,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -3342,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -3360,7 +3359,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3371,7 +3370,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -3398,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -3416,7 +3415,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3424,16 +3423,16 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -3454,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3472,7 +3471,7 @@
         <v>16</v>
       </c>
       <c r="Q12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3480,16 +3479,16 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3510,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3528,7 +3527,7 @@
         <v>16</v>
       </c>
       <c r="Q13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3536,16 +3535,16 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3566,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3584,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="Q14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -3592,16 +3591,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3622,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3640,7 +3639,7 @@
         <v>16</v>
       </c>
       <c r="Q15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -3648,16 +3647,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3678,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3696,7 +3695,7 @@
         <v>16</v>
       </c>
       <c r="Q16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -3704,16 +3703,16 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3734,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3752,7 +3751,7 @@
         <v>16</v>
       </c>
       <c r="Q17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -3760,16 +3759,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3790,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3808,7 +3807,7 @@
         <v>16</v>
       </c>
       <c r="Q18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -3816,16 +3815,16 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3846,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3864,7 +3863,7 @@
         <v>16</v>
       </c>
       <c r="Q19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -3872,16 +3871,16 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3902,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3920,7 +3919,7 @@
         <v>16</v>
       </c>
       <c r="Q20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -3928,16 +3927,16 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D21" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3958,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3976,7 +3975,7 @@
         <v>16</v>
       </c>
       <c r="Q21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -3984,16 +3983,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -4014,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -4032,7 +4031,7 @@
         <v>16</v>
       </c>
       <c r="Q22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -4040,16 +4039,16 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -4070,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -4088,7 +4087,7 @@
         <v>16</v>
       </c>
       <c r="Q23" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -4096,16 +4095,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -4126,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -4144,7 +4143,7 @@
         <v>16</v>
       </c>
       <c r="Q24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -4152,16 +4151,16 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C25" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -4182,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -4200,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="Q25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -4208,16 +4207,16 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -4238,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -4256,7 +4255,7 @@
         <v>16</v>
       </c>
       <c r="Q26" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -4264,16 +4263,16 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D27" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -4294,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -4312,7 +4311,7 @@
         <v>16</v>
       </c>
       <c r="Q27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -4320,16 +4319,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -4350,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4368,7 +4367,7 @@
         <v>16</v>
       </c>
       <c r="Q28" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -4376,16 +4375,16 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4406,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4424,7 +4423,7 @@
         <v>16</v>
       </c>
       <c r="Q29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -4432,16 +4431,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D30" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4462,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4480,7 +4479,7 @@
         <v>16</v>
       </c>
       <c r="Q30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -4488,16 +4487,16 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4518,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4536,7 +4535,7 @@
         <v>16</v>
       </c>
       <c r="Q31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -4544,16 +4543,16 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4574,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4592,7 +4591,7 @@
         <v>16</v>
       </c>
       <c r="Q32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -4600,16 +4599,16 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D33" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4630,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4648,7 +4647,7 @@
         <v>16</v>
       </c>
       <c r="Q33" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -4656,16 +4655,16 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C34" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4686,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4704,7 +4703,7 @@
         <v>16</v>
       </c>
       <c r="Q34" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -4712,16 +4711,16 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C35" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4742,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4760,7 +4759,7 @@
         <v>16</v>
       </c>
       <c r="Q35" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -4768,16 +4767,16 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C36" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4798,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4816,7 +4815,7 @@
         <v>16</v>
       </c>
       <c r="Q36" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -4824,16 +4823,16 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C37" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4854,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4872,7 +4871,7 @@
         <v>16</v>
       </c>
       <c r="Q37" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -4880,16 +4879,16 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4910,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4928,7 +4927,7 @@
         <v>16</v>
       </c>
       <c r="Q38" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -4936,16 +4935,16 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B39" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4966,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4984,7 +4983,7 @@
         <v>16</v>
       </c>
       <c r="Q39" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -4992,16 +4991,16 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C40" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -5022,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -5040,7 +5039,7 @@
         <v>16</v>
       </c>
       <c r="Q40" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -5048,16 +5047,16 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -5078,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -5096,7 +5095,7 @@
         <v>16</v>
       </c>
       <c r="Q41" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -5104,16 +5103,16 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B42" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C42" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D42" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -5134,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -5152,7 +5151,7 @@
         <v>16</v>
       </c>
       <c r="Q42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -5160,16 +5159,16 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -5190,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -5208,7 +5207,7 @@
         <v>16</v>
       </c>
       <c r="Q43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -5216,16 +5215,16 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C44" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D44" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -5246,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5264,7 +5263,7 @@
         <v>16</v>
       </c>
       <c r="Q44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -5272,16 +5271,16 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C45" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D45" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5302,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5320,7 +5319,7 @@
         <v>16</v>
       </c>
       <c r="Q45" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -5328,16 +5327,16 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D46" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5358,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5376,7 +5375,7 @@
         <v>16</v>
       </c>
       <c r="Q46" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -5384,16 +5383,16 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C47" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D47" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5414,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5432,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="Q47" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -5440,16 +5439,16 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B48" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C48" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5470,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5488,7 +5487,7 @@
         <v>16</v>
       </c>
       <c r="Q48" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -5496,16 +5495,16 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B49" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C49" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D49" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5526,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5544,7 +5543,7 @@
         <v>16</v>
       </c>
       <c r="Q49" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -5552,16 +5551,16 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5582,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5600,7 +5599,7 @@
         <v>16</v>
       </c>
       <c r="Q50" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -5608,16 +5607,16 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B51" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D51" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5638,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5656,7 +5655,7 @@
         <v>16</v>
       </c>
       <c r="Q51" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -5664,16 +5663,16 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B52" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C52" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D52" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5694,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5712,7 +5711,7 @@
         <v>16</v>
       </c>
       <c r="Q52" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -5720,16 +5719,16 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B53" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C53" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D53" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5750,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5768,7 +5767,7 @@
         <v>16</v>
       </c>
       <c r="Q53" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -5776,16 +5775,16 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C54" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D54" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5806,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5824,7 +5823,7 @@
         <v>16</v>
       </c>
       <c r="Q54" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -5832,16 +5831,16 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B55" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C55" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5862,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5880,7 +5879,7 @@
         <v>16</v>
       </c>
       <c r="Q55" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -5888,16 +5887,16 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B56" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C56" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D56" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5918,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5936,7 +5935,7 @@
         <v>16</v>
       </c>
       <c r="Q56" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -5944,16 +5943,16 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B57" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D57" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5974,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5992,7 +5991,7 @@
         <v>16</v>
       </c>
       <c r="Q57" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -6000,16 +5999,16 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C58" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -6030,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -6048,7 +6047,7 @@
         <v>16</v>
       </c>
       <c r="Q58" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -6056,16 +6055,16 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B59" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D59" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -6086,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -6104,7 +6103,7 @@
         <v>16</v>
       </c>
       <c r="Q59" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -6112,16 +6111,16 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D60" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -6142,7 +6141,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -6160,7 +6159,7 @@
         <v>16</v>
       </c>
       <c r="Q60" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -6168,16 +6167,16 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B61" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C61" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D61" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6198,7 +6197,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6216,7 +6215,7 @@
         <v>16</v>
       </c>
       <c r="Q61" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -6224,16 +6223,16 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B62" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6254,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6272,7 +6271,7 @@
         <v>16</v>
       </c>
       <c r="Q62" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="R62">
         <v>0</v>
@@ -6280,16 +6279,16 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B63" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6310,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6328,7 +6327,7 @@
         <v>16</v>
       </c>
       <c r="Q63" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -6336,16 +6335,16 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B64" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6366,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6384,7 +6383,7 @@
         <v>16</v>
       </c>
       <c r="Q64" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -6392,16 +6391,16 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B65" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D65" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6422,7 +6421,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6440,7 +6439,7 @@
         <v>16</v>
       </c>
       <c r="Q65" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="R65">
         <v>0</v>
@@ -6448,16 +6447,16 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B66" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C66" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D66" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6478,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6496,7 +6495,7 @@
         <v>16</v>
       </c>
       <c r="Q66" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R66">
         <v>0</v>
@@ -6507,7 +6506,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6534,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6552,7 +6551,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6563,7 +6562,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6590,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -6608,7 +6607,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6619,7 +6618,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6646,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L69">
         <v>4</v>
@@ -6664,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6675,7 +6674,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6702,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6720,7 +6719,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6731,7 +6730,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6758,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6776,7 +6775,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6784,10 +6783,10 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B72" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6814,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6832,7 +6831,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6843,7 +6842,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6870,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6888,7 +6887,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6896,10 +6895,10 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B74" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6926,7 +6925,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -6944,7 +6943,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6952,10 +6951,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B75" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6982,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -7000,7 +6999,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -7008,10 +7007,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B76" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -7038,7 +7037,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -7056,7 +7055,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -7064,10 +7063,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B77" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -7094,7 +7093,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -7112,7 +7111,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7120,10 +7119,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B78" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7150,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7168,7 +7167,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7176,10 +7175,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B79" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7206,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7224,7 +7223,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7235,7 +7234,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7262,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7280,7 +7279,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7288,10 +7287,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B81" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7318,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -7336,7 +7335,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7344,10 +7343,10 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B82" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7374,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7392,7 +7391,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7400,10 +7399,10 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B83" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7430,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7448,7 +7447,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7456,10 +7455,10 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B84" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7486,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7504,7 +7503,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7512,10 +7511,10 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B85" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7542,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7560,7 +7559,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7568,10 +7567,10 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B86" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7598,7 +7597,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7616,7 +7615,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7624,10 +7623,10 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B87" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7654,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7672,7 +7671,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7683,7 +7682,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7710,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -7728,7 +7727,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7736,10 +7735,10 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B89" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7766,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -7784,7 +7783,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7795,7 +7794,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7822,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -7840,7 +7839,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7848,10 +7847,10 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B91" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7878,7 +7877,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7896,7 +7895,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7904,10 +7903,10 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B92" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7934,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7952,7 +7951,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7963,7 +7962,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -7990,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8008,7 +8007,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8016,10 +8015,10 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B94" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8046,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8064,7 +8063,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8072,10 +8071,10 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B95" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8102,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8120,7 +8119,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8128,10 +8127,10 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B96" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8158,7 +8157,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8176,7 +8175,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8184,10 +8183,10 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B97" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8214,7 +8213,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8232,7 +8231,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8243,7 +8242,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8270,7 +8269,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L98">
         <v>3</v>
@@ -8279,7 +8278,7 @@
         <v>0</v>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O98">
         <v>2</v>
@@ -8288,7 +8287,7 @@
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8299,7 +8298,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8326,7 +8325,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L99">
         <v>1</v>
@@ -8335,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99">
         <v>1</v>
@@ -8344,7 +8343,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8355,7 +8354,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8370,37 +8369,37 @@
         <v>275</v>
       </c>
       <c r="G100">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H100">
         <v>0</v>
       </c>
       <c r="I100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M100">
         <v>0</v>
       </c>
       <c r="N100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P100" t="s">
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8408,10 +8407,10 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B101" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8438,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8456,7 +8455,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8464,10 +8463,10 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B102" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8494,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8512,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8520,10 +8519,10 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B103" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8550,7 +8549,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -8568,7 +8567,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8579,7 +8578,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8606,7 +8605,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8624,7 +8623,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8632,10 +8631,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B105" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8662,7 +8661,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8680,7 +8679,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8691,7 +8690,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8718,7 +8717,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8736,7 +8735,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8744,10 +8743,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B107" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8774,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8792,7 +8791,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8803,7 +8802,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8830,7 +8829,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8848,7 +8847,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8859,7 +8858,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -8886,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -8904,7 +8903,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -8912,10 +8911,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B110" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -8942,7 +8941,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -8960,7 +8959,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -8968,10 +8967,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B111" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -8998,7 +8997,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9016,7 +9015,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9027,7 +9026,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9054,7 +9053,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9072,7 +9071,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9083,7 +9082,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9110,7 +9109,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L113">
         <v>5</v>
@@ -9128,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9139,7 +9138,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9166,7 +9165,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L114">
         <v>7</v>
@@ -9184,7 +9183,7 @@
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9195,7 +9194,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9222,7 +9221,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9240,7 +9239,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9251,7 +9250,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9278,7 +9277,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L116">
         <v>3</v>
@@ -9296,7 +9295,7 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9307,7 +9306,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9334,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9352,7 +9351,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9363,7 +9362,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9390,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9408,7 +9407,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9416,10 +9415,10 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B119" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9446,7 +9445,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -9464,7 +9463,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9475,7 +9474,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9502,7 +9501,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9520,7 +9519,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9531,7 +9530,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9558,7 +9557,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -9576,7 +9575,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9587,7 +9586,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9614,7 +9613,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L122">
         <v>4</v>
@@ -9632,7 +9631,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9643,7 +9642,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9670,7 +9669,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -9688,7 +9687,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9699,7 +9698,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9726,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -9744,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9755,7 +9754,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9782,7 +9781,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -9800,7 +9799,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -9811,7 +9810,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -9838,7 +9837,7 @@
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -9856,7 +9855,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -9867,7 +9866,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -9894,7 +9893,7 @@
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L127">
         <v>7</v>
@@ -9912,7 +9911,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -9923,7 +9922,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -9950,7 +9949,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -9968,7 +9967,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -9979,7 +9978,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10006,7 +10005,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L129">
         <v>7</v>
@@ -10024,7 +10023,7 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10035,7 +10034,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10062,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10080,7 +10079,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10091,7 +10090,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10118,7 +10117,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10136,7 +10135,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10147,7 +10146,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10174,7 +10173,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L132">
         <v>18</v>
@@ -10192,7 +10191,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10203,7 +10202,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10230,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L133">
         <v>10</v>
@@ -10239,7 +10238,7 @@
         <v>6</v>
       </c>
       <c r="N133">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O133">
         <v>10</v>
@@ -10248,7 +10247,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10259,7 +10258,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10286,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L134">
         <v>13</v>
@@ -10295,7 +10294,7 @@
         <v>6</v>
       </c>
       <c r="N134">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O134">
         <v>13</v>
@@ -10304,7 +10303,7 @@
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10315,7 +10314,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10342,7 +10341,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10360,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10371,7 +10370,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10398,7 +10397,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10407,7 +10406,7 @@
         <v>1</v>
       </c>
       <c r="N136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O136">
         <v>4</v>
@@ -10416,7 +10415,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10427,7 +10426,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10454,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L137">
         <v>3</v>
@@ -10472,7 +10471,7 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10483,7 +10482,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10510,7 +10509,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L138">
         <v>3</v>
@@ -10528,7 +10527,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10539,7 +10538,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10566,7 +10565,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L139">
         <v>1</v>
@@ -10584,7 +10583,7 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10595,7 +10594,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10622,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L140">
         <v>2</v>
@@ -10640,7 +10639,7 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10651,7 +10650,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10678,7 +10677,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L141">
         <v>2</v>
@@ -10696,7 +10695,7 @@
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -10707,7 +10706,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -10734,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -10752,7 +10751,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -10763,7 +10762,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -10790,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -10808,7 +10807,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -10819,7 +10818,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -10846,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L144">
         <v>1</v>
@@ -10864,7 +10863,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -10872,10 +10871,10 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B145" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -10902,7 +10901,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -10920,7 +10919,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -10928,10 +10927,10 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B146" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -10958,7 +10957,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -10976,7 +10975,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -10987,7 +10986,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11014,7 +11013,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L147">
         <v>1</v>
@@ -11032,7 +11031,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11043,7 +11042,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11070,7 +11069,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L148">
         <v>6</v>
@@ -11088,7 +11087,7 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11099,7 +11098,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11126,7 +11125,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11135,7 +11134,7 @@
         <v>0</v>
       </c>
       <c r="N149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O149">
         <v>1</v>
@@ -11144,7 +11143,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11155,7 +11154,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11182,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11200,7 +11199,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11211,7 +11210,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11238,7 +11237,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -11256,7 +11255,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11264,16 +11263,16 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B152" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C152" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D152" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11294,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11312,7 +11311,7 @@
         <v>16</v>
       </c>
       <c r="Q152" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="R152">
         <v>0</v>
@@ -11320,16 +11319,16 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B153" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C153" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D153" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11350,7 +11349,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11368,7 +11367,7 @@
         <v>16</v>
       </c>
       <c r="Q153" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="R153">
         <v>0</v>
@@ -11376,16 +11375,16 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B154" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C154" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D154" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11406,7 +11405,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11424,7 +11423,7 @@
         <v>16</v>
       </c>
       <c r="Q154" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="R154">
         <v>0</v>
@@ -11432,16 +11431,16 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B155" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C155" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D155" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11462,7 +11461,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11480,7 +11479,7 @@
         <v>16</v>
       </c>
       <c r="Q155" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="R155">
         <v>0</v>
@@ -11488,16 +11487,16 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B156" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C156" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D156" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11518,7 +11517,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11536,7 +11535,7 @@
         <v>16</v>
       </c>
       <c r="Q156" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R156">
         <v>0</v>
@@ -11544,16 +11543,16 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B157" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C157" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D157" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11574,7 +11573,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -11592,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="Q157" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="R157">
         <v>0</v>
@@ -11600,16 +11599,16 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B158" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C158" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D158" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -11630,7 +11629,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -11648,7 +11647,7 @@
         <v>16</v>
       </c>
       <c r="Q158" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="R158">
         <v>0</v>
@@ -11656,16 +11655,16 @@
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B159" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C159" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D159" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -11686,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -11704,7 +11703,7 @@
         <v>16</v>
       </c>
       <c r="Q159" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="R159">
         <v>0</v>
@@ -11712,16 +11711,16 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B160" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C160" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D160" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -11742,7 +11741,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -11760,7 +11759,7 @@
         <v>16</v>
       </c>
       <c r="Q160" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="R160">
         <v>0</v>
@@ -11768,16 +11767,16 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B161" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C161" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D161" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -11798,7 +11797,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -11816,7 +11815,7 @@
         <v>16</v>
       </c>
       <c r="Q161" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="R161">
         <v>0</v>
@@ -11824,16 +11823,16 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B162" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C162" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D162" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -11854,7 +11853,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -11872,7 +11871,7 @@
         <v>16</v>
       </c>
       <c r="Q162" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="R162">
         <v>0</v>
@@ -11880,16 +11879,16 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B163" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C163" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D163" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -11910,7 +11909,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -11928,7 +11927,7 @@
         <v>16</v>
       </c>
       <c r="Q163" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="R163">
         <v>0</v>
@@ -11936,16 +11935,16 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B164" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C164" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D164" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -11966,7 +11965,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -11984,7 +11983,7 @@
         <v>16</v>
       </c>
       <c r="Q164" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="R164">
         <v>0</v>
@@ -11992,16 +11991,16 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B165" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C165" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D165" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12022,7 +12021,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12040,7 +12039,7 @@
         <v>16</v>
       </c>
       <c r="Q165" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="R165">
         <v>0</v>
@@ -12048,16 +12047,16 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B166" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C166" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D166" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12078,7 +12077,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12096,7 +12095,7 @@
         <v>16</v>
       </c>
       <c r="Q166" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="R166">
         <v>0</v>
@@ -12104,16 +12103,16 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B167" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C167" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D167" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12134,7 +12133,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12152,7 +12151,7 @@
         <v>16</v>
       </c>
       <c r="Q167" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="R167">
         <v>0</v>
@@ -12160,16 +12159,16 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B168" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C168" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D168" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12190,7 +12189,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12208,7 +12207,7 @@
         <v>16</v>
       </c>
       <c r="Q168" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="R168">
         <v>0</v>
@@ -12216,16 +12215,16 @@
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B169" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C169" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D169" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12246,7 +12245,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12264,7 +12263,7 @@
         <v>16</v>
       </c>
       <c r="Q169" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="R169">
         <v>0</v>
@@ -12272,16 +12271,16 @@
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B170" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C170" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D170" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12302,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12320,7 +12319,7 @@
         <v>16</v>
       </c>
       <c r="Q170" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="R170">
         <v>0</v>
@@ -12328,16 +12327,16 @@
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B171" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C171" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D171" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12358,7 +12357,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12376,7 +12375,7 @@
         <v>16</v>
       </c>
       <c r="Q171" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="R171">
         <v>0</v>
@@ -12387,7 +12386,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12414,7 +12413,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -12432,7 +12431,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12443,7 +12442,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12470,7 +12469,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L173">
         <v>6</v>
@@ -12488,7 +12487,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -12499,7 +12498,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -12526,7 +12525,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L174">
         <v>4</v>
@@ -12544,7 +12543,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -12555,7 +12554,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -12582,7 +12581,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -12600,7 +12599,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -12611,7 +12610,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -12638,7 +12637,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -12656,7 +12655,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -12667,7 +12666,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -12694,7 +12693,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -12712,7 +12711,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -12723,7 +12722,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -12750,7 +12749,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -12759,7 +12758,7 @@
         <v>1</v>
       </c>
       <c r="N178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O178">
         <v>2</v>
@@ -12768,7 +12767,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -12776,10 +12775,10 @@
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B179" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -12806,7 +12805,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -12824,7 +12823,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -12835,7 +12834,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -12862,7 +12861,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L180">
         <v>2</v>
@@ -12880,7 +12879,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -12888,10 +12887,10 @@
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B181" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -12918,7 +12917,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -12936,7 +12935,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -12947,7 +12946,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -12974,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L182">
         <v>5</v>
@@ -12992,7 +12991,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13003,7 +13002,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13030,7 +13029,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L183">
         <v>4</v>
@@ -13048,7 +13047,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13059,7 +13058,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13086,7 +13085,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -13104,7 +13103,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13115,7 +13114,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13142,7 +13141,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L185">
         <v>3</v>
@@ -13160,7 +13159,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13171,7 +13170,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13198,7 +13197,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13216,7 +13215,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13227,7 +13226,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13254,7 +13253,7 @@
         <v>4</v>
       </c>
       <c r="K187" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L187">
         <v>8</v>
@@ -13272,7 +13271,7 @@
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13283,7 +13282,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13310,7 +13309,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -13328,7 +13327,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13339,7 +13338,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13366,7 +13365,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13384,7 +13383,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -13395,7 +13394,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -13422,7 +13421,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -13440,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -13448,10 +13447,10 @@
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B191" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -13478,7 +13477,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -13496,7 +13495,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -13507,7 +13506,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -13534,7 +13533,7 @@
         <v>7</v>
       </c>
       <c r="K192" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L192">
         <v>12</v>
@@ -13552,7 +13551,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -13563,7 +13562,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -13590,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L193">
         <v>21</v>
@@ -13608,7 +13607,7 @@
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -13619,7 +13618,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -13646,7 +13645,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L194">
         <v>21</v>
@@ -13664,7 +13663,7 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -13675,7 +13674,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -13702,7 +13701,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -13720,7 +13719,7 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -13731,7 +13730,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -13758,7 +13757,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L196">
         <v>8</v>
@@ -13776,7 +13775,7 @@
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -13784,10 +13783,10 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B197" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -13814,7 +13813,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -13832,7 +13831,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -13843,7 +13842,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -13870,7 +13869,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -13888,7 +13887,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -13899,7 +13898,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -13926,7 +13925,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -13944,7 +13943,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -13952,10 +13951,10 @@
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B200" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -13982,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14000,7 +13999,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14011,7 +14010,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14038,7 +14037,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14056,7 +14055,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14064,10 +14063,10 @@
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B202" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14094,7 +14093,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14112,7 +14111,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14123,7 +14122,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14150,7 +14149,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14168,7 +14167,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14176,10 +14175,10 @@
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B204" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14206,7 +14205,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -14224,7 +14223,7 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14235,7 +14234,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14262,7 +14261,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14280,7 +14279,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14288,10 +14287,10 @@
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B206" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -14318,7 +14317,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -14336,7 +14335,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -14344,10 +14343,10 @@
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B207" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -14374,7 +14373,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -14392,7 +14391,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -14400,10 +14399,10 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B208" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -14430,7 +14429,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L208">
         <v>0</v>
@@ -14448,7 +14447,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -14456,10 +14455,10 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B209" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -14486,7 +14485,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -14504,7 +14503,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -14512,10 +14511,10 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B210" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -14542,7 +14541,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -14560,7 +14559,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -14568,10 +14567,10 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B211" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -14598,7 +14597,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -14616,7 +14615,7 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -14624,10 +14623,10 @@
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B212" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -14654,7 +14653,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -14672,7 +14671,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -14680,10 +14679,10 @@
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B213" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -14710,7 +14709,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -14728,7 +14727,7 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -14739,7 +14738,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -14766,7 +14765,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -14784,7 +14783,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -14795,7 +14794,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -14822,7 +14821,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -14840,7 +14839,7 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -14848,10 +14847,10 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B216" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -14878,7 +14877,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -14896,7 +14895,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -14907,7 +14906,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -14934,7 +14933,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L217">
         <v>6</v>
@@ -14952,7 +14951,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -14963,7 +14962,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -14990,7 +14989,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L218">
         <v>3</v>
@@ -15008,7 +15007,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15019,7 +15018,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15046,7 +15045,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L219">
         <v>3</v>
@@ -15064,7 +15063,7 @@
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15075,7 +15074,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15102,7 +15101,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L220">
         <v>3</v>
@@ -15120,7 +15119,7 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15128,10 +15127,10 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B221" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15158,7 +15157,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15176,7 +15175,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15187,7 +15186,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -15214,7 +15213,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -15232,7 +15231,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -15243,7 +15242,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -15270,7 +15269,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L223">
         <v>11</v>
@@ -15288,7 +15287,7 @@
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -15299,7 +15298,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -15326,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -15344,7 +15343,7 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -15355,7 +15354,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -15382,7 +15381,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L225">
         <v>7</v>
@@ -15400,7 +15399,7 @@
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -15411,7 +15410,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -15438,7 +15437,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -15447,7 +15446,7 @@
         <v>1</v>
       </c>
       <c r="N226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O226">
         <v>3</v>
@@ -15456,7 +15455,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -15467,7 +15466,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -15494,7 +15493,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L227">
         <v>9</v>
@@ -15503,7 +15502,7 @@
         <v>9</v>
       </c>
       <c r="N227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O227">
         <v>9</v>
@@ -15512,7 +15511,7 @@
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -15523,7 +15522,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -15550,7 +15549,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L228">
         <v>12</v>
@@ -15568,7 +15567,7 @@
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -15579,7 +15578,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -15594,37 +15593,37 @@
         <v>245</v>
       </c>
       <c r="G229">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H229">
         <v>0</v>
       </c>
       <c r="I229">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J229">
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L229">
+        <v>14</v>
+      </c>
+      <c r="M229">
+        <v>9</v>
+      </c>
+      <c r="N229">
+        <v>4</v>
+      </c>
+      <c r="O229">
         <v>13</v>
       </c>
-      <c r="M229">
-        <v>8</v>
-      </c>
-      <c r="N229">
-        <v>3</v>
-      </c>
-      <c r="O229">
-        <v>12</v>
-      </c>
       <c r="P229" t="s">
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -15635,7 +15634,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -15662,7 +15661,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -15680,7 +15679,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -15691,7 +15690,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -15718,7 +15717,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -15736,7 +15735,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -15771,7 +15770,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -15794,10 +15793,10 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>774</v>
+        <v>173</v>
       </c>
       <c r="B233" t="s">
-        <v>774</v>
+        <v>173</v>
       </c>
       <c r="C233" t="s">
         <v>120</v>
@@ -15809,7 +15808,7 @@
         <v>122</v>
       </c>
       <c r="G233">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -15821,25 +15820,25 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M233">
         <v>0</v>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P233" t="s">
         <v>13</v>
       </c>
       <c r="Q233" t="s">
-        <v>774</v>
+        <v>173</v>
       </c>
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.3">
@@ -15871,7 +15870,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -15921,7 +15920,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -15971,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -16021,7 +16020,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -16071,7 +16070,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -16121,7 +16120,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -16171,7 +16170,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -16221,7 +16220,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -16271,7 +16270,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -16321,7 +16320,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -16371,7 +16370,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -16421,7 +16420,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L245">
         <v>2</v>
@@ -16471,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -16521,7 +16520,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -16571,7 +16570,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -16621,7 +16620,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -16671,7 +16670,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -16721,7 +16720,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -16771,7 +16770,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L252">
         <v>1</v>
@@ -16821,7 +16820,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L253">
         <v>1</v>
@@ -16871,7 +16870,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -16921,7 +16920,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -16959,7 +16958,7 @@
         <v>122</v>
       </c>
       <c r="G256">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -16971,19 +16970,19 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L256">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M256">
         <v>0</v>
       </c>
       <c r="N256">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O256">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P256" t="s">
         <v>13</v>
@@ -17021,7 +17020,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -17071,7 +17070,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L258">
         <v>2</v>
@@ -17121,7 +17120,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -17149,9 +17148,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5060B6-C869-4DAE-8595-7918B4F1E2F7}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J450"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90C19953-919C-418B-B60D-05384EA8A8B8}">
+  <dimension ref="A1:J454"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -31552,6 +31550,134 @@
       </c>
       <c r="J450" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A451" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B451" t="s">
+        <v>173</v>
+      </c>
+      <c r="C451" t="s">
+        <v>120</v>
+      </c>
+      <c r="D451" t="s">
+        <v>126</v>
+      </c>
+      <c r="E451" t="s">
+        <v>168</v>
+      </c>
+      <c r="F451" t="s">
+        <v>94</v>
+      </c>
+      <c r="G451">
+        <v>0</v>
+      </c>
+      <c r="H451" t="s">
+        <v>122</v>
+      </c>
+      <c r="I451">
+        <v>1</v>
+      </c>
+      <c r="J451" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A452" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B452" t="s">
+        <v>164</v>
+      </c>
+      <c r="C452" t="s">
+        <v>24</v>
+      </c>
+      <c r="D452" t="s">
+        <v>33</v>
+      </c>
+      <c r="E452" t="s">
+        <v>100</v>
+      </c>
+      <c r="F452" t="s">
+        <v>94</v>
+      </c>
+      <c r="G452">
+        <v>275</v>
+      </c>
+      <c r="H452" t="s">
+        <v>15</v>
+      </c>
+      <c r="I452">
+        <v>1</v>
+      </c>
+      <c r="J452" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A453" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B453" t="s">
+        <v>50</v>
+      </c>
+      <c r="C453" t="s">
+        <v>24</v>
+      </c>
+      <c r="D453" t="s">
+        <v>49</v>
+      </c>
+      <c r="E453" t="s">
+        <v>100</v>
+      </c>
+      <c r="F453" t="s">
+        <v>66</v>
+      </c>
+      <c r="G453">
+        <v>245</v>
+      </c>
+      <c r="H453" t="s">
+        <v>22</v>
+      </c>
+      <c r="I453">
+        <v>1</v>
+      </c>
+      <c r="J453" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A454" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B454" t="s">
+        <v>137</v>
+      </c>
+      <c r="C454" t="s">
+        <v>120</v>
+      </c>
+      <c r="D454" t="s">
+        <v>138</v>
+      </c>
+      <c r="E454" t="s">
+        <v>133</v>
+      </c>
+      <c r="F454" t="s">
+        <v>94</v>
+      </c>
+      <c r="G454">
+        <v>0</v>
+      </c>
+      <c r="H454" t="s">
+        <v>122</v>
+      </c>
+      <c r="I454">
+        <v>1</v>
+      </c>
+      <c r="J454" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE49FD6A-6268-4328-98AF-1286875AD97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE221276-D16D-43B0-A3B3-75C9EAF73AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{4489E321-18D6-4E17-8776-D3EB5CED777E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{334F2CA3-AF52-441C-971C-2D09E07DFAC5}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5339" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5353" uniqueCount="611">
   <si>
     <t>날짜</t>
   </si>
@@ -2258,7 +2258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B44ADC-84FC-458B-8B53-B5185DA9F063}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{405986CD-0BDF-4F7B-9F65-763CBE147485}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -13008,13 +13008,13 @@
         <v>245</v>
       </c>
       <c r="G174">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H174">
         <v>0</v>
       </c>
       <c r="I174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -13023,16 +13023,16 @@
         <v>198</v>
       </c>
       <c r="L174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M174">
         <v>1</v>
       </c>
       <c r="N174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P174" t="s">
         <v>16</v>
@@ -14248,13 +14248,13 @@
         <v>245</v>
       </c>
       <c r="G194">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H194">
         <v>0</v>
       </c>
       <c r="I194">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J194">
         <v>0</v>
@@ -14263,16 +14263,16 @@
         <v>198</v>
       </c>
       <c r="L194">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M194">
         <v>14</v>
       </c>
       <c r="N194">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O194">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P194" t="s">
         <v>16</v>
@@ -18287,8 +18287,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6893C8-FD80-40DB-A33D-7F79907C4FC0}">
-  <dimension ref="A1:J473"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C984E3A1-420B-4BBB-9E95-AB664509058E}">
+  <dimension ref="A1:J475"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -32696,31 +32696,31 @@
         <v>46227</v>
       </c>
       <c r="B451" t="s">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="C451" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D451" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="E451" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="F451" t="s">
         <v>94</v>
       </c>
       <c r="G451">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="H451" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="I451">
         <v>1</v>
       </c>
       <c r="J451" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.3">
@@ -32728,25 +32728,25 @@
         <v>46227</v>
       </c>
       <c r="B452" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="C452" t="s">
         <v>24</v>
       </c>
       <c r="D452" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E452" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F452" t="s">
         <v>94</v>
       </c>
       <c r="G452">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="H452" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I452">
         <v>1</v>
@@ -32760,31 +32760,31 @@
         <v>46227</v>
       </c>
       <c r="B453" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="C453" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="D453" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E453" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="F453" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="G453">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="H453" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="I453">
         <v>1</v>
       </c>
       <c r="J453" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.3">
@@ -32792,39 +32792,39 @@
         <v>46227</v>
       </c>
       <c r="B454" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="C454" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D454" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="E454" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="F454" t="s">
         <v>94</v>
       </c>
       <c r="G454">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="H454" t="s">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="I454">
         <v>1</v>
       </c>
       <c r="J454" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B455" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="C455" t="s">
         <v>24</v>
@@ -32833,13 +32833,13 @@
         <v>49</v>
       </c>
       <c r="E455" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="F455" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="G455">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H455" t="s">
         <v>22</v>
@@ -32853,34 +32853,34 @@
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B456" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="C456" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="D456" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="E456" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="F456" t="s">
         <v>94</v>
       </c>
       <c r="G456">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="H456" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="I456">
         <v>1</v>
       </c>
       <c r="J456" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.3">
@@ -32888,13 +32888,13 @@
         <v>46230</v>
       </c>
       <c r="B457" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="C457" t="s">
         <v>24</v>
       </c>
       <c r="D457" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E457" t="s">
         <v>53</v>
@@ -32903,10 +32903,10 @@
         <v>94</v>
       </c>
       <c r="G457">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="H457" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I457">
         <v>1</v>
@@ -32920,31 +32920,31 @@
         <v>46230</v>
       </c>
       <c r="B458" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="C458" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D458" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="E458" t="s">
-        <v>175</v>
+        <v>53</v>
       </c>
       <c r="F458" t="s">
         <v>94</v>
       </c>
       <c r="G458">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="H458" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="I458">
         <v>1</v>
       </c>
       <c r="J458" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.3">
@@ -32952,31 +32952,31 @@
         <v>46230</v>
       </c>
       <c r="B459" t="s">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="C459" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D459" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="E459" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="F459" t="s">
         <v>94</v>
       </c>
       <c r="G459">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="H459" t="s">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="I459">
         <v>1</v>
       </c>
       <c r="J459" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
@@ -32984,22 +32984,22 @@
         <v>46230</v>
       </c>
       <c r="B460" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C460" t="s">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="D460" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="E460" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="F460" t="s">
         <v>94</v>
       </c>
-      <c r="G460" t="s">
-        <v>179</v>
+      <c r="G460">
+        <v>0</v>
       </c>
       <c r="H460" t="s">
         <v>122</v>
@@ -33008,7 +33008,7 @@
         <v>1</v>
       </c>
       <c r="J460" t="s">
-        <v>180</v>
+        <v>13</v>
       </c>
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.3">
@@ -33016,31 +33016,31 @@
         <v>46230</v>
       </c>
       <c r="B461" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="C461" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="D461" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="E461" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="F461" t="s">
         <v>94</v>
       </c>
       <c r="G461">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H461" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="I461">
         <v>1</v>
       </c>
       <c r="J461" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.3">
@@ -33048,31 +33048,31 @@
         <v>46230</v>
       </c>
       <c r="B462" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C462" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="D462" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="E462" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="F462" t="s">
         <v>94</v>
       </c>
-      <c r="G462">
-        <v>255</v>
+      <c r="G462" t="s">
+        <v>179</v>
       </c>
       <c r="H462" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="I462">
         <v>1</v>
       </c>
       <c r="J462" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
@@ -33080,13 +33080,13 @@
         <v>46230</v>
       </c>
       <c r="B463" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C463" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D463" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="E463" t="s">
         <v>53</v>
@@ -33095,7 +33095,7 @@
         <v>94</v>
       </c>
       <c r="G463">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H463" t="s">
         <v>22</v>
@@ -33112,13 +33112,13 @@
         <v>46230</v>
       </c>
       <c r="B464" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C464" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D464" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="E464" t="s">
         <v>53</v>
@@ -33127,10 +33127,10 @@
         <v>94</v>
       </c>
       <c r="G464">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="H464" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I464">
         <v>1</v>
@@ -33144,13 +33144,13 @@
         <v>46230</v>
       </c>
       <c r="B465" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C465" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D465" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E465" t="s">
         <v>53</v>
@@ -33159,7 +33159,7 @@
         <v>94</v>
       </c>
       <c r="G465">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H465" t="s">
         <v>22</v>
@@ -33176,13 +33176,13 @@
         <v>46230</v>
       </c>
       <c r="B466" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="C466" t="s">
         <v>24</v>
       </c>
       <c r="D466" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E466" t="s">
         <v>53</v>
@@ -33191,10 +33191,10 @@
         <v>94</v>
       </c>
       <c r="G466">
-        <v>235</v>
+        <v>275</v>
       </c>
       <c r="H466" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I466">
         <v>1</v>
@@ -33208,13 +33208,13 @@
         <v>46230</v>
       </c>
       <c r="B467" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C467" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D467" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E467" t="s">
         <v>53</v>
@@ -33223,7 +33223,7 @@
         <v>94</v>
       </c>
       <c r="G467">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H467" t="s">
         <v>22</v>
@@ -33240,13 +33240,13 @@
         <v>46230</v>
       </c>
       <c r="B468" t="s">
-        <v>181</v>
+        <v>71</v>
       </c>
       <c r="C468" t="s">
         <v>24</v>
       </c>
       <c r="D468" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E468" t="s">
         <v>53</v>
@@ -33255,7 +33255,7 @@
         <v>94</v>
       </c>
       <c r="G468">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H468" t="s">
         <v>22</v>
@@ -33272,13 +33272,13 @@
         <v>46230</v>
       </c>
       <c r="B469" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C469" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D469" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E469" t="s">
         <v>53</v>
@@ -33304,13 +33304,13 @@
         <v>46230</v>
       </c>
       <c r="B470" t="s">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="C470" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D470" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E470" t="s">
         <v>53</v>
@@ -33336,25 +33336,25 @@
         <v>46230</v>
       </c>
       <c r="B471" t="s">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="C471" t="s">
         <v>24</v>
       </c>
       <c r="D471" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="E471" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F471" t="s">
         <v>94</v>
       </c>
       <c r="G471">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="H471" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I471">
         <v>1</v>
@@ -33368,25 +33368,25 @@
         <v>46230</v>
       </c>
       <c r="B472" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C472" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D472" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E472" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F472" t="s">
         <v>94</v>
       </c>
       <c r="G472">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="H472" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I472">
         <v>1</v>
@@ -33400,30 +33400,94 @@
         <v>46230</v>
       </c>
       <c r="B473" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C473" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D473" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E473" t="s">
         <v>100</v>
       </c>
       <c r="F473" t="s">
+        <v>94</v>
+      </c>
+      <c r="G473">
+        <v>275</v>
+      </c>
+      <c r="H473" t="s">
+        <v>15</v>
+      </c>
+      <c r="I473">
+        <v>1</v>
+      </c>
+      <c r="J473" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A474" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B474" t="s">
+        <v>29</v>
+      </c>
+      <c r="C474" t="s">
+        <v>24</v>
+      </c>
+      <c r="D474" t="s">
+        <v>30</v>
+      </c>
+      <c r="E474" t="s">
+        <v>100</v>
+      </c>
+      <c r="F474" t="s">
+        <v>94</v>
+      </c>
+      <c r="G474">
+        <v>275</v>
+      </c>
+      <c r="H474" t="s">
+        <v>15</v>
+      </c>
+      <c r="I474">
+        <v>1</v>
+      </c>
+      <c r="J474" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A475" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B475" t="s">
+        <v>170</v>
+      </c>
+      <c r="C475" t="s">
+        <v>18</v>
+      </c>
+      <c r="D475" t="s">
+        <v>90</v>
+      </c>
+      <c r="E475" t="s">
+        <v>100</v>
+      </c>
+      <c r="F475" t="s">
         <v>66</v>
       </c>
-      <c r="G473">
+      <c r="G475">
         <v>245</v>
       </c>
-      <c r="H473" t="s">
-        <v>22</v>
-      </c>
-      <c r="I473">
-        <v>1</v>
-      </c>
-      <c r="J473" t="s">
+      <c r="H475" t="s">
+        <v>22</v>
+      </c>
+      <c r="I475">
+        <v>1</v>
+      </c>
+      <c r="J475" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE221276-D16D-43B0-A3B3-75C9EAF73AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A132621E-8BD9-4C94-BCB0-47D873C1A12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{334F2CA3-AF52-441C-971C-2D09E07DFAC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{FCEDDCCE-9DAC-459D-AADD-A604475A287D}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5353" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5451" uniqueCount="614">
   <si>
     <t>날짜</t>
   </si>
@@ -591,6 +591,24 @@
     <t>BJM931-WHGN275</t>
   </si>
   <si>
+    <t>카페24/바오지</t>
+  </si>
+  <si>
+    <t>유튜브쇼핑</t>
+  </si>
+  <si>
+    <t>BJM931-BK260</t>
+  </si>
+  <si>
+    <t>스토어팜/바오지</t>
+  </si>
+  <si>
+    <t>S-10RA-GYGG</t>
+  </si>
+  <si>
+    <t>S-10RA</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1059,9 +1077,6 @@
     <t>BJM931WHGN 바오지 남성 러닝화 화이트그린 280</t>
   </si>
   <si>
-    <t>BJM931-BK260</t>
-  </si>
-  <si>
     <t>BJM931BK 바오지 남성 러닝화 블랙 260</t>
   </si>
   <si>
@@ -1825,12 +1840,6 @@
   </si>
   <si>
     <t>S-10RA-GYGC</t>
-  </si>
-  <si>
-    <t>S-10RA</t>
-  </si>
-  <si>
-    <t>S-10RA-GYGG</t>
   </si>
   <si>
     <t>S-10RA-MAGC</t>
@@ -2258,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{405986CD-0BDF-4F7B-9F65-763CBE147485}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4ABF82D-2456-431D-B0E7-A573DE6ACAE6}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2267,7 +2276,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2282,46 +2291,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="J1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="K1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="M1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="N1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="O1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="R1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="S1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="T1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2329,7 +2338,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2356,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2374,7 +2383,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2391,7 +2400,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2418,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -2436,7 +2445,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2453,7 +2462,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2480,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2498,7 +2507,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2515,7 +2524,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2542,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2560,7 +2569,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2577,7 +2586,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2604,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2622,7 +2631,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2639,7 +2648,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2666,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2684,7 +2693,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2701,7 +2710,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2728,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2746,7 +2755,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2763,7 +2772,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2790,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2808,7 +2817,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2825,7 +2834,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2852,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2870,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2887,7 +2896,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2914,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2932,7 +2941,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2946,16 +2955,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D12" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2976,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3008,16 +3017,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D13" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3038,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3070,16 +3079,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B14" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3100,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3132,16 +3141,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" t="s">
         <v>218</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>219</v>
-      </c>
-      <c r="C15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D15" t="s">
-        <v>213</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3162,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3194,16 +3203,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B16" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D16" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3224,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3256,16 +3265,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B17" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C17" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D17" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3286,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3318,16 +3327,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B18" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C18" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D18" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3348,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3380,16 +3389,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C19" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D19" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3410,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3442,16 +3451,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C20" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D20" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3472,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3504,16 +3513,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C21" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D21" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3534,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3566,16 +3575,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C22" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D22" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3596,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3628,16 +3637,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D23" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3658,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3690,16 +3699,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C24" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D24" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3720,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3752,16 +3761,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D25" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3782,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3814,16 +3823,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C26" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D26" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3844,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3876,16 +3885,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C27" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D27" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3906,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3938,16 +3947,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D28" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3968,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4000,16 +4009,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C29" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D29" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4030,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4062,16 +4071,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C30" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D30" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4092,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4124,16 +4133,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C31" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D31" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4154,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4186,16 +4195,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D32" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4216,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4248,16 +4257,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D33" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4278,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4310,16 +4319,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C34" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D34" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4340,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4372,16 +4381,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s">
+        <v>266</v>
+      </c>
+      <c r="C35" t="s">
+        <v>218</v>
+      </c>
+      <c r="D35" t="s">
         <v>260</v>
-      </c>
-      <c r="C35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" t="s">
-        <v>254</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4402,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4434,16 +4443,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D36" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4464,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4496,16 +4505,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B37" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C37" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D37" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4526,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4558,16 +4567,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B38" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C38" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D38" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4588,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4620,16 +4629,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B39" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C39" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D39" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4650,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4682,16 +4691,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B40" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C40" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D40" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4712,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4744,16 +4753,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B41" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C41" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D41" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4774,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4806,16 +4815,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B42" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C42" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D42" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4836,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4868,16 +4877,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B43" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C43" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D43" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4898,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4930,16 +4939,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C44" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D44" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4960,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -4992,16 +5001,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B45" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C45" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D45" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5022,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5054,16 +5063,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B46" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C46" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D46" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5084,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5116,16 +5125,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B47" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C47" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D47" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5146,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5178,16 +5187,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B48" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D48" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5208,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5240,16 +5249,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B49" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C49" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D49" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5270,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5302,16 +5311,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B50" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C50" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D50" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5332,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5364,16 +5373,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B51" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D51" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5394,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5426,16 +5435,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B52" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C52" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D52" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5456,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5488,16 +5497,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B53" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C53" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D53" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5518,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5550,16 +5559,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B54" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C54" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D54" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5580,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5612,16 +5621,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B55" t="s">
+        <v>307</v>
+      </c>
+      <c r="C55" t="s">
+        <v>218</v>
+      </c>
+      <c r="D55" t="s">
         <v>301</v>
-      </c>
-      <c r="C55" t="s">
-        <v>212</v>
-      </c>
-      <c r="D55" t="s">
-        <v>295</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5642,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5674,16 +5683,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B56" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C56" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D56" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5704,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5736,16 +5745,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B57" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C57" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D57" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5766,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5798,16 +5807,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B58" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C58" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D58" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5828,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5860,16 +5869,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B59" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C59" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D59" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5890,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5922,16 +5931,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B60" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C60" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D60" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5952,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5984,16 +5993,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B61" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C61" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D61" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6014,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6046,16 +6055,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B62" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C62" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D62" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6076,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6108,16 +6117,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B63" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C63" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D63" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6138,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6170,16 +6179,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B64" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C64" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D64" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6200,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6232,16 +6241,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B65" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D65" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6262,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6294,16 +6303,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B66" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C66" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D66" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6324,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6359,7 +6368,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6386,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6404,7 +6413,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6421,7 +6430,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6448,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -6466,7 +6475,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6483,7 +6492,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6510,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L69">
         <v>4</v>
@@ -6528,7 +6537,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6545,7 +6554,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6572,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6590,7 +6599,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6607,7 +6616,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6634,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6652,7 +6661,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6666,10 +6675,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B72" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6696,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6714,7 +6723,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6731,7 +6740,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6758,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6776,7 +6785,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6790,10 +6799,10 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B74" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6820,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -6838,7 +6847,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6855,7 +6864,7 @@
         <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6882,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6900,7 +6909,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6914,10 +6923,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B76" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6944,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6962,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6976,10 +6985,10 @@
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>339</v>
+        <v>185</v>
       </c>
       <c r="B77" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -6994,37 +7003,37 @@
         <v>260</v>
       </c>
       <c r="G77">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H77">
         <v>0</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77">
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77">
         <v>0</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P77" t="s">
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7038,10 +7047,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B78" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7068,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7086,7 +7095,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7100,10 +7109,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B79" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7130,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7148,7 +7157,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7165,7 +7174,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7192,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7210,7 +7219,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7224,10 +7233,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B81" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7254,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -7272,7 +7281,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7286,10 +7295,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B82" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7316,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7334,7 +7343,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7348,10 +7357,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B83" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7378,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7396,7 +7405,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7410,10 +7419,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B84" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7440,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7458,7 +7467,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7472,10 +7481,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B85" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7502,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7520,7 +7529,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7534,10 +7543,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B86" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7564,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7582,7 +7591,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7596,10 +7605,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B87" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7626,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7644,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7661,7 +7670,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7688,7 +7697,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -7706,7 +7715,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7720,10 +7729,10 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B89" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7750,7 +7759,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -7768,7 +7777,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7785,7 +7794,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7812,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L90">
         <v>2</v>
@@ -7830,7 +7839,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7844,10 +7853,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B91" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7874,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7892,7 +7901,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7906,10 +7915,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B92" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7936,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7954,7 +7963,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7971,7 +7980,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -7998,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8016,7 +8025,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8030,10 +8039,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B94" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8060,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8078,7 +8087,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8092,10 +8101,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B95" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8122,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8140,7 +8149,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8154,10 +8163,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B96" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8184,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8202,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8216,10 +8225,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B97" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8246,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8264,7 +8273,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8281,7 +8290,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8308,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L98">
         <v>3</v>
@@ -8317,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="N98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98">
         <v>2</v>
@@ -8326,7 +8335,7 @@
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8343,7 +8352,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8370,7 +8379,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L99">
         <v>1</v>
@@ -8388,7 +8397,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8405,7 +8414,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8432,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8441,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="N100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O100">
         <v>3</v>
@@ -8450,7 +8459,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8464,10 +8473,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B101" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8494,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8512,7 +8521,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8526,10 +8535,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B102" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8556,7 +8565,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8574,7 +8583,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8588,10 +8597,10 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B103" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8618,7 +8627,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -8636,7 +8645,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8653,7 +8662,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8674,13 +8683,13 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8689,16 +8698,16 @@
         <v>0</v>
       </c>
       <c r="N104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P104" t="s">
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8712,10 +8721,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B105" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8742,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8760,7 +8769,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8777,7 +8786,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8804,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8822,7 +8831,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8836,10 +8845,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B107" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8866,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8884,7 +8893,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8901,7 +8910,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8928,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8946,7 +8955,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8963,7 +8972,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -8990,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -9008,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -9022,10 +9031,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B110" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -9052,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -9070,7 +9079,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -9084,10 +9093,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B111" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -9114,7 +9123,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9132,7 +9141,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9149,7 +9158,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9170,13 +9179,13 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9188,13 +9197,13 @@
         <v>1</v>
       </c>
       <c r="O112">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P112" t="s">
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9211,7 +9220,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9238,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L113">
         <v>5</v>
@@ -9256,7 +9265,7 @@
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9273,7 +9282,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9288,22 +9297,22 @@
         <v>270</v>
       </c>
       <c r="G114">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M114">
         <v>0</v>
@@ -9312,13 +9321,13 @@
         <v>3</v>
       </c>
       <c r="O114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P114" t="s">
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9335,7 +9344,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9362,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9371,7 +9380,7 @@
         <v>1</v>
       </c>
       <c r="N115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O115">
         <v>3</v>
@@ -9380,7 +9389,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9397,7 +9406,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9424,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L116">
         <v>3</v>
@@ -9433,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="N116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O116">
         <v>3</v>
@@ -9442,7 +9451,7 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9459,7 +9468,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9486,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9504,7 +9513,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9521,7 +9530,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9548,7 +9557,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9566,7 +9575,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9580,10 +9589,10 @@
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B119" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9610,7 +9619,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -9628,7 +9637,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9645,7 +9654,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9672,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9690,7 +9699,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9707,7 +9716,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9734,7 +9743,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -9752,7 +9761,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9769,7 +9778,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9796,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L122">
         <v>5</v>
@@ -9814,7 +9823,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9831,7 +9840,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9858,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -9876,7 +9885,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9893,7 +9902,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9920,7 +9929,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -9938,7 +9947,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9955,7 +9964,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9982,7 +9991,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -10000,7 +10009,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -10017,7 +10026,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -10038,13 +10047,13 @@
         <v>0</v>
       </c>
       <c r="I126">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -10056,13 +10065,13 @@
         <v>0</v>
       </c>
       <c r="O126">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P126" t="s">
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -10079,7 +10088,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -10106,7 +10115,7 @@
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L127">
         <v>7</v>
@@ -10124,7 +10133,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -10141,7 +10150,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -10168,7 +10177,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -10186,7 +10195,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -10203,7 +10212,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10218,22 +10227,22 @@
         <v>245</v>
       </c>
       <c r="G129">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H129">
         <v>0</v>
       </c>
       <c r="I129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M129">
         <v>6</v>
@@ -10242,13 +10251,13 @@
         <v>1</v>
       </c>
       <c r="O129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P129" t="s">
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10265,7 +10274,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10292,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10301,7 +10310,7 @@
         <v>5</v>
       </c>
       <c r="N130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O130">
         <v>7</v>
@@ -10310,7 +10319,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10327,7 +10336,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10354,7 +10363,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10372,7 +10381,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10389,7 +10398,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10416,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L132">
         <v>18</v>
@@ -10434,7 +10443,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10451,7 +10460,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10478,7 +10487,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L133">
         <v>10</v>
@@ -10487,7 +10496,7 @@
         <v>6</v>
       </c>
       <c r="N133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O133">
         <v>10</v>
@@ -10496,7 +10505,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10513,7 +10522,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10534,13 +10543,13 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L134">
         <v>16</v>
@@ -10549,16 +10558,16 @@
         <v>6</v>
       </c>
       <c r="N134">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O134">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P134" t="s">
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10575,7 +10584,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10602,7 +10611,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10611,7 +10620,7 @@
         <v>2</v>
       </c>
       <c r="N135">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O135">
         <v>6</v>
@@ -10620,7 +10629,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10637,7 +10646,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10664,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10682,7 +10691,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10699,7 +10708,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10726,7 +10735,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L137">
         <v>3</v>
@@ -10735,7 +10744,7 @@
         <v>0</v>
       </c>
       <c r="N137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O137">
         <v>3</v>
@@ -10744,7 +10753,7 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10761,7 +10770,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10776,37 +10785,37 @@
         <v>240</v>
       </c>
       <c r="G138">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M138">
         <v>0</v>
       </c>
       <c r="N138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P138" t="s">
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10823,7 +10832,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10838,37 +10847,37 @@
         <v>245</v>
       </c>
       <c r="G139">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H139">
         <v>0</v>
       </c>
       <c r="I139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P139" t="s">
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10885,7 +10894,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10912,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L140">
         <v>2</v>
@@ -10921,7 +10930,7 @@
         <v>0</v>
       </c>
       <c r="N140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O140">
         <v>2</v>
@@ -10930,7 +10939,7 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10947,7 +10956,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10974,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L141">
         <v>3</v>
@@ -10983,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="N141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O141">
         <v>3</v>
@@ -10992,7 +11001,7 @@
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -11009,7 +11018,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -11036,7 +11045,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -11054,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -11071,7 +11080,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -11098,7 +11107,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -11116,7 +11125,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -11133,7 +11142,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -11160,7 +11169,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -11178,7 +11187,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -11192,10 +11201,10 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B145" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -11222,7 +11231,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -11240,7 +11249,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -11254,10 +11263,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B146" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -11284,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -11302,7 +11311,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -11319,7 +11328,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11346,7 +11355,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L147">
         <v>1</v>
@@ -11364,7 +11373,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11381,7 +11390,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11408,7 +11417,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L148">
         <v>6</v>
@@ -11417,7 +11426,7 @@
         <v>1</v>
       </c>
       <c r="N148">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O148">
         <v>6</v>
@@ -11426,7 +11435,7 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11443,7 +11452,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11470,7 +11479,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11488,7 +11497,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11505,7 +11514,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11532,7 +11541,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11550,7 +11559,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11567,7 +11576,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11594,7 +11603,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -11612,7 +11621,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11626,16 +11635,16 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B152" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C152" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D152" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11656,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11688,16 +11697,16 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B153" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C153" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D153" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11718,7 +11727,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11750,16 +11759,16 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B154" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C154" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D154" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11780,7 +11789,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11812,16 +11821,16 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>468</v>
+      </c>
+      <c r="B155" t="s">
+        <v>469</v>
+      </c>
+      <c r="C155" t="s">
+        <v>218</v>
+      </c>
+      <c r="D155" t="s">
         <v>463</v>
-      </c>
-      <c r="B155" t="s">
-        <v>464</v>
-      </c>
-      <c r="C155" t="s">
-        <v>212</v>
-      </c>
-      <c r="D155" t="s">
-        <v>458</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11842,7 +11851,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11874,16 +11883,16 @@
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B156" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C156" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D156" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11904,7 +11913,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11936,16 +11945,16 @@
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B157" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C157" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D157" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11966,7 +11975,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -11998,16 +12007,16 @@
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B158" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C158" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D158" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -12028,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -12060,16 +12069,16 @@
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B159" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C159" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D159" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -12090,7 +12099,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -12122,16 +12131,16 @@
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B160" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C160" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D160" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -12152,7 +12161,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -12184,16 +12193,16 @@
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B161" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C161" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D161" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -12214,7 +12223,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -12246,16 +12255,16 @@
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B162" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C162" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D162" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -12276,7 +12285,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -12308,16 +12317,16 @@
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B163" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C163" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D163" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -12338,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -12370,16 +12379,16 @@
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B164" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C164" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D164" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -12400,7 +12409,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -12432,16 +12441,16 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B165" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C165" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D165" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12462,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12494,16 +12503,16 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B166" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C166" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D166" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12524,7 +12533,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12556,16 +12565,16 @@
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B167" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C167" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D167" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12586,7 +12595,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12618,16 +12627,16 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B168" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C168" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D168" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12648,7 +12657,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12680,16 +12689,16 @@
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B169" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C169" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D169" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12710,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12742,16 +12751,16 @@
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B170" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C170" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D170" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12772,7 +12781,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12804,16 +12813,16 @@
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B171" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C171" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D171" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12834,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12869,7 +12878,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12896,7 +12905,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -12905,7 +12914,7 @@
         <v>1</v>
       </c>
       <c r="N172">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O172">
         <v>5</v>
@@ -12914,7 +12923,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12931,7 +12940,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12946,37 +12955,37 @@
         <v>240</v>
       </c>
       <c r="G173">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H173">
         <v>0</v>
       </c>
       <c r="I173">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J173">
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L173">
+        <v>7</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>4</v>
+      </c>
+      <c r="O173">
         <v>6</v>
       </c>
-      <c r="M173">
-        <v>0</v>
-      </c>
-      <c r="N173">
-        <v>3</v>
-      </c>
-      <c r="O173">
-        <v>5</v>
-      </c>
       <c r="P173" t="s">
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -12993,7 +13002,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -13020,7 +13029,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L174">
         <v>5</v>
@@ -13029,7 +13038,7 @@
         <v>1</v>
       </c>
       <c r="N174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O174">
         <v>5</v>
@@ -13038,7 +13047,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -13055,7 +13064,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -13082,7 +13091,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -13091,7 +13100,7 @@
         <v>0</v>
       </c>
       <c r="N175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O175">
         <v>1</v>
@@ -13100,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -13117,7 +13126,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -13144,7 +13153,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -13162,7 +13171,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -13179,7 +13188,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -13206,7 +13215,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -13224,7 +13233,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -13241,7 +13250,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -13268,7 +13277,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -13286,7 +13295,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -13303,7 +13312,7 @@
         <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -13330,7 +13339,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L179">
         <v>1</v>
@@ -13348,7 +13357,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -13365,7 +13374,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -13392,7 +13401,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L180">
         <v>2</v>
@@ -13410,7 +13419,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -13424,10 +13433,10 @@
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B181" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -13454,7 +13463,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -13472,7 +13481,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -13489,7 +13498,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -13516,7 +13525,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L182">
         <v>5</v>
@@ -13525,7 +13534,7 @@
         <v>1</v>
       </c>
       <c r="N182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O182">
         <v>4</v>
@@ -13534,7 +13543,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13551,7 +13560,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13578,7 +13587,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L183">
         <v>5</v>
@@ -13596,7 +13605,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13613,7 +13622,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13640,7 +13649,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -13658,7 +13667,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13675,7 +13684,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13702,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L185">
         <v>3</v>
@@ -13720,7 +13729,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13737,7 +13746,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13764,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13773,7 +13782,7 @@
         <v>0</v>
       </c>
       <c r="N186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O186">
         <v>2</v>
@@ -13782,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13799,7 +13808,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13826,7 +13835,7 @@
         <v>4</v>
       </c>
       <c r="K187" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L187">
         <v>8</v>
@@ -13844,7 +13853,7 @@
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13861,7 +13870,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13888,7 +13897,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -13906,7 +13915,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13923,7 +13932,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13950,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13959,7 +13968,7 @@
         <v>6</v>
       </c>
       <c r="N189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O189">
         <v>7</v>
@@ -13968,7 +13977,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -13985,7 +13994,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -14012,7 +14021,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -14030,7 +14039,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14044,10 +14053,10 @@
     </row>
     <row r="191" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B191" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -14074,7 +14083,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -14092,7 +14101,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -14109,7 +14118,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -14136,7 +14145,7 @@
         <v>7</v>
       </c>
       <c r="K192" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L192">
         <v>12</v>
@@ -14154,7 +14163,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -14171,7 +14180,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -14198,7 +14207,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L193">
         <v>21</v>
@@ -14207,7 +14216,7 @@
         <v>17</v>
       </c>
       <c r="N193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O193">
         <v>21</v>
@@ -14216,7 +14225,7 @@
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -14233,7 +14242,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -14254,13 +14263,13 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J194">
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L194">
         <v>23</v>
@@ -14272,13 +14281,13 @@
         <v>3</v>
       </c>
       <c r="O194">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P194" t="s">
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -14295,7 +14304,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -14322,7 +14331,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -14340,7 +14349,7 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -14357,7 +14366,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -14384,7 +14393,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L196">
         <v>8</v>
@@ -14402,7 +14411,7 @@
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -14416,10 +14425,10 @@
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B197" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -14446,7 +14455,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -14464,7 +14473,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -14481,7 +14490,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -14508,7 +14517,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -14526,7 +14535,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -14543,7 +14552,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -14570,7 +14579,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -14588,7 +14597,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -14602,10 +14611,10 @@
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B200" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -14632,7 +14641,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14650,7 +14659,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14667,7 +14676,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14694,7 +14703,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14712,7 +14721,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14726,10 +14735,10 @@
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B202" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14756,7 +14765,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14774,7 +14783,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14791,7 +14800,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14818,7 +14827,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14827,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="N203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O203">
         <v>1</v>
@@ -14836,7 +14845,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14850,10 +14859,10 @@
     </row>
     <row r="204" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B204" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14880,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -14898,7 +14907,7 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14915,7 +14924,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14942,7 +14951,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14960,7 +14969,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14974,10 +14983,10 @@
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B206" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -15004,7 +15013,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -15022,7 +15031,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -15036,10 +15045,10 @@
     </row>
     <row r="207" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B207" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -15066,7 +15075,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -15084,7 +15093,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -15098,10 +15107,10 @@
     </row>
     <row r="208" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B208" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -15128,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L208">
         <v>0</v>
@@ -15146,7 +15155,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -15160,10 +15169,10 @@
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B209" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -15190,7 +15199,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -15208,7 +15217,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -15222,10 +15231,10 @@
     </row>
     <row r="210" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B210" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -15252,7 +15261,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -15270,7 +15279,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -15284,10 +15293,10 @@
     </row>
     <row r="211" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B211" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -15314,7 +15323,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -15332,7 +15341,7 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -15346,10 +15355,10 @@
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B212" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -15376,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -15394,7 +15403,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -15408,10 +15417,10 @@
     </row>
     <row r="213" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B213" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -15438,7 +15447,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L213">
         <v>0</v>
@@ -15456,7 +15465,7 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -15473,7 +15482,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -15500,7 +15509,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -15518,7 +15527,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15535,7 +15544,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -15562,7 +15571,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -15580,7 +15589,7 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -15594,10 +15603,10 @@
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B216" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -15624,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -15642,7 +15651,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15659,7 +15668,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -15686,7 +15695,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L217">
         <v>7</v>
@@ -15704,7 +15713,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15721,7 +15730,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -15748,7 +15757,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L218">
         <v>4</v>
@@ -15766,7 +15775,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15783,7 +15792,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15810,7 +15819,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L219">
         <v>3</v>
@@ -15828,7 +15837,7 @@
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15845,7 +15854,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15872,7 +15881,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L220">
         <v>3</v>
@@ -15890,7 +15899,7 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15904,10 +15913,10 @@
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B221" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15934,7 +15943,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15952,7 +15961,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15969,7 +15978,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -15996,7 +16005,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -16014,7 +16023,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -16031,7 +16040,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -16046,37 +16055,37 @@
         <v>240</v>
       </c>
       <c r="G223">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H223">
         <v>0</v>
       </c>
       <c r="I223">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J223">
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L223">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M223">
         <v>8</v>
       </c>
       <c r="N223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O223">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P223" t="s">
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -16093,7 +16102,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -16114,13 +16123,13 @@
         <v>0</v>
       </c>
       <c r="I224">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J224">
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -16129,16 +16138,16 @@
         <v>5</v>
       </c>
       <c r="N224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O224">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P224" t="s">
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -16155,7 +16164,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -16182,7 +16191,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L225">
         <v>7</v>
@@ -16200,7 +16209,7 @@
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -16217,7 +16226,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -16244,7 +16253,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -16262,7 +16271,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -16279,7 +16288,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -16294,37 +16303,37 @@
         <v>235</v>
       </c>
       <c r="G227">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J227">
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L227">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M227">
         <v>9</v>
       </c>
       <c r="N227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O227">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P227" t="s">
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -16341,7 +16350,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -16356,37 +16365,37 @@
         <v>240</v>
       </c>
       <c r="G228">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J228">
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L228">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M228">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N228">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O228">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P228" t="s">
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -16403,7 +16412,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -16430,7 +16439,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L229">
         <v>14</v>
@@ -16448,7 +16457,7 @@
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -16465,7 +16474,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -16492,7 +16501,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -16510,7 +16519,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -16527,7 +16536,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -16554,7 +16563,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -16572,7 +16581,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -16613,7 +16622,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -16654,7 +16663,7 @@
         <v>122</v>
       </c>
       <c r="G233">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -16666,19 +16675,19 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L233">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M233">
         <v>0</v>
       </c>
       <c r="N233">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O233">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P233" t="s">
         <v>13</v>
@@ -16692,10 +16701,10 @@
     </row>
     <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B234" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -16719,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -16745,10 +16754,10 @@
     </row>
     <row r="235" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B235" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C235" t="s">
         <v>120</v>
@@ -16772,7 +16781,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -16798,10 +16807,10 @@
     </row>
     <row r="236" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B236" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C236" t="s">
         <v>120</v>
@@ -16825,7 +16834,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -16878,7 +16887,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -16904,10 +16913,10 @@
     </row>
     <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B238" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -16931,7 +16940,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -16957,10 +16966,10 @@
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B239" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -16984,7 +16993,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -17010,10 +17019,10 @@
     </row>
     <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B240" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C240" t="s">
         <v>120</v>
@@ -17037,7 +17046,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -17090,7 +17099,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -17116,10 +17125,10 @@
     </row>
     <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B242" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C242" t="s">
         <v>120</v>
@@ -17143,7 +17152,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -17169,10 +17178,10 @@
     </row>
     <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B243" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C243" t="s">
         <v>120</v>
@@ -17196,7 +17205,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -17222,10 +17231,10 @@
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B244" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -17249,7 +17258,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -17302,7 +17311,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L245">
         <v>2</v>
@@ -17355,7 +17364,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -17408,7 +17417,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L247">
         <v>2</v>
@@ -17434,16 +17443,16 @@
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B248" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
       </c>
       <c r="D248" t="s">
-        <v>595</v>
+        <v>188</v>
       </c>
       <c r="E248" t="s">
         <v>122</v>
@@ -17461,7 +17470,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -17487,22 +17496,22 @@
     </row>
     <row r="249" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>596</v>
+        <v>187</v>
       </c>
       <c r="B249" t="s">
-        <v>596</v>
+        <v>187</v>
       </c>
       <c r="C249" t="s">
         <v>120</v>
       </c>
       <c r="D249" t="s">
-        <v>595</v>
+        <v>188</v>
       </c>
       <c r="E249" t="s">
         <v>122</v>
       </c>
       <c r="G249">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -17514,19 +17523,19 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M249">
         <v>0</v>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P249" t="s">
         <v>13</v>
@@ -17540,16 +17549,16 @@
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B250" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
       </c>
       <c r="D250" t="s">
-        <v>595</v>
+        <v>188</v>
       </c>
       <c r="E250" t="s">
         <v>122</v>
@@ -17567,7 +17576,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -17593,16 +17602,16 @@
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B251" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
       </c>
       <c r="D251" t="s">
-        <v>595</v>
+        <v>188</v>
       </c>
       <c r="E251" t="s">
         <v>122</v>
@@ -17620,7 +17629,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -17673,7 +17682,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L252">
         <v>1</v>
@@ -17726,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L253">
         <v>1</v>
@@ -17779,7 +17788,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -17832,7 +17841,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -17873,7 +17882,7 @@
         <v>122</v>
       </c>
       <c r="G256">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -17885,19 +17894,19 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L256">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M256">
         <v>0</v>
       </c>
       <c r="N256">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O256">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P256" t="s">
         <v>13</v>
@@ -17911,10 +17920,10 @@
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B257" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C257" t="s">
         <v>120</v>
@@ -17938,7 +17947,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -17979,7 +17988,7 @@
         <v>122</v>
       </c>
       <c r="G258">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -17991,19 +18000,19 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L258">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M258">
         <v>0</v>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O258">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P258" t="s">
         <v>13</v>
@@ -18017,10 +18026,10 @@
     </row>
     <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B259" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C259" t="s">
         <v>120</v>
@@ -18044,7 +18053,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -18073,7 +18082,7 @@
         <v>176</v>
       </c>
       <c r="B260" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C260" t="s">
         <v>177</v>
@@ -18097,7 +18106,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L260">
         <v>1</v>
@@ -18123,10 +18132,10 @@
     </row>
     <row r="261" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B261" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C261" t="s">
         <v>177</v>
@@ -18138,7 +18147,7 @@
         <v>122</v>
       </c>
       <c r="F261" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="G261">
         <v>2000</v>
@@ -18150,7 +18159,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -18176,10 +18185,10 @@
     </row>
     <row r="262" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B262" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C262" t="s">
         <v>177</v>
@@ -18191,7 +18200,7 @@
         <v>122</v>
       </c>
       <c r="F262" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="G262">
         <v>6000</v>
@@ -18203,7 +18212,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -18229,10 +18238,10 @@
     </row>
     <row r="263" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B263" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C263" t="s">
         <v>177</v>
@@ -18244,7 +18253,7 @@
         <v>122</v>
       </c>
       <c r="F263" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="G263">
         <v>2000</v>
@@ -18256,7 +18265,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L263">
         <v>0</v>
@@ -18287,8 +18296,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C984E3A1-420B-4BBB-9E95-AB664509058E}">
-  <dimension ref="A1:J475"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D548693A-EFE8-4380-A921-35F6E575787D}">
+  <dimension ref="A1:J489"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -33489,6 +33498,454 @@
       </c>
       <c r="J475" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A476" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B476" t="s">
+        <v>86</v>
+      </c>
+      <c r="C476" t="s">
+        <v>24</v>
+      </c>
+      <c r="D476" t="s">
+        <v>49</v>
+      </c>
+      <c r="E476" t="s">
+        <v>183</v>
+      </c>
+      <c r="F476" t="s">
+        <v>94</v>
+      </c>
+      <c r="G476">
+        <v>240</v>
+      </c>
+      <c r="H476" t="s">
+        <v>22</v>
+      </c>
+      <c r="I476">
+        <v>1</v>
+      </c>
+      <c r="J476" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A477" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B477" t="s">
+        <v>107</v>
+      </c>
+      <c r="C477" t="s">
+        <v>24</v>
+      </c>
+      <c r="D477" t="s">
+        <v>38</v>
+      </c>
+      <c r="E477" t="s">
+        <v>183</v>
+      </c>
+      <c r="F477" t="s">
+        <v>94</v>
+      </c>
+      <c r="G477">
+        <v>270</v>
+      </c>
+      <c r="H477" t="s">
+        <v>15</v>
+      </c>
+      <c r="I477">
+        <v>1</v>
+      </c>
+      <c r="J477" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A478" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B478" t="s">
+        <v>26</v>
+      </c>
+      <c r="C478" t="s">
+        <v>24</v>
+      </c>
+      <c r="D478" t="s">
+        <v>25</v>
+      </c>
+      <c r="E478" t="s">
+        <v>183</v>
+      </c>
+      <c r="F478" t="s">
+        <v>94</v>
+      </c>
+      <c r="G478">
+        <v>240</v>
+      </c>
+      <c r="H478" t="s">
+        <v>22</v>
+      </c>
+      <c r="I478">
+        <v>1</v>
+      </c>
+      <c r="J478" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A479" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B479" t="s">
+        <v>139</v>
+      </c>
+      <c r="C479" t="s">
+        <v>120</v>
+      </c>
+      <c r="D479" t="s">
+        <v>140</v>
+      </c>
+      <c r="E479" t="s">
+        <v>184</v>
+      </c>
+      <c r="F479" t="s">
+        <v>94</v>
+      </c>
+      <c r="G479">
+        <v>0</v>
+      </c>
+      <c r="H479" t="s">
+        <v>122</v>
+      </c>
+      <c r="I479">
+        <v>1</v>
+      </c>
+      <c r="J479" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A480" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B480" t="s">
+        <v>161</v>
+      </c>
+      <c r="C480" t="s">
+        <v>18</v>
+      </c>
+      <c r="D480" t="s">
+        <v>90</v>
+      </c>
+      <c r="E480" t="s">
+        <v>130</v>
+      </c>
+      <c r="F480" t="s">
+        <v>131</v>
+      </c>
+      <c r="G480">
+        <v>240</v>
+      </c>
+      <c r="H480" t="s">
+        <v>22</v>
+      </c>
+      <c r="I480">
+        <v>1</v>
+      </c>
+      <c r="J480" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A481" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B481" t="s">
+        <v>185</v>
+      </c>
+      <c r="C481" t="s">
+        <v>24</v>
+      </c>
+      <c r="D481" t="s">
+        <v>93</v>
+      </c>
+      <c r="E481" t="s">
+        <v>186</v>
+      </c>
+      <c r="F481" t="s">
+        <v>94</v>
+      </c>
+      <c r="G481">
+        <v>260</v>
+      </c>
+      <c r="H481" t="s">
+        <v>15</v>
+      </c>
+      <c r="I481">
+        <v>1</v>
+      </c>
+      <c r="J481" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A482" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B482" t="s">
+        <v>74</v>
+      </c>
+      <c r="C482" t="s">
+        <v>18</v>
+      </c>
+      <c r="D482" t="s">
+        <v>21</v>
+      </c>
+      <c r="E482" t="s">
+        <v>186</v>
+      </c>
+      <c r="F482" t="s">
+        <v>94</v>
+      </c>
+      <c r="G482">
+        <v>245</v>
+      </c>
+      <c r="H482" t="s">
+        <v>22</v>
+      </c>
+      <c r="I482">
+        <v>1</v>
+      </c>
+      <c r="J482" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A483" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B483" t="s">
+        <v>76</v>
+      </c>
+      <c r="C483" t="s">
+        <v>24</v>
+      </c>
+      <c r="D483" t="s">
+        <v>49</v>
+      </c>
+      <c r="E483" t="s">
+        <v>186</v>
+      </c>
+      <c r="F483" t="s">
+        <v>66</v>
+      </c>
+      <c r="G483">
+        <v>240</v>
+      </c>
+      <c r="H483" t="s">
+        <v>22</v>
+      </c>
+      <c r="I483">
+        <v>1</v>
+      </c>
+      <c r="J483" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A484" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B484" t="s">
+        <v>165</v>
+      </c>
+      <c r="C484" t="s">
+        <v>18</v>
+      </c>
+      <c r="D484" t="s">
+        <v>90</v>
+      </c>
+      <c r="E484" t="s">
+        <v>186</v>
+      </c>
+      <c r="F484" t="s">
+        <v>66</v>
+      </c>
+      <c r="G484">
+        <v>245</v>
+      </c>
+      <c r="H484" t="s">
+        <v>22</v>
+      </c>
+      <c r="I484">
+        <v>1</v>
+      </c>
+      <c r="J484" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A485" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B485" t="s">
+        <v>70</v>
+      </c>
+      <c r="C485" t="s">
+        <v>24</v>
+      </c>
+      <c r="D485" t="s">
+        <v>49</v>
+      </c>
+      <c r="E485" t="s">
+        <v>186</v>
+      </c>
+      <c r="F485" t="s">
+        <v>94</v>
+      </c>
+      <c r="G485">
+        <v>235</v>
+      </c>
+      <c r="H485" t="s">
+        <v>22</v>
+      </c>
+      <c r="I485">
+        <v>1</v>
+      </c>
+      <c r="J485" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A486" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B486" t="s">
+        <v>173</v>
+      </c>
+      <c r="C486" t="s">
+        <v>120</v>
+      </c>
+      <c r="D486" t="s">
+        <v>126</v>
+      </c>
+      <c r="E486" t="s">
+        <v>133</v>
+      </c>
+      <c r="F486" t="s">
+        <v>94</v>
+      </c>
+      <c r="G486">
+        <v>0</v>
+      </c>
+      <c r="H486" t="s">
+        <v>122</v>
+      </c>
+      <c r="I486">
+        <v>1</v>
+      </c>
+      <c r="J486" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A487" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B487" t="s">
+        <v>137</v>
+      </c>
+      <c r="C487" t="s">
+        <v>120</v>
+      </c>
+      <c r="D487" t="s">
+        <v>138</v>
+      </c>
+      <c r="E487" t="s">
+        <v>133</v>
+      </c>
+      <c r="F487" t="s">
+        <v>94</v>
+      </c>
+      <c r="G487">
+        <v>0</v>
+      </c>
+      <c r="H487" t="s">
+        <v>122</v>
+      </c>
+      <c r="I487">
+        <v>1</v>
+      </c>
+      <c r="J487" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A488" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B488" t="s">
+        <v>187</v>
+      </c>
+      <c r="C488" t="s">
+        <v>120</v>
+      </c>
+      <c r="D488" t="s">
+        <v>188</v>
+      </c>
+      <c r="E488" t="s">
+        <v>133</v>
+      </c>
+      <c r="F488" t="s">
+        <v>94</v>
+      </c>
+      <c r="G488">
+        <v>0</v>
+      </c>
+      <c r="H488" t="s">
+        <v>122</v>
+      </c>
+      <c r="I488">
+        <v>1</v>
+      </c>
+      <c r="J488" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A489" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B489" t="s">
+        <v>173</v>
+      </c>
+      <c r="C489" t="s">
+        <v>120</v>
+      </c>
+      <c r="D489" t="s">
+        <v>126</v>
+      </c>
+      <c r="E489" t="s">
+        <v>133</v>
+      </c>
+      <c r="F489" t="s">
+        <v>94</v>
+      </c>
+      <c r="G489">
+        <v>0</v>
+      </c>
+      <c r="H489" t="s">
+        <v>122</v>
+      </c>
+      <c r="I489">
+        <v>1</v>
+      </c>
+      <c r="J489" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A132621E-8BD9-4C94-BCB0-47D873C1A12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F0EEBE6-0C4B-499F-9C45-723766AF247B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{FCEDDCCE-9DAC-459D-AADD-A604475A287D}"/>
+    <workbookView xWindow="12795" yWindow="1245" windowWidth="23250" windowHeight="10890" xr2:uid="{48791067-37B7-4C0E-89C2-5133B3E545EF}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5451" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5663" uniqueCount="616">
   <si>
     <t>날짜</t>
   </si>
@@ -609,6 +609,45 @@
     <t>S-10RA</t>
   </si>
   <si>
+    <t>BTG-11130</t>
+  </si>
+  <si>
+    <t>쿠팡로켓</t>
+  </si>
+  <si>
+    <t>3m</t>
+  </si>
+  <si>
+    <t>BTG-12200</t>
+  </si>
+  <si>
+    <t>원형</t>
+  </si>
+  <si>
+    <t>1m</t>
+  </si>
+  <si>
+    <t>쿠팡그로스</t>
+  </si>
+  <si>
+    <t>DPW770-AP255</t>
+  </si>
+  <si>
+    <t>DPW771-AP245</t>
+  </si>
+  <si>
+    <t>X-20FS-GYGC</t>
+  </si>
+  <si>
+    <t>DPW771-BK240</t>
+  </si>
+  <si>
+    <t>DPW771-BK255</t>
+  </si>
+  <si>
+    <t>DPW771-LBL240</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1620,9 +1659,6 @@
     <t>DPW770AP 바오지 여성 러닝화 살구색 250</t>
   </si>
   <si>
-    <t>DPW770-AP255</t>
-  </si>
-  <si>
     <t>DPW770AP 바오지 여성 러닝화 살구색 255</t>
   </si>
   <si>
@@ -1680,9 +1716,6 @@
     <t>DPW771AP 바오지 여성 러닝화 살구색 240</t>
   </si>
   <si>
-    <t>DPW771-AP245</t>
-  </si>
-  <si>
     <t>DPW771AP 바오지 여성 러닝화 살구색 245</t>
   </si>
   <si>
@@ -1704,9 +1737,6 @@
     <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/fc7ca9ac124b00497e04f2f57b93b418.jpg</t>
   </si>
   <si>
-    <t>DPW771-BK240</t>
-  </si>
-  <si>
     <t>DPW771BK 바오지 여성 러닝화 블랙 240</t>
   </si>
   <si>
@@ -1722,9 +1752,6 @@
     <t>DPW771BK 바오지 여성 러닝화 블랙 250</t>
   </si>
   <si>
-    <t>DPW771-BK255</t>
-  </si>
-  <si>
     <t>DPW771BK 바오지 여성 러닝화 블랙 255</t>
   </si>
   <si>
@@ -1737,9 +1764,6 @@
     <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/9e874b053bcd998829e1022dcc741b05.jpg</t>
   </si>
   <si>
-    <t>DPW771-LBL240</t>
-  </si>
-  <si>
     <t>DPW771LBL 바오지 여성 러닝화 연블루 240</t>
   </si>
   <si>
@@ -1818,9 +1842,6 @@
     <t>X-10H-MAGG</t>
   </si>
   <si>
-    <t>X-20FS-GYGC</t>
-  </si>
-  <si>
     <t>X-20FS-MAGC</t>
   </si>
   <si>
@@ -1854,34 +1875,19 @@
     <t>R-10FB-BRMB</t>
   </si>
   <si>
+    <t>볼트겔 클리어겔 롤형 테이프 1m</t>
+  </si>
+  <si>
+    <t>BTG-11120</t>
+  </si>
+  <si>
     <t>볼트겔 클리어겔 롤형 테이프 1.5m</t>
   </si>
   <si>
-    <t>BTG-11120</t>
-  </si>
-  <si>
-    <t>볼트겔 클리어겔 롤형 테이프 1m</t>
-  </si>
-  <si>
-    <t>1m</t>
-  </si>
-  <si>
-    <t>BTG-11130</t>
-  </si>
-  <si>
     <t>볼트겔 클리어겔 롤형 테이프 3m</t>
   </si>
   <si>
-    <t>3m</t>
-  </si>
-  <si>
-    <t>BTG-12200</t>
-  </si>
-  <si>
     <t>볼트겔 클리어겔 원형 스티커</t>
-  </si>
-  <si>
-    <t>원형</t>
   </si>
 </sst>
 </file>
@@ -2267,7 +2273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4ABF82D-2456-431D-B0E7-A573DE6ACAE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F351ABB1-9D6A-4987-A767-4E90DFCF8E18}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2276,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2291,46 +2297,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="I1" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="J1" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="K1" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="L1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="M1" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="N1" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="O1" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="R1" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="S1" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="T1" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2338,7 +2344,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2365,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2383,7 +2389,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2400,7 +2406,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2427,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -2445,7 +2451,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2462,7 +2468,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2489,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2507,7 +2513,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2524,7 +2530,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2551,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2569,7 +2575,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2586,7 +2592,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2613,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2631,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2648,7 +2654,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2675,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2693,7 +2699,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2710,7 +2716,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2737,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2755,7 +2761,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2772,7 +2778,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2799,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2817,7 +2823,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2834,7 +2840,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2861,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2879,7 +2885,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2896,7 +2902,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2923,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2941,7 +2947,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2955,16 +2961,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B12" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D12" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2985,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3017,16 +3023,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B13" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D13" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3047,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3079,16 +3085,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3109,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3141,16 +3147,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D15" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3171,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3203,16 +3209,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B16" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="C16" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D16" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3233,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3265,16 +3271,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B17" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D17" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3295,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3327,16 +3333,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" t="s">
         <v>231</v>
       </c>
-      <c r="C18" t="s">
-        <v>218</v>
-      </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3357,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3389,16 +3395,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19" t="s">
         <v>232</v>
-      </c>
-      <c r="B19" t="s">
-        <v>233</v>
-      </c>
-      <c r="C19" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" t="s">
-        <v>219</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3419,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3451,16 +3457,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B20" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D20" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3481,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3513,16 +3519,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D21" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3543,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3575,16 +3581,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D22" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3605,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3637,16 +3643,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="C23" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D23" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3667,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3699,16 +3705,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D24" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3729,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3761,16 +3767,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C25" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D25" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3791,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3823,16 +3829,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C26" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D26" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3853,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3885,16 +3891,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D27" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3915,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3947,16 +3953,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C28" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D28" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3977,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4009,16 +4015,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D29" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4039,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4071,16 +4077,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D30" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4101,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4133,16 +4139,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C31" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D31" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4163,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4195,16 +4201,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C32" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D32" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4225,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4257,16 +4263,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D33" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4287,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4319,16 +4325,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D34" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4349,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4381,16 +4387,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="C35" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D35" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4411,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4443,16 +4449,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="C36" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D36" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4473,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4505,16 +4511,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C37" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D37" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4535,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4567,16 +4573,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D38" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4597,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4629,16 +4635,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>286</v>
+      </c>
+      <c r="B39" t="s">
+        <v>287</v>
+      </c>
+      <c r="C39" t="s">
+        <v>231</v>
+      </c>
+      <c r="D39" t="s">
         <v>273</v>
-      </c>
-      <c r="B39" t="s">
-        <v>274</v>
-      </c>
-      <c r="C39" t="s">
-        <v>218</v>
-      </c>
-      <c r="D39" t="s">
-        <v>260</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4659,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4691,16 +4697,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C40" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D40" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4721,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4753,16 +4759,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B41" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D41" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4783,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4815,16 +4821,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C42" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D42" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4845,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4877,16 +4883,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C43" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D43" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4907,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4939,16 +4945,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B44" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C44" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4969,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5001,16 +5007,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B45" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="C45" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D45" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5031,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5063,16 +5069,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="B46" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="C46" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D46" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5093,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5125,16 +5131,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B47" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="C47" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D47" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5155,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5187,16 +5193,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B48" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C48" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D48" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5217,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5249,16 +5255,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B49" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C49" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D49" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5279,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5311,16 +5317,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B50" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="C50" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D50" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5341,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5373,16 +5379,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="B51" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C51" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D51" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5403,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5435,16 +5441,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="B52" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C52" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D52" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5465,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5497,16 +5503,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="B53" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="C53" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D53" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5527,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5559,16 +5565,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B54" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C54" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D54" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5589,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5621,16 +5627,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="B55" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C55" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D55" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5651,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5683,16 +5689,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B56" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="C56" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D56" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5713,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5745,16 +5751,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="B57" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C57" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D57" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5775,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5807,16 +5813,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="B58" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="C58" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D58" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5837,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5869,16 +5875,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>327</v>
+      </c>
+      <c r="B59" t="s">
+        <v>328</v>
+      </c>
+      <c r="C59" t="s">
+        <v>231</v>
+      </c>
+      <c r="D59" t="s">
         <v>314</v>
-      </c>
-      <c r="B59" t="s">
-        <v>315</v>
-      </c>
-      <c r="C59" t="s">
-        <v>218</v>
-      </c>
-      <c r="D59" t="s">
-        <v>301</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5899,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5931,16 +5937,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="B60" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C60" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D60" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5961,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5993,16 +5999,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B61" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D61" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6023,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6055,16 +6061,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="B62" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="C62" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D62" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6085,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6117,16 +6123,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="B63" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D63" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6147,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6179,16 +6185,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B64" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="C64" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D64" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6209,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6241,16 +6247,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B65" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C65" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D65" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6271,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6303,16 +6309,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="B66" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="C66" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D66" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6333,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6368,7 +6374,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6395,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6413,7 +6419,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6430,7 +6436,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6457,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -6475,7 +6481,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6492,7 +6498,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6507,37 +6513,37 @@
         <v>270</v>
       </c>
       <c r="G69">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M69">
         <v>0</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O69">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P69" t="s">
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6554,7 +6560,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6581,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6599,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6616,7 +6622,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6643,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6661,7 +6667,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6675,10 +6681,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B72" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6705,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6723,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6740,7 +6746,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6767,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6785,7 +6791,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6799,10 +6805,10 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="B74" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6829,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -6847,7 +6853,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6864,7 +6870,7 @@
         <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6891,7 +6897,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6909,7 +6915,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6923,10 +6929,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B76" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6953,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6971,7 +6977,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6988,7 +6994,7 @@
         <v>185</v>
       </c>
       <c r="B77" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -7015,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -7033,7 +7039,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7047,10 +7053,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B78" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7077,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7095,7 +7101,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7109,10 +7115,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B79" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7139,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7157,7 +7163,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7174,7 +7180,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7201,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7219,7 +7225,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7233,10 +7239,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="B81" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7263,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -7281,7 +7287,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7295,10 +7301,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="B82" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7325,7 +7331,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7343,7 +7349,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7357,10 +7363,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="B83" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7387,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7405,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7419,10 +7425,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B84" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7449,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7467,7 +7473,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7481,10 +7487,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="B85" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7511,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7529,7 +7535,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7543,10 +7549,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="B86" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7573,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7591,7 +7597,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7605,10 +7611,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="B87" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7635,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7653,7 +7659,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7670,7 +7676,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7697,7 +7703,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -7715,7 +7721,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7729,10 +7735,10 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="B89" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7759,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -7777,7 +7783,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7794,7 +7800,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7821,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L90">
         <v>2</v>
@@ -7839,7 +7845,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7853,10 +7859,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B91" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7883,7 +7889,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7901,7 +7907,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7915,10 +7921,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="B92" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7945,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7963,7 +7969,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7980,7 +7986,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -8007,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8025,7 +8031,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8039,10 +8045,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B94" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8069,7 +8075,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8087,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8101,10 +8107,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="B95" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8131,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8149,7 +8155,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8163,10 +8169,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="B96" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8193,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8211,7 +8217,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8225,10 +8231,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B97" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8255,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8273,7 +8279,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8290,7 +8296,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8305,37 +8311,37 @@
         <v>265</v>
       </c>
       <c r="G98">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
       <c r="I98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L98">
+        <v>4</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98">
         <v>3</v>
       </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98">
-        <v>2</v>
-      </c>
       <c r="P98" t="s">
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8352,7 +8358,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8379,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L99">
         <v>1</v>
@@ -8397,7 +8403,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8414,7 +8420,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8441,7 +8447,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8459,7 +8465,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8473,10 +8479,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="B101" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8503,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8521,7 +8527,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8535,10 +8541,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="B102" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8565,7 +8571,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8583,7 +8589,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8597,10 +8603,10 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="B103" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8627,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -8645,7 +8651,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8662,7 +8668,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8689,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8707,7 +8713,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8721,10 +8727,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B105" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8751,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8769,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8786,7 +8792,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8813,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8831,7 +8837,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8845,10 +8851,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="B107" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8875,7 +8881,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8893,7 +8899,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8910,7 +8916,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8937,7 +8943,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8955,7 +8961,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8972,7 +8978,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -8999,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -9017,7 +9023,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -9031,10 +9037,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="B110" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -9061,7 +9067,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -9079,7 +9085,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -9093,10 +9099,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="B111" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -9123,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9141,7 +9147,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9158,7 +9164,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9185,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9194,7 +9200,7 @@
         <v>0</v>
       </c>
       <c r="N112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O112">
         <v>3</v>
@@ -9203,7 +9209,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9220,7 +9226,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9235,37 +9241,37 @@
         <v>265</v>
       </c>
       <c r="G113">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L113">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M113">
         <v>3</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P113" t="s">
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9282,7 +9288,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9309,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L114">
         <v>8</v>
@@ -9318,7 +9324,7 @@
         <v>0</v>
       </c>
       <c r="N114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O114">
         <v>8</v>
@@ -9327,7 +9333,7 @@
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9344,7 +9350,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9371,7 +9377,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9389,7 +9395,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9406,7 +9412,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9433,7 +9439,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L116">
         <v>3</v>
@@ -9451,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9468,7 +9474,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9495,7 +9501,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9513,7 +9519,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9530,7 +9536,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9557,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9575,7 +9581,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9589,10 +9595,10 @@
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="B119" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9619,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -9637,7 +9643,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9654,7 +9660,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9681,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9699,7 +9705,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9716,7 +9722,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9743,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -9761,7 +9767,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9778,7 +9784,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9805,7 +9811,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="L122">
         <v>5</v>
@@ -9823,7 +9829,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9840,7 +9846,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9867,7 +9873,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -9885,7 +9891,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9902,7 +9908,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9929,7 +9935,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -9947,7 +9953,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9964,7 +9970,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9991,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -10009,7 +10015,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -10026,7 +10032,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -10053,7 +10059,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -10071,7 +10077,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -10088,7 +10094,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -10115,7 +10121,7 @@
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="L127">
         <v>7</v>
@@ -10133,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -10150,7 +10156,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -10177,7 +10183,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -10195,7 +10201,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -10212,7 +10218,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10239,7 +10245,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L129">
         <v>8</v>
@@ -10257,7 +10263,7 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10274,7 +10280,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10301,7 +10307,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10319,7 +10325,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10336,7 +10342,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10363,7 +10369,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10381,7 +10387,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10398,7 +10404,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10425,7 +10431,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L132">
         <v>18</v>
@@ -10443,7 +10449,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10460,7 +10466,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10487,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L133">
         <v>10</v>
@@ -10505,7 +10511,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10522,7 +10528,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10549,7 +10555,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L134">
         <v>16</v>
@@ -10558,7 +10564,7 @@
         <v>6</v>
       </c>
       <c r="N134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O134">
         <v>14</v>
@@ -10567,7 +10573,7 @@
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10584,7 +10590,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10611,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10629,7 +10635,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10646,7 +10652,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10673,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10691,7 +10697,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10708,7 +10714,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10735,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L137">
         <v>3</v>
@@ -10753,7 +10759,7 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10770,7 +10776,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10797,7 +10803,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L138">
         <v>4</v>
@@ -10815,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10832,7 +10838,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10859,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L139">
         <v>2</v>
@@ -10877,7 +10883,7 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10894,7 +10900,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10921,7 +10927,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L140">
         <v>2</v>
@@ -10939,7 +10945,7 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10956,7 +10962,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10983,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L141">
         <v>3</v>
@@ -11001,7 +11007,7 @@
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -11018,7 +11024,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -11045,7 +11051,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -11063,7 +11069,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -11080,7 +11086,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -11107,7 +11113,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -11125,7 +11131,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -11142,7 +11148,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -11169,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -11187,7 +11193,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -11201,10 +11207,10 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="B145" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -11231,7 +11237,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -11249,7 +11255,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -11263,10 +11269,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="B146" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -11293,7 +11299,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -11311,7 +11317,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -11328,7 +11334,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11355,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L147">
         <v>1</v>
@@ -11373,7 +11379,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11390,7 +11396,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11417,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L148">
         <v>6</v>
@@ -11435,7 +11441,7 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11452,7 +11458,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11479,7 +11485,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11497,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11514,7 +11520,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11541,7 +11547,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11559,7 +11565,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11576,7 +11582,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11603,7 +11609,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -11621,7 +11627,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11635,16 +11641,16 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="B152" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="C152" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D152" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11665,7 +11671,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11697,16 +11703,16 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="B153" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C153" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D153" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11727,7 +11733,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11759,16 +11765,16 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="B154" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="C154" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D154" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11789,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11821,16 +11827,16 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="B155" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="C155" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D155" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11851,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11883,16 +11889,16 @@
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B156" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="C156" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D156" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11913,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11945,16 +11951,16 @@
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="B157" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="C157" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D157" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11975,7 +11981,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -12007,16 +12013,16 @@
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="B158" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="C158" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D158" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -12037,7 +12043,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -12069,16 +12075,16 @@
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>489</v>
+      </c>
+      <c r="B159" t="s">
+        <v>490</v>
+      </c>
+      <c r="C159" t="s">
+        <v>231</v>
+      </c>
+      <c r="D159" t="s">
         <v>476</v>
-      </c>
-      <c r="B159" t="s">
-        <v>477</v>
-      </c>
-      <c r="C159" t="s">
-        <v>218</v>
-      </c>
-      <c r="D159" t="s">
-        <v>463</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -12099,7 +12105,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -12131,16 +12137,16 @@
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="B160" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="C160" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D160" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -12161,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -12193,16 +12199,16 @@
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="B161" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="C161" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D161" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -12223,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -12255,16 +12261,16 @@
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="B162" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="C162" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D162" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -12285,7 +12291,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -12317,16 +12323,16 @@
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="B163" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="C163" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D163" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -12347,7 +12353,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -12379,16 +12385,16 @@
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="B164" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="C164" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D164" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -12409,7 +12415,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -12441,16 +12447,16 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="B165" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="C165" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D165" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12471,7 +12477,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12503,16 +12509,16 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="B166" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="C166" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D166" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12533,7 +12539,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12565,16 +12571,16 @@
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="B167" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="C167" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D167" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12595,7 +12601,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12627,16 +12633,16 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="B168" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="C168" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D168" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12657,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12689,16 +12695,16 @@
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="B169" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="C169" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D169" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12719,7 +12725,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12751,16 +12757,16 @@
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="B170" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="C170" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D170" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12781,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12813,16 +12819,16 @@
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="B171" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="C171" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D171" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12843,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12878,7 +12884,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12905,7 +12911,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -12923,7 +12929,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12940,7 +12946,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12967,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L173">
         <v>7</v>
@@ -12976,7 +12982,7 @@
         <v>0</v>
       </c>
       <c r="N173">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O173">
         <v>6</v>
@@ -12985,7 +12991,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -13002,7 +13008,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -13029,7 +13035,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L174">
         <v>5</v>
@@ -13047,7 +13053,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -13064,7 +13070,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -13091,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -13109,7 +13115,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -13126,7 +13132,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -13153,7 +13159,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -13171,7 +13177,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -13188,7 +13194,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -13215,7 +13221,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -13233,7 +13239,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -13250,7 +13256,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -13277,7 +13283,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -13295,7 +13301,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -13312,7 +13318,7 @@
         <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -13339,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L179">
         <v>1</v>
@@ -13357,7 +13363,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -13374,7 +13380,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -13401,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L180">
         <v>2</v>
@@ -13419,7 +13425,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -13433,10 +13439,10 @@
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="B181" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -13463,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -13481,7 +13487,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -13498,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -13525,7 +13531,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L182">
         <v>5</v>
@@ -13534,7 +13540,7 @@
         <v>1</v>
       </c>
       <c r="N182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O182">
         <v>4</v>
@@ -13543,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13560,7 +13566,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13587,7 +13593,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L183">
         <v>5</v>
@@ -13605,7 +13611,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13622,7 +13628,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13649,7 +13655,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -13667,7 +13673,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13684,7 +13690,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13711,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L185">
         <v>3</v>
@@ -13729,7 +13735,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13746,7 +13752,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13773,7 +13779,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13782,7 +13788,7 @@
         <v>0</v>
       </c>
       <c r="N186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O186">
         <v>2</v>
@@ -13791,7 +13797,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13808,7 +13814,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13835,7 +13841,7 @@
         <v>4</v>
       </c>
       <c r="K187" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="L187">
         <v>8</v>
@@ -13853,7 +13859,7 @@
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13870,7 +13876,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13897,7 +13903,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -13915,7 +13921,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13932,7 +13938,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13959,7 +13965,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13977,7 +13983,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -13994,7 +14000,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -14021,7 +14027,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -14039,7 +14045,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14053,10 +14059,10 @@
     </row>
     <row r="191" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>526</v>
+        <v>196</v>
       </c>
       <c r="B191" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -14071,37 +14077,37 @@
         <v>255</v>
       </c>
       <c r="G191">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H191">
         <v>0</v>
       </c>
       <c r="I191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J191">
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M191">
         <v>0</v>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P191" t="s">
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -14118,7 +14124,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -14145,7 +14151,7 @@
         <v>7</v>
       </c>
       <c r="K192" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="L192">
         <v>12</v>
@@ -14163,7 +14169,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -14180,7 +14186,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -14195,37 +14201,37 @@
         <v>240</v>
       </c>
       <c r="G193">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J193">
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L193">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M193">
         <v>17</v>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O193">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P193" t="s">
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -14242,7 +14248,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -14269,7 +14275,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L194">
         <v>23</v>
@@ -14287,7 +14293,7 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -14304,7 +14310,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -14331,7 +14337,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -14349,7 +14355,7 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -14366,7 +14372,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -14381,37 +14387,37 @@
         <v>255</v>
       </c>
       <c r="G196">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H196">
         <v>0</v>
       </c>
       <c r="I196">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J196">
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L196">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M196">
         <v>7</v>
       </c>
       <c r="N196">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O196">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P196" t="s">
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -14425,10 +14431,10 @@
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B197" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -14455,7 +14461,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -14473,7 +14479,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -14490,7 +14496,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -14517,7 +14523,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -14535,7 +14541,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -14552,7 +14558,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -14579,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -14597,7 +14603,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -14611,10 +14617,10 @@
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="B200" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -14641,7 +14647,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14659,7 +14665,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14676,7 +14682,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14703,7 +14709,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14721,7 +14727,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14735,10 +14741,10 @@
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B202" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14765,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14783,7 +14789,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14800,7 +14806,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14827,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14845,7 +14851,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14859,10 +14865,10 @@
     </row>
     <row r="204" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>546</v>
+        <v>197</v>
       </c>
       <c r="B204" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14877,37 +14883,37 @@
         <v>245</v>
       </c>
       <c r="G204">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H204">
         <v>0</v>
       </c>
       <c r="I204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204">
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204">
         <v>0</v>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P204" t="s">
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14924,7 +14930,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14951,7 +14957,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14969,7 +14975,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14983,10 +14989,10 @@
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="B206" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -15013,7 +15019,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -15031,7 +15037,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -15045,10 +15051,10 @@
     </row>
     <row r="207" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="B207" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -15075,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -15093,7 +15099,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -15107,10 +15113,10 @@
     </row>
     <row r="208" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>554</v>
+        <v>199</v>
       </c>
       <c r="B208" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -15125,37 +15131,37 @@
         <v>240</v>
       </c>
       <c r="G208">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H208">
         <v>0</v>
       </c>
       <c r="I208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J208">
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P208" t="s">
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -15169,10 +15175,10 @@
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="B209" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -15199,7 +15205,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -15217,7 +15223,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -15231,10 +15237,10 @@
     </row>
     <row r="210" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="B210" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -15261,7 +15267,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -15279,7 +15285,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -15293,10 +15299,10 @@
     </row>
     <row r="211" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>560</v>
+        <v>200</v>
       </c>
       <c r="B211" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -15311,37 +15317,37 @@
         <v>255</v>
       </c>
       <c r="G211">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H211">
         <v>0</v>
       </c>
       <c r="I211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J211">
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P211" t="s">
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -15355,10 +15361,10 @@
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="B212" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -15385,7 +15391,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -15403,7 +15409,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -15417,10 +15423,10 @@
     </row>
     <row r="213" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>565</v>
+        <v>201</v>
       </c>
       <c r="B213" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -15435,37 +15441,37 @@
         <v>240</v>
       </c>
       <c r="G213">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H213">
         <v>0</v>
       </c>
       <c r="I213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J213">
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P213" t="s">
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -15482,7 +15488,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -15509,7 +15515,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -15527,7 +15533,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15544,7 +15550,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -15559,37 +15565,37 @@
         <v>250</v>
       </c>
       <c r="G215">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H215">
         <v>0</v>
       </c>
       <c r="I215">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J215">
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L215">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O215">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P215" t="s">
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -15603,10 +15609,10 @@
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B216" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -15633,7 +15639,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -15651,7 +15657,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15668,7 +15674,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -15695,7 +15701,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L217">
         <v>7</v>
@@ -15713,7 +15719,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15730,7 +15736,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -15757,7 +15763,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L218">
         <v>4</v>
@@ -15775,7 +15781,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15792,7 +15798,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15807,37 +15813,37 @@
         <v>245</v>
       </c>
       <c r="G219">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H219">
         <v>0</v>
       </c>
       <c r="I219">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J219">
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L219">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M219">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O219">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P219" t="s">
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15854,7 +15860,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15869,37 +15875,37 @@
         <v>250</v>
       </c>
       <c r="G220">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H220">
         <v>0</v>
       </c>
       <c r="I220">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J220">
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L220">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M220">
         <v>2</v>
       </c>
       <c r="N220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O220">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P220" t="s">
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15913,10 +15919,10 @@
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="B221" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15943,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15961,7 +15967,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15978,7 +15984,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -16005,7 +16011,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -16023,7 +16029,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -16040,7 +16046,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -16067,7 +16073,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L223">
         <v>13</v>
@@ -16085,7 +16091,7 @@
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -16102,7 +16108,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -16129,7 +16135,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -16147,7 +16153,7 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -16164,7 +16170,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -16179,37 +16185,37 @@
         <v>250</v>
       </c>
       <c r="G225">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H225">
         <v>0</v>
       </c>
       <c r="I225">
+        <v>8</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225" t="s">
+        <v>217</v>
+      </c>
+      <c r="L225">
+        <v>8</v>
+      </c>
+      <c r="M225">
         <v>7</v>
       </c>
-      <c r="J225">
-        <v>0</v>
-      </c>
-      <c r="K225" t="s">
-        <v>204</v>
-      </c>
-      <c r="L225">
-        <v>7</v>
-      </c>
-      <c r="M225">
-        <v>6</v>
-      </c>
       <c r="N225">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O225">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P225" t="s">
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -16226,7 +16232,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -16253,7 +16259,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -16271,7 +16277,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -16288,7 +16294,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -16303,37 +16309,37 @@
         <v>235</v>
       </c>
       <c r="G227">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J227">
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L227">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M227">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N227">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O227">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P227" t="s">
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -16350,7 +16356,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -16365,37 +16371,37 @@
         <v>240</v>
       </c>
       <c r="G228">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J228">
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L228">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M228">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N228">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O228">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P228" t="s">
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -16412,7 +16418,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -16439,7 +16445,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L229">
         <v>14</v>
@@ -16457,7 +16463,7 @@
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -16474,7 +16480,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -16501,7 +16507,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -16519,7 +16525,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -16536,7 +16542,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -16563,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -16581,7 +16587,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -16622,7 +16628,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -16663,7 +16669,7 @@
         <v>122</v>
       </c>
       <c r="G233">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -16675,19 +16681,19 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L233">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M233">
         <v>0</v>
       </c>
       <c r="N233">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O233">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P233" t="s">
         <v>13</v>
@@ -16701,10 +16707,10 @@
     </row>
     <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="B234" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -16728,7 +16734,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -16754,10 +16760,10 @@
     </row>
     <row r="235" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="B235" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C235" t="s">
         <v>120</v>
@@ -16781,7 +16787,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -16807,10 +16813,10 @@
     </row>
     <row r="236" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>592</v>
+        <v>198</v>
       </c>
       <c r="B236" t="s">
-        <v>592</v>
+        <v>198</v>
       </c>
       <c r="C236" t="s">
         <v>120</v>
@@ -16822,7 +16828,7 @@
         <v>122</v>
       </c>
       <c r="G236">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -16834,19 +16840,19 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M236">
         <v>0</v>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P236" t="s">
         <v>13</v>
@@ -16887,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -16913,10 +16919,10 @@
     </row>
     <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B238" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -16940,7 +16946,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -16966,10 +16972,10 @@
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="B239" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -16993,7 +16999,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -17019,10 +17025,10 @@
     </row>
     <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B240" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="C240" t="s">
         <v>120</v>
@@ -17046,7 +17052,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -17099,7 +17105,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -17125,10 +17131,10 @@
     </row>
     <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="B242" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="C242" t="s">
         <v>120</v>
@@ -17152,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -17178,10 +17184,10 @@
     </row>
     <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B243" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="C243" t="s">
         <v>120</v>
@@ -17205,7 +17211,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -17231,10 +17237,10 @@
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="B244" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -17258,7 +17264,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -17311,7 +17317,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L245">
         <v>2</v>
@@ -17364,7 +17370,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -17417,7 +17423,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L247">
         <v>2</v>
@@ -17443,10 +17449,10 @@
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B248" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
@@ -17470,7 +17476,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -17523,7 +17529,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L249">
         <v>1</v>
@@ -17549,10 +17555,10 @@
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="B250" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
@@ -17576,7 +17582,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -17602,10 +17608,10 @@
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B251" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
@@ -17629,7 +17635,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -17682,7 +17688,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L252">
         <v>1</v>
@@ -17723,7 +17729,7 @@
         <v>122</v>
       </c>
       <c r="G253">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -17735,19 +17741,19 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M253">
         <v>0</v>
       </c>
       <c r="N253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P253" t="s">
         <v>13</v>
@@ -17788,7 +17794,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -17841,7 +17847,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -17894,7 +17900,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L256">
         <v>5</v>
@@ -17920,10 +17926,10 @@
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="B257" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="C257" t="s">
         <v>120</v>
@@ -17947,7 +17953,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -18000,7 +18006,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L258">
         <v>3</v>
@@ -18026,10 +18032,10 @@
     </row>
     <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B259" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="C259" t="s">
         <v>120</v>
@@ -18053,7 +18059,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -18082,7 +18088,7 @@
         <v>176</v>
       </c>
       <c r="B260" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="C260" t="s">
         <v>177</v>
@@ -18094,10 +18100,10 @@
         <v>122</v>
       </c>
       <c r="F260" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="G260">
-        <v>1999</v>
+        <v>1987</v>
       </c>
       <c r="I260">
         <v>0</v>
@@ -18106,36 +18112,36 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L260">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M260">
         <v>0</v>
       </c>
       <c r="N260">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O260">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P260" t="s">
         <v>180</v>
       </c>
       <c r="S260">
-        <v>8400</v>
+        <v>6900</v>
       </c>
       <c r="T260">
-        <v>8400</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="261" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="B261" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="C261" t="s">
         <v>177</v>
@@ -18147,7 +18153,7 @@
         <v>122</v>
       </c>
       <c r="F261" t="s">
-        <v>607</v>
+        <v>179</v>
       </c>
       <c r="G261">
         <v>2000</v>
@@ -18159,7 +18165,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -18177,18 +18183,18 @@
         <v>180</v>
       </c>
       <c r="S261">
-        <v>6900</v>
+        <v>8400</v>
       </c>
       <c r="T261">
-        <v>6900</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="262" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>608</v>
+        <v>189</v>
       </c>
       <c r="B262" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="C262" t="s">
         <v>177</v>
@@ -18200,10 +18206,10 @@
         <v>122</v>
       </c>
       <c r="F262" t="s">
-        <v>610</v>
+        <v>191</v>
       </c>
       <c r="G262">
-        <v>6000</v>
+        <v>5988</v>
       </c>
       <c r="I262">
         <v>0</v>
@@ -18212,19 +18218,19 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L262">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M262">
         <v>0</v>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P262" t="s">
         <v>180</v>
@@ -18238,10 +18244,10 @@
     </row>
     <row r="263" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>611</v>
+        <v>192</v>
       </c>
       <c r="B263" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C263" t="s">
         <v>177</v>
@@ -18253,10 +18259,10 @@
         <v>122</v>
       </c>
       <c r="F263" t="s">
-        <v>613</v>
+        <v>193</v>
       </c>
       <c r="G263">
-        <v>2000</v>
+        <v>1988</v>
       </c>
       <c r="I263">
         <v>0</v>
@@ -18265,19 +18271,19 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="L263">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M263">
         <v>0</v>
       </c>
       <c r="N263">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P263" t="s">
         <v>180</v>
@@ -18296,8 +18302,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D548693A-EFE8-4380-A921-35F6E575787D}">
-  <dimension ref="A1:J489"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E666D6ED-265C-4952-8BAA-8BFB4A3A91F3}">
+  <dimension ref="A1:J518"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -33945,6 +33951,934 @@
         <v>1</v>
       </c>
       <c r="J489" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A490" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B490" t="s">
+        <v>189</v>
+      </c>
+      <c r="C490" t="s">
+        <v>177</v>
+      </c>
+      <c r="D490" t="s">
+        <v>178</v>
+      </c>
+      <c r="E490" t="s">
+        <v>190</v>
+      </c>
+      <c r="F490" t="s">
+        <v>94</v>
+      </c>
+      <c r="G490" t="s">
+        <v>191</v>
+      </c>
+      <c r="H490" t="s">
+        <v>122</v>
+      </c>
+      <c r="I490">
+        <v>2</v>
+      </c>
+      <c r="J490" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A491" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B491" t="s">
+        <v>189</v>
+      </c>
+      <c r="C491" t="s">
+        <v>177</v>
+      </c>
+      <c r="D491" t="s">
+        <v>178</v>
+      </c>
+      <c r="E491" t="s">
+        <v>190</v>
+      </c>
+      <c r="F491" t="s">
+        <v>94</v>
+      </c>
+      <c r="G491" t="s">
+        <v>191</v>
+      </c>
+      <c r="H491" t="s">
+        <v>122</v>
+      </c>
+      <c r="I491">
+        <v>4</v>
+      </c>
+      <c r="J491" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A492" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B492" t="s">
+        <v>189</v>
+      </c>
+      <c r="C492" t="s">
+        <v>177</v>
+      </c>
+      <c r="D492" t="s">
+        <v>178</v>
+      </c>
+      <c r="E492" t="s">
+        <v>190</v>
+      </c>
+      <c r="F492" t="s">
+        <v>94</v>
+      </c>
+      <c r="G492" t="s">
+        <v>191</v>
+      </c>
+      <c r="H492" t="s">
+        <v>122</v>
+      </c>
+      <c r="I492">
+        <v>6</v>
+      </c>
+      <c r="J492" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A493" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B493" t="s">
+        <v>192</v>
+      </c>
+      <c r="C493" t="s">
+        <v>177</v>
+      </c>
+      <c r="D493" t="s">
+        <v>178</v>
+      </c>
+      <c r="E493" t="s">
+        <v>190</v>
+      </c>
+      <c r="F493" t="s">
+        <v>94</v>
+      </c>
+      <c r="G493" t="s">
+        <v>193</v>
+      </c>
+      <c r="H493" t="s">
+        <v>122</v>
+      </c>
+      <c r="I493">
+        <v>2</v>
+      </c>
+      <c r="J493" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A494" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B494" t="s">
+        <v>192</v>
+      </c>
+      <c r="C494" t="s">
+        <v>177</v>
+      </c>
+      <c r="D494" t="s">
+        <v>178</v>
+      </c>
+      <c r="E494" t="s">
+        <v>190</v>
+      </c>
+      <c r="F494" t="s">
+        <v>94</v>
+      </c>
+      <c r="G494" t="s">
+        <v>193</v>
+      </c>
+      <c r="H494" t="s">
+        <v>122</v>
+      </c>
+      <c r="I494">
+        <v>4</v>
+      </c>
+      <c r="J494" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A495" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B495" t="s">
+        <v>192</v>
+      </c>
+      <c r="C495" t="s">
+        <v>177</v>
+      </c>
+      <c r="D495" t="s">
+        <v>178</v>
+      </c>
+      <c r="E495" t="s">
+        <v>190</v>
+      </c>
+      <c r="F495" t="s">
+        <v>94</v>
+      </c>
+      <c r="G495" t="s">
+        <v>193</v>
+      </c>
+      <c r="H495" t="s">
+        <v>122</v>
+      </c>
+      <c r="I495">
+        <v>6</v>
+      </c>
+      <c r="J495" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A496" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B496" t="s">
+        <v>176</v>
+      </c>
+      <c r="C496" t="s">
+        <v>177</v>
+      </c>
+      <c r="D496" t="s">
+        <v>178</v>
+      </c>
+      <c r="E496" t="s">
+        <v>190</v>
+      </c>
+      <c r="F496" t="s">
+        <v>94</v>
+      </c>
+      <c r="G496" t="s">
+        <v>194</v>
+      </c>
+      <c r="H496" t="s">
+        <v>122</v>
+      </c>
+      <c r="I496">
+        <v>2</v>
+      </c>
+      <c r="J496" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A497" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B497" t="s">
+        <v>176</v>
+      </c>
+      <c r="C497" t="s">
+        <v>177</v>
+      </c>
+      <c r="D497" t="s">
+        <v>178</v>
+      </c>
+      <c r="E497" t="s">
+        <v>190</v>
+      </c>
+      <c r="F497" t="s">
+        <v>94</v>
+      </c>
+      <c r="G497" t="s">
+        <v>194</v>
+      </c>
+      <c r="H497" t="s">
+        <v>122</v>
+      </c>
+      <c r="I497">
+        <v>4</v>
+      </c>
+      <c r="J497" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A498" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B498" t="s">
+        <v>176</v>
+      </c>
+      <c r="C498" t="s">
+        <v>177</v>
+      </c>
+      <c r="D498" t="s">
+        <v>178</v>
+      </c>
+      <c r="E498" t="s">
+        <v>190</v>
+      </c>
+      <c r="F498" t="s">
+        <v>94</v>
+      </c>
+      <c r="G498" t="s">
+        <v>194</v>
+      </c>
+      <c r="H498" t="s">
+        <v>122</v>
+      </c>
+      <c r="I498">
+        <v>6</v>
+      </c>
+      <c r="J498" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A499" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B499" t="s">
+        <v>143</v>
+      </c>
+      <c r="C499" t="s">
+        <v>11</v>
+      </c>
+      <c r="D499" t="s">
+        <v>12</v>
+      </c>
+      <c r="E499" t="s">
+        <v>195</v>
+      </c>
+      <c r="F499" t="s">
+        <v>94</v>
+      </c>
+      <c r="G499">
+        <v>270</v>
+      </c>
+      <c r="H499" t="s">
+        <v>15</v>
+      </c>
+      <c r="I499">
+        <v>5</v>
+      </c>
+      <c r="J499" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A500" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B500" t="s">
+        <v>32</v>
+      </c>
+      <c r="C500" t="s">
+        <v>24</v>
+      </c>
+      <c r="D500" t="s">
+        <v>33</v>
+      </c>
+      <c r="E500" t="s">
+        <v>53</v>
+      </c>
+      <c r="F500" t="s">
+        <v>94</v>
+      </c>
+      <c r="G500">
+        <v>265</v>
+      </c>
+      <c r="H500" t="s">
+        <v>15</v>
+      </c>
+      <c r="I500">
+        <v>1</v>
+      </c>
+      <c r="J500" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A501" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B501" t="s">
+        <v>98</v>
+      </c>
+      <c r="C501" t="s">
+        <v>24</v>
+      </c>
+      <c r="D501" t="s">
+        <v>49</v>
+      </c>
+      <c r="E501" t="s">
+        <v>53</v>
+      </c>
+      <c r="F501" t="s">
+        <v>94</v>
+      </c>
+      <c r="G501">
+        <v>250</v>
+      </c>
+      <c r="H501" t="s">
+        <v>22</v>
+      </c>
+      <c r="I501">
+        <v>1</v>
+      </c>
+      <c r="J501" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A502" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B502" t="s">
+        <v>196</v>
+      </c>
+      <c r="C502" t="s">
+        <v>24</v>
+      </c>
+      <c r="D502" t="s">
+        <v>40</v>
+      </c>
+      <c r="E502" t="s">
+        <v>53</v>
+      </c>
+      <c r="F502" t="s">
+        <v>94</v>
+      </c>
+      <c r="G502">
+        <v>255</v>
+      </c>
+      <c r="H502" t="s">
+        <v>22</v>
+      </c>
+      <c r="I502">
+        <v>1</v>
+      </c>
+      <c r="J502" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A503" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B503" t="s">
+        <v>65</v>
+      </c>
+      <c r="C503" t="s">
+        <v>24</v>
+      </c>
+      <c r="D503" t="s">
+        <v>40</v>
+      </c>
+      <c r="E503" t="s">
+        <v>53</v>
+      </c>
+      <c r="F503" t="s">
+        <v>94</v>
+      </c>
+      <c r="G503">
+        <v>255</v>
+      </c>
+      <c r="H503" t="s">
+        <v>22</v>
+      </c>
+      <c r="I503">
+        <v>1</v>
+      </c>
+      <c r="J503" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A504" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B504" t="s">
+        <v>96</v>
+      </c>
+      <c r="C504" t="s">
+        <v>24</v>
+      </c>
+      <c r="D504" t="s">
+        <v>38</v>
+      </c>
+      <c r="E504" t="s">
+        <v>53</v>
+      </c>
+      <c r="F504" t="s">
+        <v>94</v>
+      </c>
+      <c r="G504">
+        <v>265</v>
+      </c>
+      <c r="H504" t="s">
+        <v>15</v>
+      </c>
+      <c r="I504">
+        <v>1</v>
+      </c>
+      <c r="J504" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A505" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B505" t="s">
+        <v>197</v>
+      </c>
+      <c r="C505" t="s">
+        <v>24</v>
+      </c>
+      <c r="D505" t="s">
+        <v>47</v>
+      </c>
+      <c r="E505" t="s">
+        <v>53</v>
+      </c>
+      <c r="F505" t="s">
+        <v>94</v>
+      </c>
+      <c r="G505">
+        <v>245</v>
+      </c>
+      <c r="H505" t="s">
+        <v>22</v>
+      </c>
+      <c r="I505">
+        <v>1</v>
+      </c>
+      <c r="J505" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A506" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B506" t="s">
+        <v>67</v>
+      </c>
+      <c r="C506" t="s">
+        <v>24</v>
+      </c>
+      <c r="D506" t="s">
+        <v>40</v>
+      </c>
+      <c r="E506" t="s">
+        <v>13</v>
+      </c>
+      <c r="F506" t="s">
+        <v>87</v>
+      </c>
+      <c r="G506">
+        <v>240</v>
+      </c>
+      <c r="H506" t="s">
+        <v>22</v>
+      </c>
+      <c r="I506">
+        <v>1</v>
+      </c>
+      <c r="J506" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="507" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A507" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B507" t="s">
+        <v>198</v>
+      </c>
+      <c r="C507" t="s">
+        <v>120</v>
+      </c>
+      <c r="D507" t="s">
+        <v>128</v>
+      </c>
+      <c r="E507" t="s">
+        <v>13</v>
+      </c>
+      <c r="F507" t="s">
+        <v>87</v>
+      </c>
+      <c r="G507">
+        <v>0</v>
+      </c>
+      <c r="H507" t="s">
+        <v>122</v>
+      </c>
+      <c r="I507">
+        <v>1</v>
+      </c>
+      <c r="J507" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A508" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B508" t="s">
+        <v>173</v>
+      </c>
+      <c r="C508" t="s">
+        <v>120</v>
+      </c>
+      <c r="D508" t="s">
+        <v>126</v>
+      </c>
+      <c r="E508" t="s">
+        <v>13</v>
+      </c>
+      <c r="F508" t="s">
+        <v>14</v>
+      </c>
+      <c r="G508">
+        <v>0</v>
+      </c>
+      <c r="H508" t="s">
+        <v>122</v>
+      </c>
+      <c r="I508">
+        <v>1</v>
+      </c>
+      <c r="J508" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A509" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B509" t="s">
+        <v>173</v>
+      </c>
+      <c r="C509" t="s">
+        <v>120</v>
+      </c>
+      <c r="D509" t="s">
+        <v>126</v>
+      </c>
+      <c r="E509" t="s">
+        <v>13</v>
+      </c>
+      <c r="F509" t="s">
+        <v>14</v>
+      </c>
+      <c r="G509">
+        <v>0</v>
+      </c>
+      <c r="H509" t="s">
+        <v>122</v>
+      </c>
+      <c r="I509">
+        <v>1</v>
+      </c>
+      <c r="J509" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A510" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B510" t="s">
+        <v>199</v>
+      </c>
+      <c r="C510" t="s">
+        <v>24</v>
+      </c>
+      <c r="D510" t="s">
+        <v>47</v>
+      </c>
+      <c r="E510" t="s">
+        <v>100</v>
+      </c>
+      <c r="F510" t="s">
+        <v>66</v>
+      </c>
+      <c r="G510">
+        <v>240</v>
+      </c>
+      <c r="H510" t="s">
+        <v>22</v>
+      </c>
+      <c r="I510">
+        <v>1</v>
+      </c>
+      <c r="J510" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A511" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B511" t="s">
+        <v>115</v>
+      </c>
+      <c r="C511" t="s">
+        <v>24</v>
+      </c>
+      <c r="D511" t="s">
+        <v>49</v>
+      </c>
+      <c r="E511" t="s">
+        <v>100</v>
+      </c>
+      <c r="F511" t="s">
+        <v>66</v>
+      </c>
+      <c r="G511">
+        <v>250</v>
+      </c>
+      <c r="H511" t="s">
+        <v>22</v>
+      </c>
+      <c r="I511">
+        <v>1</v>
+      </c>
+      <c r="J511" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A512" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B512" t="s">
+        <v>70</v>
+      </c>
+      <c r="C512" t="s">
+        <v>24</v>
+      </c>
+      <c r="D512" t="s">
+        <v>49</v>
+      </c>
+      <c r="E512" t="s">
+        <v>100</v>
+      </c>
+      <c r="F512" t="s">
+        <v>66</v>
+      </c>
+      <c r="G512">
+        <v>235</v>
+      </c>
+      <c r="H512" t="s">
+        <v>22</v>
+      </c>
+      <c r="I512">
+        <v>1</v>
+      </c>
+      <c r="J512" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A513" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B513" t="s">
+        <v>76</v>
+      </c>
+      <c r="C513" t="s">
+        <v>24</v>
+      </c>
+      <c r="D513" t="s">
+        <v>49</v>
+      </c>
+      <c r="E513" t="s">
+        <v>100</v>
+      </c>
+      <c r="F513" t="s">
+        <v>66</v>
+      </c>
+      <c r="G513">
+        <v>240</v>
+      </c>
+      <c r="H513" t="s">
+        <v>22</v>
+      </c>
+      <c r="I513">
+        <v>1</v>
+      </c>
+      <c r="J513" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A514" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B514" t="s">
+        <v>109</v>
+      </c>
+      <c r="C514" t="s">
+        <v>24</v>
+      </c>
+      <c r="D514" t="s">
+        <v>47</v>
+      </c>
+      <c r="E514" t="s">
+        <v>100</v>
+      </c>
+      <c r="F514" t="s">
+        <v>66</v>
+      </c>
+      <c r="G514">
+        <v>250</v>
+      </c>
+      <c r="H514" t="s">
+        <v>22</v>
+      </c>
+      <c r="I514">
+        <v>1</v>
+      </c>
+      <c r="J514" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A515" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B515" t="s">
+        <v>200</v>
+      </c>
+      <c r="C515" t="s">
+        <v>24</v>
+      </c>
+      <c r="D515" t="s">
+        <v>47</v>
+      </c>
+      <c r="E515" t="s">
+        <v>100</v>
+      </c>
+      <c r="F515" t="s">
+        <v>66</v>
+      </c>
+      <c r="G515">
+        <v>255</v>
+      </c>
+      <c r="H515" t="s">
+        <v>22</v>
+      </c>
+      <c r="I515">
+        <v>1</v>
+      </c>
+      <c r="J515" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A516" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B516" t="s">
+        <v>201</v>
+      </c>
+      <c r="C516" t="s">
+        <v>24</v>
+      </c>
+      <c r="D516" t="s">
+        <v>47</v>
+      </c>
+      <c r="E516" t="s">
+        <v>100</v>
+      </c>
+      <c r="F516" t="s">
+        <v>66</v>
+      </c>
+      <c r="G516">
+        <v>240</v>
+      </c>
+      <c r="H516" t="s">
+        <v>22</v>
+      </c>
+      <c r="I516">
+        <v>1</v>
+      </c>
+      <c r="J516" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A517" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B517" t="s">
+        <v>103</v>
+      </c>
+      <c r="C517" t="s">
+        <v>24</v>
+      </c>
+      <c r="D517" t="s">
+        <v>49</v>
+      </c>
+      <c r="E517" t="s">
+        <v>100</v>
+      </c>
+      <c r="F517" t="s">
+        <v>66</v>
+      </c>
+      <c r="G517">
+        <v>245</v>
+      </c>
+      <c r="H517" t="s">
+        <v>22</v>
+      </c>
+      <c r="I517">
+        <v>1</v>
+      </c>
+      <c r="J517" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A518" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B518" t="s">
+        <v>167</v>
+      </c>
+      <c r="C518" t="s">
+        <v>120</v>
+      </c>
+      <c r="D518" t="s">
+        <v>121</v>
+      </c>
+      <c r="E518" t="s">
+        <v>133</v>
+      </c>
+      <c r="F518" t="s">
+        <v>94</v>
+      </c>
+      <c r="G518">
+        <v>0</v>
+      </c>
+      <c r="H518" t="s">
+        <v>122</v>
+      </c>
+      <c r="I518">
+        <v>1</v>
+      </c>
+      <c r="J518" t="s">
         <v>13</v>
       </c>
     </row>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F0EEBE6-0C4B-499F-9C45-723766AF247B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0BCADCD-0EEC-46F8-AB45-CB9DCADD4E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12795" yWindow="1245" windowWidth="23250" windowHeight="10890" xr2:uid="{48791067-37B7-4C0E-89C2-5133B3E545EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{4BAC1833-0BAB-412D-BDA6-55991D984B65}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -2273,7 +2273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F351ABB1-9D6A-4987-A767-4E90DFCF8E18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66D8F61-D102-4A95-8AF7-550F68DB04D8}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -9324,7 +9324,7 @@
         <v>0</v>
       </c>
       <c r="N114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114">
         <v>8</v>
@@ -9386,7 +9386,7 @@
         <v>1</v>
       </c>
       <c r="N115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115">
         <v>3</v>
@@ -10750,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="N137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137">
         <v>3</v>
@@ -10874,7 +10874,7 @@
         <v>2</v>
       </c>
       <c r="N139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O139">
         <v>2</v>
@@ -10998,7 +10998,7 @@
         <v>0</v>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O141">
         <v>3</v>
@@ -11122,7 +11122,7 @@
         <v>1</v>
       </c>
       <c r="N143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O143">
         <v>1</v>
@@ -11184,7 +11184,7 @@
         <v>1</v>
       </c>
       <c r="N144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O144">
         <v>2</v>
@@ -11370,7 +11370,7 @@
         <v>0</v>
       </c>
       <c r="N147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O147">
         <v>1</v>
@@ -11432,7 +11432,7 @@
         <v>1</v>
       </c>
       <c r="N148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O148">
         <v>6</v>
@@ -12982,7 +12982,7 @@
         <v>0</v>
       </c>
       <c r="N173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O173">
         <v>6</v>
@@ -13850,7 +13850,7 @@
         <v>3</v>
       </c>
       <c r="N187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O187">
         <v>6</v>
@@ -14408,7 +14408,7 @@
         <v>7</v>
       </c>
       <c r="N196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O196">
         <v>9</v>
@@ -15896,7 +15896,7 @@
         <v>2</v>
       </c>
       <c r="N220">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O220">
         <v>4</v>
@@ -16082,7 +16082,7 @@
         <v>8</v>
       </c>
       <c r="N223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O223">
         <v>13</v>
@@ -16144,7 +16144,7 @@
         <v>5</v>
       </c>
       <c r="N224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O224">
         <v>9</v>
@@ -16330,7 +16330,7 @@
         <v>10</v>
       </c>
       <c r="N227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O227">
         <v>12</v>
@@ -16392,7 +16392,7 @@
         <v>11</v>
       </c>
       <c r="N228">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O228">
         <v>14</v>
@@ -16454,7 +16454,7 @@
         <v>9</v>
       </c>
       <c r="N229">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O229">
         <v>13</v>
@@ -17326,7 +17326,7 @@
         <v>0</v>
       </c>
       <c r="N245">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O245">
         <v>2</v>
@@ -17379,7 +17379,7 @@
         <v>0</v>
       </c>
       <c r="N246">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O246">
         <v>1</v>
@@ -17697,7 +17697,7 @@
         <v>0</v>
       </c>
       <c r="N252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O252">
         <v>1</v>
@@ -17750,7 +17750,7 @@
         <v>0</v>
       </c>
       <c r="N253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O253">
         <v>2</v>
@@ -18302,7 +18302,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E666D6ED-265C-4952-8BAA-8BFB4A3A91F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1491D8-0F5E-492E-8165-3D8448B8A03B}">
   <dimension ref="A1:J518"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0BCADCD-0EEC-46F8-AB45-CB9DCADD4E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B169714-12E6-4C9B-8DF6-435CE74DECCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{4BAC1833-0BAB-412D-BDA6-55991D984B65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{02046495-837B-4CA9-A279-0E291960FFFC}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5663" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5768" uniqueCount="614">
   <si>
     <t>날짜</t>
   </si>
@@ -201,7 +201,7 @@
     <t>DPM647-BK260</t>
   </si>
   <si>
-    <t>바오지/카페24</t>
+    <t>카페24/바오지</t>
   </si>
   <si>
     <t>블랙</t>
@@ -342,7 +342,7 @@
     <t>ECW304-BK240</t>
   </si>
   <si>
-    <t>바오지/스토어팜</t>
+    <t>스토어팜/바오지</t>
   </si>
   <si>
     <t>DPM647-BK280</t>
@@ -591,18 +591,12 @@
     <t>BJM931-WHGN275</t>
   </si>
   <si>
-    <t>카페24/바오지</t>
-  </si>
-  <si>
     <t>유튜브쇼핑</t>
   </si>
   <si>
     <t>BJM931-BK260</t>
   </si>
   <si>
-    <t>스토어팜/바오지</t>
-  </si>
-  <si>
     <t>S-10RA-GYGG</t>
   </si>
   <si>
@@ -648,6 +642,9 @@
     <t>DPW771-LBL240</t>
   </si>
   <si>
+    <t>DPW771-BK235</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1726,9 +1723,6 @@
   </si>
   <si>
     <t>DPW771AP 바오지 여성 러닝화 살구색 255</t>
-  </si>
-  <si>
-    <t>DPW771-BK235</t>
   </si>
   <si>
     <t>DPW771BK 바오지 여성 러닝화 블랙 235</t>
@@ -2273,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66D8F61-D102-4A95-8AF7-550F68DB04D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73761355-B4E7-4C82-9D2A-9AD267F1974F}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2282,7 +2276,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2297,46 +2291,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" t="s">
         <v>203</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>204</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>205</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>206</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>207</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>208</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>209</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>210</v>
-      </c>
-      <c r="O1" t="s">
-        <v>211</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
+        <v>211</v>
+      </c>
+      <c r="R1" t="s">
         <v>212</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>213</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>214</v>
-      </c>
-      <c r="T1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2344,7 +2338,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2371,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2389,7 +2383,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2406,7 +2400,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2433,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -2451,7 +2445,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2468,7 +2462,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2495,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2513,7 +2507,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2530,7 +2524,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2557,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2575,7 +2569,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2592,7 +2586,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2619,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2637,7 +2631,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2654,7 +2648,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2681,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2699,7 +2693,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2716,7 +2710,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2743,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2761,7 +2755,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2778,7 +2772,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2805,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2823,7 +2817,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2840,7 +2834,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2867,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2885,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2902,7 +2896,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2929,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2947,7 +2941,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2961,16 +2955,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" t="s">
         <v>229</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>230</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>231</v>
-      </c>
-      <c r="D12" t="s">
-        <v>232</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2991,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3023,16 +3017,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" t="s">
         <v>233</v>
       </c>
-      <c r="B13" t="s">
-        <v>234</v>
-      </c>
       <c r="C13" t="s">
+        <v>230</v>
+      </c>
+      <c r="D13" t="s">
         <v>231</v>
-      </c>
-      <c r="D13" t="s">
-        <v>232</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3053,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3085,16 +3079,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" t="s">
         <v>235</v>
       </c>
-      <c r="B14" t="s">
-        <v>236</v>
-      </c>
       <c r="C14" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" t="s">
         <v>231</v>
-      </c>
-      <c r="D14" t="s">
-        <v>232</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3115,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3147,16 +3141,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" t="s">
         <v>237</v>
       </c>
-      <c r="B15" t="s">
-        <v>238</v>
-      </c>
       <c r="C15" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" t="s">
         <v>231</v>
-      </c>
-      <c r="D15" t="s">
-        <v>232</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3177,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3209,16 +3203,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B16" t="s">
         <v>239</v>
       </c>
-      <c r="B16" t="s">
-        <v>240</v>
-      </c>
       <c r="C16" t="s">
+        <v>230</v>
+      </c>
+      <c r="D16" t="s">
         <v>231</v>
-      </c>
-      <c r="D16" t="s">
-        <v>232</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3239,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3271,16 +3265,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="B17" t="s">
-        <v>242</v>
-      </c>
       <c r="C17" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" t="s">
         <v>231</v>
-      </c>
-      <c r="D17" t="s">
-        <v>232</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3301,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3333,16 +3327,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" t="s">
         <v>243</v>
       </c>
-      <c r="B18" t="s">
-        <v>244</v>
-      </c>
       <c r="C18" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" t="s">
         <v>231</v>
-      </c>
-      <c r="D18" t="s">
-        <v>232</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3363,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3395,16 +3389,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>244</v>
+      </c>
+      <c r="B19" t="s">
         <v>245</v>
       </c>
-      <c r="B19" t="s">
-        <v>246</v>
-      </c>
       <c r="C19" t="s">
+        <v>230</v>
+      </c>
+      <c r="D19" t="s">
         <v>231</v>
-      </c>
-      <c r="D19" t="s">
-        <v>232</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3425,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3457,16 +3451,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>246</v>
+      </c>
+      <c r="B20" t="s">
         <v>247</v>
       </c>
-      <c r="B20" t="s">
-        <v>248</v>
-      </c>
       <c r="C20" t="s">
+        <v>230</v>
+      </c>
+      <c r="D20" t="s">
         <v>231</v>
-      </c>
-      <c r="D20" t="s">
-        <v>232</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3487,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3519,16 +3513,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>248</v>
+      </c>
+      <c r="B21" t="s">
         <v>249</v>
       </c>
-      <c r="B21" t="s">
-        <v>250</v>
-      </c>
       <c r="C21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D21" t="s">
         <v>231</v>
-      </c>
-      <c r="D21" t="s">
-        <v>232</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3549,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3581,16 +3575,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>250</v>
+      </c>
+      <c r="B22" t="s">
         <v>251</v>
       </c>
-      <c r="B22" t="s">
-        <v>252</v>
-      </c>
       <c r="C22" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" t="s">
         <v>231</v>
-      </c>
-      <c r="D22" t="s">
-        <v>232</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3611,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3643,16 +3637,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>252</v>
+      </c>
+      <c r="B23" t="s">
         <v>253</v>
       </c>
-      <c r="B23" t="s">
-        <v>254</v>
-      </c>
       <c r="C23" t="s">
+        <v>230</v>
+      </c>
+      <c r="D23" t="s">
         <v>231</v>
-      </c>
-      <c r="D23" t="s">
-        <v>232</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3673,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3705,16 +3699,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>254</v>
+      </c>
+      <c r="B24" t="s">
         <v>255</v>
       </c>
-      <c r="B24" t="s">
-        <v>256</v>
-      </c>
       <c r="C24" t="s">
+        <v>230</v>
+      </c>
+      <c r="D24" t="s">
         <v>231</v>
-      </c>
-      <c r="D24" t="s">
-        <v>232</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3735,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3767,16 +3761,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25" t="s">
         <v>257</v>
       </c>
-      <c r="B25" t="s">
-        <v>258</v>
-      </c>
       <c r="C25" t="s">
+        <v>230</v>
+      </c>
+      <c r="D25" t="s">
         <v>231</v>
-      </c>
-      <c r="D25" t="s">
-        <v>232</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3797,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3829,16 +3823,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" t="s">
         <v>259</v>
       </c>
-      <c r="B26" t="s">
-        <v>260</v>
-      </c>
       <c r="C26" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" t="s">
         <v>231</v>
-      </c>
-      <c r="D26" t="s">
-        <v>232</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3859,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3891,16 +3885,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>260</v>
+      </c>
+      <c r="B27" t="s">
         <v>261</v>
       </c>
-      <c r="B27" t="s">
-        <v>262</v>
-      </c>
       <c r="C27" t="s">
+        <v>230</v>
+      </c>
+      <c r="D27" t="s">
         <v>231</v>
-      </c>
-      <c r="D27" t="s">
-        <v>232</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3921,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3953,16 +3947,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" t="s">
         <v>263</v>
       </c>
-      <c r="B28" t="s">
-        <v>264</v>
-      </c>
       <c r="C28" t="s">
+        <v>230</v>
+      </c>
+      <c r="D28" t="s">
         <v>231</v>
-      </c>
-      <c r="D28" t="s">
-        <v>232</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3983,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4015,16 +4009,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B29" t="s">
         <v>265</v>
       </c>
-      <c r="B29" t="s">
-        <v>266</v>
-      </c>
       <c r="C29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D29" t="s">
         <v>231</v>
-      </c>
-      <c r="D29" t="s">
-        <v>232</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4045,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4077,16 +4071,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B30" t="s">
         <v>267</v>
       </c>
-      <c r="B30" t="s">
-        <v>268</v>
-      </c>
       <c r="C30" t="s">
+        <v>230</v>
+      </c>
+      <c r="D30" t="s">
         <v>231</v>
-      </c>
-      <c r="D30" t="s">
-        <v>232</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4107,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4139,16 +4133,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B31" t="s">
         <v>269</v>
       </c>
-      <c r="B31" t="s">
-        <v>270</v>
-      </c>
       <c r="C31" t="s">
+        <v>230</v>
+      </c>
+      <c r="D31" t="s">
         <v>231</v>
-      </c>
-      <c r="D31" t="s">
-        <v>232</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4169,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4201,16 +4195,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>270</v>
+      </c>
+      <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>230</v>
+      </c>
+      <c r="D32" t="s">
         <v>272</v>
-      </c>
-      <c r="C32" t="s">
-        <v>231</v>
-      </c>
-      <c r="D32" t="s">
-        <v>273</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4231,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4263,16 +4257,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>273</v>
+      </c>
+      <c r="B33" t="s">
         <v>274</v>
       </c>
-      <c r="B33" t="s">
-        <v>275</v>
-      </c>
       <c r="C33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D33" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4293,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4325,16 +4319,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>275</v>
+      </c>
+      <c r="B34" t="s">
         <v>276</v>
       </c>
-      <c r="B34" t="s">
-        <v>277</v>
-      </c>
       <c r="C34" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4355,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4387,16 +4381,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>277</v>
+      </c>
+      <c r="B35" t="s">
         <v>278</v>
       </c>
-      <c r="B35" t="s">
-        <v>279</v>
-      </c>
       <c r="C35" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4417,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4449,16 +4443,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>279</v>
+      </c>
+      <c r="B36" t="s">
         <v>280</v>
       </c>
-      <c r="B36" t="s">
-        <v>281</v>
-      </c>
       <c r="C36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4479,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4511,16 +4505,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>281</v>
+      </c>
+      <c r="B37" t="s">
         <v>282</v>
       </c>
-      <c r="B37" t="s">
-        <v>283</v>
-      </c>
       <c r="C37" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4541,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4573,16 +4567,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>283</v>
+      </c>
+      <c r="B38" t="s">
         <v>284</v>
       </c>
-      <c r="B38" t="s">
-        <v>285</v>
-      </c>
       <c r="C38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4603,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4635,16 +4629,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39" t="s">
         <v>286</v>
       </c>
-      <c r="B39" t="s">
-        <v>287</v>
-      </c>
       <c r="C39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4665,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4697,16 +4691,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>287</v>
+      </c>
+      <c r="B40" t="s">
         <v>288</v>
       </c>
-      <c r="B40" t="s">
-        <v>289</v>
-      </c>
       <c r="C40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4727,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4759,16 +4753,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>289</v>
+      </c>
+      <c r="B41" t="s">
         <v>290</v>
       </c>
-      <c r="B41" t="s">
-        <v>291</v>
-      </c>
       <c r="C41" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4789,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4821,16 +4815,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>291</v>
+      </c>
+      <c r="B42" t="s">
         <v>292</v>
       </c>
-      <c r="B42" t="s">
-        <v>293</v>
-      </c>
       <c r="C42" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4851,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4883,16 +4877,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" t="s">
         <v>294</v>
       </c>
-      <c r="B43" t="s">
-        <v>295</v>
-      </c>
       <c r="C43" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D43" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4913,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4945,16 +4939,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>295</v>
+      </c>
+      <c r="B44" t="s">
         <v>296</v>
       </c>
-      <c r="B44" t="s">
-        <v>297</v>
-      </c>
       <c r="C44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4975,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5007,16 +5001,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>297</v>
+      </c>
+      <c r="B45" t="s">
         <v>298</v>
       </c>
-      <c r="B45" t="s">
-        <v>299</v>
-      </c>
       <c r="C45" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5037,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5069,16 +5063,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>299</v>
+      </c>
+      <c r="B46" t="s">
         <v>300</v>
       </c>
-      <c r="B46" t="s">
-        <v>301</v>
-      </c>
       <c r="C46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5099,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5131,16 +5125,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>301</v>
+      </c>
+      <c r="B47" t="s">
         <v>302</v>
       </c>
-      <c r="B47" t="s">
-        <v>303</v>
-      </c>
       <c r="C47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5161,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5193,16 +5187,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>303</v>
+      </c>
+      <c r="B48" t="s">
         <v>304</v>
       </c>
-      <c r="B48" t="s">
-        <v>305</v>
-      </c>
       <c r="C48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5223,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5255,16 +5249,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>305</v>
+      </c>
+      <c r="B49" t="s">
         <v>306</v>
       </c>
-      <c r="B49" t="s">
-        <v>307</v>
-      </c>
       <c r="C49" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D49" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5285,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5317,16 +5311,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>307</v>
+      </c>
+      <c r="B50" t="s">
         <v>308</v>
       </c>
-      <c r="B50" t="s">
-        <v>309</v>
-      </c>
       <c r="C50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5347,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5379,16 +5373,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>309</v>
+      </c>
+      <c r="B51" t="s">
         <v>310</v>
       </c>
-      <c r="B51" t="s">
-        <v>311</v>
-      </c>
       <c r="C51" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D51" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5409,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5441,16 +5435,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>311</v>
+      </c>
+      <c r="B52" t="s">
         <v>312</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>230</v>
+      </c>
+      <c r="D52" t="s">
         <v>313</v>
-      </c>
-      <c r="C52" t="s">
-        <v>231</v>
-      </c>
-      <c r="D52" t="s">
-        <v>314</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5471,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5503,16 +5497,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>314</v>
+      </c>
+      <c r="B53" t="s">
         <v>315</v>
       </c>
-      <c r="B53" t="s">
-        <v>316</v>
-      </c>
       <c r="C53" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5533,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5565,16 +5559,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>316</v>
+      </c>
+      <c r="B54" t="s">
         <v>317</v>
       </c>
-      <c r="B54" t="s">
-        <v>318</v>
-      </c>
       <c r="C54" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5595,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5627,16 +5621,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>318</v>
+      </c>
+      <c r="B55" t="s">
         <v>319</v>
       </c>
-      <c r="B55" t="s">
-        <v>320</v>
-      </c>
       <c r="C55" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5657,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5689,16 +5683,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>320</v>
+      </c>
+      <c r="B56" t="s">
         <v>321</v>
       </c>
-      <c r="B56" t="s">
-        <v>322</v>
-      </c>
       <c r="C56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5719,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5751,16 +5745,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>322</v>
+      </c>
+      <c r="B57" t="s">
         <v>323</v>
       </c>
-      <c r="B57" t="s">
-        <v>324</v>
-      </c>
       <c r="C57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D57" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5781,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5813,16 +5807,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>324</v>
+      </c>
+      <c r="B58" t="s">
         <v>325</v>
       </c>
-      <c r="B58" t="s">
-        <v>326</v>
-      </c>
       <c r="C58" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D58" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5843,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5875,16 +5869,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>326</v>
+      </c>
+      <c r="B59" t="s">
         <v>327</v>
       </c>
-      <c r="B59" t="s">
-        <v>328</v>
-      </c>
       <c r="C59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D59" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5905,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5937,16 +5931,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>328</v>
+      </c>
+      <c r="B60" t="s">
         <v>329</v>
       </c>
-      <c r="B60" t="s">
-        <v>330</v>
-      </c>
       <c r="C60" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D60" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5967,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5999,16 +5993,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>330</v>
+      </c>
+      <c r="B61" t="s">
         <v>331</v>
       </c>
-      <c r="B61" t="s">
-        <v>332</v>
-      </c>
       <c r="C61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D61" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6029,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6061,16 +6055,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>332</v>
+      </c>
+      <c r="B62" t="s">
         <v>333</v>
       </c>
-      <c r="B62" t="s">
-        <v>334</v>
-      </c>
       <c r="C62" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D62" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6091,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6123,16 +6117,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>334</v>
+      </c>
+      <c r="B63" t="s">
         <v>335</v>
       </c>
-      <c r="B63" t="s">
-        <v>336</v>
-      </c>
       <c r="C63" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6153,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6185,16 +6179,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>336</v>
+      </c>
+      <c r="B64" t="s">
         <v>337</v>
       </c>
-      <c r="B64" t="s">
-        <v>338</v>
-      </c>
       <c r="C64" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D64" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6215,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6247,16 +6241,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>338</v>
+      </c>
+      <c r="B65" t="s">
         <v>339</v>
       </c>
-      <c r="B65" t="s">
-        <v>340</v>
-      </c>
       <c r="C65" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D65" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6277,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6309,16 +6303,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>340</v>
+      </c>
+      <c r="B66" t="s">
         <v>341</v>
       </c>
-      <c r="B66" t="s">
-        <v>342</v>
-      </c>
       <c r="C66" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D66" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6339,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6374,7 +6368,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6401,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6419,7 +6413,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6436,7 +6430,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6463,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -6481,7 +6475,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6498,7 +6492,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6525,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L69">
         <v>9</v>
@@ -6543,7 +6537,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6560,7 +6554,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6587,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6605,7 +6599,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6622,7 +6616,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6649,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6667,7 +6661,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6681,10 +6675,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>348</v>
+      </c>
+      <c r="B72" t="s">
         <v>349</v>
-      </c>
-      <c r="B72" t="s">
-        <v>350</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6711,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6729,7 +6723,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6746,7 +6740,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6773,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6791,7 +6785,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6805,10 +6799,10 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>352</v>
+      </c>
+      <c r="B74" t="s">
         <v>353</v>
-      </c>
-      <c r="B74" t="s">
-        <v>354</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6835,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -6853,7 +6847,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6870,7 +6864,7 @@
         <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6897,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6915,7 +6909,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6929,10 +6923,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>355</v>
+      </c>
+      <c r="B76" t="s">
         <v>356</v>
-      </c>
-      <c r="B76" t="s">
-        <v>357</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6959,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6977,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6991,10 +6985,10 @@
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -7021,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -7039,7 +7033,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7053,10 +7047,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>359</v>
+      </c>
+      <c r="B78" t="s">
         <v>360</v>
-      </c>
-      <c r="B78" t="s">
-        <v>361</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7083,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7101,7 +7095,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7115,10 +7109,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>361</v>
+      </c>
+      <c r="B79" t="s">
         <v>362</v>
-      </c>
-      <c r="B79" t="s">
-        <v>363</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7145,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7163,7 +7157,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7180,7 +7174,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7207,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7225,7 +7219,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7239,10 +7233,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>364</v>
+      </c>
+      <c r="B81" t="s">
         <v>365</v>
-      </c>
-      <c r="B81" t="s">
-        <v>366</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7269,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -7287,7 +7281,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7301,10 +7295,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>366</v>
+      </c>
+      <c r="B82" t="s">
         <v>367</v>
-      </c>
-      <c r="B82" t="s">
-        <v>368</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7331,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7349,7 +7343,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7363,10 +7357,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>369</v>
+      </c>
+      <c r="B83" t="s">
         <v>370</v>
-      </c>
-      <c r="B83" t="s">
-        <v>371</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7393,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7411,7 +7405,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7425,10 +7419,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>371</v>
+      </c>
+      <c r="B84" t="s">
         <v>372</v>
-      </c>
-      <c r="B84" t="s">
-        <v>373</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7455,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7473,7 +7467,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7487,10 +7481,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>373</v>
+      </c>
+      <c r="B85" t="s">
         <v>374</v>
-      </c>
-      <c r="B85" t="s">
-        <v>375</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7517,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7535,7 +7529,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7549,10 +7543,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>375</v>
+      </c>
+      <c r="B86" t="s">
         <v>376</v>
-      </c>
-      <c r="B86" t="s">
-        <v>377</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7579,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7597,7 +7591,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7611,10 +7605,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>377</v>
+      </c>
+      <c r="B87" t="s">
         <v>378</v>
-      </c>
-      <c r="B87" t="s">
-        <v>379</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7641,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7659,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7676,7 +7670,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7703,7 +7697,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -7721,7 +7715,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7735,10 +7729,10 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>381</v>
+      </c>
+      <c r="B89" t="s">
         <v>382</v>
-      </c>
-      <c r="B89" t="s">
-        <v>383</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7765,7 +7759,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -7783,7 +7777,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7800,7 +7794,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7827,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L90">
         <v>2</v>
@@ -7845,7 +7839,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7859,10 +7853,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>384</v>
+      </c>
+      <c r="B91" t="s">
         <v>385</v>
-      </c>
-      <c r="B91" t="s">
-        <v>386</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7889,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7907,7 +7901,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7921,10 +7915,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>386</v>
+      </c>
+      <c r="B92" t="s">
         <v>387</v>
-      </c>
-      <c r="B92" t="s">
-        <v>388</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7951,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7969,7 +7963,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7986,7 +7980,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -8013,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8031,7 +8025,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8045,10 +8039,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>390</v>
+      </c>
+      <c r="B94" t="s">
         <v>391</v>
-      </c>
-      <c r="B94" t="s">
-        <v>392</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8075,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8093,7 +8087,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8107,10 +8101,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>392</v>
+      </c>
+      <c r="B95" t="s">
         <v>393</v>
-      </c>
-      <c r="B95" t="s">
-        <v>394</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8137,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8155,7 +8149,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8169,10 +8163,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>394</v>
+      </c>
+      <c r="B96" t="s">
         <v>395</v>
-      </c>
-      <c r="B96" t="s">
-        <v>396</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8199,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8217,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8231,10 +8225,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>396</v>
+      </c>
+      <c r="B97" t="s">
         <v>397</v>
-      </c>
-      <c r="B97" t="s">
-        <v>398</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8261,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8279,7 +8273,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8296,7 +8290,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8311,37 +8305,37 @@
         <v>265</v>
       </c>
       <c r="G98">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
       <c r="I98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L98">
+        <v>5</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98">
         <v>4</v>
       </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>1</v>
-      </c>
-      <c r="O98">
-        <v>3</v>
-      </c>
       <c r="P98" t="s">
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8358,7 +8352,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8385,7 +8379,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L99">
         <v>1</v>
@@ -8403,7 +8397,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8420,7 +8414,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8447,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8465,7 +8459,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8479,10 +8473,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>402</v>
+      </c>
+      <c r="B101" t="s">
         <v>403</v>
-      </c>
-      <c r="B101" t="s">
-        <v>404</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8509,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8527,7 +8521,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8541,10 +8535,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>404</v>
+      </c>
+      <c r="B102" t="s">
         <v>405</v>
-      </c>
-      <c r="B102" t="s">
-        <v>406</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8571,7 +8565,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8589,7 +8583,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8603,10 +8597,10 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>407</v>
+      </c>
+      <c r="B103" t="s">
         <v>408</v>
-      </c>
-      <c r="B103" t="s">
-        <v>409</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8633,7 +8627,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -8651,7 +8645,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8668,7 +8662,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8695,7 +8689,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8713,7 +8707,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8727,10 +8721,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>410</v>
+      </c>
+      <c r="B105" t="s">
         <v>411</v>
-      </c>
-      <c r="B105" t="s">
-        <v>412</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8757,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8775,7 +8769,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8792,7 +8786,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8819,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8837,7 +8831,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8851,10 +8845,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>413</v>
+      </c>
+      <c r="B107" t="s">
         <v>414</v>
-      </c>
-      <c r="B107" t="s">
-        <v>415</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8881,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8899,7 +8893,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8916,7 +8910,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8943,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8961,7 +8955,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8978,7 +8972,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -9005,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -9023,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -9037,10 +9031,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>418</v>
+      </c>
+      <c r="B110" t="s">
         <v>419</v>
-      </c>
-      <c r="B110" t="s">
-        <v>420</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -9067,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -9085,7 +9079,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -9099,10 +9093,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>420</v>
+      </c>
+      <c r="B111" t="s">
         <v>421</v>
-      </c>
-      <c r="B111" t="s">
-        <v>422</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -9129,7 +9123,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9147,7 +9141,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9164,7 +9158,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9191,7 +9185,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9209,7 +9203,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9226,7 +9220,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9253,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L113">
         <v>6</v>
@@ -9271,7 +9265,7 @@
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9288,7 +9282,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9303,37 +9297,37 @@
         <v>270</v>
       </c>
       <c r="G114">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L114">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M114">
         <v>0</v>
       </c>
       <c r="N114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O114">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P114" t="s">
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9350,7 +9344,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9377,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9395,7 +9389,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9412,7 +9406,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9439,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L116">
         <v>3</v>
@@ -9457,7 +9451,7 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9474,7 +9468,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9501,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9519,7 +9513,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9536,7 +9530,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9563,7 +9557,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9581,7 +9575,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9595,10 +9589,10 @@
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
+        <v>431</v>
+      </c>
+      <c r="B119" t="s">
         <v>432</v>
-      </c>
-      <c r="B119" t="s">
-        <v>433</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9625,7 +9619,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -9643,7 +9637,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9660,7 +9654,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9687,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9705,7 +9699,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9722,7 +9716,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9749,7 +9743,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -9767,7 +9761,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9784,7 +9778,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9811,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L122">
         <v>5</v>
@@ -9829,7 +9823,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9846,7 +9840,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9873,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -9891,7 +9885,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9908,7 +9902,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9935,7 +9929,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -9953,7 +9947,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9970,7 +9964,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9997,7 +9991,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -10015,7 +10009,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -10032,7 +10026,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -10059,7 +10053,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -10077,7 +10071,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -10094,7 +10088,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -10109,37 +10103,37 @@
         <v>235</v>
       </c>
       <c r="G127">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H127">
         <v>0</v>
       </c>
       <c r="I127">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J127">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K127" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L127">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M127">
         <v>5</v>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O127">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P127" t="s">
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -10156,7 +10150,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -10183,7 +10177,7 @@
         <v>5</v>
       </c>
       <c r="K128" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L128">
         <v>13</v>
@@ -10201,7 +10195,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -10218,7 +10212,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10233,37 +10227,37 @@
         <v>245</v>
       </c>
       <c r="G129">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H129">
         <v>0</v>
       </c>
       <c r="I129">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L129">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M129">
         <v>6</v>
       </c>
       <c r="N129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O129">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P129" t="s">
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10280,7 +10274,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10307,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10325,7 +10319,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10342,7 +10336,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10369,7 +10363,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10387,7 +10381,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10404,7 +10398,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10431,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L132">
         <v>18</v>
@@ -10449,7 +10443,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10466,7 +10460,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10493,7 +10487,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L133">
         <v>10</v>
@@ -10511,7 +10505,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10528,7 +10522,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10555,7 +10549,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L134">
         <v>16</v>
@@ -10573,7 +10567,7 @@
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10590,7 +10584,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10617,7 +10611,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10635,7 +10629,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10652,7 +10646,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10679,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10697,7 +10691,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10714,7 +10708,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10741,7 +10735,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L137">
         <v>3</v>
@@ -10759,7 +10753,7 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10776,7 +10770,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10803,7 +10797,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L138">
         <v>4</v>
@@ -10821,7 +10815,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10838,7 +10832,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10865,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L139">
         <v>2</v>
@@ -10883,7 +10877,7 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10900,7 +10894,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10915,37 +10909,37 @@
         <v>250</v>
       </c>
       <c r="G140">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H140">
         <v>0</v>
       </c>
       <c r="I140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M140">
         <v>0</v>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P140" t="s">
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10962,7 +10956,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10977,37 +10971,37 @@
         <v>255</v>
       </c>
       <c r="G141">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H141">
         <v>0</v>
       </c>
       <c r="I141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M141">
         <v>0</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P141" t="s">
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -11024,7 +11018,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -11051,7 +11045,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -11069,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -11086,7 +11080,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -11113,7 +11107,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -11131,7 +11125,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -11148,7 +11142,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -11175,7 +11169,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -11193,7 +11187,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -11207,10 +11201,10 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>463</v>
+      </c>
+      <c r="B145" t="s">
         <v>464</v>
-      </c>
-      <c r="B145" t="s">
-        <v>465</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -11237,7 +11231,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -11255,7 +11249,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -11269,10 +11263,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>465</v>
+      </c>
+      <c r="B146" t="s">
         <v>466</v>
-      </c>
-      <c r="B146" t="s">
-        <v>467</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -11299,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -11317,7 +11311,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -11334,7 +11328,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11361,7 +11355,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L147">
         <v>1</v>
@@ -11379,7 +11373,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11396,7 +11390,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11423,13 +11417,13 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L148">
         <v>6</v>
       </c>
       <c r="M148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N148">
         <v>0</v>
@@ -11441,7 +11435,7 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11458,7 +11452,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11485,7 +11479,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11503,7 +11497,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11520,7 +11514,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11547,7 +11541,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11565,7 +11559,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11582,7 +11576,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11609,7 +11603,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -11627,7 +11621,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11641,16 +11635,16 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>473</v>
+      </c>
+      <c r="B152" t="s">
         <v>474</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
+        <v>230</v>
+      </c>
+      <c r="D152" t="s">
         <v>475</v>
-      </c>
-      <c r="C152" t="s">
-        <v>231</v>
-      </c>
-      <c r="D152" t="s">
-        <v>476</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11671,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11703,16 +11697,16 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>476</v>
+      </c>
+      <c r="B153" t="s">
         <v>477</v>
       </c>
-      <c r="B153" t="s">
-        <v>478</v>
-      </c>
       <c r="C153" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D153" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11733,7 +11727,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11765,16 +11759,16 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>478</v>
+      </c>
+      <c r="B154" t="s">
         <v>479</v>
       </c>
-      <c r="B154" t="s">
-        <v>480</v>
-      </c>
       <c r="C154" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D154" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11795,7 +11789,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11827,16 +11821,16 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>480</v>
+      </c>
+      <c r="B155" t="s">
         <v>481</v>
       </c>
-      <c r="B155" t="s">
-        <v>482</v>
-      </c>
       <c r="C155" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11857,7 +11851,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11889,16 +11883,16 @@
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
+        <v>482</v>
+      </c>
+      <c r="B156" t="s">
         <v>483</v>
       </c>
-      <c r="B156" t="s">
-        <v>484</v>
-      </c>
       <c r="C156" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D156" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11919,7 +11913,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11951,16 +11945,16 @@
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>484</v>
+      </c>
+      <c r="B157" t="s">
         <v>485</v>
       </c>
-      <c r="B157" t="s">
-        <v>486</v>
-      </c>
       <c r="C157" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D157" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11981,7 +11975,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -12013,16 +12007,16 @@
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>486</v>
+      </c>
+      <c r="B158" t="s">
         <v>487</v>
       </c>
-      <c r="B158" t="s">
-        <v>488</v>
-      </c>
       <c r="C158" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D158" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -12043,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -12075,16 +12069,16 @@
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>488</v>
+      </c>
+      <c r="B159" t="s">
         <v>489</v>
       </c>
-      <c r="B159" t="s">
-        <v>490</v>
-      </c>
       <c r="C159" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D159" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -12105,7 +12099,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -12137,16 +12131,16 @@
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>490</v>
+      </c>
+      <c r="B160" t="s">
         <v>491</v>
       </c>
-      <c r="B160" t="s">
-        <v>492</v>
-      </c>
       <c r="C160" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D160" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -12167,7 +12161,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -12199,16 +12193,16 @@
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>492</v>
+      </c>
+      <c r="B161" t="s">
         <v>493</v>
       </c>
-      <c r="B161" t="s">
-        <v>494</v>
-      </c>
       <c r="C161" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D161" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -12229,7 +12223,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -12261,16 +12255,16 @@
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>494</v>
+      </c>
+      <c r="B162" t="s">
         <v>495</v>
       </c>
-      <c r="B162" t="s">
-        <v>496</v>
-      </c>
       <c r="C162" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D162" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -12291,7 +12285,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -12323,16 +12317,16 @@
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
+        <v>496</v>
+      </c>
+      <c r="B163" t="s">
         <v>497</v>
       </c>
-      <c r="B163" t="s">
-        <v>498</v>
-      </c>
       <c r="C163" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D163" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -12353,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -12385,16 +12379,16 @@
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>498</v>
+      </c>
+      <c r="B164" t="s">
         <v>499</v>
       </c>
-      <c r="B164" t="s">
-        <v>500</v>
-      </c>
       <c r="C164" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D164" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -12415,7 +12409,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -12447,16 +12441,16 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>500</v>
+      </c>
+      <c r="B165" t="s">
         <v>501</v>
       </c>
-      <c r="B165" t="s">
-        <v>502</v>
-      </c>
       <c r="C165" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D165" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12477,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12509,16 +12503,16 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>502</v>
+      </c>
+      <c r="B166" t="s">
         <v>503</v>
       </c>
-      <c r="B166" t="s">
-        <v>504</v>
-      </c>
       <c r="C166" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D166" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12539,7 +12533,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12571,16 +12565,16 @@
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>504</v>
+      </c>
+      <c r="B167" t="s">
         <v>505</v>
       </c>
-      <c r="B167" t="s">
-        <v>506</v>
-      </c>
       <c r="C167" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D167" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12601,7 +12595,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12633,16 +12627,16 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>506</v>
+      </c>
+      <c r="B168" t="s">
         <v>507</v>
       </c>
-      <c r="B168" t="s">
-        <v>508</v>
-      </c>
       <c r="C168" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D168" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12663,7 +12657,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12695,16 +12689,16 @@
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>508</v>
+      </c>
+      <c r="B169" t="s">
         <v>509</v>
       </c>
-      <c r="B169" t="s">
-        <v>510</v>
-      </c>
       <c r="C169" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D169" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12725,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12757,16 +12751,16 @@
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
+        <v>510</v>
+      </c>
+      <c r="B170" t="s">
         <v>511</v>
       </c>
-      <c r="B170" t="s">
-        <v>512</v>
-      </c>
       <c r="C170" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D170" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12787,7 +12781,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12819,16 +12813,16 @@
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>512</v>
+      </c>
+      <c r="B171" t="s">
         <v>513</v>
       </c>
-      <c r="B171" t="s">
-        <v>514</v>
-      </c>
       <c r="C171" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D171" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12849,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12884,7 +12878,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12911,7 +12905,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -12929,7 +12923,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12946,7 +12940,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L173">
         <v>7</v>
@@ -12991,7 +12985,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -13008,7 +13002,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -13035,7 +13029,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L174">
         <v>5</v>
@@ -13053,7 +13047,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -13070,7 +13064,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -13097,7 +13091,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -13115,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -13132,7 +13126,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -13159,7 +13153,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -13177,7 +13171,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -13194,7 +13188,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -13221,7 +13215,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -13239,7 +13233,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -13256,7 +13250,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -13283,7 +13277,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -13301,7 +13295,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -13318,7 +13312,7 @@
         <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -13345,7 +13339,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L179">
         <v>1</v>
@@ -13363,7 +13357,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -13380,7 +13374,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -13407,7 +13401,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L180">
         <v>2</v>
@@ -13425,7 +13419,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -13439,10 +13433,10 @@
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>525</v>
+      </c>
+      <c r="B181" t="s">
         <v>526</v>
-      </c>
-      <c r="B181" t="s">
-        <v>527</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -13469,7 +13463,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -13487,7 +13481,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -13504,7 +13498,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -13531,7 +13525,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L182">
         <v>5</v>
@@ -13549,7 +13543,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13566,7 +13560,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13593,7 +13587,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L183">
         <v>5</v>
@@ -13611,7 +13605,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13628,7 +13622,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13655,7 +13649,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -13673,7 +13667,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13690,7 +13684,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13717,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L185">
         <v>3</v>
@@ -13735,7 +13729,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13752,7 +13746,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13779,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13797,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13814,7 +13808,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13829,37 +13823,37 @@
         <v>235</v>
       </c>
       <c r="G187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H187">
         <v>0</v>
       </c>
       <c r="I187">
+        <v>7</v>
+      </c>
+      <c r="J187">
         <v>6</v>
       </c>
-      <c r="J187">
-        <v>4</v>
-      </c>
       <c r="K187" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L187">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M187">
         <v>3</v>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O187">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P187" t="s">
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13876,7 +13870,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13903,7 +13897,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -13921,7 +13915,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13938,7 +13932,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13965,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13983,7 +13977,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -14000,7 +13994,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -14027,7 +14021,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -14045,7 +14039,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14059,10 +14053,10 @@
     </row>
     <row r="191" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -14089,7 +14083,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L191">
         <v>1</v>
@@ -14107,7 +14101,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -14124,7 +14118,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -14139,37 +14133,37 @@
         <v>235</v>
       </c>
       <c r="G192">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H192">
         <v>0</v>
       </c>
       <c r="I192">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J192">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K192" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L192">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M192">
         <v>8</v>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O192">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P192" t="s">
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -14186,7 +14180,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -14201,37 +14195,37 @@
         <v>240</v>
       </c>
       <c r="G193">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J193">
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L193">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M193">
         <v>17</v>
       </c>
       <c r="N193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O193">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P193" t="s">
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -14248,7 +14242,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -14275,7 +14269,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L194">
         <v>23</v>
@@ -14293,7 +14287,7 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -14310,7 +14304,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -14337,7 +14331,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -14355,7 +14349,7 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -14372,7 +14366,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -14399,7 +14393,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L196">
         <v>9</v>
@@ -14417,7 +14411,7 @@
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -14431,10 +14425,10 @@
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
+        <v>545</v>
+      </c>
+      <c r="B197" t="s">
         <v>546</v>
-      </c>
-      <c r="B197" t="s">
-        <v>547</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -14461,7 +14455,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -14479,7 +14473,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -14496,7 +14490,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -14523,7 +14517,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -14541,7 +14535,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -14558,7 +14552,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -14585,7 +14579,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -14603,7 +14597,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -14617,10 +14611,10 @@
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
+        <v>550</v>
+      </c>
+      <c r="B200" t="s">
         <v>551</v>
-      </c>
-      <c r="B200" t="s">
-        <v>552</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -14647,7 +14641,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14665,7 +14659,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14682,7 +14676,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14709,7 +14703,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14727,7 +14721,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14741,10 +14735,10 @@
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
+        <v>553</v>
+      </c>
+      <c r="B202" t="s">
         <v>554</v>
-      </c>
-      <c r="B202" t="s">
-        <v>555</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14771,7 +14765,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14789,7 +14783,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14806,7 +14800,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14833,7 +14827,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14851,7 +14845,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14865,10 +14859,10 @@
     </row>
     <row r="204" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B204" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14895,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L204">
         <v>1</v>
@@ -14913,7 +14907,7 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14930,7 +14924,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14957,7 +14951,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14975,7 +14969,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14989,10 +14983,10 @@
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
+        <v>559</v>
+      </c>
+      <c r="B206" t="s">
         <v>560</v>
-      </c>
-      <c r="B206" t="s">
-        <v>561</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -15019,7 +15013,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -15037,7 +15031,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -15051,10 +15045,10 @@
     </row>
     <row r="207" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>562</v>
+        <v>200</v>
       </c>
       <c r="B207" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -15069,37 +15063,37 @@
         <v>235</v>
       </c>
       <c r="G207">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H207">
         <v>0</v>
       </c>
       <c r="I207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207">
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P207" t="s">
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -15113,10 +15107,10 @@
     </row>
     <row r="208" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B208" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -15143,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L208">
         <v>1</v>
@@ -15161,7 +15155,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -15175,10 +15169,10 @@
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B209" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -15205,7 +15199,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -15223,7 +15217,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -15237,10 +15231,10 @@
     </row>
     <row r="210" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B210" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -15267,7 +15261,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -15285,7 +15279,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -15299,10 +15293,10 @@
     </row>
     <row r="211" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B211" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -15329,7 +15323,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L211">
         <v>1</v>
@@ -15347,7 +15341,7 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -15361,10 +15355,10 @@
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B212" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -15391,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -15409,7 +15403,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -15423,10 +15417,10 @@
     </row>
     <row r="213" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B213" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -15441,37 +15435,37 @@
         <v>240</v>
       </c>
       <c r="G213">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H213">
         <v>0</v>
       </c>
       <c r="I213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J213">
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P213" t="s">
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -15488,7 +15482,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -15515,7 +15509,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -15533,7 +15527,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15550,7 +15544,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -15577,7 +15571,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L215">
         <v>2</v>
@@ -15595,7 +15589,7 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -15609,10 +15603,10 @@
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B216" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -15639,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -15657,7 +15651,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15674,7 +15668,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -15701,7 +15695,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L217">
         <v>7</v>
@@ -15719,7 +15713,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15736,7 +15730,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -15763,7 +15757,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L218">
         <v>4</v>
@@ -15781,7 +15775,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15798,7 +15792,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15813,37 +15807,37 @@
         <v>245</v>
       </c>
       <c r="G219">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H219">
         <v>0</v>
       </c>
       <c r="I219">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J219">
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L219">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M219">
+        <v>3</v>
+      </c>
+      <c r="N219">
         <v>2</v>
       </c>
-      <c r="N219">
-        <v>1</v>
-      </c>
       <c r="O219">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P219" t="s">
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15860,7 +15854,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15887,7 +15881,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L220">
         <v>4</v>
@@ -15905,7 +15899,7 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15919,10 +15913,10 @@
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B221" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15949,7 +15943,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15967,7 +15961,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15984,7 +15978,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -16011,7 +16005,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -16029,7 +16023,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -16046,7 +16040,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -16061,37 +16055,37 @@
         <v>240</v>
       </c>
       <c r="G223">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H223">
         <v>0</v>
       </c>
       <c r="I223">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J223">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="L223">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M223">
         <v>8</v>
       </c>
       <c r="N223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O223">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P223" t="s">
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -16108,7 +16102,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -16135,7 +16129,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -16153,7 +16147,7 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -16170,7 +16164,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -16197,7 +16191,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L225">
         <v>8</v>
@@ -16215,7 +16209,7 @@
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -16232,7 +16226,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -16259,7 +16253,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -16277,7 +16271,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -16294,7 +16288,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -16321,7 +16315,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L227">
         <v>12</v>
@@ -16339,7 +16333,7 @@
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -16356,7 +16350,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -16383,7 +16377,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L228">
         <v>14</v>
@@ -16401,7 +16395,7 @@
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -16418,7 +16412,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -16433,37 +16427,37 @@
         <v>245</v>
       </c>
       <c r="G229">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H229">
         <v>0</v>
       </c>
       <c r="I229">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J229">
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L229">
+        <v>15</v>
+      </c>
+      <c r="M229">
+        <v>10</v>
+      </c>
+      <c r="N229">
+        <v>3</v>
+      </c>
+      <c r="O229">
         <v>14</v>
       </c>
-      <c r="M229">
-        <v>9</v>
-      </c>
-      <c r="N229">
-        <v>2</v>
-      </c>
-      <c r="O229">
-        <v>13</v>
-      </c>
       <c r="P229" t="s">
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -16480,7 +16474,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -16507,7 +16501,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -16525,7 +16519,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -16542,7 +16536,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -16569,7 +16563,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -16587,7 +16581,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -16628,7 +16622,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -16681,7 +16675,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L233">
         <v>5</v>
@@ -16707,10 +16701,10 @@
     </row>
     <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B234" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -16734,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -16760,10 +16754,10 @@
     </row>
     <row r="235" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B235" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C235" t="s">
         <v>120</v>
@@ -16787,7 +16781,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -16813,10 +16807,10 @@
     </row>
     <row r="236" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B236" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C236" t="s">
         <v>120</v>
@@ -16840,7 +16834,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L236">
         <v>1</v>
@@ -16893,7 +16887,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -16919,10 +16913,10 @@
     </row>
     <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B238" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -16946,7 +16940,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -16972,10 +16966,10 @@
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B239" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -16999,7 +16993,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -17025,10 +17019,10 @@
     </row>
     <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B240" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C240" t="s">
         <v>120</v>
@@ -17052,7 +17046,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -17105,7 +17099,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -17131,10 +17125,10 @@
     </row>
     <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B242" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C242" t="s">
         <v>120</v>
@@ -17158,7 +17152,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -17184,10 +17178,10 @@
     </row>
     <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B243" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C243" t="s">
         <v>120</v>
@@ -17211,7 +17205,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -17237,10 +17231,10 @@
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B244" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -17264,7 +17258,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -17317,7 +17311,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L245">
         <v>2</v>
@@ -17370,7 +17364,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -17423,7 +17417,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L247">
         <v>2</v>
@@ -17449,16 +17443,16 @@
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B248" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
       </c>
       <c r="D248" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E248" t="s">
         <v>122</v>
@@ -17476,7 +17470,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -17502,16 +17496,16 @@
     </row>
     <row r="249" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B249" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C249" t="s">
         <v>120</v>
       </c>
       <c r="D249" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E249" t="s">
         <v>122</v>
@@ -17529,7 +17523,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L249">
         <v>1</v>
@@ -17555,16 +17549,16 @@
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B250" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
       </c>
       <c r="D250" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E250" t="s">
         <v>122</v>
@@ -17582,7 +17576,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -17608,16 +17602,16 @@
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B251" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
       </c>
       <c r="D251" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E251" t="s">
         <v>122</v>
@@ -17635,7 +17629,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -17688,7 +17682,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L252">
         <v>1</v>
@@ -17741,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L253">
         <v>2</v>
@@ -17794,7 +17788,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -17847,7 +17841,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -17900,7 +17894,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L256">
         <v>5</v>
@@ -17926,10 +17920,10 @@
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B257" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C257" t="s">
         <v>120</v>
@@ -17953,7 +17947,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -18006,7 +18000,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L258">
         <v>3</v>
@@ -18032,10 +18026,10 @@
     </row>
     <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B259" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C259" t="s">
         <v>120</v>
@@ -18059,7 +18053,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -18088,7 +18082,7 @@
         <v>176</v>
       </c>
       <c r="B260" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C260" t="s">
         <v>177</v>
@@ -18100,7 +18094,7 @@
         <v>122</v>
       </c>
       <c r="F260" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G260">
         <v>1987</v>
@@ -18112,7 +18106,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L260">
         <v>13</v>
@@ -18138,10 +18132,10 @@
     </row>
     <row r="261" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B261" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C261" t="s">
         <v>177</v>
@@ -18165,7 +18159,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -18191,10 +18185,10 @@
     </row>
     <row r="262" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B262" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C262" t="s">
         <v>177</v>
@@ -18206,7 +18200,7 @@
         <v>122</v>
       </c>
       <c r="F262" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G262">
         <v>5988</v>
@@ -18218,7 +18212,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L262">
         <v>12</v>
@@ -18244,10 +18238,10 @@
     </row>
     <row r="263" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B263" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C263" t="s">
         <v>177</v>
@@ -18259,7 +18253,7 @@
         <v>122</v>
       </c>
       <c r="F263" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G263">
         <v>1988</v>
@@ -18271,7 +18265,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L263">
         <v>12</v>
@@ -18302,8 +18296,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1491D8-0F5E-492E-8165-3D8448B8A03B}">
-  <dimension ref="A1:J518"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5071C80F-2A89-4649-8313-C9C1C19F7C0E}">
+  <dimension ref="A1:J533"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -31859,7 +31853,7 @@
         <v>53</v>
       </c>
       <c r="F424" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="G424">
         <v>240</v>
@@ -33520,7 +33514,7 @@
         <v>49</v>
       </c>
       <c r="E476" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="F476" t="s">
         <v>94</v>
@@ -33552,7 +33546,7 @@
         <v>38</v>
       </c>
       <c r="E477" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="F477" t="s">
         <v>94</v>
@@ -33584,7 +33578,7 @@
         <v>25</v>
       </c>
       <c r="E478" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
       <c r="F478" t="s">
         <v>94</v>
@@ -33616,7 +33610,7 @@
         <v>140</v>
       </c>
       <c r="E479" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F479" t="s">
         <v>94</v>
@@ -33671,7 +33665,7 @@
         <v>46231</v>
       </c>
       <c r="B481" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C481" t="s">
         <v>24</v>
@@ -33680,7 +33674,7 @@
         <v>93</v>
       </c>
       <c r="E481" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="F481" t="s">
         <v>94</v>
@@ -33712,7 +33706,7 @@
         <v>21</v>
       </c>
       <c r="E482" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="F482" t="s">
         <v>94</v>
@@ -33744,7 +33738,7 @@
         <v>49</v>
       </c>
       <c r="E483" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="F483" t="s">
         <v>66</v>
@@ -33776,7 +33770,7 @@
         <v>90</v>
       </c>
       <c r="E484" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="F484" t="s">
         <v>66</v>
@@ -33808,7 +33802,7 @@
         <v>49</v>
       </c>
       <c r="E485" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="F485" t="s">
         <v>94</v>
@@ -33895,13 +33889,13 @@
         <v>46231</v>
       </c>
       <c r="B488" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C488" t="s">
         <v>120</v>
       </c>
       <c r="D488" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E488" t="s">
         <v>133</v>
@@ -33959,7 +33953,7 @@
         <v>46232</v>
       </c>
       <c r="B490" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C490" t="s">
         <v>177</v>
@@ -33968,13 +33962,13 @@
         <v>178</v>
       </c>
       <c r="E490" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F490" t="s">
         <v>94</v>
       </c>
       <c r="G490" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H490" t="s">
         <v>122</v>
@@ -33991,7 +33985,7 @@
         <v>46232</v>
       </c>
       <c r="B491" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C491" t="s">
         <v>177</v>
@@ -34000,13 +33994,13 @@
         <v>178</v>
       </c>
       <c r="E491" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F491" t="s">
         <v>94</v>
       </c>
       <c r="G491" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H491" t="s">
         <v>122</v>
@@ -34023,7 +34017,7 @@
         <v>46232</v>
       </c>
       <c r="B492" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C492" t="s">
         <v>177</v>
@@ -34032,13 +34026,13 @@
         <v>178</v>
       </c>
       <c r="E492" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F492" t="s">
         <v>94</v>
       </c>
       <c r="G492" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H492" t="s">
         <v>122</v>
@@ -34055,7 +34049,7 @@
         <v>46232</v>
       </c>
       <c r="B493" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C493" t="s">
         <v>177</v>
@@ -34064,13 +34058,13 @@
         <v>178</v>
       </c>
       <c r="E493" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F493" t="s">
         <v>94</v>
       </c>
       <c r="G493" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H493" t="s">
         <v>122</v>
@@ -34087,7 +34081,7 @@
         <v>46232</v>
       </c>
       <c r="B494" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C494" t="s">
         <v>177</v>
@@ -34096,13 +34090,13 @@
         <v>178</v>
       </c>
       <c r="E494" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F494" t="s">
         <v>94</v>
       </c>
       <c r="G494" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H494" t="s">
         <v>122</v>
@@ -34119,7 +34113,7 @@
         <v>46232</v>
       </c>
       <c r="B495" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C495" t="s">
         <v>177</v>
@@ -34128,13 +34122,13 @@
         <v>178</v>
       </c>
       <c r="E495" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F495" t="s">
         <v>94</v>
       </c>
       <c r="G495" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H495" t="s">
         <v>122</v>
@@ -34160,13 +34154,13 @@
         <v>178</v>
       </c>
       <c r="E496" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F496" t="s">
         <v>94</v>
       </c>
       <c r="G496" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H496" t="s">
         <v>122</v>
@@ -34192,13 +34186,13 @@
         <v>178</v>
       </c>
       <c r="E497" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F497" t="s">
         <v>94</v>
       </c>
       <c r="G497" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H497" t="s">
         <v>122</v>
@@ -34224,13 +34218,13 @@
         <v>178</v>
       </c>
       <c r="E498" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F498" t="s">
         <v>94</v>
       </c>
       <c r="G498" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H498" t="s">
         <v>122</v>
@@ -34256,7 +34250,7 @@
         <v>12</v>
       </c>
       <c r="E499" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F499" t="s">
         <v>94</v>
@@ -34343,7 +34337,7 @@
         <v>46232</v>
       </c>
       <c r="B502" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C502" t="s">
         <v>24</v>
@@ -34439,7 +34433,7 @@
         <v>46232</v>
       </c>
       <c r="B505" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C505" t="s">
         <v>24</v>
@@ -34503,7 +34497,7 @@
         <v>46232</v>
       </c>
       <c r="B507" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C507" t="s">
         <v>120</v>
@@ -34599,7 +34593,7 @@
         <v>46232</v>
       </c>
       <c r="B510" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C510" t="s">
         <v>24</v>
@@ -34759,7 +34753,7 @@
         <v>46232</v>
       </c>
       <c r="B515" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C515" t="s">
         <v>24</v>
@@ -34791,7 +34785,7 @@
         <v>46232</v>
       </c>
       <c r="B516" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C516" t="s">
         <v>24</v>
@@ -34880,6 +34874,486 @@
       </c>
       <c r="J518" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A519" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B519" t="s">
+        <v>43</v>
+      </c>
+      <c r="C519" t="s">
+        <v>24</v>
+      </c>
+      <c r="D519" t="s">
+        <v>40</v>
+      </c>
+      <c r="E519" t="s">
+        <v>100</v>
+      </c>
+      <c r="F519" t="s">
+        <v>94</v>
+      </c>
+      <c r="G519">
+        <v>235</v>
+      </c>
+      <c r="H519" t="s">
+        <v>22</v>
+      </c>
+      <c r="I519">
+        <v>1</v>
+      </c>
+      <c r="J519" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A520" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B520" t="s">
+        <v>39</v>
+      </c>
+      <c r="C520" t="s">
+        <v>24</v>
+      </c>
+      <c r="D520" t="s">
+        <v>40</v>
+      </c>
+      <c r="E520" t="s">
+        <v>100</v>
+      </c>
+      <c r="F520" t="s">
+        <v>94</v>
+      </c>
+      <c r="G520">
+        <v>235</v>
+      </c>
+      <c r="H520" t="s">
+        <v>22</v>
+      </c>
+      <c r="I520">
+        <v>1</v>
+      </c>
+      <c r="J520" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="521" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A521" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B521" t="s">
+        <v>200</v>
+      </c>
+      <c r="C521" t="s">
+        <v>24</v>
+      </c>
+      <c r="D521" t="s">
+        <v>47</v>
+      </c>
+      <c r="E521" t="s">
+        <v>100</v>
+      </c>
+      <c r="F521" t="s">
+        <v>66</v>
+      </c>
+      <c r="G521">
+        <v>235</v>
+      </c>
+      <c r="H521" t="s">
+        <v>22</v>
+      </c>
+      <c r="I521">
+        <v>1</v>
+      </c>
+      <c r="J521" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A522" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B522" t="s">
+        <v>50</v>
+      </c>
+      <c r="C522" t="s">
+        <v>24</v>
+      </c>
+      <c r="D522" t="s">
+        <v>49</v>
+      </c>
+      <c r="E522" t="s">
+        <v>100</v>
+      </c>
+      <c r="F522" t="s">
+        <v>66</v>
+      </c>
+      <c r="G522">
+        <v>245</v>
+      </c>
+      <c r="H522" t="s">
+        <v>22</v>
+      </c>
+      <c r="I522">
+        <v>1</v>
+      </c>
+      <c r="J522" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A523" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B523" t="s">
+        <v>32</v>
+      </c>
+      <c r="C523" t="s">
+        <v>24</v>
+      </c>
+      <c r="D523" t="s">
+        <v>33</v>
+      </c>
+      <c r="E523" t="s">
+        <v>100</v>
+      </c>
+      <c r="F523" t="s">
+        <v>94</v>
+      </c>
+      <c r="G523">
+        <v>265</v>
+      </c>
+      <c r="H523" t="s">
+        <v>15</v>
+      </c>
+      <c r="I523">
+        <v>1</v>
+      </c>
+      <c r="J523" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A524" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B524" t="s">
+        <v>199</v>
+      </c>
+      <c r="C524" t="s">
+        <v>24</v>
+      </c>
+      <c r="D524" t="s">
+        <v>47</v>
+      </c>
+      <c r="E524" t="s">
+        <v>100</v>
+      </c>
+      <c r="F524" t="s">
+        <v>66</v>
+      </c>
+      <c r="G524">
+        <v>240</v>
+      </c>
+      <c r="H524" t="s">
+        <v>22</v>
+      </c>
+      <c r="I524">
+        <v>1</v>
+      </c>
+      <c r="J524" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A525" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B525" t="s">
+        <v>82</v>
+      </c>
+      <c r="C525" t="s">
+        <v>18</v>
+      </c>
+      <c r="D525" t="s">
+        <v>21</v>
+      </c>
+      <c r="E525" t="s">
+        <v>100</v>
+      </c>
+      <c r="F525" t="s">
+        <v>94</v>
+      </c>
+      <c r="G525">
+        <v>235</v>
+      </c>
+      <c r="H525" t="s">
+        <v>22</v>
+      </c>
+      <c r="I525">
+        <v>1</v>
+      </c>
+      <c r="J525" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A526" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B526" t="s">
+        <v>103</v>
+      </c>
+      <c r="C526" t="s">
+        <v>24</v>
+      </c>
+      <c r="D526" t="s">
+        <v>49</v>
+      </c>
+      <c r="E526" t="s">
+        <v>100</v>
+      </c>
+      <c r="F526" t="s">
+        <v>66</v>
+      </c>
+      <c r="G526">
+        <v>245</v>
+      </c>
+      <c r="H526" t="s">
+        <v>22</v>
+      </c>
+      <c r="I526">
+        <v>1</v>
+      </c>
+      <c r="J526" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A527" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B527" t="s">
+        <v>104</v>
+      </c>
+      <c r="C527" t="s">
+        <v>18</v>
+      </c>
+      <c r="D527" t="s">
+        <v>90</v>
+      </c>
+      <c r="E527" t="s">
+        <v>100</v>
+      </c>
+      <c r="F527" t="s">
+        <v>94</v>
+      </c>
+      <c r="G527">
+        <v>250</v>
+      </c>
+      <c r="H527" t="s">
+        <v>22</v>
+      </c>
+      <c r="I527">
+        <v>1</v>
+      </c>
+      <c r="J527" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="528" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A528" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B528" t="s">
+        <v>162</v>
+      </c>
+      <c r="C528" t="s">
+        <v>18</v>
+      </c>
+      <c r="D528" t="s">
+        <v>90</v>
+      </c>
+      <c r="E528" t="s">
+        <v>53</v>
+      </c>
+      <c r="F528" t="s">
+        <v>94</v>
+      </c>
+      <c r="G528">
+        <v>255</v>
+      </c>
+      <c r="H528" t="s">
+        <v>22</v>
+      </c>
+      <c r="I528">
+        <v>1</v>
+      </c>
+      <c r="J528" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="529" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A529" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B529" t="s">
+        <v>82</v>
+      </c>
+      <c r="C529" t="s">
+        <v>18</v>
+      </c>
+      <c r="D529" t="s">
+        <v>21</v>
+      </c>
+      <c r="E529" t="s">
+        <v>53</v>
+      </c>
+      <c r="F529" t="s">
+        <v>94</v>
+      </c>
+      <c r="G529">
+        <v>235</v>
+      </c>
+      <c r="H529" t="s">
+        <v>22</v>
+      </c>
+      <c r="I529">
+        <v>1</v>
+      </c>
+      <c r="J529" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="530" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A530" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B530" t="s">
+        <v>67</v>
+      </c>
+      <c r="C530" t="s">
+        <v>24</v>
+      </c>
+      <c r="D530" t="s">
+        <v>40</v>
+      </c>
+      <c r="E530" t="s">
+        <v>53</v>
+      </c>
+      <c r="F530" t="s">
+        <v>94</v>
+      </c>
+      <c r="G530">
+        <v>240</v>
+      </c>
+      <c r="H530" t="s">
+        <v>22</v>
+      </c>
+      <c r="I530">
+        <v>1</v>
+      </c>
+      <c r="J530" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="531" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A531" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B531" t="s">
+        <v>86</v>
+      </c>
+      <c r="C531" t="s">
+        <v>24</v>
+      </c>
+      <c r="D531" t="s">
+        <v>49</v>
+      </c>
+      <c r="E531" t="s">
+        <v>53</v>
+      </c>
+      <c r="F531" t="s">
+        <v>94</v>
+      </c>
+      <c r="G531">
+        <v>240</v>
+      </c>
+      <c r="H531" t="s">
+        <v>22</v>
+      </c>
+      <c r="I531">
+        <v>1</v>
+      </c>
+      <c r="J531" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A532" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B532" t="s">
+        <v>74</v>
+      </c>
+      <c r="C532" t="s">
+        <v>18</v>
+      </c>
+      <c r="D532" t="s">
+        <v>21</v>
+      </c>
+      <c r="E532" t="s">
+        <v>53</v>
+      </c>
+      <c r="F532" t="s">
+        <v>94</v>
+      </c>
+      <c r="G532">
+        <v>245</v>
+      </c>
+      <c r="H532" t="s">
+        <v>22</v>
+      </c>
+      <c r="I532">
+        <v>1</v>
+      </c>
+      <c r="J532" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A533" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B533" t="s">
+        <v>107</v>
+      </c>
+      <c r="C533" t="s">
+        <v>24</v>
+      </c>
+      <c r="D533" t="s">
+        <v>38</v>
+      </c>
+      <c r="E533" t="s">
+        <v>53</v>
+      </c>
+      <c r="F533" t="s">
+        <v>94</v>
+      </c>
+      <c r="G533">
+        <v>270</v>
+      </c>
+      <c r="H533" t="s">
+        <v>15</v>
+      </c>
+      <c r="I533">
+        <v>1</v>
+      </c>
+      <c r="J533" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B169714-12E6-4C9B-8DF6-435CE74DECCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAEA74A2-967C-4A97-B139-4724C30D98CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{02046495-837B-4CA9-A279-0E291960FFFC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{A571B92E-D843-4FFC-8EEE-99D4ACAEA14F}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5768" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="614">
   <si>
     <t>날짜</t>
   </si>
@@ -645,6 +645,15 @@
     <t>DPW771-BK235</t>
   </si>
   <si>
+    <t>BTG-11120</t>
+  </si>
+  <si>
+    <t>X-10H-MAGG</t>
+  </si>
+  <si>
+    <t>DPW771-BK250</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1740,9 +1749,6 @@
     <t>DPW771BK 바오지 여성 러닝화 블랙 245</t>
   </si>
   <si>
-    <t>DPW771-BK250</t>
-  </si>
-  <si>
     <t>DPW771BK 바오지 여성 러닝화 블랙 250</t>
   </si>
   <si>
@@ -1833,9 +1839,6 @@
     <t>X-10H-MAGC</t>
   </si>
   <si>
-    <t>X-10H-MAGG</t>
-  </si>
-  <si>
     <t>X-20FS-MAGC</t>
   </si>
   <si>
@@ -1870,9 +1873,6 @@
   </si>
   <si>
     <t>볼트겔 클리어겔 롤형 테이프 1m</t>
-  </si>
-  <si>
-    <t>BTG-11120</t>
   </si>
   <si>
     <t>볼트겔 클리어겔 롤형 테이프 1.5m</t>
@@ -2267,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73761355-B4E7-4C82-9D2A-9AD267F1974F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A0DDC4-D06F-4887-B9A8-F41B5C4DEB78}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2276,7 +2276,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2291,46 +2291,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="R1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="S1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="T1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2338,7 +2338,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2365,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2383,7 +2383,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2400,7 +2400,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>4</v>
@@ -2445,7 +2445,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2507,7 +2507,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2524,7 +2524,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2569,7 +2569,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2586,7 +2586,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2631,7 +2631,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2648,7 +2648,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2675,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2755,7 +2755,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2772,7 +2772,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2817,7 +2817,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2879,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2941,7 +2941,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2955,16 +2955,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B12" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C12" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D12" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3017,16 +3017,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C13" t="s">
         <v>233</v>
       </c>
-      <c r="C13" t="s">
-        <v>230</v>
-      </c>
       <c r="D13" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3079,16 +3079,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" t="s">
         <v>234</v>
-      </c>
-      <c r="B14" t="s">
-        <v>235</v>
-      </c>
-      <c r="C14" t="s">
-        <v>230</v>
-      </c>
-      <c r="D14" t="s">
-        <v>231</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3141,16 +3141,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D15" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3203,16 +3203,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B16" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C16" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D16" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3265,16 +3265,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C17" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3327,16 +3327,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C18" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D18" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3389,16 +3389,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B19" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C19" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D19" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3451,16 +3451,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B20" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C20" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D20" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3513,16 +3513,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C21" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D21" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3575,16 +3575,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C22" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D22" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3637,16 +3637,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B23" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C23" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D23" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3699,16 +3699,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D24" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3761,16 +3761,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D25" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3823,16 +3823,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C26" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D26" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3885,16 +3885,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C27" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D27" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3947,16 +3947,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C28" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D28" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3977,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4009,16 +4009,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C29" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D29" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4039,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4071,16 +4071,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C30" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D30" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4101,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4133,16 +4133,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C31" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D31" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4195,16 +4195,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C32" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D32" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4257,16 +4257,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C33" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D33" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4319,16 +4319,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" t="s">
+        <v>279</v>
+      </c>
+      <c r="C34" t="s">
+        <v>233</v>
+      </c>
+      <c r="D34" t="s">
         <v>275</v>
-      </c>
-      <c r="B34" t="s">
-        <v>276</v>
-      </c>
-      <c r="C34" t="s">
-        <v>230</v>
-      </c>
-      <c r="D34" t="s">
-        <v>272</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4381,16 +4381,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C35" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D35" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4411,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4443,16 +4443,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C36" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D36" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4505,16 +4505,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C37" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D37" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4567,16 +4567,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C38" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D38" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4597,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4629,16 +4629,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C39" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D39" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4691,16 +4691,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C40" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D40" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4721,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4753,16 +4753,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B41" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C41" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D41" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4815,16 +4815,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B42" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C42" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D42" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4877,16 +4877,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B43" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C43" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D43" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4939,16 +4939,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B44" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C44" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D44" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5001,16 +5001,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B45" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C45" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D45" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5031,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5063,16 +5063,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B46" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D46" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5125,16 +5125,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B47" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C47" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D47" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5187,16 +5187,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B48" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C48" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D48" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5249,16 +5249,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B49" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C49" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D49" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5279,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5311,16 +5311,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B50" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C50" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D50" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5373,16 +5373,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B51" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C51" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D51" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5403,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5435,16 +5435,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B52" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C52" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5465,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5497,16 +5497,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C53" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5559,16 +5559,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>319</v>
+      </c>
+      <c r="B54" t="s">
+        <v>320</v>
+      </c>
+      <c r="C54" t="s">
+        <v>233</v>
+      </c>
+      <c r="D54" t="s">
         <v>316</v>
-      </c>
-      <c r="B54" t="s">
-        <v>317</v>
-      </c>
-      <c r="C54" t="s">
-        <v>230</v>
-      </c>
-      <c r="D54" t="s">
-        <v>313</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5589,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5621,16 +5621,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B55" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C55" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5683,16 +5683,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B56" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C56" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D56" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5713,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5745,16 +5745,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B57" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C57" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D57" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5807,16 +5807,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C58" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D58" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5837,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5869,16 +5869,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C59" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D59" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5931,16 +5931,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C60" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D60" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5961,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5993,16 +5993,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B61" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C61" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D61" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6023,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6055,16 +6055,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B62" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C62" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D62" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6085,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6117,16 +6117,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B63" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C63" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D63" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6147,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6179,16 +6179,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B64" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C64" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D64" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6209,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6241,16 +6241,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B65" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C65" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D65" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6271,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6303,16 +6303,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B66" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C66" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D66" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6368,7 +6368,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6395,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6413,7 +6413,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6457,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L68">
         <v>3</v>
@@ -6475,7 +6475,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6492,7 +6492,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6519,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L69">
         <v>9</v>
@@ -6537,7 +6537,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6554,7 +6554,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6581,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6599,7 +6599,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6616,7 +6616,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6643,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6661,7 +6661,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6675,10 +6675,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B72" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6705,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6723,7 +6723,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6767,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6785,7 +6785,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6799,10 +6799,10 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B74" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6864,7 +6864,7 @@
         <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6909,7 +6909,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6923,10 +6923,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B76" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6988,7 +6988,7 @@
         <v>184</v>
       </c>
       <c r="B77" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -7033,7 +7033,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7047,10 +7047,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B78" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7077,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B79" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7157,7 +7157,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7201,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7219,7 +7219,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7233,10 +7233,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B81" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -7281,7 +7281,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B82" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7325,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7343,7 +7343,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7357,10 +7357,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B83" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7419,10 +7419,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B84" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7449,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7467,7 +7467,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7481,10 +7481,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B85" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7529,7 +7529,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7543,10 +7543,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B86" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7591,7 +7591,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7605,10 +7605,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B87" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7635,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7653,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7670,7 +7670,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7697,7 +7697,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -7715,7 +7715,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7729,10 +7729,10 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B89" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7759,7 +7759,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -7777,7 +7777,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7794,7 +7794,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7821,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L90">
         <v>2</v>
@@ -7839,7 +7839,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7853,10 +7853,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B91" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7901,7 +7901,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7915,10 +7915,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B92" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7945,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7963,7 +7963,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7980,7 +7980,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -8007,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8025,7 +8025,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8039,10 +8039,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B94" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8087,7 +8087,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8101,10 +8101,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B95" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8131,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8149,7 +8149,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B96" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8225,10 +8225,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B97" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8255,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8273,7 +8273,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8290,7 +8290,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8317,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L98">
         <v>5</v>
@@ -8335,7 +8335,7 @@
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8352,7 +8352,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8367,37 +8367,37 @@
         <v>270</v>
       </c>
       <c r="G99">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H99">
         <v>0</v>
       </c>
       <c r="I99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M99">
         <v>0</v>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P99" t="s">
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8414,7 +8414,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8459,7 +8459,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8473,10 +8473,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B101" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8521,7 +8521,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B102" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8565,7 +8565,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8583,7 +8583,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8597,10 +8597,10 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B103" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8627,7 +8627,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -8645,7 +8645,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8662,7 +8662,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8689,7 +8689,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8707,7 +8707,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8721,10 +8721,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B105" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8751,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8769,7 +8769,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8786,7 +8786,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8813,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8831,7 +8831,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8845,10 +8845,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B107" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8893,7 +8893,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8910,7 +8910,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8955,7 +8955,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8972,7 +8972,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -8999,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -9017,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -9031,10 +9031,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B110" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -9061,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -9079,7 +9079,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -9093,10 +9093,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B111" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -9123,7 +9123,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9141,7 +9141,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9158,7 +9158,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9185,7 +9185,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9203,7 +9203,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9220,7 +9220,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9247,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L113">
         <v>6</v>
@@ -9265,7 +9265,7 @@
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9282,7 +9282,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9309,7 +9309,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L114">
         <v>9</v>
@@ -9327,7 +9327,7 @@
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9344,7 +9344,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9371,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9389,7 +9389,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9406,7 +9406,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L116">
         <v>3</v>
@@ -9451,7 +9451,7 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9468,7 +9468,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9495,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9513,7 +9513,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9530,7 +9530,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9557,7 +9557,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9575,7 +9575,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9589,10 +9589,10 @@
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B119" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9619,7 +9619,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -9637,7 +9637,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9654,7 +9654,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9681,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9699,7 +9699,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9716,7 +9716,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9731,37 +9731,37 @@
         <v>280</v>
       </c>
       <c r="G121">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H121">
         <v>0</v>
       </c>
       <c r="I121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M121">
         <v>1</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P121" t="s">
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9805,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L122">
         <v>5</v>
@@ -9823,7 +9823,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9840,7 +9840,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9867,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -9885,7 +9885,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9902,7 +9902,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9929,7 +9929,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L124">
         <v>2</v>
@@ -9947,7 +9947,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9964,7 +9964,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9991,7 +9991,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -10009,7 +10009,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -10053,7 +10053,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -10071,7 +10071,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -10088,7 +10088,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -10115,7 +10115,7 @@
         <v>8</v>
       </c>
       <c r="K127" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L127">
         <v>9</v>
@@ -10133,7 +10133,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -10150,7 +10150,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -10165,37 +10165,37 @@
         <v>240</v>
       </c>
       <c r="G128">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J128">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K128" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L128">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M128">
         <v>11</v>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O128">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P128" t="s">
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -10212,7 +10212,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10239,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L129">
         <v>9</v>
@@ -10257,7 +10257,7 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10274,7 +10274,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10301,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10319,7 +10319,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10336,7 +10336,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10363,7 +10363,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10381,7 +10381,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10398,7 +10398,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10425,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L132">
         <v>18</v>
@@ -10434,7 +10434,7 @@
         <v>10</v>
       </c>
       <c r="N132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132">
         <v>14</v>
@@ -10443,7 +10443,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10460,7 +10460,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10487,7 +10487,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L133">
         <v>10</v>
@@ -10505,7 +10505,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10522,7 +10522,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10549,7 +10549,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L134">
         <v>16</v>
@@ -10567,7 +10567,7 @@
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10584,7 +10584,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10611,7 +10611,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10629,7 +10629,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10646,7 +10646,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10673,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10691,7 +10691,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10723,37 +10723,37 @@
         <v>235</v>
       </c>
       <c r="G137">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H137">
         <v>0</v>
       </c>
       <c r="I137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J137">
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M137">
         <v>0</v>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P137" t="s">
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10770,7 +10770,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10797,7 +10797,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L138">
         <v>4</v>
@@ -10806,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="N138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O138">
         <v>4</v>
@@ -10815,7 +10815,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10832,7 +10832,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10859,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L139">
         <v>2</v>
@@ -10877,7 +10877,7 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10894,7 +10894,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L140">
         <v>3</v>
@@ -10939,7 +10939,7 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10956,7 +10956,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10971,37 +10971,37 @@
         <v>255</v>
       </c>
       <c r="G141">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H141">
         <v>0</v>
       </c>
       <c r="I141">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L141">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M141">
         <v>0</v>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O141">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P141" t="s">
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -11018,7 +11018,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -11045,7 +11045,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -11063,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -11080,7 +11080,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -11107,7 +11107,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -11125,7 +11125,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -11142,7 +11142,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -11169,7 +11169,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -11187,7 +11187,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -11201,10 +11201,10 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B145" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -11231,7 +11231,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -11249,7 +11249,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -11263,10 +11263,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B146" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -11293,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -11311,7 +11311,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -11328,7 +11328,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11343,37 +11343,37 @@
         <v>235</v>
       </c>
       <c r="G147">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M147">
         <v>0</v>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P147" t="s">
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11390,7 +11390,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11417,7 +11417,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L148">
         <v>6</v>
@@ -11435,7 +11435,7 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11452,7 +11452,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11479,7 +11479,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11497,7 +11497,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11514,7 +11514,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11541,7 +11541,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11559,7 +11559,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11576,7 +11576,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11603,7 +11603,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -11621,7 +11621,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11635,16 +11635,16 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B152" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C152" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D152" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11665,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11697,16 +11697,16 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B153" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C153" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D153" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11727,7 +11727,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11759,16 +11759,16 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>481</v>
+      </c>
+      <c r="B154" t="s">
+        <v>482</v>
+      </c>
+      <c r="C154" t="s">
+        <v>233</v>
+      </c>
+      <c r="D154" t="s">
         <v>478</v>
-      </c>
-      <c r="B154" t="s">
-        <v>479</v>
-      </c>
-      <c r="C154" t="s">
-        <v>230</v>
-      </c>
-      <c r="D154" t="s">
-        <v>475</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11789,7 +11789,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11821,16 +11821,16 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B155" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C155" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D155" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11851,7 +11851,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11883,16 +11883,16 @@
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B156" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C156" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D156" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11913,7 +11913,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11945,16 +11945,16 @@
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B157" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C157" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D157" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11975,7 +11975,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -12007,16 +12007,16 @@
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B158" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C158" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D158" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -12037,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -12069,16 +12069,16 @@
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B159" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C159" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D159" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -12099,7 +12099,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -12131,16 +12131,16 @@
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B160" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C160" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D160" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -12161,7 +12161,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -12193,16 +12193,16 @@
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B161" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C161" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D161" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -12223,7 +12223,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -12255,16 +12255,16 @@
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B162" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C162" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D162" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -12285,7 +12285,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -12317,16 +12317,16 @@
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B163" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C163" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D163" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -12347,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -12379,16 +12379,16 @@
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B164" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C164" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D164" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -12409,7 +12409,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -12441,16 +12441,16 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B165" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C165" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D165" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12503,16 +12503,16 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B166" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C166" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D166" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12533,7 +12533,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12565,16 +12565,16 @@
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B167" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C167" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D167" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12595,7 +12595,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12627,16 +12627,16 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B168" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C168" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D168" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12657,7 +12657,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12689,16 +12689,16 @@
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B169" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C169" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D169" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12719,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12751,16 +12751,16 @@
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B170" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C170" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D170" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12781,7 +12781,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12813,16 +12813,16 @@
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B171" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C171" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D171" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12878,7 +12878,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12905,7 +12905,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -12923,7 +12923,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12940,7 +12940,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12967,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L173">
         <v>7</v>
@@ -12985,7 +12985,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -13002,7 +13002,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -13029,7 +13029,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L174">
         <v>5</v>
@@ -13047,7 +13047,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -13064,7 +13064,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -13091,7 +13091,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -13109,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -13126,7 +13126,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -13153,7 +13153,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -13171,7 +13171,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -13188,7 +13188,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -13215,7 +13215,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -13233,7 +13233,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -13250,7 +13250,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -13277,7 +13277,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -13295,7 +13295,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -13312,7 +13312,7 @@
         <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -13327,37 +13327,37 @@
         <v>245</v>
       </c>
       <c r="G179">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H179">
         <v>0</v>
       </c>
       <c r="I179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J179">
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M179">
         <v>0</v>
       </c>
       <c r="N179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P179" t="s">
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -13401,7 +13401,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L180">
         <v>2</v>
@@ -13419,7 +13419,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -13433,10 +13433,10 @@
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B181" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -13463,7 +13463,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -13481,7 +13481,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -13498,7 +13498,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -13525,7 +13525,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L182">
         <v>5</v>
@@ -13543,7 +13543,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13587,7 +13587,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L183">
         <v>5</v>
@@ -13605,7 +13605,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13622,7 +13622,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13649,7 +13649,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -13667,7 +13667,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13684,7 +13684,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13699,37 +13699,37 @@
         <v>250</v>
       </c>
       <c r="G185">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H185">
         <v>0</v>
       </c>
       <c r="I185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J185">
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M185">
         <v>1</v>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P185" t="s">
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13746,7 +13746,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13773,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13791,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13808,7 +13808,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13835,7 +13835,7 @@
         <v>6</v>
       </c>
       <c r="K187" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L187">
         <v>9</v>
@@ -13853,7 +13853,7 @@
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13870,7 +13870,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13897,7 +13897,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13932,7 +13932,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13959,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13977,7 +13977,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -13994,7 +13994,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -14021,7 +14021,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -14030,7 +14030,7 @@
         <v>7</v>
       </c>
       <c r="N190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O190">
         <v>8</v>
@@ -14039,7 +14039,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14056,7 +14056,7 @@
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -14083,7 +14083,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L191">
         <v>1</v>
@@ -14101,7 +14101,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -14118,7 +14118,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -14145,7 +14145,7 @@
         <v>9</v>
       </c>
       <c r="K192" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L192">
         <v>13</v>
@@ -14163,7 +14163,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -14180,7 +14180,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -14195,37 +14195,37 @@
         <v>240</v>
       </c>
       <c r="G193">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J193">
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L193">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M193">
         <v>17</v>
       </c>
       <c r="N193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O193">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P193" t="s">
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -14242,7 +14242,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -14269,7 +14269,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L194">
         <v>23</v>
@@ -14278,7 +14278,7 @@
         <v>14</v>
       </c>
       <c r="N194">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O194">
         <v>19</v>
@@ -14287,7 +14287,7 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -14304,7 +14304,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -14331,7 +14331,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L195">
         <v>11</v>
@@ -14349,7 +14349,7 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -14366,7 +14366,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -14393,7 +14393,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L196">
         <v>9</v>
@@ -14411,7 +14411,7 @@
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -14425,10 +14425,10 @@
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B197" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -14455,7 +14455,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -14473,7 +14473,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -14517,7 +14517,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -14535,7 +14535,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -14552,7 +14552,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -14579,7 +14579,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -14597,7 +14597,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -14611,10 +14611,10 @@
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B200" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -14641,7 +14641,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14676,7 +14676,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14703,7 +14703,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14721,7 +14721,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14735,10 +14735,10 @@
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B202" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14765,7 +14765,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14783,7 +14783,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14800,7 +14800,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14827,7 +14827,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14845,7 +14845,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14862,7 +14862,7 @@
         <v>195</v>
       </c>
       <c r="B204" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L204">
         <v>1</v>
@@ -14907,7 +14907,7 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14924,7 +14924,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14951,7 +14951,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14969,7 +14969,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14983,10 +14983,10 @@
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B206" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -15013,7 +15013,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -15031,7 +15031,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -15048,7 +15048,7 @@
         <v>200</v>
       </c>
       <c r="B207" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -15075,7 +15075,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L207">
         <v>1</v>
@@ -15093,7 +15093,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>197</v>
       </c>
       <c r="B208" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L208">
         <v>1</v>
@@ -15155,7 +15155,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -15169,10 +15169,10 @@
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B209" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -15199,7 +15199,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -15231,10 +15231,10 @@
     </row>
     <row r="210" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>566</v>
+        <v>203</v>
       </c>
       <c r="B210" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -15249,37 +15249,37 @@
         <v>250</v>
       </c>
       <c r="G210">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H210">
         <v>0</v>
       </c>
       <c r="I210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J210">
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210">
         <v>0</v>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P210" t="s">
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -15296,7 +15296,7 @@
         <v>198</v>
       </c>
       <c r="B211" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -15323,7 +15323,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L211">
         <v>1</v>
@@ -15341,7 +15341,7 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -15355,10 +15355,10 @@
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B212" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -15385,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -15403,7 +15403,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>199</v>
       </c>
       <c r="B213" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -15447,7 +15447,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L213">
         <v>2</v>
@@ -15465,7 +15465,7 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -15482,7 +15482,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -15509,7 +15509,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -15527,7 +15527,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15544,7 +15544,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -15559,37 +15559,37 @@
         <v>250</v>
       </c>
       <c r="G215">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H215">
         <v>0</v>
       </c>
       <c r="I215">
+        <v>3</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215" t="s">
+        <v>219</v>
+      </c>
+      <c r="L215">
+        <v>3</v>
+      </c>
+      <c r="M215">
         <v>2</v>
       </c>
-      <c r="J215">
-        <v>0</v>
-      </c>
-      <c r="K215" t="s">
-        <v>216</v>
-      </c>
-      <c r="L215">
+      <c r="N215">
         <v>2</v>
       </c>
-      <c r="M215">
-        <v>1</v>
-      </c>
-      <c r="N215">
-        <v>1</v>
-      </c>
       <c r="O215">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P215" t="s">
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -15603,10 +15603,10 @@
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B216" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -15651,7 +15651,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15668,7 +15668,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -15695,7 +15695,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L217">
         <v>7</v>
@@ -15713,7 +15713,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15730,7 +15730,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -15757,7 +15757,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L218">
         <v>4</v>
@@ -15775,7 +15775,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15792,7 +15792,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15819,7 +15819,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L219">
         <v>5</v>
@@ -15837,7 +15837,7 @@
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15854,7 +15854,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15881,7 +15881,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L220">
         <v>4</v>
@@ -15899,7 +15899,7 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15913,10 +15913,10 @@
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B221" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15943,7 +15943,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15961,7 +15961,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15978,7 +15978,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -16005,7 +16005,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -16023,7 +16023,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -16067,7 +16067,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L223">
         <v>14</v>
@@ -16085,7 +16085,7 @@
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -16102,7 +16102,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -16129,7 +16129,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -16147,7 +16147,7 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -16164,7 +16164,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -16191,7 +16191,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L225">
         <v>8</v>
@@ -16200,7 +16200,7 @@
         <v>7</v>
       </c>
       <c r="N225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O225">
         <v>8</v>
@@ -16209,7 +16209,7 @@
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -16226,7 +16226,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -16253,7 +16253,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -16271,7 +16271,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -16288,7 +16288,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -16303,37 +16303,37 @@
         <v>235</v>
       </c>
       <c r="G227">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J227">
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L227">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M227">
         <v>10</v>
       </c>
       <c r="N227">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O227">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P227" t="s">
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -16350,7 +16350,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -16377,7 +16377,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L228">
         <v>14</v>
@@ -16395,7 +16395,7 @@
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -16412,7 +16412,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -16439,7 +16439,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L229">
         <v>15</v>
@@ -16448,7 +16448,7 @@
         <v>10</v>
       </c>
       <c r="N229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O229">
         <v>14</v>
@@ -16457,7 +16457,7 @@
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -16474,7 +16474,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -16501,7 +16501,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -16519,7 +16519,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -16536,7 +16536,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -16563,7 +16563,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -16581,7 +16581,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -16622,7 +16622,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L232">
         <v>2</v>
@@ -16675,7 +16675,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L233">
         <v>5</v>
@@ -16701,10 +16701,10 @@
     </row>
     <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B234" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -16754,10 +16754,10 @@
     </row>
     <row r="235" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>597</v>
+        <v>202</v>
       </c>
       <c r="B235" t="s">
-        <v>597</v>
+        <v>202</v>
       </c>
       <c r="C235" t="s">
         <v>120</v>
@@ -16769,7 +16769,7 @@
         <v>122</v>
       </c>
       <c r="G235">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -16781,19 +16781,19 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M235">
         <v>0</v>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P235" t="s">
         <v>13</v>
@@ -16834,7 +16834,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L236">
         <v>1</v>
@@ -16887,7 +16887,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -16913,10 +16913,10 @@
     </row>
     <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B238" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -16940,7 +16940,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -16966,10 +16966,10 @@
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B239" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -16993,7 +16993,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -17019,10 +17019,10 @@
     </row>
     <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B240" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C240" t="s">
         <v>120</v>
@@ -17046,7 +17046,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -17099,7 +17099,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -17125,10 +17125,10 @@
     </row>
     <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B242" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C242" t="s">
         <v>120</v>
@@ -17152,7 +17152,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -17178,10 +17178,10 @@
     </row>
     <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B243" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C243" t="s">
         <v>120</v>
@@ -17205,7 +17205,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -17231,10 +17231,10 @@
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B244" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -17258,7 +17258,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -17311,7 +17311,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L245">
         <v>2</v>
@@ -17364,7 +17364,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -17417,7 +17417,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L247">
         <v>2</v>
@@ -17443,10 +17443,10 @@
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B248" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
@@ -17470,7 +17470,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -17523,7 +17523,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L249">
         <v>1</v>
@@ -17549,10 +17549,10 @@
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B250" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
@@ -17576,7 +17576,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -17602,10 +17602,10 @@
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B251" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
@@ -17629,7 +17629,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L252">
         <v>1</v>
@@ -17723,7 +17723,7 @@
         <v>122</v>
       </c>
       <c r="G253">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -17735,19 +17735,19 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L253">
+        <v>3</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
         <v>2</v>
       </c>
-      <c r="M253">
-        <v>0</v>
-      </c>
-      <c r="N253">
-        <v>1</v>
-      </c>
       <c r="O253">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P253" t="s">
         <v>13</v>
@@ -17788,7 +17788,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -17841,7 +17841,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L255">
         <v>1</v>
@@ -17894,7 +17894,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L256">
         <v>5</v>
@@ -17903,7 +17903,7 @@
         <v>0</v>
       </c>
       <c r="N256">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O256">
         <v>5</v>
@@ -17920,10 +17920,10 @@
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B257" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C257" t="s">
         <v>120</v>
@@ -17947,7 +17947,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -18000,7 +18000,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L258">
         <v>3</v>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B259" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C259" t="s">
         <v>120</v>
@@ -18053,7 +18053,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>176</v>
       </c>
       <c r="B260" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C260" t="s">
         <v>177</v>
@@ -18106,7 +18106,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L260">
         <v>13</v>
@@ -18132,7 +18132,7 @@
     </row>
     <row r="261" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>610</v>
+        <v>201</v>
       </c>
       <c r="B261" t="s">
         <v>611</v>
@@ -18150,7 +18150,7 @@
         <v>179</v>
       </c>
       <c r="G261">
-        <v>2000</v>
+        <v>1988</v>
       </c>
       <c r="I261">
         <v>0</v>
@@ -18159,19 +18159,19 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L261">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M261">
         <v>0</v>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P261" t="s">
         <v>180</v>
@@ -18212,7 +18212,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L262">
         <v>12</v>
@@ -18265,7 +18265,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L263">
         <v>12</v>
@@ -18296,8 +18296,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5071C80F-2A89-4649-8313-C9C1C19F7C0E}">
-  <dimension ref="A1:J533"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{892C8708-1C5E-48E9-88C5-A95B689D3887}">
+  <dimension ref="A1:J550"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -35353,6 +35353,550 @@
         <v>1</v>
       </c>
       <c r="J533" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A534" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B534" t="s">
+        <v>181</v>
+      </c>
+      <c r="C534" t="s">
+        <v>24</v>
+      </c>
+      <c r="D534" t="s">
+        <v>25</v>
+      </c>
+      <c r="E534" t="s">
+        <v>53</v>
+      </c>
+      <c r="F534" t="s">
+        <v>94</v>
+      </c>
+      <c r="G534">
+        <v>245</v>
+      </c>
+      <c r="H534" t="s">
+        <v>22</v>
+      </c>
+      <c r="I534">
+        <v>1</v>
+      </c>
+      <c r="J534" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="535" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A535" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B535" t="s">
+        <v>70</v>
+      </c>
+      <c r="C535" t="s">
+        <v>24</v>
+      </c>
+      <c r="D535" t="s">
+        <v>49</v>
+      </c>
+      <c r="E535" t="s">
+        <v>53</v>
+      </c>
+      <c r="F535" t="s">
+        <v>94</v>
+      </c>
+      <c r="G535">
+        <v>235</v>
+      </c>
+      <c r="H535" t="s">
+        <v>22</v>
+      </c>
+      <c r="I535">
+        <v>1</v>
+      </c>
+      <c r="J535" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A536" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B536" t="s">
+        <v>108</v>
+      </c>
+      <c r="C536" t="s">
+        <v>24</v>
+      </c>
+      <c r="D536" t="s">
+        <v>25</v>
+      </c>
+      <c r="E536" t="s">
+        <v>53</v>
+      </c>
+      <c r="F536" t="s">
+        <v>94</v>
+      </c>
+      <c r="G536">
+        <v>250</v>
+      </c>
+      <c r="H536" t="s">
+        <v>22</v>
+      </c>
+      <c r="I536">
+        <v>1</v>
+      </c>
+      <c r="J536" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A537" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B537" t="s">
+        <v>167</v>
+      </c>
+      <c r="C537" t="s">
+        <v>120</v>
+      </c>
+      <c r="D537" t="s">
+        <v>121</v>
+      </c>
+      <c r="E537" t="s">
+        <v>175</v>
+      </c>
+      <c r="F537" t="s">
+        <v>94</v>
+      </c>
+      <c r="G537">
+        <v>0</v>
+      </c>
+      <c r="H537" t="s">
+        <v>122</v>
+      </c>
+      <c r="I537">
+        <v>1</v>
+      </c>
+      <c r="J537" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="538" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A538" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B538" t="s">
+        <v>89</v>
+      </c>
+      <c r="C538" t="s">
+        <v>18</v>
+      </c>
+      <c r="D538" t="s">
+        <v>90</v>
+      </c>
+      <c r="E538" t="s">
+        <v>100</v>
+      </c>
+      <c r="F538" t="s">
+        <v>94</v>
+      </c>
+      <c r="G538">
+        <v>235</v>
+      </c>
+      <c r="H538" t="s">
+        <v>22</v>
+      </c>
+      <c r="I538">
+        <v>1</v>
+      </c>
+      <c r="J538" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="539" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A539" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B539" t="s">
+        <v>162</v>
+      </c>
+      <c r="C539" t="s">
+        <v>18</v>
+      </c>
+      <c r="D539" t="s">
+        <v>90</v>
+      </c>
+      <c r="E539" t="s">
+        <v>100</v>
+      </c>
+      <c r="F539" t="s">
+        <v>94</v>
+      </c>
+      <c r="G539">
+        <v>255</v>
+      </c>
+      <c r="H539" t="s">
+        <v>22</v>
+      </c>
+      <c r="I539">
+        <v>1</v>
+      </c>
+      <c r="J539" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="540" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A540" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B540" t="s">
+        <v>201</v>
+      </c>
+      <c r="C540" t="s">
+        <v>177</v>
+      </c>
+      <c r="D540" t="s">
+        <v>178</v>
+      </c>
+      <c r="E540" t="s">
+        <v>188</v>
+      </c>
+      <c r="F540" t="s">
+        <v>94</v>
+      </c>
+      <c r="G540" t="s">
+        <v>179</v>
+      </c>
+      <c r="H540" t="s">
+        <v>122</v>
+      </c>
+      <c r="I540">
+        <v>2</v>
+      </c>
+      <c r="J540" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="541" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A541" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B541" t="s">
+        <v>201</v>
+      </c>
+      <c r="C541" t="s">
+        <v>177</v>
+      </c>
+      <c r="D541" t="s">
+        <v>178</v>
+      </c>
+      <c r="E541" t="s">
+        <v>188</v>
+      </c>
+      <c r="F541" t="s">
+        <v>94</v>
+      </c>
+      <c r="G541" t="s">
+        <v>179</v>
+      </c>
+      <c r="H541" t="s">
+        <v>122</v>
+      </c>
+      <c r="I541">
+        <v>4</v>
+      </c>
+      <c r="J541" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="542" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A542" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B542" t="s">
+        <v>201</v>
+      </c>
+      <c r="C542" t="s">
+        <v>177</v>
+      </c>
+      <c r="D542" t="s">
+        <v>178</v>
+      </c>
+      <c r="E542" t="s">
+        <v>188</v>
+      </c>
+      <c r="F542" t="s">
+        <v>94</v>
+      </c>
+      <c r="G542" t="s">
+        <v>179</v>
+      </c>
+      <c r="H542" t="s">
+        <v>122</v>
+      </c>
+      <c r="I542">
+        <v>6</v>
+      </c>
+      <c r="J542" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="543" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A543" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B543" t="s">
+        <v>202</v>
+      </c>
+      <c r="C543" t="s">
+        <v>120</v>
+      </c>
+      <c r="D543" t="s">
+        <v>126</v>
+      </c>
+      <c r="E543" t="s">
+        <v>133</v>
+      </c>
+      <c r="F543" t="s">
+        <v>94</v>
+      </c>
+      <c r="G543">
+        <v>0</v>
+      </c>
+      <c r="H543" t="s">
+        <v>122</v>
+      </c>
+      <c r="I543">
+        <v>1</v>
+      </c>
+      <c r="J543" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="544" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A544" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B544" t="s">
+        <v>67</v>
+      </c>
+      <c r="C544" t="s">
+        <v>24</v>
+      </c>
+      <c r="D544" t="s">
+        <v>40</v>
+      </c>
+      <c r="E544" t="s">
+        <v>53</v>
+      </c>
+      <c r="F544" t="s">
+        <v>94</v>
+      </c>
+      <c r="G544">
+        <v>240</v>
+      </c>
+      <c r="H544" t="s">
+        <v>22</v>
+      </c>
+      <c r="I544">
+        <v>1</v>
+      </c>
+      <c r="J544" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A545" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B545" t="s">
+        <v>97</v>
+      </c>
+      <c r="C545" t="s">
+        <v>24</v>
+      </c>
+      <c r="D545" t="s">
+        <v>38</v>
+      </c>
+      <c r="E545" t="s">
+        <v>53</v>
+      </c>
+      <c r="F545" t="s">
+        <v>94</v>
+      </c>
+      <c r="G545">
+        <v>280</v>
+      </c>
+      <c r="H545" t="s">
+        <v>15</v>
+      </c>
+      <c r="I545">
+        <v>1</v>
+      </c>
+      <c r="J545" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A546" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B546" t="s">
+        <v>171</v>
+      </c>
+      <c r="C546" t="s">
+        <v>18</v>
+      </c>
+      <c r="D546" t="s">
+        <v>90</v>
+      </c>
+      <c r="E546" t="s">
+        <v>53</v>
+      </c>
+      <c r="F546" t="s">
+        <v>94</v>
+      </c>
+      <c r="G546">
+        <v>235</v>
+      </c>
+      <c r="H546" t="s">
+        <v>22</v>
+      </c>
+      <c r="I546">
+        <v>1</v>
+      </c>
+      <c r="J546" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A547" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B547" t="s">
+        <v>203</v>
+      </c>
+      <c r="C547" t="s">
+        <v>24</v>
+      </c>
+      <c r="D547" t="s">
+        <v>47</v>
+      </c>
+      <c r="E547" t="s">
+        <v>53</v>
+      </c>
+      <c r="F547" t="s">
+        <v>94</v>
+      </c>
+      <c r="G547">
+        <v>250</v>
+      </c>
+      <c r="H547" t="s">
+        <v>22</v>
+      </c>
+      <c r="I547">
+        <v>1</v>
+      </c>
+      <c r="J547" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A548" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B548" t="s">
+        <v>158</v>
+      </c>
+      <c r="C548" t="s">
+        <v>24</v>
+      </c>
+      <c r="D548" t="s">
+        <v>33</v>
+      </c>
+      <c r="E548" t="s">
+        <v>53</v>
+      </c>
+      <c r="F548" t="s">
+        <v>94</v>
+      </c>
+      <c r="G548">
+        <v>270</v>
+      </c>
+      <c r="H548" t="s">
+        <v>15</v>
+      </c>
+      <c r="I548">
+        <v>1</v>
+      </c>
+      <c r="J548" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A549" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B549" t="s">
+        <v>69</v>
+      </c>
+      <c r="C549" t="s">
+        <v>18</v>
+      </c>
+      <c r="D549" t="s">
+        <v>21</v>
+      </c>
+      <c r="E549" t="s">
+        <v>53</v>
+      </c>
+      <c r="F549" t="s">
+        <v>94</v>
+      </c>
+      <c r="G549">
+        <v>240</v>
+      </c>
+      <c r="H549" t="s">
+        <v>22</v>
+      </c>
+      <c r="I549">
+        <v>1</v>
+      </c>
+      <c r="J549" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A550" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B550" t="s">
+        <v>109</v>
+      </c>
+      <c r="C550" t="s">
+        <v>24</v>
+      </c>
+      <c r="D550" t="s">
+        <v>47</v>
+      </c>
+      <c r="E550" t="s">
+        <v>100</v>
+      </c>
+      <c r="F550" t="s">
+        <v>66</v>
+      </c>
+      <c r="G550">
+        <v>250</v>
+      </c>
+      <c r="H550" t="s">
+        <v>22</v>
+      </c>
+      <c r="I550">
+        <v>1</v>
+      </c>
+      <c r="J550" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAEA74A2-967C-4A97-B139-4724C30D98CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{692C0987-0AC1-4C92-B948-F9C2D295FDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{A571B92E-D843-4FFC-8EEE-99D4ACAEA14F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{C6E149FC-A481-4BF4-9021-747FE4DEC56A}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6094" uniqueCount="615">
   <si>
     <t>날짜</t>
   </si>
@@ -654,6 +654,15 @@
     <t>DPW771-BK250</t>
   </si>
   <si>
+    <t>R-10FB-BRMB</t>
+  </si>
+  <si>
+    <t>DPM647-GY270</t>
+  </si>
+  <si>
+    <t>쿠팡/알파플러스</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1344,9 +1353,6 @@
     <t>DPM647GY 바오지 남성 러닝화 그레이 265</t>
   </si>
   <si>
-    <t>DPM647-GY270</t>
-  </si>
-  <si>
     <t>DPM647GY 바오지 남성 러닝화 그레이 270</t>
   </si>
   <si>
@@ -1867,9 +1873,6 @@
   </si>
   <si>
     <t>R-10F-BRMB</t>
-  </si>
-  <si>
-    <t>R-10FB-BRMB</t>
   </si>
   <si>
     <t>볼트겔 클리어겔 롤형 테이프 1m</t>
@@ -2267,7 +2270,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A0DDC4-D06F-4887-B9A8-F41B5C4DEB78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCD4711-3105-4837-8904-D21C6B3000B4}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2276,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2291,46 +2294,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="N1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="R1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="S1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="T1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2338,7 +2341,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2365,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2383,7 +2386,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2400,7 +2403,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2415,37 +2418,37 @@
         <v>265</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3" t="s">
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2462,7 +2465,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2489,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2507,7 +2510,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2524,7 +2527,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2551,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2569,7 +2572,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2586,7 +2589,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2613,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2631,7 +2634,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2648,7 +2651,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2675,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2693,7 +2696,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2710,7 +2713,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2737,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2755,7 +2758,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2772,7 +2775,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2799,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2817,7 +2820,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2834,7 +2837,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2861,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2879,7 +2882,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2896,7 +2899,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2923,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2941,7 +2944,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2955,16 +2958,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C12" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2985,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3017,16 +3020,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" t="s">
         <v>236</v>
       </c>
-      <c r="C13" t="s">
-        <v>233</v>
-      </c>
       <c r="D13" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3047,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3079,16 +3082,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14" t="s">
+        <v>241</v>
+      </c>
+      <c r="C14" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" t="s">
         <v>237</v>
-      </c>
-      <c r="B14" t="s">
-        <v>238</v>
-      </c>
-      <c r="C14" t="s">
-        <v>233</v>
-      </c>
-      <c r="D14" t="s">
-        <v>234</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3109,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3141,16 +3144,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3171,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3203,16 +3206,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B16" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C16" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D16" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3233,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3265,16 +3268,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3295,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3327,16 +3330,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B18" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C18" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D18" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3357,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3389,16 +3392,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B19" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D19" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3419,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3451,16 +3454,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B20" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C20" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D20" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3481,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3513,16 +3516,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C21" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D21" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3543,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3575,16 +3578,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C22" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D22" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3605,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3637,16 +3640,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D23" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3667,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3699,16 +3702,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C24" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D24" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3729,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3761,16 +3764,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D25" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3791,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3823,16 +3826,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C26" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D26" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3853,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3885,16 +3888,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C27" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D27" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3915,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3947,16 +3950,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C28" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D28" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3977,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4009,16 +4012,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C29" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D29" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4039,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4071,16 +4074,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C30" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D30" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4101,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4133,16 +4136,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C31" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D31" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4163,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4195,16 +4198,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B32" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C32" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D32" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4225,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4257,16 +4260,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C33" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D33" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4287,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4319,16 +4322,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>281</v>
+      </c>
+      <c r="B34" t="s">
+        <v>282</v>
+      </c>
+      <c r="C34" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" t="s">
         <v>278</v>
-      </c>
-      <c r="B34" t="s">
-        <v>279</v>
-      </c>
-      <c r="C34" t="s">
-        <v>233</v>
-      </c>
-      <c r="D34" t="s">
-        <v>275</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4349,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4381,16 +4384,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C35" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D35" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4411,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4443,16 +4446,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C36" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D36" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4473,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4505,16 +4508,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C37" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D37" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4535,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4567,16 +4570,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C38" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D38" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4597,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4629,16 +4632,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B39" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C39" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D39" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4659,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4691,16 +4694,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B40" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D40" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4721,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4753,16 +4756,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C41" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D41" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4783,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4815,16 +4818,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C42" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D42" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4845,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4877,16 +4880,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C43" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D43" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4907,7 +4910,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4939,16 +4942,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B44" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C44" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D44" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4969,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5001,16 +5004,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B45" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C45" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D45" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5031,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5063,16 +5066,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C46" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D46" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5093,7 +5096,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5125,16 +5128,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C47" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D47" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5155,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5187,16 +5190,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B48" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C48" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D48" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5217,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5249,16 +5252,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B49" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D49" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5279,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5311,16 +5314,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B50" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C50" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D50" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5341,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5373,16 +5376,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C51" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D51" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5403,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5435,16 +5438,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C52" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5465,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5497,16 +5500,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B53" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C53" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5527,7 +5530,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5559,16 +5562,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>322</v>
+      </c>
+      <c r="B54" t="s">
+        <v>323</v>
+      </c>
+      <c r="C54" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" t="s">
         <v>319</v>
-      </c>
-      <c r="B54" t="s">
-        <v>320</v>
-      </c>
-      <c r="C54" t="s">
-        <v>233</v>
-      </c>
-      <c r="D54" t="s">
-        <v>316</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5589,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5621,16 +5624,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B55" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C55" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5651,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5683,16 +5686,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C56" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5713,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5745,16 +5748,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C57" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5775,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5807,16 +5810,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B58" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C58" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5837,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5869,16 +5872,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B59" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C59" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D59" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5899,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5931,16 +5934,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B60" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C60" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D60" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5961,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5993,16 +5996,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B61" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C61" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D61" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6023,7 +6026,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6055,16 +6058,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B62" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C62" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D62" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6085,7 +6088,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6117,16 +6120,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B63" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C63" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D63" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6147,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6179,16 +6182,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B64" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C64" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D64" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6209,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6241,16 +6244,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B65" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C65" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D65" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6271,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6303,16 +6306,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B66" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C66" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D66" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6333,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6368,7 +6371,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6395,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6413,7 +6416,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6430,7 +6433,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6445,37 +6448,37 @@
         <v>265</v>
       </c>
       <c r="G68">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="I68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L68">
+        <v>4</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68">
         <v>3</v>
       </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>2</v>
-      </c>
       <c r="P68" t="s">
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6492,7 +6495,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6519,7 +6522,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L69">
         <v>9</v>
@@ -6537,7 +6540,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6554,7 +6557,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6581,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6599,7 +6602,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6616,7 +6619,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6643,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6661,7 +6664,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6675,10 +6678,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B72" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6705,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6723,7 +6726,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6740,7 +6743,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6767,7 +6770,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6785,7 +6788,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6799,10 +6802,10 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B74" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6829,7 +6832,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -6847,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6864,7 +6867,7 @@
         <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6891,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6909,7 +6912,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6923,10 +6926,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B76" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6953,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6971,7 +6974,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6988,7 +6991,7 @@
         <v>184</v>
       </c>
       <c r="B77" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -7015,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -7033,7 +7036,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7047,10 +7050,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B78" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7077,7 +7080,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7095,7 +7098,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7109,10 +7112,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B79" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7139,7 +7142,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7157,7 +7160,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7174,7 +7177,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7201,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7219,7 +7222,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7233,10 +7236,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B81" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7263,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -7281,7 +7284,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7295,10 +7298,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B82" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7325,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7343,7 +7346,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7357,10 +7360,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B83" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7387,7 +7390,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7405,7 +7408,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7419,10 +7422,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B84" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7449,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7467,7 +7470,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7481,10 +7484,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B85" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7511,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7529,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7543,10 +7546,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B86" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7573,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7591,7 +7594,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7605,10 +7608,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B87" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7635,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7653,7 +7656,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7670,7 +7673,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7685,37 +7688,37 @@
         <v>265</v>
       </c>
       <c r="G88">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88">
         <v>0</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P88" t="s">
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7729,10 +7732,10 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B89" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7759,7 +7762,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -7777,7 +7780,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7794,7 +7797,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7821,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L90">
         <v>2</v>
@@ -7839,7 +7842,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7853,10 +7856,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B91" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7883,7 +7886,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7901,7 +7904,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7915,10 +7918,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B92" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7945,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7963,7 +7966,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7980,7 +7983,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -8007,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8025,7 +8028,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8039,10 +8042,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B94" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8069,7 +8072,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8087,7 +8090,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8101,10 +8104,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B95" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8131,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8149,7 +8152,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8163,10 +8166,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B96" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8193,7 +8196,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8211,7 +8214,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8225,10 +8228,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B97" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8255,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8273,7 +8276,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8290,7 +8293,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8317,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L98">
         <v>5</v>
@@ -8335,7 +8338,7 @@
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8352,7 +8355,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8379,7 +8382,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L99">
         <v>2</v>
@@ -8397,7 +8400,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8414,7 +8417,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8441,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8450,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="N100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O100">
         <v>3</v>
@@ -8459,7 +8462,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8473,10 +8476,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B101" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8503,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8521,7 +8524,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8535,10 +8538,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B102" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8565,7 +8568,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8583,7 +8586,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8597,10 +8600,10 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B103" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8627,7 +8630,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -8645,7 +8648,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8662,7 +8665,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8689,7 +8692,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8707,7 +8710,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8721,10 +8724,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B105" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8751,7 +8754,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8769,7 +8772,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8786,7 +8789,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8813,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8831,7 +8834,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8845,10 +8848,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B107" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8875,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8893,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8910,7 +8913,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8937,7 +8940,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8955,7 +8958,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8972,7 +8975,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -8999,7 +9002,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -9017,7 +9020,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -9031,10 +9034,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B110" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -9061,7 +9064,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -9079,7 +9082,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -9093,10 +9096,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B111" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -9123,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9141,7 +9144,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9158,7 +9161,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9185,7 +9188,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9203,7 +9206,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9220,7 +9223,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9235,37 +9238,37 @@
         <v>265</v>
       </c>
       <c r="G113">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M113">
         <v>3</v>
       </c>
       <c r="N113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O113">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P113" t="s">
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9282,7 +9285,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9297,37 +9300,37 @@
         <v>270</v>
       </c>
       <c r="G114">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L114">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M114">
         <v>0</v>
       </c>
       <c r="N114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O114">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P114" t="s">
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9344,7 +9347,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9371,7 +9374,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9389,7 +9392,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9406,7 +9409,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9421,37 +9424,37 @@
         <v>280</v>
       </c>
       <c r="G116">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H116">
         <v>0</v>
       </c>
       <c r="I116">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L116">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M116">
         <v>0</v>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P116" t="s">
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9468,7 +9471,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9495,7 +9498,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9513,7 +9516,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9530,7 +9533,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9557,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9575,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9589,10 +9592,10 @@
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>434</v>
+        <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9607,37 +9610,37 @@
         <v>270</v>
       </c>
       <c r="G119">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H119">
         <v>0</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M119">
         <v>0</v>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P119" t="s">
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9654,7 +9657,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9681,7 +9684,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9699,7 +9702,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9716,7 +9719,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9743,7 +9746,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L121">
         <v>2</v>
@@ -9761,7 +9764,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9778,7 +9781,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9805,7 +9808,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L122">
         <v>5</v>
@@ -9823,7 +9826,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9840,7 +9843,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9867,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -9885,7 +9888,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9902,7 +9905,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9917,37 +9920,37 @@
         <v>270</v>
       </c>
       <c r="G124">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H124">
         <v>0</v>
       </c>
       <c r="I124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M124">
         <v>2</v>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P124" t="s">
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9964,7 +9967,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9991,7 +9994,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -10009,7 +10012,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -10026,7 +10029,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -10053,7 +10056,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -10071,7 +10074,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -10088,7 +10091,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -10103,37 +10106,37 @@
         <v>235</v>
       </c>
       <c r="G127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127">
         <v>0</v>
       </c>
       <c r="I127">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J127">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K127" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L127">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M127">
         <v>5</v>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O127">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P127" t="s">
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -10150,7 +10153,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -10177,7 +10180,7 @@
         <v>7</v>
       </c>
       <c r="K128" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L128">
         <v>14</v>
@@ -10195,7 +10198,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -10212,7 +10215,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10239,7 +10242,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L129">
         <v>9</v>
@@ -10257,7 +10260,7 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10274,7 +10277,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10301,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10319,7 +10322,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10336,7 +10339,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10363,7 +10366,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10381,7 +10384,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10398,7 +10401,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10425,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L132">
         <v>18</v>
@@ -10443,7 +10446,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10460,7 +10463,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10487,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L133">
         <v>10</v>
@@ -10505,7 +10508,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10522,7 +10525,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10549,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L134">
         <v>16</v>
@@ -10567,7 +10570,7 @@
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10584,7 +10587,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10611,7 +10614,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10629,7 +10632,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10646,7 +10649,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10673,7 +10676,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10691,7 +10694,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10708,7 +10711,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10735,7 +10738,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L137">
         <v>4</v>
@@ -10753,7 +10756,7 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10770,7 +10773,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10797,7 +10800,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L138">
         <v>4</v>
@@ -10815,7 +10818,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10832,7 +10835,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10847,37 +10850,37 @@
         <v>245</v>
       </c>
       <c r="G139">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H139">
         <v>0</v>
       </c>
       <c r="I139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M139">
         <v>2</v>
       </c>
       <c r="N139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P139" t="s">
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10894,7 +10897,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10921,7 +10924,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L140">
         <v>3</v>
@@ -10939,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10956,7 +10959,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10983,7 +10986,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L141">
         <v>5</v>
@@ -11001,7 +11004,7 @@
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -11018,7 +11021,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -11045,7 +11048,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -11063,7 +11066,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -11080,7 +11083,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -11107,7 +11110,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -11125,7 +11128,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -11142,7 +11145,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -11169,7 +11172,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -11187,7 +11190,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -11201,10 +11204,10 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B145" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -11231,7 +11234,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -11249,7 +11252,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -11263,10 +11266,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B146" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -11293,7 +11296,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -11311,7 +11314,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -11328,7 +11331,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11355,7 +11358,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L147">
         <v>2</v>
@@ -11373,7 +11376,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11390,7 +11393,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11417,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L148">
         <v>6</v>
@@ -11435,7 +11438,7 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11452,7 +11455,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11479,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11497,7 +11500,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11514,7 +11517,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11541,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11559,7 +11562,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11576,7 +11579,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11603,7 +11606,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -11621,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11635,16 +11638,16 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B152" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C152" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D152" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11665,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11697,16 +11700,16 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B153" t="s">
+        <v>482</v>
+      </c>
+      <c r="C153" t="s">
+        <v>236</v>
+      </c>
+      <c r="D153" t="s">
         <v>480</v>
-      </c>
-      <c r="C153" t="s">
-        <v>233</v>
-      </c>
-      <c r="D153" t="s">
-        <v>478</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11727,7 +11730,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11759,16 +11762,16 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B154" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C154" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D154" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11789,7 +11792,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11821,16 +11824,16 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B155" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C155" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D155" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11851,7 +11854,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11883,16 +11886,16 @@
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B156" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C156" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D156" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11913,7 +11916,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11945,16 +11948,16 @@
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B157" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C157" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D157" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11975,7 +11978,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -12007,16 +12010,16 @@
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B158" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C158" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D158" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -12037,7 +12040,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -12069,16 +12072,16 @@
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B159" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C159" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D159" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -12099,7 +12102,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -12131,16 +12134,16 @@
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B160" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C160" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D160" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -12161,7 +12164,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -12193,16 +12196,16 @@
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B161" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C161" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D161" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -12223,7 +12226,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -12255,16 +12258,16 @@
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B162" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C162" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -12285,7 +12288,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -12317,16 +12320,16 @@
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B163" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C163" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D163" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -12347,7 +12350,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -12379,16 +12382,16 @@
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B164" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C164" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D164" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -12409,7 +12412,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -12441,16 +12444,16 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B165" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C165" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D165" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12471,7 +12474,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12503,16 +12506,16 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B166" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C166" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D166" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12533,7 +12536,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12565,16 +12568,16 @@
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B167" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C167" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D167" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12595,7 +12598,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12627,16 +12630,16 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B168" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C168" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12657,7 +12660,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12689,16 +12692,16 @@
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B169" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C169" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D169" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12719,7 +12722,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12751,16 +12754,16 @@
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B170" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C170" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D170" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12781,7 +12784,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12813,16 +12816,16 @@
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B171" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C171" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D171" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12843,7 +12846,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12878,7 +12881,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12905,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -12923,7 +12926,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12940,7 +12943,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12967,7 +12970,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L173">
         <v>7</v>
@@ -12985,7 +12988,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -13002,7 +13005,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -13029,7 +13032,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L174">
         <v>5</v>
@@ -13038,7 +13041,7 @@
         <v>1</v>
       </c>
       <c r="N174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O174">
         <v>5</v>
@@ -13047,7 +13050,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -13064,7 +13067,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -13091,7 +13094,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -13109,7 +13112,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -13126,7 +13129,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -13153,7 +13156,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -13171,7 +13174,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -13188,7 +13191,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -13215,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -13233,7 +13236,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -13250,7 +13253,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -13277,7 +13280,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -13295,7 +13298,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -13312,7 +13315,7 @@
         <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -13339,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L179">
         <v>2</v>
@@ -13357,7 +13360,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -13374,7 +13377,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -13389,37 +13392,37 @@
         <v>250</v>
       </c>
       <c r="G180">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H180">
         <v>0</v>
       </c>
       <c r="I180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J180">
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M180">
         <v>1</v>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P180" t="s">
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -13433,10 +13436,10 @@
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B181" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -13463,7 +13466,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -13481,7 +13484,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -13498,7 +13501,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -13525,7 +13528,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L182">
         <v>5</v>
@@ -13543,7 +13546,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13560,7 +13563,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13587,7 +13590,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L183">
         <v>5</v>
@@ -13605,7 +13608,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13622,7 +13625,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13637,37 +13640,37 @@
         <v>245</v>
       </c>
       <c r="G184">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H184">
         <v>0</v>
       </c>
       <c r="I184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J184">
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M184">
         <v>1</v>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P184" t="s">
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13684,7 +13687,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13711,7 +13714,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L185">
         <v>4</v>
@@ -13729,7 +13732,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13746,7 +13749,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13773,7 +13776,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13791,7 +13794,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13808,7 +13811,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13835,7 +13838,7 @@
         <v>6</v>
       </c>
       <c r="K187" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L187">
         <v>9</v>
@@ -13853,7 +13856,7 @@
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13870,7 +13873,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13897,7 +13900,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -13915,7 +13918,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13932,7 +13935,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13959,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13977,7 +13980,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -13994,7 +13997,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -14021,7 +14024,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -14039,7 +14042,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14056,7 +14059,7 @@
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -14083,7 +14086,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L191">
         <v>1</v>
@@ -14101,7 +14104,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -14118,7 +14121,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -14145,7 +14148,7 @@
         <v>9</v>
       </c>
       <c r="K192" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L192">
         <v>13</v>
@@ -14163,7 +14166,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -14180,7 +14183,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -14207,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L193">
         <v>24</v>
@@ -14225,7 +14228,7 @@
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -14242,7 +14245,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -14257,22 +14260,22 @@
         <v>245</v>
       </c>
       <c r="G194">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H194">
         <v>0</v>
       </c>
       <c r="I194">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J194">
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L194">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M194">
         <v>14</v>
@@ -14281,13 +14284,13 @@
         <v>2</v>
       </c>
       <c r="O194">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P194" t="s">
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -14304,7 +14307,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -14319,37 +14322,37 @@
         <v>250</v>
       </c>
       <c r="G195">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H195">
         <v>0</v>
       </c>
       <c r="I195">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J195">
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L195">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M195">
         <v>8</v>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P195" t="s">
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -14366,7 +14369,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -14393,7 +14396,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L196">
         <v>9</v>
@@ -14411,7 +14414,7 @@
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -14425,10 +14428,10 @@
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B197" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -14455,7 +14458,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -14473,7 +14476,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -14490,7 +14493,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -14517,7 +14520,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -14535,7 +14538,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -14552,7 +14555,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -14579,7 +14582,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -14597,7 +14600,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -14611,10 +14614,10 @@
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B200" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -14641,7 +14644,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14659,7 +14662,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14676,7 +14679,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14703,7 +14706,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14721,7 +14724,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14735,10 +14738,10 @@
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B202" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14765,7 +14768,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14783,7 +14786,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14800,7 +14803,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14827,7 +14830,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14845,7 +14848,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14862,7 +14865,7 @@
         <v>195</v>
       </c>
       <c r="B204" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14889,7 +14892,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L204">
         <v>1</v>
@@ -14907,7 +14910,7 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14924,7 +14927,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14951,7 +14954,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14969,7 +14972,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14983,10 +14986,10 @@
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B206" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -15013,7 +15016,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -15031,7 +15034,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -15048,7 +15051,7 @@
         <v>200</v>
       </c>
       <c r="B207" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -15075,7 +15078,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L207">
         <v>1</v>
@@ -15093,7 +15096,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -15110,7 +15113,7 @@
         <v>197</v>
       </c>
       <c r="B208" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -15137,7 +15140,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L208">
         <v>1</v>
@@ -15155,7 +15158,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -15169,10 +15172,10 @@
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B209" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -15199,7 +15202,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -15217,7 +15220,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -15234,7 +15237,7 @@
         <v>203</v>
       </c>
       <c r="B210" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -15261,7 +15264,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L210">
         <v>1</v>
@@ -15279,7 +15282,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -15296,7 +15299,7 @@
         <v>198</v>
       </c>
       <c r="B211" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -15311,37 +15314,37 @@
         <v>255</v>
       </c>
       <c r="G211">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H211">
         <v>0</v>
       </c>
       <c r="I211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J211">
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P211" t="s">
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -15355,10 +15358,10 @@
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B212" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -15385,7 +15388,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -15403,7 +15406,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -15420,7 +15423,7 @@
         <v>199</v>
       </c>
       <c r="B213" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -15447,7 +15450,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L213">
         <v>2</v>
@@ -15465,7 +15468,7 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -15482,7 +15485,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -15497,37 +15500,37 @@
         <v>245</v>
       </c>
       <c r="G214">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H214">
         <v>0</v>
       </c>
       <c r="I214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J214">
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P214" t="s">
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15544,7 +15547,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -15571,7 +15574,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L215">
         <v>3</v>
@@ -15589,7 +15592,7 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -15603,10 +15606,10 @@
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B216" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -15633,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -15651,7 +15654,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15668,7 +15671,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -15695,7 +15698,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L217">
         <v>7</v>
@@ -15713,7 +15716,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15730,7 +15733,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -15757,7 +15760,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L218">
         <v>4</v>
@@ -15775,7 +15778,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15792,7 +15795,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15819,7 +15822,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L219">
         <v>5</v>
@@ -15837,7 +15840,7 @@
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15854,7 +15857,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15881,7 +15884,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L220">
         <v>4</v>
@@ -15899,7 +15902,7 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15913,10 +15916,10 @@
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B221" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15943,7 +15946,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15961,7 +15964,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15978,7 +15981,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -16005,7 +16008,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -16023,7 +16026,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -16040,7 +16043,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -16067,7 +16070,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L223">
         <v>14</v>
@@ -16085,7 +16088,7 @@
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -16102,7 +16105,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -16129,7 +16132,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -16147,7 +16150,7 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -16164,7 +16167,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -16179,37 +16182,37 @@
         <v>250</v>
       </c>
       <c r="G225">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H225">
         <v>0</v>
       </c>
       <c r="I225">
+        <v>10</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225" t="s">
+        <v>222</v>
+      </c>
+      <c r="L225">
+        <v>10</v>
+      </c>
+      <c r="M225">
         <v>8</v>
       </c>
-      <c r="J225">
-        <v>0</v>
-      </c>
-      <c r="K225" t="s">
-        <v>219</v>
-      </c>
-      <c r="L225">
-        <v>8</v>
-      </c>
-      <c r="M225">
-        <v>7</v>
-      </c>
       <c r="N225">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O225">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P225" t="s">
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -16226,7 +16229,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -16253,7 +16256,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -16271,7 +16274,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -16288,7 +16291,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -16303,37 +16306,37 @@
         <v>235</v>
       </c>
       <c r="G227">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J227">
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L227">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M227">
         <v>10</v>
       </c>
       <c r="N227">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O227">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P227" t="s">
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -16350,7 +16353,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -16365,37 +16368,37 @@
         <v>240</v>
       </c>
       <c r="G228">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J228">
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L228">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M228">
         <v>11</v>
       </c>
       <c r="N228">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O228">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P228" t="s">
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -16412,7 +16415,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -16439,7 +16442,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L229">
         <v>15</v>
@@ -16448,7 +16451,7 @@
         <v>10</v>
       </c>
       <c r="N229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O229">
         <v>14</v>
@@ -16457,7 +16460,7 @@
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -16474,7 +16477,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -16501,7 +16504,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -16519,7 +16522,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -16536,7 +16539,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -16563,7 +16566,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -16581,7 +16584,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -16610,7 +16613,7 @@
         <v>122</v>
       </c>
       <c r="G232">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -16622,19 +16625,19 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M232">
         <v>0</v>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P232" t="s">
         <v>13</v>
@@ -16663,7 +16666,7 @@
         <v>122</v>
       </c>
       <c r="G233">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -16675,19 +16678,19 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L233">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M233">
         <v>0</v>
       </c>
       <c r="N233">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O233">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P233" t="s">
         <v>13</v>
@@ -16701,10 +16704,10 @@
     </row>
     <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B234" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -16728,7 +16731,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -16781,7 +16784,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L235">
         <v>1</v>
@@ -16834,7 +16837,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L236">
         <v>1</v>
@@ -16887,7 +16890,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -16913,10 +16916,10 @@
     </row>
     <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B238" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -16940,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -16966,10 +16969,10 @@
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B239" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -16993,7 +16996,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -17019,10 +17022,10 @@
     </row>
     <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B240" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C240" t="s">
         <v>120</v>
@@ -17046,7 +17049,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -17099,7 +17102,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L241">
         <v>1</v>
@@ -17125,10 +17128,10 @@
     </row>
     <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B242" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C242" t="s">
         <v>120</v>
@@ -17152,7 +17155,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -17178,10 +17181,10 @@
     </row>
     <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B243" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C243" t="s">
         <v>120</v>
@@ -17205,7 +17208,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -17231,10 +17234,10 @@
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B244" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -17258,7 +17261,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -17311,7 +17314,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L245">
         <v>2</v>
@@ -17364,7 +17367,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -17417,7 +17420,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L247">
         <v>2</v>
@@ -17443,10 +17446,10 @@
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B248" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
@@ -17470,7 +17473,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -17523,7 +17526,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L249">
         <v>1</v>
@@ -17549,10 +17552,10 @@
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B250" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
@@ -17576,7 +17579,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -17602,10 +17605,10 @@
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B251" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
@@ -17629,7 +17632,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -17682,7 +17685,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L252">
         <v>1</v>
@@ -17723,7 +17726,7 @@
         <v>122</v>
       </c>
       <c r="G253">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -17735,19 +17738,19 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L253">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M253">
         <v>0</v>
       </c>
       <c r="N253">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O253">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P253" t="s">
         <v>13</v>
@@ -17788,7 +17791,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -17829,7 +17832,7 @@
         <v>122</v>
       </c>
       <c r="G255">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -17841,19 +17844,19 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L255">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M255">
         <v>0</v>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O255">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P255" t="s">
         <v>13</v>
@@ -17894,7 +17897,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L256">
         <v>5</v>
@@ -17903,7 +17906,7 @@
         <v>0</v>
       </c>
       <c r="N256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O256">
         <v>5</v>
@@ -17920,10 +17923,10 @@
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B257" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C257" t="s">
         <v>120</v>
@@ -17947,7 +17950,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L257">
         <v>0</v>
@@ -18000,7 +18003,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L258">
         <v>3</v>
@@ -18026,10 +18029,10 @@
     </row>
     <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>609</v>
+        <v>204</v>
       </c>
       <c r="B259" t="s">
-        <v>609</v>
+        <v>204</v>
       </c>
       <c r="C259" t="s">
         <v>120</v>
@@ -18041,7 +18044,7 @@
         <v>122</v>
       </c>
       <c r="G259">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H259">
         <v>0</v>
@@ -18053,19 +18056,19 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M259">
         <v>0</v>
       </c>
       <c r="N259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P259" t="s">
         <v>13</v>
@@ -18082,7 +18085,7 @@
         <v>176</v>
       </c>
       <c r="B260" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C260" t="s">
         <v>177</v>
@@ -18106,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L260">
         <v>13</v>
@@ -18135,7 +18138,7 @@
         <v>201</v>
       </c>
       <c r="B261" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C261" t="s">
         <v>177</v>
@@ -18159,7 +18162,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L261">
         <v>12</v>
@@ -18188,7 +18191,7 @@
         <v>187</v>
       </c>
       <c r="B262" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C262" t="s">
         <v>177</v>
@@ -18212,7 +18215,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L262">
         <v>12</v>
@@ -18241,7 +18244,7 @@
         <v>190</v>
       </c>
       <c r="B263" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C263" t="s">
         <v>177</v>
@@ -18256,7 +18259,7 @@
         <v>191</v>
       </c>
       <c r="G263">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="I263">
         <v>0</v>
@@ -18265,19 +18268,19 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L263">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M263">
         <v>0</v>
       </c>
       <c r="N263">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O263">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P263" t="s">
         <v>180</v>
@@ -18296,8 +18299,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{892C8708-1C5E-48E9-88C5-A95B689D3887}">
-  <dimension ref="A1:J550"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB3E4D61-26B4-4D01-AF16-B9CCEE3895AC}">
+  <dimension ref="A1:J579"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -35897,6 +35900,934 @@
         <v>1</v>
       </c>
       <c r="J550" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A551" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B551" t="s">
+        <v>173</v>
+      </c>
+      <c r="C551" t="s">
+        <v>120</v>
+      </c>
+      <c r="D551" t="s">
+        <v>126</v>
+      </c>
+      <c r="E551" t="s">
+        <v>133</v>
+      </c>
+      <c r="F551" t="s">
+        <v>94</v>
+      </c>
+      <c r="G551">
+        <v>0</v>
+      </c>
+      <c r="H551" t="s">
+        <v>122</v>
+      </c>
+      <c r="I551">
+        <v>1</v>
+      </c>
+      <c r="J551" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A552" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B552" t="s">
+        <v>204</v>
+      </c>
+      <c r="C552" t="s">
+        <v>120</v>
+      </c>
+      <c r="D552" t="s">
+        <v>140</v>
+      </c>
+      <c r="E552" t="s">
+        <v>133</v>
+      </c>
+      <c r="F552" t="s">
+        <v>94</v>
+      </c>
+      <c r="G552">
+        <v>0</v>
+      </c>
+      <c r="H552" t="s">
+        <v>122</v>
+      </c>
+      <c r="I552">
+        <v>1</v>
+      </c>
+      <c r="J552" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A553" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B553" t="s">
+        <v>167</v>
+      </c>
+      <c r="C553" t="s">
+        <v>120</v>
+      </c>
+      <c r="D553" t="s">
+        <v>121</v>
+      </c>
+      <c r="E553" t="s">
+        <v>133</v>
+      </c>
+      <c r="F553" t="s">
+        <v>94</v>
+      </c>
+      <c r="G553">
+        <v>0</v>
+      </c>
+      <c r="H553" t="s">
+        <v>122</v>
+      </c>
+      <c r="I553">
+        <v>1</v>
+      </c>
+      <c r="J553" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A554" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B554" t="s">
+        <v>132</v>
+      </c>
+      <c r="C554" t="s">
+        <v>120</v>
+      </c>
+      <c r="D554" t="s">
+        <v>121</v>
+      </c>
+      <c r="E554" t="s">
+        <v>133</v>
+      </c>
+      <c r="F554" t="s">
+        <v>94</v>
+      </c>
+      <c r="G554">
+        <v>0</v>
+      </c>
+      <c r="H554" t="s">
+        <v>122</v>
+      </c>
+      <c r="I554">
+        <v>1</v>
+      </c>
+      <c r="J554" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A555" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B555" t="s">
+        <v>198</v>
+      </c>
+      <c r="C555" t="s">
+        <v>24</v>
+      </c>
+      <c r="D555" t="s">
+        <v>47</v>
+      </c>
+      <c r="E555" t="s">
+        <v>100</v>
+      </c>
+      <c r="F555" t="s">
+        <v>66</v>
+      </c>
+      <c r="G555">
+        <v>255</v>
+      </c>
+      <c r="H555" t="s">
+        <v>22</v>
+      </c>
+      <c r="I555">
+        <v>1</v>
+      </c>
+      <c r="J555" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A556" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B556" t="s">
+        <v>46</v>
+      </c>
+      <c r="C556" t="s">
+        <v>24</v>
+      </c>
+      <c r="D556" t="s">
+        <v>47</v>
+      </c>
+      <c r="E556" t="s">
+        <v>100</v>
+      </c>
+      <c r="F556" t="s">
+        <v>66</v>
+      </c>
+      <c r="G556">
+        <v>245</v>
+      </c>
+      <c r="H556" t="s">
+        <v>22</v>
+      </c>
+      <c r="I556">
+        <v>1</v>
+      </c>
+      <c r="J556" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A557" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B557" t="s">
+        <v>115</v>
+      </c>
+      <c r="C557" t="s">
+        <v>24</v>
+      </c>
+      <c r="D557" t="s">
+        <v>49</v>
+      </c>
+      <c r="E557" t="s">
+        <v>100</v>
+      </c>
+      <c r="F557" t="s">
+        <v>66</v>
+      </c>
+      <c r="G557">
+        <v>250</v>
+      </c>
+      <c r="H557" t="s">
+        <v>22</v>
+      </c>
+      <c r="I557">
+        <v>1</v>
+      </c>
+      <c r="J557" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="558" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A558" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B558" t="s">
+        <v>205</v>
+      </c>
+      <c r="C558" t="s">
+        <v>24</v>
+      </c>
+      <c r="D558" t="s">
+        <v>38</v>
+      </c>
+      <c r="E558" t="s">
+        <v>100</v>
+      </c>
+      <c r="F558" t="s">
+        <v>94</v>
+      </c>
+      <c r="G558">
+        <v>270</v>
+      </c>
+      <c r="H558" t="s">
+        <v>15</v>
+      </c>
+      <c r="I558">
+        <v>1</v>
+      </c>
+      <c r="J558" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A559" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B559" t="s">
+        <v>106</v>
+      </c>
+      <c r="C559" t="s">
+        <v>24</v>
+      </c>
+      <c r="D559" t="s">
+        <v>30</v>
+      </c>
+      <c r="E559" t="s">
+        <v>100</v>
+      </c>
+      <c r="F559" t="s">
+        <v>94</v>
+      </c>
+      <c r="G559">
+        <v>265</v>
+      </c>
+      <c r="H559" t="s">
+        <v>15</v>
+      </c>
+      <c r="I559">
+        <v>1</v>
+      </c>
+      <c r="J559" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A560" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B560" t="s">
+        <v>107</v>
+      </c>
+      <c r="C560" t="s">
+        <v>24</v>
+      </c>
+      <c r="D560" t="s">
+        <v>38</v>
+      </c>
+      <c r="E560" t="s">
+        <v>100</v>
+      </c>
+      <c r="F560" t="s">
+        <v>94</v>
+      </c>
+      <c r="G560">
+        <v>270</v>
+      </c>
+      <c r="H560" t="s">
+        <v>15</v>
+      </c>
+      <c r="I560">
+        <v>1</v>
+      </c>
+      <c r="J560" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="561" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A561" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B561" t="s">
+        <v>76</v>
+      </c>
+      <c r="C561" t="s">
+        <v>24</v>
+      </c>
+      <c r="D561" t="s">
+        <v>49</v>
+      </c>
+      <c r="E561" t="s">
+        <v>100</v>
+      </c>
+      <c r="F561" t="s">
+        <v>94</v>
+      </c>
+      <c r="G561">
+        <v>240</v>
+      </c>
+      <c r="H561" t="s">
+        <v>22</v>
+      </c>
+      <c r="I561">
+        <v>1</v>
+      </c>
+      <c r="J561" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="562" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A562" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B562" t="s">
+        <v>157</v>
+      </c>
+      <c r="C562" t="s">
+        <v>24</v>
+      </c>
+      <c r="D562" t="s">
+        <v>25</v>
+      </c>
+      <c r="E562" t="s">
+        <v>100</v>
+      </c>
+      <c r="F562" t="s">
+        <v>94</v>
+      </c>
+      <c r="G562">
+        <v>245</v>
+      </c>
+      <c r="H562" t="s">
+        <v>22</v>
+      </c>
+      <c r="I562">
+        <v>1</v>
+      </c>
+      <c r="J562" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="563" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A563" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B563" t="s">
+        <v>205</v>
+      </c>
+      <c r="C563" t="s">
+        <v>24</v>
+      </c>
+      <c r="D563" t="s">
+        <v>38</v>
+      </c>
+      <c r="E563" t="s">
+        <v>100</v>
+      </c>
+      <c r="F563" t="s">
+        <v>94</v>
+      </c>
+      <c r="G563">
+        <v>270</v>
+      </c>
+      <c r="H563" t="s">
+        <v>15</v>
+      </c>
+      <c r="I563">
+        <v>1</v>
+      </c>
+      <c r="J563" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="564" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A564" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B564" t="s">
+        <v>165</v>
+      </c>
+      <c r="C564" t="s">
+        <v>18</v>
+      </c>
+      <c r="D564" t="s">
+        <v>90</v>
+      </c>
+      <c r="E564" t="s">
+        <v>100</v>
+      </c>
+      <c r="F564" t="s">
+        <v>94</v>
+      </c>
+      <c r="G564">
+        <v>245</v>
+      </c>
+      <c r="H564" t="s">
+        <v>22</v>
+      </c>
+      <c r="I564">
+        <v>1</v>
+      </c>
+      <c r="J564" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="565" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A565" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B565" t="s">
+        <v>70</v>
+      </c>
+      <c r="C565" t="s">
+        <v>24</v>
+      </c>
+      <c r="D565" t="s">
+        <v>49</v>
+      </c>
+      <c r="E565" t="s">
+        <v>100</v>
+      </c>
+      <c r="F565" t="s">
+        <v>94</v>
+      </c>
+      <c r="G565">
+        <v>235</v>
+      </c>
+      <c r="H565" t="s">
+        <v>22</v>
+      </c>
+      <c r="I565">
+        <v>1</v>
+      </c>
+      <c r="J565" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="566" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A566" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B566" t="s">
+        <v>10</v>
+      </c>
+      <c r="C566" t="s">
+        <v>11</v>
+      </c>
+      <c r="D566" t="s">
+        <v>12</v>
+      </c>
+      <c r="E566" t="s">
+        <v>100</v>
+      </c>
+      <c r="F566" t="s">
+        <v>94</v>
+      </c>
+      <c r="G566">
+        <v>265</v>
+      </c>
+      <c r="H566" t="s">
+        <v>15</v>
+      </c>
+      <c r="I566">
+        <v>1</v>
+      </c>
+      <c r="J566" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="567" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A567" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B567" t="s">
+        <v>173</v>
+      </c>
+      <c r="C567" t="s">
+        <v>120</v>
+      </c>
+      <c r="D567" t="s">
+        <v>126</v>
+      </c>
+      <c r="E567" t="s">
+        <v>168</v>
+      </c>
+      <c r="F567" t="s">
+        <v>94</v>
+      </c>
+      <c r="G567">
+        <v>0</v>
+      </c>
+      <c r="H567" t="s">
+        <v>122</v>
+      </c>
+      <c r="I567">
+        <v>1</v>
+      </c>
+      <c r="J567" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="568" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A568" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B568" t="s">
+        <v>167</v>
+      </c>
+      <c r="C568" t="s">
+        <v>120</v>
+      </c>
+      <c r="D568" t="s">
+        <v>121</v>
+      </c>
+      <c r="E568" t="s">
+        <v>168</v>
+      </c>
+      <c r="F568" t="s">
+        <v>94</v>
+      </c>
+      <c r="G568">
+        <v>0</v>
+      </c>
+      <c r="H568" t="s">
+        <v>122</v>
+      </c>
+      <c r="I568">
+        <v>1</v>
+      </c>
+      <c r="J568" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="569" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A569" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B569" t="s">
+        <v>190</v>
+      </c>
+      <c r="C569" t="s">
+        <v>177</v>
+      </c>
+      <c r="D569" t="s">
+        <v>178</v>
+      </c>
+      <c r="E569" t="s">
+        <v>168</v>
+      </c>
+      <c r="F569" t="s">
+        <v>94</v>
+      </c>
+      <c r="G569" t="s">
+        <v>191</v>
+      </c>
+      <c r="H569" t="s">
+        <v>122</v>
+      </c>
+      <c r="I569">
+        <v>1</v>
+      </c>
+      <c r="J569" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="570" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A570" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B570" t="s">
+        <v>125</v>
+      </c>
+      <c r="C570" t="s">
+        <v>120</v>
+      </c>
+      <c r="D570" t="s">
+        <v>126</v>
+      </c>
+      <c r="E570" t="s">
+        <v>175</v>
+      </c>
+      <c r="F570" t="s">
+        <v>94</v>
+      </c>
+      <c r="G570">
+        <v>0</v>
+      </c>
+      <c r="H570" t="s">
+        <v>122</v>
+      </c>
+      <c r="I570">
+        <v>1</v>
+      </c>
+      <c r="J570" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="571" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A571" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B571" t="s">
+        <v>110</v>
+      </c>
+      <c r="C571" t="s">
+        <v>24</v>
+      </c>
+      <c r="D571" t="s">
+        <v>25</v>
+      </c>
+      <c r="E571" t="s">
+        <v>53</v>
+      </c>
+      <c r="F571" t="s">
+        <v>94</v>
+      </c>
+      <c r="G571">
+        <v>250</v>
+      </c>
+      <c r="H571" t="s">
+        <v>22</v>
+      </c>
+      <c r="I571">
+        <v>1</v>
+      </c>
+      <c r="J571" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="572" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A572" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B572" t="s">
+        <v>82</v>
+      </c>
+      <c r="C572" t="s">
+        <v>18</v>
+      </c>
+      <c r="D572" t="s">
+        <v>21</v>
+      </c>
+      <c r="E572" t="s">
+        <v>53</v>
+      </c>
+      <c r="F572" t="s">
+        <v>94</v>
+      </c>
+      <c r="G572">
+        <v>235</v>
+      </c>
+      <c r="H572" t="s">
+        <v>22</v>
+      </c>
+      <c r="I572">
+        <v>1</v>
+      </c>
+      <c r="J572" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="573" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A573" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B573" t="s">
+        <v>96</v>
+      </c>
+      <c r="C573" t="s">
+        <v>24</v>
+      </c>
+      <c r="D573" t="s">
+        <v>38</v>
+      </c>
+      <c r="E573" t="s">
+        <v>53</v>
+      </c>
+      <c r="F573" t="s">
+        <v>94</v>
+      </c>
+      <c r="G573">
+        <v>265</v>
+      </c>
+      <c r="H573" t="s">
+        <v>15</v>
+      </c>
+      <c r="I573">
+        <v>1</v>
+      </c>
+      <c r="J573" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="574" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A574" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B574" t="s">
+        <v>115</v>
+      </c>
+      <c r="C574" t="s">
+        <v>24</v>
+      </c>
+      <c r="D574" t="s">
+        <v>49</v>
+      </c>
+      <c r="E574" t="s">
+        <v>53</v>
+      </c>
+      <c r="F574" t="s">
+        <v>94</v>
+      </c>
+      <c r="G574">
+        <v>250</v>
+      </c>
+      <c r="H574" t="s">
+        <v>22</v>
+      </c>
+      <c r="I574">
+        <v>1</v>
+      </c>
+      <c r="J574" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="575" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A575" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B575" t="s">
+        <v>95</v>
+      </c>
+      <c r="C575" t="s">
+        <v>24</v>
+      </c>
+      <c r="D575" t="s">
+        <v>38</v>
+      </c>
+      <c r="E575" t="s">
+        <v>53</v>
+      </c>
+      <c r="F575" t="s">
+        <v>94</v>
+      </c>
+      <c r="G575">
+        <v>270</v>
+      </c>
+      <c r="H575" t="s">
+        <v>15</v>
+      </c>
+      <c r="I575">
+        <v>1</v>
+      </c>
+      <c r="J575" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="576" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A576" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B576" t="s">
+        <v>44</v>
+      </c>
+      <c r="C576" t="s">
+        <v>24</v>
+      </c>
+      <c r="D576" t="s">
+        <v>40</v>
+      </c>
+      <c r="E576" t="s">
+        <v>53</v>
+      </c>
+      <c r="F576" t="s">
+        <v>94</v>
+      </c>
+      <c r="G576">
+        <v>245</v>
+      </c>
+      <c r="H576" t="s">
+        <v>22</v>
+      </c>
+      <c r="I576">
+        <v>1</v>
+      </c>
+      <c r="J576" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="577" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A577" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B577" t="s">
+        <v>101</v>
+      </c>
+      <c r="C577" t="s">
+        <v>24</v>
+      </c>
+      <c r="D577" t="s">
+        <v>38</v>
+      </c>
+      <c r="E577" t="s">
+        <v>53</v>
+      </c>
+      <c r="F577" t="s">
+        <v>94</v>
+      </c>
+      <c r="G577">
+        <v>280</v>
+      </c>
+      <c r="H577" t="s">
+        <v>15</v>
+      </c>
+      <c r="I577">
+        <v>1</v>
+      </c>
+      <c r="J577" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="578" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A578" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B578" t="s">
+        <v>45</v>
+      </c>
+      <c r="C578" t="s">
+        <v>24</v>
+      </c>
+      <c r="D578" t="s">
+        <v>40</v>
+      </c>
+      <c r="E578" t="s">
+        <v>53</v>
+      </c>
+      <c r="F578" t="s">
+        <v>94</v>
+      </c>
+      <c r="G578">
+        <v>250</v>
+      </c>
+      <c r="H578" t="s">
+        <v>22</v>
+      </c>
+      <c r="I578">
+        <v>1</v>
+      </c>
+      <c r="J578" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="579" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A579" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B579" t="s">
+        <v>102</v>
+      </c>
+      <c r="C579" t="s">
+        <v>18</v>
+      </c>
+      <c r="D579" t="s">
+        <v>19</v>
+      </c>
+      <c r="E579" t="s">
+        <v>206</v>
+      </c>
+      <c r="F579" t="s">
+        <v>94</v>
+      </c>
+      <c r="G579">
+        <v>265</v>
+      </c>
+      <c r="H579" t="s">
+        <v>15</v>
+      </c>
+      <c r="I579">
+        <v>1</v>
+      </c>
+      <c r="J579" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{692C0987-0AC1-4C92-B948-F9C2D295FDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3AA500B-B4EF-4861-A01D-F40532B40C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{C6E149FC-A481-4BF4-9021-747FE4DEC56A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89FA3E3E-1521-4A20-BF7A-0973049BFDEA}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6094" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6287" uniqueCount="616">
   <si>
     <t>날짜</t>
   </si>
@@ -663,6 +663,27 @@
     <t>쿠팡/알파플러스</t>
   </si>
   <si>
+    <t>알리</t>
+  </si>
+  <si>
+    <t>X-20FA-GYGC</t>
+  </si>
+  <si>
+    <t>X-20FA-MAGC</t>
+  </si>
+  <si>
+    <t>X-20FA-MAGG</t>
+  </si>
+  <si>
+    <t>R-10F-BRMB</t>
+  </si>
+  <si>
+    <t>DPM641-APGY270</t>
+  </si>
+  <si>
+    <t>BJM931-WHGN270</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1116,9 +1137,6 @@
     <t>BJM931WHGN 바오지 남성 러닝화 화이트그린 265</t>
   </si>
   <si>
-    <t>BJM931-WHGN270</t>
-  </si>
-  <si>
     <t>BJM931WHGN 바오지 남성 러닝화 화이트그린 270</t>
   </si>
   <si>
@@ -1203,9 +1221,6 @@
     <t>DPM641APGY 바오지 남성 러닝화 살구그레이 265</t>
   </si>
   <si>
-    <t>DPM641-APGY270</t>
-  </si>
-  <si>
     <t>DPM641APGY 바오지 남성 러닝화 살구그레이 270</t>
   </si>
   <si>
@@ -1851,15 +1866,6 @@
     <t>X-20FS-MAGG</t>
   </si>
   <si>
-    <t>X-20FA-GYGC</t>
-  </si>
-  <si>
-    <t>X-20FA-MAGC</t>
-  </si>
-  <si>
-    <t>X-20FA-MAGG</t>
-  </si>
-  <si>
     <t>S-10HA-GYGC</t>
   </si>
   <si>
@@ -1870,9 +1876,6 @@
   </si>
   <si>
     <t>S-10RA-MAGG</t>
-  </si>
-  <si>
-    <t>R-10F-BRMB</t>
   </si>
   <si>
     <t>볼트겔 클리어겔 롤형 테이프 1m</t>
@@ -2270,7 +2273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCD4711-3105-4837-8904-D21C6B3000B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74345007-3239-4506-B929-9F280439916C}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2279,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2294,46 +2297,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="H1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="I1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="J1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="K1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="M1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="N1" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="O1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="R1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="S1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="T1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2341,7 +2344,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2368,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2386,7 +2389,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2403,7 +2406,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2418,37 +2421,37 @@
         <v>265</v>
       </c>
       <c r="G3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" t="s">
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2465,7 +2468,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2492,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2510,7 +2513,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2527,7 +2530,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2554,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2572,7 +2575,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2589,7 +2592,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2616,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2634,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2651,7 +2654,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2678,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2696,7 +2699,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2713,7 +2716,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2740,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2758,7 +2761,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2775,7 +2778,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2802,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2820,7 +2823,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2837,7 +2840,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2864,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2882,7 +2885,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2899,7 +2902,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2926,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2944,7 +2947,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2958,16 +2961,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C12" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2988,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3020,16 +3023,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C13" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D13" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3050,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3082,16 +3085,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B14" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C14" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3112,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3144,16 +3147,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" t="s">
         <v>243</v>
       </c>
-      <c r="C15" t="s">
-        <v>236</v>
-      </c>
       <c r="D15" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3174,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3206,16 +3209,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" t="s">
+        <v>243</v>
+      </c>
+      <c r="D16" t="s">
         <v>244</v>
-      </c>
-      <c r="B16" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" t="s">
-        <v>236</v>
-      </c>
-      <c r="D16" t="s">
-        <v>237</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3236,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3268,16 +3271,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C17" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D17" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3298,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3330,16 +3333,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B18" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D18" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3360,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3392,16 +3395,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C19" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D19" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3422,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3454,16 +3457,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B20" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C20" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D20" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3484,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3516,16 +3519,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B21" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3546,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3578,16 +3581,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B22" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C22" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D22" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3608,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3640,16 +3643,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C23" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D23" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3670,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3702,16 +3705,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C24" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D24" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3732,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3764,16 +3767,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C25" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D25" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3794,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3826,16 +3829,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C26" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D26" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3856,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3888,16 +3891,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C27" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D27" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3918,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3950,16 +3953,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D28" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3980,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4012,16 +4015,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C29" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D29" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4042,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4074,16 +4077,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C30" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D30" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4104,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4136,16 +4139,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C31" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D31" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4166,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4198,16 +4201,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C32" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D32" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4228,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4260,16 +4263,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C33" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D33" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4290,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4322,16 +4325,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C34" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D34" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4352,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4384,16 +4387,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B35" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C35" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D35" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4414,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4446,16 +4449,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>292</v>
+      </c>
+      <c r="B36" t="s">
+        <v>293</v>
+      </c>
+      <c r="C36" t="s">
+        <v>243</v>
+      </c>
+      <c r="D36" t="s">
         <v>285</v>
-      </c>
-      <c r="B36" t="s">
-        <v>286</v>
-      </c>
-      <c r="C36" t="s">
-        <v>236</v>
-      </c>
-      <c r="D36" t="s">
-        <v>278</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4476,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4508,16 +4511,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C37" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D37" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4538,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4570,16 +4573,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C38" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D38" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4600,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4632,16 +4635,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C39" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D39" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4662,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4694,16 +4697,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C40" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D40" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4724,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4756,16 +4759,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C41" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D41" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4786,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4818,16 +4821,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D42" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4848,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4880,16 +4883,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C43" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D43" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4910,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4942,16 +4945,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C44" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D44" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4972,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5004,16 +5007,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C45" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D45" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5034,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5066,16 +5069,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C46" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D46" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5096,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5128,16 +5131,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C47" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D47" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5158,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5190,16 +5193,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C48" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D48" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5220,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5252,16 +5255,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B49" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D49" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5282,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5314,16 +5317,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B50" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C50" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D50" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5344,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5376,16 +5379,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B51" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C51" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D51" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5406,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5438,16 +5441,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C52" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5468,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5500,16 +5503,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C53" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D53" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5530,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5562,16 +5565,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B54" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C54" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D54" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5592,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5624,16 +5627,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C55" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5654,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5686,16 +5689,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>333</v>
+      </c>
+      <c r="B56" t="s">
+        <v>334</v>
+      </c>
+      <c r="C56" t="s">
+        <v>243</v>
+      </c>
+      <c r="D56" t="s">
         <v>326</v>
-      </c>
-      <c r="B56" t="s">
-        <v>327</v>
-      </c>
-      <c r="C56" t="s">
-        <v>236</v>
-      </c>
-      <c r="D56" t="s">
-        <v>319</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5716,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5748,16 +5751,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B57" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C57" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5778,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5810,16 +5813,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B58" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C58" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5840,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5872,16 +5875,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B59" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="C59" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5902,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5934,16 +5937,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B60" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C60" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5964,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5996,16 +5999,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B61" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C61" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6026,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6058,16 +6061,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B62" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C62" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6088,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6120,16 +6123,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C63" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D63" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6150,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6182,16 +6185,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B64" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C64" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D64" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6212,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6244,16 +6247,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B65" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C65" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D65" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6274,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6306,16 +6309,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B66" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C66" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D66" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6336,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6371,7 +6374,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6398,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6416,7 +6419,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6433,7 +6436,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6460,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L68">
         <v>4</v>
@@ -6478,7 +6481,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6495,7 +6498,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6522,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L69">
         <v>9</v>
@@ -6540,7 +6543,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6557,7 +6560,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6584,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6602,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6619,7 +6622,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6646,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6664,7 +6667,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6678,10 +6681,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B72" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6708,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6726,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6743,7 +6746,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6770,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6788,7 +6791,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6802,10 +6805,10 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>358</v>
+        <v>213</v>
       </c>
       <c r="B74" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6820,37 +6823,37 @@
         <v>270</v>
       </c>
       <c r="G74">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74">
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74">
         <v>0</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" t="s">
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6867,7 +6870,7 @@
         <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6894,7 +6897,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6903,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="N75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75">
         <v>1</v>
@@ -6912,7 +6915,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6926,10 +6929,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B76" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6956,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6974,7 +6977,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6991,7 +6994,7 @@
         <v>184</v>
       </c>
       <c r="B77" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -7018,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -7036,7 +7039,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7050,10 +7053,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B78" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7080,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7098,7 +7101,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7112,10 +7115,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B79" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7142,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7160,7 +7163,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7177,7 +7180,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7204,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7222,7 +7225,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7236,10 +7239,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B81" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7266,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -7284,7 +7287,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7298,10 +7301,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B82" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7328,7 +7331,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7346,7 +7349,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7360,10 +7363,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B83" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7390,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7408,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7422,10 +7425,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B84" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7452,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7470,7 +7473,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7484,10 +7487,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B85" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7514,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7532,7 +7535,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7546,10 +7549,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B86" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7576,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7594,7 +7597,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7608,10 +7611,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B87" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7638,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7656,7 +7659,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7673,7 +7676,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7700,7 +7703,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L88">
         <v>2</v>
@@ -7718,7 +7721,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7732,10 +7735,10 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>387</v>
+        <v>212</v>
       </c>
       <c r="B89" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7750,37 +7753,37 @@
         <v>270</v>
       </c>
       <c r="G89">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H89">
         <v>0</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89">
         <v>0</v>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" t="s">
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7797,7 +7800,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7824,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L90">
         <v>2</v>
@@ -7833,7 +7836,7 @@
         <v>0</v>
       </c>
       <c r="N90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90">
         <v>1</v>
@@ -7842,7 +7845,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7856,10 +7859,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B91" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7886,7 +7889,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7904,7 +7907,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7918,10 +7921,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B92" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7948,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7966,7 +7969,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7983,7 +7986,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -8010,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8028,7 +8031,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8042,10 +8045,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B94" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8072,7 +8075,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8090,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8104,10 +8107,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B95" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8134,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8152,7 +8155,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8166,10 +8169,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B96" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8196,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8214,7 +8217,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8228,10 +8231,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B97" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8258,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8276,7 +8279,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8293,7 +8296,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8320,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L98">
         <v>5</v>
@@ -8338,7 +8341,7 @@
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8355,7 +8358,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8382,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L99">
         <v>2</v>
@@ -8400,7 +8403,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8417,7 +8420,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8444,7 +8447,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8453,7 +8456,7 @@
         <v>0</v>
       </c>
       <c r="N100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O100">
         <v>3</v>
@@ -8462,7 +8465,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8476,10 +8479,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B101" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8506,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8524,7 +8527,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8538,10 +8541,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B102" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8568,7 +8571,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8586,7 +8589,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8600,10 +8603,10 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B103" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8630,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -8648,7 +8651,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8665,7 +8668,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8692,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8710,7 +8713,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8724,10 +8727,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B105" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8754,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8772,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8789,7 +8792,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8816,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8834,7 +8837,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8848,10 +8851,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B107" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8878,7 +8881,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8896,7 +8899,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8913,7 +8916,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8940,7 +8943,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8958,7 +8961,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8975,7 +8978,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -9002,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -9020,7 +9023,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -9034,10 +9037,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B110" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -9064,7 +9067,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -9082,7 +9085,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -9096,10 +9099,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B111" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -9126,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9144,7 +9147,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9161,7 +9164,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9188,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9206,7 +9209,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9223,7 +9226,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9250,7 +9253,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L113">
         <v>7</v>
@@ -9268,7 +9271,7 @@
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9285,7 +9288,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9312,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L114">
         <v>10</v>
@@ -9330,7 +9333,7 @@
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9347,7 +9350,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9374,7 +9377,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9392,7 +9395,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9409,7 +9412,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9436,7 +9439,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L116">
         <v>4</v>
@@ -9454,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9471,7 +9474,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9498,7 +9501,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9516,7 +9519,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9533,7 +9536,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9560,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9578,7 +9581,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9595,7 +9598,7 @@
         <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9622,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L119">
         <v>2</v>
@@ -9640,7 +9643,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9657,7 +9660,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9684,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9702,7 +9705,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9719,7 +9722,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9746,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L121">
         <v>2</v>
@@ -9764,7 +9767,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9781,7 +9784,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9808,7 +9811,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L122">
         <v>5</v>
@@ -9817,7 +9820,7 @@
         <v>2</v>
       </c>
       <c r="N122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O122">
         <v>4</v>
@@ -9826,7 +9829,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9843,7 +9846,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9870,7 +9873,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -9888,7 +9891,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9905,7 +9908,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9932,7 +9935,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L124">
         <v>3</v>
@@ -9950,7 +9953,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9967,7 +9970,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9994,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -10012,7 +10015,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -10029,7 +10032,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -10056,7 +10059,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -10074,7 +10077,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -10091,7 +10094,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -10118,7 +10121,7 @@
         <v>10</v>
       </c>
       <c r="K127" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L127">
         <v>10</v>
@@ -10136,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -10153,7 +10156,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -10180,7 +10183,7 @@
         <v>7</v>
       </c>
       <c r="K128" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L128">
         <v>14</v>
@@ -10198,7 +10201,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -10215,7 +10218,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10242,7 +10245,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L129">
         <v>9</v>
@@ -10260,7 +10263,7 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10277,7 +10280,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10304,7 +10307,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10322,7 +10325,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10339,7 +10342,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10366,7 +10369,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10384,7 +10387,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10401,7 +10404,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10428,7 +10431,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L132">
         <v>18</v>
@@ -10446,7 +10449,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10463,7 +10466,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10478,37 +10481,37 @@
         <v>240</v>
       </c>
       <c r="G133">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J133">
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L133">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M133">
         <v>6</v>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P133" t="s">
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10525,7 +10528,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10540,37 +10543,37 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L134">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M134">
         <v>6</v>
       </c>
       <c r="N134">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O134">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P134" t="s">
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10587,7 +10590,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10614,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10632,7 +10635,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10649,7 +10652,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10676,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10694,7 +10697,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10711,7 +10714,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10738,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L137">
         <v>4</v>
@@ -10756,7 +10759,7 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10773,7 +10776,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10800,7 +10803,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L138">
         <v>4</v>
@@ -10818,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10835,7 +10838,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10862,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L139">
         <v>3</v>
@@ -10880,7 +10883,7 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10897,7 +10900,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10924,7 +10927,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L140">
         <v>3</v>
@@ -10942,7 +10945,7 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10959,7 +10962,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10986,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L141">
         <v>5</v>
@@ -10995,7 +10998,7 @@
         <v>0</v>
       </c>
       <c r="N141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O141">
         <v>5</v>
@@ -11004,7 +11007,7 @@
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -11021,7 +11024,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -11048,7 +11051,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -11066,7 +11069,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -11083,7 +11086,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -11110,7 +11113,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -11128,7 +11131,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -11145,7 +11148,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -11172,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -11181,7 +11184,7 @@
         <v>1</v>
       </c>
       <c r="N144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O144">
         <v>2</v>
@@ -11190,7 +11193,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -11204,10 +11207,10 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B145" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -11234,7 +11237,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -11252,7 +11255,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -11266,10 +11269,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B146" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -11296,7 +11299,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -11314,7 +11317,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -11331,7 +11334,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11358,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L147">
         <v>2</v>
@@ -11376,7 +11379,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11393,7 +11396,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11420,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L148">
         <v>6</v>
@@ -11438,7 +11441,7 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11455,7 +11458,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11482,7 +11485,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11500,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11517,7 +11520,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11544,7 +11547,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11562,7 +11565,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11579,7 +11582,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11606,7 +11609,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -11624,7 +11627,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11638,16 +11641,16 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B152" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C152" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D152" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11668,7 +11671,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11700,16 +11703,16 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B153" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C153" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D153" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11730,7 +11733,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11762,16 +11765,16 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B154" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C154" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D154" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11792,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11824,16 +11827,16 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>490</v>
+      </c>
+      <c r="B155" t="s">
+        <v>491</v>
+      </c>
+      <c r="C155" t="s">
+        <v>243</v>
+      </c>
+      <c r="D155" t="s">
         <v>485</v>
-      </c>
-      <c r="B155" t="s">
-        <v>486</v>
-      </c>
-      <c r="C155" t="s">
-        <v>236</v>
-      </c>
-      <c r="D155" t="s">
-        <v>480</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11854,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11886,16 +11889,16 @@
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B156" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C156" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D156" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11916,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11948,16 +11951,16 @@
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B157" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C157" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D157" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11978,7 +11981,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -12010,16 +12013,16 @@
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B158" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C158" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D158" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -12040,7 +12043,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -12072,16 +12075,16 @@
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B159" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C159" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D159" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -12102,7 +12105,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -12134,16 +12137,16 @@
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B160" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C160" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D160" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -12164,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -12196,16 +12199,16 @@
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B161" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C161" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D161" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -12226,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -12258,16 +12261,16 @@
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B162" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C162" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D162" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -12288,7 +12291,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -12320,16 +12323,16 @@
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B163" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C163" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D163" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -12350,7 +12353,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -12382,16 +12385,16 @@
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B164" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C164" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D164" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -12412,7 +12415,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -12444,16 +12447,16 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B165" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C165" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D165" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12474,7 +12477,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12506,16 +12509,16 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B166" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C166" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D166" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12536,7 +12539,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12568,16 +12571,16 @@
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B167" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C167" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D167" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12598,7 +12601,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12630,16 +12633,16 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B168" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C168" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D168" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12660,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12692,16 +12695,16 @@
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B169" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C169" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D169" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12722,7 +12725,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12754,16 +12757,16 @@
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B170" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C170" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D170" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12784,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12816,16 +12819,16 @@
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B171" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C171" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D171" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12846,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12881,7 +12884,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12908,7 +12911,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -12926,7 +12929,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12943,7 +12946,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12970,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L173">
         <v>7</v>
@@ -12988,7 +12991,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -13005,7 +13008,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -13032,7 +13035,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L174">
         <v>5</v>
@@ -13050,7 +13053,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -13067,7 +13070,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -13094,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -13112,7 +13115,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -13129,7 +13132,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -13156,7 +13159,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -13174,7 +13177,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -13191,7 +13194,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -13218,7 +13221,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -13236,7 +13239,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -13253,7 +13256,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -13280,7 +13283,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -13298,7 +13301,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -13315,7 +13318,7 @@
         <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -13342,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L179">
         <v>2</v>
@@ -13351,7 +13354,7 @@
         <v>0</v>
       </c>
       <c r="N179">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O179">
         <v>2</v>
@@ -13360,7 +13363,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -13377,7 +13380,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -13404,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L180">
         <v>3</v>
@@ -13422,7 +13425,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -13436,10 +13439,10 @@
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B181" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -13466,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -13484,7 +13487,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -13501,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -13528,7 +13531,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L182">
         <v>5</v>
@@ -13546,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13563,7 +13566,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13590,7 +13593,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L183">
         <v>5</v>
@@ -13599,7 +13602,7 @@
         <v>2</v>
       </c>
       <c r="N183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O183">
         <v>4</v>
@@ -13608,7 +13611,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13625,7 +13628,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13652,7 +13655,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L184">
         <v>2</v>
@@ -13670,7 +13673,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13687,7 +13690,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13714,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L185">
         <v>4</v>
@@ -13732,7 +13735,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13749,7 +13752,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13776,7 +13779,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13794,7 +13797,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13811,7 +13814,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13838,7 +13841,7 @@
         <v>6</v>
       </c>
       <c r="K187" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L187">
         <v>9</v>
@@ -13856,7 +13859,7 @@
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13873,7 +13876,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13900,7 +13903,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L188">
         <v>8</v>
@@ -13918,7 +13921,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13935,7 +13938,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13962,7 +13965,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13980,7 +13983,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -13997,7 +14000,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -14024,7 +14027,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -14042,7 +14045,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14059,7 +14062,7 @@
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -14086,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L191">
         <v>1</v>
@@ -14104,7 +14107,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -14121,7 +14124,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -14148,7 +14151,7 @@
         <v>9</v>
       </c>
       <c r="K192" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L192">
         <v>13</v>
@@ -14166,7 +14169,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -14183,7 +14186,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -14198,37 +14201,37 @@
         <v>240</v>
       </c>
       <c r="G193">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K193" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L193">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M193">
         <v>17</v>
       </c>
       <c r="N193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O193">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P193" t="s">
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -14245,7 +14248,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -14272,7 +14275,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L194">
         <v>24</v>
@@ -14281,7 +14284,7 @@
         <v>14</v>
       </c>
       <c r="N194">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O194">
         <v>20</v>
@@ -14290,7 +14293,7 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -14307,7 +14310,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -14334,7 +14337,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L195">
         <v>12</v>
@@ -14352,7 +14355,7 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -14369,7 +14372,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -14396,7 +14399,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L196">
         <v>9</v>
@@ -14414,7 +14417,7 @@
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -14428,10 +14431,10 @@
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B197" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -14458,7 +14461,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -14476,7 +14479,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -14493,7 +14496,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -14520,7 +14523,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -14538,7 +14541,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -14555,7 +14558,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -14582,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -14600,7 +14603,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -14614,10 +14617,10 @@
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B200" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -14644,7 +14647,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14662,7 +14665,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14679,7 +14682,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14706,7 +14709,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14724,7 +14727,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14738,10 +14741,10 @@
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B202" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14768,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14786,7 +14789,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14803,7 +14806,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14830,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14848,7 +14851,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14865,7 +14868,7 @@
         <v>195</v>
       </c>
       <c r="B204" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14880,37 +14883,37 @@
         <v>245</v>
       </c>
       <c r="G204">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H204">
         <v>0</v>
       </c>
       <c r="I204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J204">
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P204" t="s">
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14927,7 +14930,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14954,7 +14957,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14972,7 +14975,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14986,10 +14989,10 @@
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B206" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -15016,7 +15019,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -15034,7 +15037,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -15051,7 +15054,7 @@
         <v>200</v>
       </c>
       <c r="B207" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -15078,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L207">
         <v>1</v>
@@ -15096,7 +15099,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -15113,7 +15116,7 @@
         <v>197</v>
       </c>
       <c r="B208" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -15140,7 +15143,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L208">
         <v>1</v>
@@ -15158,7 +15161,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -15172,10 +15175,10 @@
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B209" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -15202,7 +15205,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -15220,7 +15223,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -15237,7 +15240,7 @@
         <v>203</v>
       </c>
       <c r="B210" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -15264,7 +15267,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L210">
         <v>1</v>
@@ -15282,7 +15285,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -15299,7 +15302,7 @@
         <v>198</v>
       </c>
       <c r="B211" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -15326,7 +15329,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L211">
         <v>2</v>
@@ -15344,7 +15347,7 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -15358,10 +15361,10 @@
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B212" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -15388,7 +15391,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -15406,7 +15409,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -15423,7 +15426,7 @@
         <v>199</v>
       </c>
       <c r="B213" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -15450,7 +15453,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L213">
         <v>2</v>
@@ -15468,7 +15471,7 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -15485,7 +15488,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -15512,7 +15515,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L214">
         <v>2</v>
@@ -15530,7 +15533,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15547,7 +15550,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -15574,7 +15577,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L215">
         <v>3</v>
@@ -15592,7 +15595,7 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -15606,10 +15609,10 @@
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B216" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -15636,7 +15639,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -15654,7 +15657,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15671,7 +15674,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -15698,7 +15701,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L217">
         <v>7</v>
@@ -15707,7 +15710,7 @@
         <v>6</v>
       </c>
       <c r="N217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O217">
         <v>7</v>
@@ -15716,7 +15719,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15733,7 +15736,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -15760,7 +15763,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L218">
         <v>4</v>
@@ -15769,7 +15772,7 @@
         <v>3</v>
       </c>
       <c r="N218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O218">
         <v>4</v>
@@ -15778,7 +15781,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15795,7 +15798,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15822,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L219">
         <v>5</v>
@@ -15840,7 +15843,7 @@
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15857,7 +15860,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15884,7 +15887,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L220">
         <v>4</v>
@@ -15902,7 +15905,7 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15916,10 +15919,10 @@
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B221" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15946,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15964,7 +15967,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15981,7 +15984,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -16008,7 +16011,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -16026,7 +16029,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -16043,7 +16046,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -16070,7 +16073,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L223">
         <v>14</v>
@@ -16079,7 +16082,7 @@
         <v>8</v>
       </c>
       <c r="N223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O223">
         <v>14</v>
@@ -16088,7 +16091,7 @@
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -16105,7 +16108,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -16132,7 +16135,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -16150,7 +16153,7 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -16167,7 +16170,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -16194,7 +16197,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L225">
         <v>10</v>
@@ -16212,7 +16215,7 @@
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -16229,7 +16232,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -16256,7 +16259,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -16274,7 +16277,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -16291,7 +16294,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -16318,7 +16321,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L227">
         <v>14</v>
@@ -16327,7 +16330,7 @@
         <v>10</v>
       </c>
       <c r="N227">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O227">
         <v>14</v>
@@ -16336,7 +16339,7 @@
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -16353,7 +16356,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -16380,7 +16383,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L228">
         <v>15</v>
@@ -16398,7 +16401,7 @@
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -16415,7 +16418,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -16442,7 +16445,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L229">
         <v>15</v>
@@ -16460,7 +16463,7 @@
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -16477,7 +16480,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -16504,7 +16507,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -16522,7 +16525,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -16539,7 +16542,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -16566,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -16584,7 +16587,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -16613,7 +16616,7 @@
         <v>122</v>
       </c>
       <c r="G232">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -16625,19 +16628,19 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L232">
+        <v>5</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
         <v>3</v>
       </c>
-      <c r="M232">
-        <v>0</v>
-      </c>
-      <c r="N232">
-        <v>1</v>
-      </c>
       <c r="O232">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P232" t="s">
         <v>13</v>
@@ -16678,7 +16681,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L233">
         <v>7</v>
@@ -16704,10 +16707,10 @@
     </row>
     <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="B234" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -16731,7 +16734,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -16784,7 +16787,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L235">
         <v>1</v>
@@ -16837,7 +16840,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L236">
         <v>1</v>
@@ -16890,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L237">
         <v>1</v>
@@ -16916,10 +16919,10 @@
     </row>
     <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B238" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -16943,7 +16946,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -16969,10 +16972,10 @@
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B239" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -16996,7 +16999,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -17022,10 +17025,10 @@
     </row>
     <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>603</v>
+        <v>208</v>
       </c>
       <c r="B240" t="s">
-        <v>603</v>
+        <v>208</v>
       </c>
       <c r="C240" t="s">
         <v>120</v>
@@ -17037,7 +17040,7 @@
         <v>122</v>
       </c>
       <c r="G240">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -17049,19 +17052,19 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L240">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M240">
         <v>0</v>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P240" t="s">
         <v>13</v>
@@ -17090,7 +17093,7 @@
         <v>122</v>
       </c>
       <c r="G241">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H241">
         <v>0</v>
@@ -17102,19 +17105,19 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L241">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M241">
         <v>0</v>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O241">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P241" t="s">
         <v>13</v>
@@ -17128,10 +17131,10 @@
     </row>
     <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>604</v>
+        <v>209</v>
       </c>
       <c r="B242" t="s">
-        <v>604</v>
+        <v>209</v>
       </c>
       <c r="C242" t="s">
         <v>120</v>
@@ -17143,7 +17146,7 @@
         <v>122</v>
       </c>
       <c r="G242">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H242">
         <v>0</v>
@@ -17155,19 +17158,19 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L242">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M242">
         <v>0</v>
       </c>
       <c r="N242">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O242">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P242" t="s">
         <v>13</v>
@@ -17181,10 +17184,10 @@
     </row>
     <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>605</v>
+        <v>210</v>
       </c>
       <c r="B243" t="s">
-        <v>605</v>
+        <v>210</v>
       </c>
       <c r="C243" t="s">
         <v>120</v>
@@ -17196,7 +17199,7 @@
         <v>122</v>
       </c>
       <c r="G243">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -17208,19 +17211,19 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M243">
         <v>0</v>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P243" t="s">
         <v>13</v>
@@ -17234,10 +17237,10 @@
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B244" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -17261,7 +17264,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -17314,7 +17317,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L245">
         <v>2</v>
@@ -17367,7 +17370,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -17420,7 +17423,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L247">
         <v>2</v>
@@ -17429,7 +17432,7 @@
         <v>0</v>
       </c>
       <c r="N247">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O247">
         <v>2</v>
@@ -17446,10 +17449,10 @@
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B248" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
@@ -17473,7 +17476,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -17514,7 +17517,7 @@
         <v>122</v>
       </c>
       <c r="G249">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -17526,19 +17529,19 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M249">
         <v>0</v>
       </c>
       <c r="N249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P249" t="s">
         <v>13</v>
@@ -17552,10 +17555,10 @@
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B250" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
@@ -17579,7 +17582,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -17605,10 +17608,10 @@
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B251" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
@@ -17632,7 +17635,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -17673,7 +17676,7 @@
         <v>122</v>
       </c>
       <c r="G252">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -17685,19 +17688,19 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L252">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M252">
         <v>0</v>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O252">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P252" t="s">
         <v>13</v>
@@ -17726,7 +17729,7 @@
         <v>122</v>
       </c>
       <c r="G253">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -17738,19 +17741,19 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L253">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M253">
         <v>0</v>
       </c>
       <c r="N253">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O253">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P253" t="s">
         <v>13</v>
@@ -17779,7 +17782,7 @@
         <v>122</v>
       </c>
       <c r="G254">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H254">
         <v>0</v>
@@ -17791,19 +17794,19 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L254">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M254">
         <v>0</v>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O254">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P254" t="s">
         <v>13</v>
@@ -17832,7 +17835,7 @@
         <v>122</v>
       </c>
       <c r="G255">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -17844,19 +17847,19 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L255">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M255">
         <v>0</v>
       </c>
       <c r="N255">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O255">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P255" t="s">
         <v>13</v>
@@ -17885,7 +17888,7 @@
         <v>122</v>
       </c>
       <c r="G256">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -17897,19 +17900,19 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L256">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M256">
         <v>0</v>
       </c>
       <c r="N256">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O256">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P256" t="s">
         <v>13</v>
@@ -17923,10 +17926,10 @@
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>610</v>
+        <v>211</v>
       </c>
       <c r="B257" t="s">
-        <v>610</v>
+        <v>211</v>
       </c>
       <c r="C257" t="s">
         <v>120</v>
@@ -17938,7 +17941,7 @@
         <v>122</v>
       </c>
       <c r="G257">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -17950,19 +17953,19 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M257">
         <v>0</v>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P257" t="s">
         <v>13</v>
@@ -17991,7 +17994,7 @@
         <v>122</v>
       </c>
       <c r="G258">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -18003,19 +18006,19 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L258">
+        <v>5</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
+      </c>
+      <c r="N258">
         <v>3</v>
       </c>
-      <c r="M258">
-        <v>0</v>
-      </c>
-      <c r="N258">
-        <v>1</v>
-      </c>
       <c r="O258">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P258" t="s">
         <v>13</v>
@@ -18044,7 +18047,7 @@
         <v>122</v>
       </c>
       <c r="G259">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H259">
         <v>0</v>
@@ -18056,19 +18059,19 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L259">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M259">
         <v>0</v>
       </c>
       <c r="N259">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O259">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P259" t="s">
         <v>13</v>
@@ -18085,7 +18088,7 @@
         <v>176</v>
       </c>
       <c r="B260" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C260" t="s">
         <v>177</v>
@@ -18100,7 +18103,7 @@
         <v>192</v>
       </c>
       <c r="G260">
-        <v>1987</v>
+        <v>1981</v>
       </c>
       <c r="I260">
         <v>0</v>
@@ -18109,19 +18112,19 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L260">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M260">
         <v>0</v>
       </c>
       <c r="N260">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O260">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="P260" t="s">
         <v>180</v>
@@ -18138,7 +18141,7 @@
         <v>201</v>
       </c>
       <c r="B261" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C261" t="s">
         <v>177</v>
@@ -18162,7 +18165,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L261">
         <v>12</v>
@@ -18191,7 +18194,7 @@
         <v>187</v>
       </c>
       <c r="B262" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C262" t="s">
         <v>177</v>
@@ -18206,7 +18209,7 @@
         <v>189</v>
       </c>
       <c r="G262">
-        <v>5988</v>
+        <v>5982</v>
       </c>
       <c r="I262">
         <v>0</v>
@@ -18215,19 +18218,19 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L262">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M262">
         <v>0</v>
       </c>
       <c r="N262">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O262">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P262" t="s">
         <v>180</v>
@@ -18244,7 +18247,7 @@
         <v>190</v>
       </c>
       <c r="B263" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C263" t="s">
         <v>177</v>
@@ -18259,7 +18262,7 @@
         <v>191</v>
       </c>
       <c r="G263">
-        <v>1987</v>
+        <v>1983</v>
       </c>
       <c r="I263">
         <v>0</v>
@@ -18268,19 +18271,19 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L263">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M263">
         <v>0</v>
       </c>
       <c r="N263">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O263">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P263" t="s">
         <v>180</v>
@@ -18299,8 +18302,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB3E4D61-26B4-4D01-AF16-B9CCEE3895AC}">
-  <dimension ref="A1:J579"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43371F8D-EC53-49F2-A643-7D177B6DF52B}">
+  <dimension ref="A1:J606"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -36828,6 +36831,870 @@
         <v>1</v>
       </c>
       <c r="J579" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="580" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A580" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B580" t="s">
+        <v>102</v>
+      </c>
+      <c r="C580" t="s">
+        <v>18</v>
+      </c>
+      <c r="D580" t="s">
+        <v>19</v>
+      </c>
+      <c r="E580" t="s">
+        <v>206</v>
+      </c>
+      <c r="F580" t="s">
+        <v>94</v>
+      </c>
+      <c r="G580">
+        <v>265</v>
+      </c>
+      <c r="H580" t="s">
+        <v>15</v>
+      </c>
+      <c r="I580">
+        <v>1</v>
+      </c>
+      <c r="J580" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="581" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A581" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B581" t="s">
+        <v>195</v>
+      </c>
+      <c r="C581" t="s">
+        <v>24</v>
+      </c>
+      <c r="D581" t="s">
+        <v>47</v>
+      </c>
+      <c r="E581" t="s">
+        <v>100</v>
+      </c>
+      <c r="F581" t="s">
+        <v>66</v>
+      </c>
+      <c r="G581">
+        <v>245</v>
+      </c>
+      <c r="H581" t="s">
+        <v>22</v>
+      </c>
+      <c r="I581">
+        <v>1</v>
+      </c>
+      <c r="J581" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="582" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A582" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B582" t="s">
+        <v>125</v>
+      </c>
+      <c r="C582" t="s">
+        <v>120</v>
+      </c>
+      <c r="D582" t="s">
+        <v>126</v>
+      </c>
+      <c r="E582" t="s">
+        <v>133</v>
+      </c>
+      <c r="F582" t="s">
+        <v>94</v>
+      </c>
+      <c r="G582">
+        <v>0</v>
+      </c>
+      <c r="H582" t="s">
+        <v>122</v>
+      </c>
+      <c r="I582">
+        <v>1</v>
+      </c>
+      <c r="J582" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="583" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A583" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B583" t="s">
+        <v>185</v>
+      </c>
+      <c r="C583" t="s">
+        <v>120</v>
+      </c>
+      <c r="D583" t="s">
+        <v>186</v>
+      </c>
+      <c r="E583" t="s">
+        <v>133</v>
+      </c>
+      <c r="F583" t="s">
+        <v>94</v>
+      </c>
+      <c r="G583">
+        <v>0</v>
+      </c>
+      <c r="H583" t="s">
+        <v>122</v>
+      </c>
+      <c r="I583">
+        <v>1</v>
+      </c>
+      <c r="J583" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="584" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A584" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B584" t="s">
+        <v>125</v>
+      </c>
+      <c r="C584" t="s">
+        <v>120</v>
+      </c>
+      <c r="D584" t="s">
+        <v>126</v>
+      </c>
+      <c r="E584" t="s">
+        <v>133</v>
+      </c>
+      <c r="F584" t="s">
+        <v>94</v>
+      </c>
+      <c r="G584">
+        <v>0</v>
+      </c>
+      <c r="H584" t="s">
+        <v>122</v>
+      </c>
+      <c r="I584">
+        <v>1</v>
+      </c>
+      <c r="J584" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="585" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A585" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B585" t="s">
+        <v>167</v>
+      </c>
+      <c r="C585" t="s">
+        <v>120</v>
+      </c>
+      <c r="D585" t="s">
+        <v>121</v>
+      </c>
+      <c r="E585" t="s">
+        <v>207</v>
+      </c>
+      <c r="F585" t="s">
+        <v>94</v>
+      </c>
+      <c r="G585">
+        <v>0</v>
+      </c>
+      <c r="H585" t="s">
+        <v>122</v>
+      </c>
+      <c r="I585">
+        <v>1</v>
+      </c>
+      <c r="J585" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="586" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A586" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B586" t="s">
+        <v>176</v>
+      </c>
+      <c r="C586" t="s">
+        <v>177</v>
+      </c>
+      <c r="D586" t="s">
+        <v>178</v>
+      </c>
+      <c r="E586" t="s">
+        <v>188</v>
+      </c>
+      <c r="F586" t="s">
+        <v>94</v>
+      </c>
+      <c r="G586" t="s">
+        <v>192</v>
+      </c>
+      <c r="H586" t="s">
+        <v>122</v>
+      </c>
+      <c r="I586">
+        <v>2</v>
+      </c>
+      <c r="J586" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="587" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A587" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B587" t="s">
+        <v>187</v>
+      </c>
+      <c r="C587" t="s">
+        <v>177</v>
+      </c>
+      <c r="D587" t="s">
+        <v>178</v>
+      </c>
+      <c r="E587" t="s">
+        <v>188</v>
+      </c>
+      <c r="F587" t="s">
+        <v>94</v>
+      </c>
+      <c r="G587" t="s">
+        <v>189</v>
+      </c>
+      <c r="H587" t="s">
+        <v>122</v>
+      </c>
+      <c r="I587">
+        <v>6</v>
+      </c>
+      <c r="J587" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="588" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A588" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B588" t="s">
+        <v>208</v>
+      </c>
+      <c r="C588" t="s">
+        <v>120</v>
+      </c>
+      <c r="D588" t="s">
+        <v>135</v>
+      </c>
+      <c r="E588" t="s">
+        <v>188</v>
+      </c>
+      <c r="F588" t="s">
+        <v>94</v>
+      </c>
+      <c r="G588">
+        <v>0</v>
+      </c>
+      <c r="H588" t="s">
+        <v>122</v>
+      </c>
+      <c r="I588">
+        <v>2</v>
+      </c>
+      <c r="J588" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="589" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A589" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B589" t="s">
+        <v>134</v>
+      </c>
+      <c r="C589" t="s">
+        <v>120</v>
+      </c>
+      <c r="D589" t="s">
+        <v>135</v>
+      </c>
+      <c r="E589" t="s">
+        <v>188</v>
+      </c>
+      <c r="F589" t="s">
+        <v>94</v>
+      </c>
+      <c r="G589">
+        <v>0</v>
+      </c>
+      <c r="H589" t="s">
+        <v>122</v>
+      </c>
+      <c r="I589">
+        <v>2</v>
+      </c>
+      <c r="J589" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="590" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A590" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B590" t="s">
+        <v>190</v>
+      </c>
+      <c r="C590" t="s">
+        <v>177</v>
+      </c>
+      <c r="D590" t="s">
+        <v>178</v>
+      </c>
+      <c r="E590" t="s">
+        <v>188</v>
+      </c>
+      <c r="F590" t="s">
+        <v>94</v>
+      </c>
+      <c r="G590" t="s">
+        <v>191</v>
+      </c>
+      <c r="H590" t="s">
+        <v>122</v>
+      </c>
+      <c r="I590">
+        <v>4</v>
+      </c>
+      <c r="J590" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="591" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A591" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B591" t="s">
+        <v>119</v>
+      </c>
+      <c r="C591" t="s">
+        <v>120</v>
+      </c>
+      <c r="D591" t="s">
+        <v>121</v>
+      </c>
+      <c r="E591" t="s">
+        <v>188</v>
+      </c>
+      <c r="F591" t="s">
+        <v>94</v>
+      </c>
+      <c r="G591">
+        <v>0</v>
+      </c>
+      <c r="H591" t="s">
+        <v>122</v>
+      </c>
+      <c r="I591">
+        <v>2</v>
+      </c>
+      <c r="J591" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="592" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A592" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B592" t="s">
+        <v>132</v>
+      </c>
+      <c r="C592" t="s">
+        <v>120</v>
+      </c>
+      <c r="D592" t="s">
+        <v>121</v>
+      </c>
+      <c r="E592" t="s">
+        <v>188</v>
+      </c>
+      <c r="F592" t="s">
+        <v>94</v>
+      </c>
+      <c r="G592">
+        <v>0</v>
+      </c>
+      <c r="H592" t="s">
+        <v>122</v>
+      </c>
+      <c r="I592">
+        <v>2</v>
+      </c>
+      <c r="J592" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="593" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A593" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B593" t="s">
+        <v>209</v>
+      </c>
+      <c r="C593" t="s">
+        <v>120</v>
+      </c>
+      <c r="D593" t="s">
+        <v>135</v>
+      </c>
+      <c r="E593" t="s">
+        <v>188</v>
+      </c>
+      <c r="F593" t="s">
+        <v>94</v>
+      </c>
+      <c r="G593">
+        <v>0</v>
+      </c>
+      <c r="H593" t="s">
+        <v>122</v>
+      </c>
+      <c r="I593">
+        <v>2</v>
+      </c>
+      <c r="J593" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="594" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A594" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B594" t="s">
+        <v>210</v>
+      </c>
+      <c r="C594" t="s">
+        <v>120</v>
+      </c>
+      <c r="D594" t="s">
+        <v>135</v>
+      </c>
+      <c r="E594" t="s">
+        <v>188</v>
+      </c>
+      <c r="F594" t="s">
+        <v>94</v>
+      </c>
+      <c r="G594">
+        <v>0</v>
+      </c>
+      <c r="H594" t="s">
+        <v>122</v>
+      </c>
+      <c r="I594">
+        <v>2</v>
+      </c>
+      <c r="J594" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="595" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A595" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B595" t="s">
+        <v>176</v>
+      </c>
+      <c r="C595" t="s">
+        <v>177</v>
+      </c>
+      <c r="D595" t="s">
+        <v>178</v>
+      </c>
+      <c r="E595" t="s">
+        <v>188</v>
+      </c>
+      <c r="F595" t="s">
+        <v>94</v>
+      </c>
+      <c r="G595" t="s">
+        <v>192</v>
+      </c>
+      <c r="H595" t="s">
+        <v>122</v>
+      </c>
+      <c r="I595">
+        <v>4</v>
+      </c>
+      <c r="J595" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="596" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A596" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B596" t="s">
+        <v>139</v>
+      </c>
+      <c r="C596" t="s">
+        <v>120</v>
+      </c>
+      <c r="D596" t="s">
+        <v>140</v>
+      </c>
+      <c r="E596" t="s">
+        <v>188</v>
+      </c>
+      <c r="F596" t="s">
+        <v>94</v>
+      </c>
+      <c r="G596">
+        <v>0</v>
+      </c>
+      <c r="H596" t="s">
+        <v>122</v>
+      </c>
+      <c r="I596">
+        <v>2</v>
+      </c>
+      <c r="J596" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A597" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B597" t="s">
+        <v>204</v>
+      </c>
+      <c r="C597" t="s">
+        <v>120</v>
+      </c>
+      <c r="D597" t="s">
+        <v>140</v>
+      </c>
+      <c r="E597" t="s">
+        <v>188</v>
+      </c>
+      <c r="F597" t="s">
+        <v>94</v>
+      </c>
+      <c r="G597">
+        <v>0</v>
+      </c>
+      <c r="H597" t="s">
+        <v>122</v>
+      </c>
+      <c r="I597">
+        <v>2</v>
+      </c>
+      <c r="J597" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="598" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A598" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B598" t="s">
+        <v>137</v>
+      </c>
+      <c r="C598" t="s">
+        <v>120</v>
+      </c>
+      <c r="D598" t="s">
+        <v>138</v>
+      </c>
+      <c r="E598" t="s">
+        <v>188</v>
+      </c>
+      <c r="F598" t="s">
+        <v>94</v>
+      </c>
+      <c r="G598">
+        <v>0</v>
+      </c>
+      <c r="H598" t="s">
+        <v>122</v>
+      </c>
+      <c r="I598">
+        <v>2</v>
+      </c>
+      <c r="J598" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="599" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A599" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B599" t="s">
+        <v>211</v>
+      </c>
+      <c r="C599" t="s">
+        <v>120</v>
+      </c>
+      <c r="D599" t="s">
+        <v>138</v>
+      </c>
+      <c r="E599" t="s">
+        <v>188</v>
+      </c>
+      <c r="F599" t="s">
+        <v>94</v>
+      </c>
+      <c r="G599">
+        <v>0</v>
+      </c>
+      <c r="H599" t="s">
+        <v>122</v>
+      </c>
+      <c r="I599">
+        <v>2</v>
+      </c>
+      <c r="J599" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="600" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A600" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B600" t="s">
+        <v>169</v>
+      </c>
+      <c r="C600" t="s">
+        <v>120</v>
+      </c>
+      <c r="D600" t="s">
+        <v>121</v>
+      </c>
+      <c r="E600" t="s">
+        <v>188</v>
+      </c>
+      <c r="F600" t="s">
+        <v>94</v>
+      </c>
+      <c r="G600">
+        <v>0</v>
+      </c>
+      <c r="H600" t="s">
+        <v>122</v>
+      </c>
+      <c r="I600">
+        <v>2</v>
+      </c>
+      <c r="J600" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="601" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A601" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B601" t="s">
+        <v>167</v>
+      </c>
+      <c r="C601" t="s">
+        <v>120</v>
+      </c>
+      <c r="D601" t="s">
+        <v>121</v>
+      </c>
+      <c r="E601" t="s">
+        <v>188</v>
+      </c>
+      <c r="F601" t="s">
+        <v>94</v>
+      </c>
+      <c r="G601">
+        <v>0</v>
+      </c>
+      <c r="H601" t="s">
+        <v>122</v>
+      </c>
+      <c r="I601">
+        <v>2</v>
+      </c>
+      <c r="J601" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A602" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B602" t="s">
+        <v>67</v>
+      </c>
+      <c r="C602" t="s">
+        <v>24</v>
+      </c>
+      <c r="D602" t="s">
+        <v>40</v>
+      </c>
+      <c r="E602" t="s">
+        <v>130</v>
+      </c>
+      <c r="F602" t="s">
+        <v>94</v>
+      </c>
+      <c r="G602">
+        <v>240</v>
+      </c>
+      <c r="H602" t="s">
+        <v>22</v>
+      </c>
+      <c r="I602">
+        <v>1</v>
+      </c>
+      <c r="J602" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="603" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A603" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B603" t="s">
+        <v>78</v>
+      </c>
+      <c r="C603" t="s">
+        <v>18</v>
+      </c>
+      <c r="D603" t="s">
+        <v>21</v>
+      </c>
+      <c r="E603" t="s">
+        <v>130</v>
+      </c>
+      <c r="F603" t="s">
+        <v>94</v>
+      </c>
+      <c r="G603">
+        <v>240</v>
+      </c>
+      <c r="H603" t="s">
+        <v>22</v>
+      </c>
+      <c r="I603">
+        <v>1</v>
+      </c>
+      <c r="J603" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="604" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A604" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B604" t="s">
+        <v>212</v>
+      </c>
+      <c r="C604" t="s">
+        <v>24</v>
+      </c>
+      <c r="D604" t="s">
+        <v>30</v>
+      </c>
+      <c r="E604" t="s">
+        <v>130</v>
+      </c>
+      <c r="F604" t="s">
+        <v>94</v>
+      </c>
+      <c r="G604">
+        <v>270</v>
+      </c>
+      <c r="H604" t="s">
+        <v>15</v>
+      </c>
+      <c r="I604">
+        <v>1</v>
+      </c>
+      <c r="J604" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="605" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A605" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B605" t="s">
+        <v>213</v>
+      </c>
+      <c r="C605" t="s">
+        <v>24</v>
+      </c>
+      <c r="D605" t="s">
+        <v>93</v>
+      </c>
+      <c r="E605" t="s">
+        <v>130</v>
+      </c>
+      <c r="F605" t="s">
+        <v>94</v>
+      </c>
+      <c r="G605">
+        <v>270</v>
+      </c>
+      <c r="H605" t="s">
+        <v>15</v>
+      </c>
+      <c r="I605">
+        <v>1</v>
+      </c>
+      <c r="J605" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="606" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A606" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B606" t="s">
+        <v>61</v>
+      </c>
+      <c r="C606" t="s">
+        <v>18</v>
+      </c>
+      <c r="D606" t="s">
+        <v>21</v>
+      </c>
+      <c r="E606" t="s">
+        <v>53</v>
+      </c>
+      <c r="F606" t="s">
+        <v>94</v>
+      </c>
+      <c r="G606">
+        <v>245</v>
+      </c>
+      <c r="H606" t="s">
+        <v>22</v>
+      </c>
+      <c r="I606">
+        <v>1</v>
+      </c>
+      <c r="J606" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3AA500B-B4EF-4861-A01D-F40532B40C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35F3909A-8540-4BE6-B20B-E71AB04C681E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{89FA3E3E-1521-4A20-BF7A-0973049BFDEA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{350BBA77-1C9F-4D8D-AE32-AE1C180B77B1}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6287" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6448" uniqueCount="616">
   <si>
     <t>날짜</t>
   </si>
@@ -684,6 +684,21 @@
     <t>BJM931-WHGN270</t>
   </si>
   <si>
+    <t>X-20FS-MAGC</t>
+  </si>
+  <si>
+    <t>X-20FS-MAGG</t>
+  </si>
+  <si>
+    <t>S-10RA-MAGC</t>
+  </si>
+  <si>
+    <t>X-10H-MAGC</t>
+  </si>
+  <si>
+    <t>DPM644-BK265</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1296,9 +1311,6 @@
     <t>https://ecimg.cafe24img.com/pg2850b59880769092/doogenkorea2/web/product/medium/20260511/42d5aa739d3370e66e2d8d12d782c91f.jpg</t>
   </si>
   <si>
-    <t>DPM644-BK265</t>
-  </si>
-  <si>
     <t>DPM644BK 바오지 남성 러닝화 블랙 265</t>
   </si>
   <si>
@@ -1857,22 +1869,10 @@
     <t>ECW304WHPK 바오지 여성 러닝화 화이트핑크 255</t>
   </si>
   <si>
-    <t>X-10H-MAGC</t>
-  </si>
-  <si>
-    <t>X-20FS-MAGC</t>
-  </si>
-  <si>
-    <t>X-20FS-MAGG</t>
-  </si>
-  <si>
     <t>S-10HA-GYGC</t>
   </si>
   <si>
     <t>S-10RA-GYGC</t>
-  </si>
-  <si>
-    <t>S-10RA-MAGC</t>
   </si>
   <si>
     <t>S-10RA-MAGG</t>
@@ -2273,7 +2273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74345007-3239-4506-B929-9F280439916C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFDFECA-6A42-4082-92B2-02E22FDF7C51}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2282,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2297,46 +2297,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="N1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="O1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="R1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="S1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="T1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2344,7 +2344,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2371,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2389,7 +2389,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2406,7 +2406,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -2451,7 +2451,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2468,7 +2468,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L4">
         <v>4</v>
@@ -2513,7 +2513,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2575,7 +2575,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2592,7 +2592,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2637,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2699,7 +2699,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2761,7 +2761,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2778,7 +2778,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2823,7 +2823,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2840,7 +2840,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2885,7 +2885,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2947,7 +2947,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2961,16 +2961,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B12" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D12" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3023,16 +3023,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B13" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D13" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3085,16 +3085,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" t="s">
         <v>248</v>
       </c>
-      <c r="C14" t="s">
-        <v>243</v>
-      </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3147,16 +3147,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" t="s">
+        <v>248</v>
+      </c>
+      <c r="D15" t="s">
         <v>249</v>
-      </c>
-      <c r="B15" t="s">
-        <v>250</v>
-      </c>
-      <c r="C15" t="s">
-        <v>243</v>
-      </c>
-      <c r="D15" t="s">
-        <v>244</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3209,16 +3209,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B16" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C16" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3271,16 +3271,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B17" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C17" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D17" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3301,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3333,16 +3333,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B18" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C18" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D18" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3395,16 +3395,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C19" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D19" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3457,16 +3457,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B20" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C20" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D20" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3519,16 +3519,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B21" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C21" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D21" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3581,16 +3581,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B22" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C22" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D22" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3643,16 +3643,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B23" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C23" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D23" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3705,16 +3705,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C24" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D24" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3767,16 +3767,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C25" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D25" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C26" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D26" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3891,16 +3891,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C27" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D27" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3921,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3953,16 +3953,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C28" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4015,16 +4015,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C29" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D29" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4077,16 +4077,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C30" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D30" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4107,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4139,16 +4139,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C31" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D31" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4201,16 +4201,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C32" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D32" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4263,16 +4263,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C33" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D33" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4325,16 +4325,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C34" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D34" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4355,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4387,16 +4387,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>295</v>
+      </c>
+      <c r="B35" t="s">
+        <v>296</v>
+      </c>
+      <c r="C35" t="s">
+        <v>248</v>
+      </c>
+      <c r="D35" t="s">
         <v>290</v>
-      </c>
-      <c r="B35" t="s">
-        <v>291</v>
-      </c>
-      <c r="C35" t="s">
-        <v>243</v>
-      </c>
-      <c r="D35" t="s">
-        <v>285</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4449,16 +4449,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C36" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D36" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4511,16 +4511,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C37" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D37" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4573,16 +4573,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C38" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D38" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4603,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4635,16 +4635,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C39" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D39" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4665,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4697,16 +4697,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C40" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D40" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4759,16 +4759,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C41" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D41" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4789,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4821,16 +4821,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C42" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D42" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4883,16 +4883,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C43" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D43" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4945,16 +4945,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C44" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D44" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5007,16 +5007,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B45" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C45" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D45" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5069,16 +5069,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C46" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D46" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5131,16 +5131,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D47" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5193,16 +5193,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C48" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D48" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5255,16 +5255,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B49" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C49" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D49" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5317,16 +5317,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B50" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C50" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D50" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5347,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5379,16 +5379,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B51" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C51" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D51" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5409,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5441,16 +5441,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C52" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D52" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5503,16 +5503,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C53" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D53" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5533,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5565,16 +5565,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C54" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D54" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5627,16 +5627,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>336</v>
+      </c>
+      <c r="B55" t="s">
+        <v>337</v>
+      </c>
+      <c r="C55" t="s">
+        <v>248</v>
+      </c>
+      <c r="D55" t="s">
         <v>331</v>
-      </c>
-      <c r="B55" t="s">
-        <v>332</v>
-      </c>
-      <c r="C55" t="s">
-        <v>243</v>
-      </c>
-      <c r="D55" t="s">
-        <v>326</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5657,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5689,16 +5689,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C56" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D56" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5719,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5751,16 +5751,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B57" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C57" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D57" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5813,16 +5813,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C58" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5875,16 +5875,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B59" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C59" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5937,16 +5937,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B60" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C60" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D60" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5967,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5999,16 +5999,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B61" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C61" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D61" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6061,16 +6061,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B62" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C62" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6123,16 +6123,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B63" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C63" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6153,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6185,16 +6185,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C64" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6215,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6247,16 +6247,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B65" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C65" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6277,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6309,16 +6309,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B66" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C66" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6339,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6374,7 +6374,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6401,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6419,7 +6419,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6436,7 +6436,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6463,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L68">
         <v>4</v>
@@ -6481,7 +6481,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6498,7 +6498,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6525,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L69">
         <v>9</v>
@@ -6543,7 +6543,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6560,7 +6560,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6605,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6622,7 +6622,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6667,7 +6667,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B72" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6729,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6773,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6791,7 +6791,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6808,7 +6808,7 @@
         <v>213</v>
       </c>
       <c r="B74" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6835,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L74">
         <v>1</v>
@@ -6853,7 +6853,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6897,7 +6897,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6929,10 +6929,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B76" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6959,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6977,7 +6977,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6994,7 +6994,7 @@
         <v>184</v>
       </c>
       <c r="B77" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -7030,7 +7030,7 @@
         <v>0</v>
       </c>
       <c r="N77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77">
         <v>1</v>
@@ -7039,7 +7039,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7053,10 +7053,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B78" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7101,7 +7101,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B79" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7163,7 +7163,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7180,7 +7180,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7207,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7225,7 +7225,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B81" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7269,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -7287,7 +7287,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7301,10 +7301,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B82" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7331,7 +7331,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7349,7 +7349,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7363,10 +7363,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B83" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7411,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7425,10 +7425,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B84" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7455,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7473,7 +7473,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7487,10 +7487,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B85" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7517,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7535,7 +7535,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7549,10 +7549,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B86" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7597,7 +7597,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7611,10 +7611,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B87" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7641,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7659,7 +7659,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7676,7 +7676,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7703,7 +7703,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L88">
         <v>2</v>
@@ -7721,7 +7721,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7738,7 +7738,7 @@
         <v>212</v>
       </c>
       <c r="B89" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7765,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L89">
         <v>1</v>
@@ -7783,7 +7783,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7800,7 +7800,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L90">
         <v>2</v>
@@ -7845,7 +7845,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7859,10 +7859,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B91" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7889,7 +7889,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7907,7 +7907,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7921,10 +7921,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B92" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7951,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7969,7 +7969,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7986,7 +7986,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -8013,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8031,7 +8031,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8045,10 +8045,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B94" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8075,7 +8075,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8093,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8107,10 +8107,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B95" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8137,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8169,10 +8169,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B96" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8217,7 +8217,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B97" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8261,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8279,7 +8279,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8311,37 +8311,37 @@
         <v>265</v>
       </c>
       <c r="G98">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
       <c r="I98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L98">
+        <v>6</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>3</v>
+      </c>
+      <c r="O98">
         <v>5</v>
       </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>2</v>
-      </c>
-      <c r="O98">
-        <v>4</v>
-      </c>
       <c r="P98" t="s">
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8358,7 +8358,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8385,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L99">
         <v>2</v>
@@ -8403,7 +8403,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8420,7 +8420,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8447,7 +8447,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8465,7 +8465,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8479,10 +8479,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B101" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8509,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8527,7 +8527,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8541,10 +8541,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B102" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8571,7 +8571,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8589,7 +8589,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8603,10 +8603,10 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8621,37 +8621,37 @@
         <v>265</v>
       </c>
       <c r="G103">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H103">
         <v>0</v>
       </c>
       <c r="I103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103">
         <v>0</v>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P103" t="s">
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8668,7 +8668,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8695,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8713,7 +8713,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8727,10 +8727,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B105" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8757,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8775,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8792,7 +8792,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8819,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8837,7 +8837,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8851,10 +8851,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B107" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8881,7 +8881,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8899,7 +8899,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8916,7 +8916,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8943,7 +8943,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8961,7 +8961,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8978,7 +8978,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -9005,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -9023,7 +9023,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B110" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -9067,7 +9067,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -9085,7 +9085,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B111" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9147,7 +9147,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9164,7 +9164,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9209,7 +9209,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9226,7 +9226,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9241,37 +9241,37 @@
         <v>265</v>
       </c>
       <c r="G113">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L113">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M113">
         <v>3</v>
       </c>
       <c r="N113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O113">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P113" t="s">
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9315,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L114">
         <v>10</v>
@@ -9324,7 +9324,7 @@
         <v>0</v>
       </c>
       <c r="N114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O114">
         <v>10</v>
@@ -9333,7 +9333,7 @@
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9350,7 +9350,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9377,7 +9377,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9395,7 +9395,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9412,7 +9412,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9427,37 +9427,37 @@
         <v>280</v>
       </c>
       <c r="G116">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H116">
         <v>0</v>
       </c>
       <c r="I116">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L116">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M116">
         <v>0</v>
       </c>
       <c r="N116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O116">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P116" t="s">
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9474,7 +9474,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9501,7 +9501,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9519,7 +9519,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9536,7 +9536,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9563,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9581,7 +9581,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9598,7 +9598,7 @@
         <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L119">
         <v>2</v>
@@ -9643,7 +9643,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9660,7 +9660,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9687,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9705,7 +9705,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9722,7 +9722,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L121">
         <v>2</v>
@@ -9767,7 +9767,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9784,7 +9784,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9811,7 +9811,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L122">
         <v>5</v>
@@ -9829,7 +9829,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9846,7 +9846,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9861,37 +9861,37 @@
         <v>265</v>
       </c>
       <c r="G123">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H123">
         <v>0</v>
       </c>
       <c r="I123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M123">
         <v>0</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P123" t="s">
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9908,7 +9908,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9935,7 +9935,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L124">
         <v>3</v>
@@ -9953,7 +9953,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9970,7 +9970,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9997,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -10015,7 +10015,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -10032,7 +10032,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -10059,7 +10059,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -10077,7 +10077,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -10094,7 +10094,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -10121,7 +10121,7 @@
         <v>10</v>
       </c>
       <c r="K127" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L127">
         <v>10</v>
@@ -10139,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -10156,7 +10156,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -10183,7 +10183,7 @@
         <v>7</v>
       </c>
       <c r="K128" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L128">
         <v>14</v>
@@ -10201,7 +10201,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -10218,7 +10218,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10245,7 +10245,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L129">
         <v>9</v>
@@ -10254,7 +10254,7 @@
         <v>6</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O129">
         <v>9</v>
@@ -10263,7 +10263,7 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10280,7 +10280,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10307,7 +10307,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10325,7 +10325,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10342,7 +10342,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10369,7 +10369,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10387,7 +10387,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10404,7 +10404,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10431,7 +10431,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L132">
         <v>18</v>
@@ -10449,7 +10449,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10466,7 +10466,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L133">
         <v>11</v>
@@ -10511,7 +10511,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10528,7 +10528,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10555,7 +10555,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L134">
         <v>17</v>
@@ -10573,7 +10573,7 @@
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10590,7 +10590,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10617,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10635,7 +10635,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10652,7 +10652,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10679,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10697,7 +10697,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10714,7 +10714,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10741,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L137">
         <v>4</v>
@@ -10759,7 +10759,7 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10776,7 +10776,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10803,7 +10803,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L138">
         <v>4</v>
@@ -10812,7 +10812,7 @@
         <v>0</v>
       </c>
       <c r="N138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O138">
         <v>4</v>
@@ -10821,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10865,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L139">
         <v>3</v>
@@ -10874,7 +10874,7 @@
         <v>2</v>
       </c>
       <c r="N139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O139">
         <v>3</v>
@@ -10883,7 +10883,7 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10927,7 +10927,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L140">
         <v>3</v>
@@ -10945,7 +10945,7 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10962,7 +10962,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10989,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L141">
         <v>5</v>
@@ -11007,7 +11007,7 @@
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -11024,7 +11024,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -11051,7 +11051,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -11069,7 +11069,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -11086,7 +11086,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -11113,7 +11113,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -11131,7 +11131,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -11148,7 +11148,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -11175,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -11193,7 +11193,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -11207,10 +11207,10 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B145" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -11237,7 +11237,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -11255,7 +11255,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -11269,10 +11269,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B146" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -11299,7 +11299,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -11317,7 +11317,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -11334,7 +11334,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11361,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L147">
         <v>2</v>
@@ -11379,7 +11379,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11423,7 +11423,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L148">
         <v>6</v>
@@ -11441,7 +11441,7 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11458,7 +11458,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11485,7 +11485,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11503,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11520,7 +11520,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11547,7 +11547,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11565,7 +11565,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11582,7 +11582,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11597,37 +11597,37 @@
         <v>255</v>
       </c>
       <c r="G151">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J151">
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M151">
         <v>0</v>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P151" t="s">
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11641,16 +11641,16 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B152" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C152" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D152" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11671,7 +11671,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11703,16 +11703,16 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B153" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C153" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D153" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11733,7 +11733,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11765,16 +11765,16 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B154" t="s">
+        <v>493</v>
+      </c>
+      <c r="C154" t="s">
+        <v>248</v>
+      </c>
+      <c r="D154" t="s">
         <v>489</v>
-      </c>
-      <c r="C154" t="s">
-        <v>243</v>
-      </c>
-      <c r="D154" t="s">
-        <v>485</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11795,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11827,16 +11827,16 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B155" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C155" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D155" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11889,16 +11889,16 @@
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B156" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C156" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D156" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11919,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11951,16 +11951,16 @@
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B157" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C157" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D157" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11981,7 +11981,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -12013,16 +12013,16 @@
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B158" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C158" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D158" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -12043,7 +12043,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -12075,16 +12075,16 @@
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B159" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C159" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D159" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -12105,7 +12105,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -12137,16 +12137,16 @@
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B160" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C160" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D160" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -12167,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -12199,16 +12199,16 @@
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B161" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C161" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D161" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -12261,16 +12261,16 @@
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B162" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C162" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D162" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -12291,7 +12291,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -12323,16 +12323,16 @@
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B163" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C163" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D163" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -12353,7 +12353,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -12385,16 +12385,16 @@
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B164" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C164" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D164" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -12415,7 +12415,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -12447,16 +12447,16 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B165" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C165" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D165" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12477,7 +12477,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12509,16 +12509,16 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B166" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C166" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D166" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12539,7 +12539,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12571,16 +12571,16 @@
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B167" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C167" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D167" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12601,7 +12601,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12633,16 +12633,16 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B168" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C168" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D168" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12663,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12695,16 +12695,16 @@
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B169" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C169" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D169" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12725,7 +12725,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12757,16 +12757,16 @@
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B170" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C170" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D170" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12787,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12819,16 +12819,16 @@
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B171" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C171" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D171" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12849,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12884,7 +12884,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12911,7 +12911,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -12929,7 +12929,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12946,7 +12946,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12973,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L173">
         <v>7</v>
@@ -12982,7 +12982,7 @@
         <v>0</v>
       </c>
       <c r="N173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O173">
         <v>6</v>
@@ -12991,7 +12991,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -13008,7 +13008,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -13035,7 +13035,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L174">
         <v>5</v>
@@ -13053,7 +13053,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -13070,7 +13070,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -13097,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -13115,7 +13115,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -13159,7 +13159,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -13177,7 +13177,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -13194,7 +13194,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -13209,37 +13209,37 @@
         <v>235</v>
       </c>
       <c r="G177">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H177">
         <v>0</v>
       </c>
       <c r="I177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J177">
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M177">
         <v>1</v>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P177" t="s">
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -13256,7 +13256,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -13283,7 +13283,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -13301,7 +13301,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -13318,7 +13318,7 @@
         <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -13345,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L179">
         <v>2</v>
@@ -13363,7 +13363,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -13380,7 +13380,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -13407,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L180">
         <v>3</v>
@@ -13425,7 +13425,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B181" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -13469,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -13487,7 +13487,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -13519,37 +13519,37 @@
         <v>235</v>
       </c>
       <c r="G182">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H182">
         <v>0</v>
       </c>
       <c r="I182">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J182">
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L182">
+        <v>6</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>1</v>
+      </c>
+      <c r="O182">
         <v>5</v>
       </c>
-      <c r="M182">
-        <v>1</v>
-      </c>
-      <c r="N182">
-        <v>0</v>
-      </c>
-      <c r="O182">
-        <v>4</v>
-      </c>
       <c r="P182" t="s">
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13566,7 +13566,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13593,7 +13593,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L183">
         <v>5</v>
@@ -13611,7 +13611,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13628,7 +13628,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13655,7 +13655,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L184">
         <v>2</v>
@@ -13673,7 +13673,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13690,7 +13690,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13717,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L185">
         <v>4</v>
@@ -13735,7 +13735,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13752,7 +13752,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13779,7 +13779,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13797,7 +13797,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13841,7 +13841,7 @@
         <v>6</v>
       </c>
       <c r="K187" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L187">
         <v>9</v>
@@ -13859,7 +13859,7 @@
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13876,7 +13876,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13891,37 +13891,37 @@
         <v>240</v>
       </c>
       <c r="G188">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H188">
         <v>0</v>
       </c>
       <c r="I188">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J188">
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L188">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M188">
         <v>7</v>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O188">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P188" t="s">
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13965,7 +13965,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13983,7 +13983,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -14000,7 +14000,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -14027,7 +14027,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -14089,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L191">
         <v>1</v>
@@ -14107,7 +14107,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -14124,7 +14124,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -14151,7 +14151,7 @@
         <v>9</v>
       </c>
       <c r="K192" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L192">
         <v>13</v>
@@ -14169,7 +14169,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -14186,7 +14186,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -14201,37 +14201,37 @@
         <v>240</v>
       </c>
       <c r="G193">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J193">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K193" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L193">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M193">
         <v>17</v>
       </c>
       <c r="N193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O193">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P193" t="s">
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -14248,7 +14248,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -14275,7 +14275,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L194">
         <v>24</v>
@@ -14293,7 +14293,7 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -14310,7 +14310,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -14337,7 +14337,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L195">
         <v>12</v>
@@ -14355,7 +14355,7 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -14399,7 +14399,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L196">
         <v>9</v>
@@ -14417,7 +14417,7 @@
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -14431,10 +14431,10 @@
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B197" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -14461,7 +14461,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -14479,7 +14479,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -14496,7 +14496,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -14523,7 +14523,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -14541,7 +14541,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -14558,7 +14558,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -14585,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -14603,7 +14603,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -14617,10 +14617,10 @@
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B200" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -14647,7 +14647,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14665,7 +14665,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14682,7 +14682,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14709,7 +14709,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14727,7 +14727,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14741,10 +14741,10 @@
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B202" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14771,7 +14771,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14789,7 +14789,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14806,7 +14806,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14833,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14851,7 +14851,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14868,7 +14868,7 @@
         <v>195</v>
       </c>
       <c r="B204" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14895,7 +14895,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L204">
         <v>2</v>
@@ -14913,7 +14913,7 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14930,7 +14930,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14957,7 +14957,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14975,7 +14975,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14989,10 +14989,10 @@
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B206" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -15019,7 +15019,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -15037,7 +15037,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -15054,7 +15054,7 @@
         <v>200</v>
       </c>
       <c r="B207" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -15081,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L207">
         <v>1</v>
@@ -15099,7 +15099,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -15116,7 +15116,7 @@
         <v>197</v>
       </c>
       <c r="B208" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -15143,7 +15143,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L208">
         <v>1</v>
@@ -15161,7 +15161,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -15175,10 +15175,10 @@
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B209" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -15205,7 +15205,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -15240,7 +15240,7 @@
         <v>203</v>
       </c>
       <c r="B210" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -15267,7 +15267,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L210">
         <v>1</v>
@@ -15285,7 +15285,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -15302,7 +15302,7 @@
         <v>198</v>
       </c>
       <c r="B211" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -15329,7 +15329,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L211">
         <v>2</v>
@@ -15347,7 +15347,7 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -15361,10 +15361,10 @@
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B212" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -15391,7 +15391,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -15409,7 +15409,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -15426,7 +15426,7 @@
         <v>199</v>
       </c>
       <c r="B213" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -15453,7 +15453,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L213">
         <v>2</v>
@@ -15471,7 +15471,7 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -15488,7 +15488,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -15515,7 +15515,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L214">
         <v>2</v>
@@ -15533,7 +15533,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15550,7 +15550,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -15577,7 +15577,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L215">
         <v>3</v>
@@ -15595,7 +15595,7 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -15609,10 +15609,10 @@
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B216" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -15639,7 +15639,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -15657,7 +15657,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15674,7 +15674,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -15701,7 +15701,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L217">
         <v>7</v>
@@ -15719,7 +15719,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15736,7 +15736,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -15763,7 +15763,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L218">
         <v>4</v>
@@ -15781,7 +15781,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15798,7 +15798,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15825,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L219">
         <v>5</v>
@@ -15843,7 +15843,7 @@
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15860,7 +15860,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15887,7 +15887,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L220">
         <v>4</v>
@@ -15905,7 +15905,7 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15919,10 +15919,10 @@
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B221" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15949,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15967,7 +15967,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15984,7 +15984,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -16011,7 +16011,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -16029,7 +16029,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -16046,7 +16046,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -16073,7 +16073,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="L223">
         <v>14</v>
@@ -16082,7 +16082,7 @@
         <v>8</v>
       </c>
       <c r="N223">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O223">
         <v>14</v>
@@ -16091,7 +16091,7 @@
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -16108,7 +16108,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -16135,7 +16135,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -16153,7 +16153,7 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -16170,7 +16170,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -16197,7 +16197,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L225">
         <v>10</v>
@@ -16215,7 +16215,7 @@
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -16259,7 +16259,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -16277,7 +16277,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -16294,7 +16294,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -16309,22 +16309,22 @@
         <v>235</v>
       </c>
       <c r="G227">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J227">
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L227">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M227">
         <v>10</v>
@@ -16333,13 +16333,13 @@
         <v>4</v>
       </c>
       <c r="O227">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P227" t="s">
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -16356,7 +16356,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -16371,22 +16371,22 @@
         <v>240</v>
       </c>
       <c r="G228">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J228">
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L228">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M228">
         <v>11</v>
@@ -16395,13 +16395,13 @@
         <v>3</v>
       </c>
       <c r="O228">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P228" t="s">
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -16418,7 +16418,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -16445,7 +16445,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L229">
         <v>15</v>
@@ -16463,7 +16463,7 @@
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -16480,7 +16480,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -16507,7 +16507,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -16525,7 +16525,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -16542,7 +16542,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -16569,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -16587,7 +16587,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -16616,7 +16616,7 @@
         <v>122</v>
       </c>
       <c r="G232">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -16628,19 +16628,19 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L232">
+        <v>7</v>
+      </c>
+      <c r="M232">
+        <v>1</v>
+      </c>
+      <c r="N232">
         <v>5</v>
       </c>
-      <c r="M232">
-        <v>0</v>
-      </c>
-      <c r="N232">
-        <v>3</v>
-      </c>
       <c r="O232">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P232" t="s">
         <v>13</v>
@@ -16669,7 +16669,7 @@
         <v>122</v>
       </c>
       <c r="G233">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -16681,19 +16681,19 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L233">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N233">
         <v>6</v>
       </c>
       <c r="O233">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P233" t="s">
         <v>13</v>
@@ -16707,10 +16707,10 @@
     </row>
     <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>605</v>
+        <v>217</v>
       </c>
       <c r="B234" t="s">
-        <v>605</v>
+        <v>217</v>
       </c>
       <c r="C234" t="s">
         <v>120</v>
@@ -16722,7 +16722,7 @@
         <v>122</v>
       </c>
       <c r="G234">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -16734,19 +16734,19 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M234">
         <v>0</v>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P234" t="s">
         <v>13</v>
@@ -16787,7 +16787,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L235">
         <v>1</v>
@@ -16828,7 +16828,7 @@
         <v>122</v>
       </c>
       <c r="G236">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -16840,19 +16840,19 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L236">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M236">
         <v>0</v>
       </c>
       <c r="N236">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O236">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P236" t="s">
         <v>13</v>
@@ -16881,7 +16881,7 @@
         <v>122</v>
       </c>
       <c r="G237">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H237">
         <v>0</v>
@@ -16893,19 +16893,19 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L237">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M237">
         <v>0</v>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O237">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P237" t="s">
         <v>13</v>
@@ -16919,10 +16919,10 @@
     </row>
     <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>606</v>
+        <v>214</v>
       </c>
       <c r="B238" t="s">
-        <v>606</v>
+        <v>214</v>
       </c>
       <c r="C238" t="s">
         <v>120</v>
@@ -16934,7 +16934,7 @@
         <v>122</v>
       </c>
       <c r="G238">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H238">
         <v>0</v>
@@ -16946,19 +16946,19 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M238">
         <v>0</v>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P238" t="s">
         <v>13</v>
@@ -16972,10 +16972,10 @@
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>607</v>
+        <v>215</v>
       </c>
       <c r="B239" t="s">
-        <v>607</v>
+        <v>215</v>
       </c>
       <c r="C239" t="s">
         <v>120</v>
@@ -16987,7 +16987,7 @@
         <v>122</v>
       </c>
       <c r="G239">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H239">
         <v>0</v>
@@ -16999,19 +16999,19 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M239">
         <v>0</v>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P239" t="s">
         <v>13</v>
@@ -17052,7 +17052,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L240">
         <v>2</v>
@@ -17105,7 +17105,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L241">
         <v>3</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L242">
         <v>2</v>
@@ -17211,7 +17211,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L243">
         <v>2</v>
@@ -17237,10 +17237,10 @@
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B244" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -17264,7 +17264,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -17317,7 +17317,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L245">
         <v>2</v>
@@ -17370,7 +17370,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -17423,7 +17423,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L247">
         <v>2</v>
@@ -17449,10 +17449,10 @@
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B248" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
@@ -17476,7 +17476,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -17529,7 +17529,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L249">
         <v>2</v>
@@ -17538,7 +17538,7 @@
         <v>0</v>
       </c>
       <c r="N249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O249">
         <v>2</v>
@@ -17555,10 +17555,10 @@
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>610</v>
+        <v>216</v>
       </c>
       <c r="B250" t="s">
-        <v>610</v>
+        <v>216</v>
       </c>
       <c r="C250" t="s">
         <v>120</v>
@@ -17570,7 +17570,7 @@
         <v>122</v>
       </c>
       <c r="G250">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -17582,19 +17582,19 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P250" t="s">
         <v>13</v>
@@ -17635,7 +17635,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -17676,7 +17676,7 @@
         <v>122</v>
       </c>
       <c r="G252">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -17688,19 +17688,19 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L252">
+        <v>4</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
         <v>3</v>
       </c>
-      <c r="M252">
-        <v>0</v>
-      </c>
-      <c r="N252">
-        <v>2</v>
-      </c>
       <c r="O252">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P252" t="s">
         <v>13</v>
@@ -17741,7 +17741,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L253">
         <v>8</v>
@@ -17794,7 +17794,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L254">
         <v>3</v>
@@ -17847,7 +17847,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L255">
         <v>4</v>
@@ -17900,7 +17900,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L256">
         <v>7</v>
@@ -17909,7 +17909,7 @@
         <v>0</v>
       </c>
       <c r="N256">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O256">
         <v>7</v>
@@ -17953,7 +17953,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L257">
         <v>2</v>
@@ -18006,7 +18006,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L258">
         <v>5</v>
@@ -18015,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="N258">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O258">
         <v>5</v>
@@ -18059,7 +18059,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L259">
         <v>3</v>
@@ -18112,7 +18112,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L260">
         <v>19</v>
@@ -18165,7 +18165,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L261">
         <v>12</v>
@@ -18218,7 +18218,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L262">
         <v>18</v>
@@ -18271,7 +18271,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L263">
         <v>17</v>
@@ -18302,8 +18302,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43371F8D-EC53-49F2-A643-7D177B6DF52B}">
-  <dimension ref="A1:J606"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{120C5B02-1A81-4220-BD62-5564806F5E7C}">
+  <dimension ref="A1:J629"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -37695,6 +37695,742 @@
         <v>1</v>
       </c>
       <c r="J606" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A607" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B607" t="s">
+        <v>117</v>
+      </c>
+      <c r="C607" t="s">
+        <v>24</v>
+      </c>
+      <c r="D607" t="s">
+        <v>38</v>
+      </c>
+      <c r="E607" t="s">
+        <v>53</v>
+      </c>
+      <c r="F607" t="s">
+        <v>94</v>
+      </c>
+      <c r="G607">
+        <v>265</v>
+      </c>
+      <c r="H607" t="s">
+        <v>15</v>
+      </c>
+      <c r="I607">
+        <v>1</v>
+      </c>
+      <c r="J607" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="608" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A608" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B608" t="s">
+        <v>96</v>
+      </c>
+      <c r="C608" t="s">
+        <v>24</v>
+      </c>
+      <c r="D608" t="s">
+        <v>38</v>
+      </c>
+      <c r="E608" t="s">
+        <v>53</v>
+      </c>
+      <c r="F608" t="s">
+        <v>94</v>
+      </c>
+      <c r="G608">
+        <v>265</v>
+      </c>
+      <c r="H608" t="s">
+        <v>15</v>
+      </c>
+      <c r="I608">
+        <v>1</v>
+      </c>
+      <c r="J608" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="609" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A609" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B609" t="s">
+        <v>32</v>
+      </c>
+      <c r="C609" t="s">
+        <v>24</v>
+      </c>
+      <c r="D609" t="s">
+        <v>33</v>
+      </c>
+      <c r="E609" t="s">
+        <v>53</v>
+      </c>
+      <c r="F609" t="s">
+        <v>94</v>
+      </c>
+      <c r="G609">
+        <v>265</v>
+      </c>
+      <c r="H609" t="s">
+        <v>15</v>
+      </c>
+      <c r="I609">
+        <v>1</v>
+      </c>
+      <c r="J609" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="610" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A610" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B610" t="s">
+        <v>67</v>
+      </c>
+      <c r="C610" t="s">
+        <v>24</v>
+      </c>
+      <c r="D610" t="s">
+        <v>40</v>
+      </c>
+      <c r="E610" t="s">
+        <v>53</v>
+      </c>
+      <c r="F610" t="s">
+        <v>94</v>
+      </c>
+      <c r="G610">
+        <v>240</v>
+      </c>
+      <c r="H610" t="s">
+        <v>22</v>
+      </c>
+      <c r="I610">
+        <v>1</v>
+      </c>
+      <c r="J610" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="611" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A611" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B611" t="s">
+        <v>76</v>
+      </c>
+      <c r="C611" t="s">
+        <v>24</v>
+      </c>
+      <c r="D611" t="s">
+        <v>49</v>
+      </c>
+      <c r="E611" t="s">
+        <v>53</v>
+      </c>
+      <c r="F611" t="s">
+        <v>94</v>
+      </c>
+      <c r="G611">
+        <v>240</v>
+      </c>
+      <c r="H611" t="s">
+        <v>22</v>
+      </c>
+      <c r="I611">
+        <v>1</v>
+      </c>
+      <c r="J611" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="612" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A612" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B612" t="s">
+        <v>27</v>
+      </c>
+      <c r="C612" t="s">
+        <v>24</v>
+      </c>
+      <c r="D612" t="s">
+        <v>25</v>
+      </c>
+      <c r="E612" t="s">
+        <v>53</v>
+      </c>
+      <c r="F612" t="s">
+        <v>94</v>
+      </c>
+      <c r="G612">
+        <v>235</v>
+      </c>
+      <c r="H612" t="s">
+        <v>22</v>
+      </c>
+      <c r="I612">
+        <v>1</v>
+      </c>
+      <c r="J612" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="613" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A613" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B613" t="s">
+        <v>101</v>
+      </c>
+      <c r="C613" t="s">
+        <v>24</v>
+      </c>
+      <c r="D613" t="s">
+        <v>38</v>
+      </c>
+      <c r="E613" t="s">
+        <v>53</v>
+      </c>
+      <c r="F613" t="s">
+        <v>94</v>
+      </c>
+      <c r="G613">
+        <v>280</v>
+      </c>
+      <c r="H613" t="s">
+        <v>15</v>
+      </c>
+      <c r="I613">
+        <v>1</v>
+      </c>
+      <c r="J613" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="614" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A614" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B614" t="s">
+        <v>70</v>
+      </c>
+      <c r="C614" t="s">
+        <v>24</v>
+      </c>
+      <c r="D614" t="s">
+        <v>49</v>
+      </c>
+      <c r="E614" t="s">
+        <v>53</v>
+      </c>
+      <c r="F614" t="s">
+        <v>94</v>
+      </c>
+      <c r="G614">
+        <v>235</v>
+      </c>
+      <c r="H614" t="s">
+        <v>22</v>
+      </c>
+      <c r="I614">
+        <v>1</v>
+      </c>
+      <c r="J614" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="615" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A615" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B615" t="s">
+        <v>41</v>
+      </c>
+      <c r="C615" t="s">
+        <v>24</v>
+      </c>
+      <c r="D615" t="s">
+        <v>40</v>
+      </c>
+      <c r="E615" t="s">
+        <v>53</v>
+      </c>
+      <c r="F615" t="s">
+        <v>94</v>
+      </c>
+      <c r="G615">
+        <v>240</v>
+      </c>
+      <c r="H615" t="s">
+        <v>22</v>
+      </c>
+      <c r="I615">
+        <v>1</v>
+      </c>
+      <c r="J615" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="616" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A616" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B616" t="s">
+        <v>214</v>
+      </c>
+      <c r="C616" t="s">
+        <v>120</v>
+      </c>
+      <c r="D616" t="s">
+        <v>128</v>
+      </c>
+      <c r="E616" t="s">
+        <v>188</v>
+      </c>
+      <c r="F616" t="s">
+        <v>94</v>
+      </c>
+      <c r="G616">
+        <v>0</v>
+      </c>
+      <c r="H616" t="s">
+        <v>122</v>
+      </c>
+      <c r="I616">
+        <v>2</v>
+      </c>
+      <c r="J616" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="617" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A617" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B617" t="s">
+        <v>196</v>
+      </c>
+      <c r="C617" t="s">
+        <v>120</v>
+      </c>
+      <c r="D617" t="s">
+        <v>128</v>
+      </c>
+      <c r="E617" t="s">
+        <v>188</v>
+      </c>
+      <c r="F617" t="s">
+        <v>94</v>
+      </c>
+      <c r="G617">
+        <v>0</v>
+      </c>
+      <c r="H617" t="s">
+        <v>122</v>
+      </c>
+      <c r="I617">
+        <v>2</v>
+      </c>
+      <c r="J617" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="618" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A618" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B618" t="s">
+        <v>127</v>
+      </c>
+      <c r="C618" t="s">
+        <v>120</v>
+      </c>
+      <c r="D618" t="s">
+        <v>128</v>
+      </c>
+      <c r="E618" t="s">
+        <v>188</v>
+      </c>
+      <c r="F618" t="s">
+        <v>94</v>
+      </c>
+      <c r="G618">
+        <v>0</v>
+      </c>
+      <c r="H618" t="s">
+        <v>122</v>
+      </c>
+      <c r="I618">
+        <v>2</v>
+      </c>
+      <c r="J618" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="619" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A619" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B619" t="s">
+        <v>215</v>
+      </c>
+      <c r="C619" t="s">
+        <v>120</v>
+      </c>
+      <c r="D619" t="s">
+        <v>128</v>
+      </c>
+      <c r="E619" t="s">
+        <v>188</v>
+      </c>
+      <c r="F619" t="s">
+        <v>94</v>
+      </c>
+      <c r="G619">
+        <v>0</v>
+      </c>
+      <c r="H619" t="s">
+        <v>122</v>
+      </c>
+      <c r="I619">
+        <v>2</v>
+      </c>
+      <c r="J619" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="620" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A620" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B620" t="s">
+        <v>169</v>
+      </c>
+      <c r="C620" t="s">
+        <v>120</v>
+      </c>
+      <c r="D620" t="s">
+        <v>121</v>
+      </c>
+      <c r="E620" t="s">
+        <v>133</v>
+      </c>
+      <c r="F620" t="s">
+        <v>94</v>
+      </c>
+      <c r="G620">
+        <v>0</v>
+      </c>
+      <c r="H620" t="s">
+        <v>122</v>
+      </c>
+      <c r="I620">
+        <v>1</v>
+      </c>
+      <c r="J620" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="621" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A621" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B621" t="s">
+        <v>216</v>
+      </c>
+      <c r="C621" t="s">
+        <v>120</v>
+      </c>
+      <c r="D621" t="s">
+        <v>186</v>
+      </c>
+      <c r="E621" t="s">
+        <v>133</v>
+      </c>
+      <c r="F621" t="s">
+        <v>66</v>
+      </c>
+      <c r="G621">
+        <v>0</v>
+      </c>
+      <c r="H621" t="s">
+        <v>122</v>
+      </c>
+      <c r="I621">
+        <v>1</v>
+      </c>
+      <c r="J621" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="622" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A622" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B622" t="s">
+        <v>173</v>
+      </c>
+      <c r="C622" t="s">
+        <v>120</v>
+      </c>
+      <c r="D622" t="s">
+        <v>126</v>
+      </c>
+      <c r="E622" t="s">
+        <v>133</v>
+      </c>
+      <c r="F622" t="s">
+        <v>66</v>
+      </c>
+      <c r="G622">
+        <v>0</v>
+      </c>
+      <c r="H622" t="s">
+        <v>122</v>
+      </c>
+      <c r="I622">
+        <v>1</v>
+      </c>
+      <c r="J622" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="623" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A623" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B623" t="s">
+        <v>125</v>
+      </c>
+      <c r="C623" t="s">
+        <v>120</v>
+      </c>
+      <c r="D623" t="s">
+        <v>126</v>
+      </c>
+      <c r="E623" t="s">
+        <v>133</v>
+      </c>
+      <c r="F623" t="s">
+        <v>66</v>
+      </c>
+      <c r="G623">
+        <v>0</v>
+      </c>
+      <c r="H623" t="s">
+        <v>122</v>
+      </c>
+      <c r="I623">
+        <v>1</v>
+      </c>
+      <c r="J623" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="624" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A624" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B624" t="s">
+        <v>217</v>
+      </c>
+      <c r="C624" t="s">
+        <v>120</v>
+      </c>
+      <c r="D624" t="s">
+        <v>126</v>
+      </c>
+      <c r="E624" t="s">
+        <v>133</v>
+      </c>
+      <c r="F624" t="s">
+        <v>94</v>
+      </c>
+      <c r="G624">
+        <v>0</v>
+      </c>
+      <c r="H624" t="s">
+        <v>122</v>
+      </c>
+      <c r="I624">
+        <v>1</v>
+      </c>
+      <c r="J624" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="625" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A625" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B625" t="s">
+        <v>173</v>
+      </c>
+      <c r="C625" t="s">
+        <v>120</v>
+      </c>
+      <c r="D625" t="s">
+        <v>126</v>
+      </c>
+      <c r="E625" t="s">
+        <v>133</v>
+      </c>
+      <c r="F625" t="s">
+        <v>94</v>
+      </c>
+      <c r="G625">
+        <v>0</v>
+      </c>
+      <c r="H625" t="s">
+        <v>122</v>
+      </c>
+      <c r="I625">
+        <v>1</v>
+      </c>
+      <c r="J625" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="626" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A626" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B626" t="s">
+        <v>125</v>
+      </c>
+      <c r="C626" t="s">
+        <v>120</v>
+      </c>
+      <c r="D626" t="s">
+        <v>126</v>
+      </c>
+      <c r="E626" t="s">
+        <v>133</v>
+      </c>
+      <c r="F626" t="s">
+        <v>94</v>
+      </c>
+      <c r="G626">
+        <v>0</v>
+      </c>
+      <c r="H626" t="s">
+        <v>122</v>
+      </c>
+      <c r="I626">
+        <v>1</v>
+      </c>
+      <c r="J626" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="627" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A627" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B627" t="s">
+        <v>218</v>
+      </c>
+      <c r="C627" t="s">
+        <v>24</v>
+      </c>
+      <c r="D627" t="s">
+        <v>33</v>
+      </c>
+      <c r="E627" t="s">
+        <v>100</v>
+      </c>
+      <c r="F627" t="s">
+        <v>94</v>
+      </c>
+      <c r="G627">
+        <v>265</v>
+      </c>
+      <c r="H627" t="s">
+        <v>15</v>
+      </c>
+      <c r="I627">
+        <v>1</v>
+      </c>
+      <c r="J627" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="628" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A628" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B628" t="s">
+        <v>155</v>
+      </c>
+      <c r="C628" t="s">
+        <v>24</v>
+      </c>
+      <c r="D628" t="s">
+        <v>25</v>
+      </c>
+      <c r="E628" t="s">
+        <v>100</v>
+      </c>
+      <c r="F628" t="s">
+        <v>94</v>
+      </c>
+      <c r="G628">
+        <v>235</v>
+      </c>
+      <c r="H628" t="s">
+        <v>22</v>
+      </c>
+      <c r="I628">
+        <v>1</v>
+      </c>
+      <c r="J628" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="629" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A629" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B629" t="s">
+        <v>116</v>
+      </c>
+      <c r="C629" t="s">
+        <v>18</v>
+      </c>
+      <c r="D629" t="s">
+        <v>90</v>
+      </c>
+      <c r="E629" t="s">
+        <v>100</v>
+      </c>
+      <c r="F629" t="s">
+        <v>94</v>
+      </c>
+      <c r="G629">
+        <v>255</v>
+      </c>
+      <c r="H629" t="s">
+        <v>22</v>
+      </c>
+      <c r="I629">
+        <v>1</v>
+      </c>
+      <c r="J629" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35F3909A-8540-4BE6-B20B-E71AB04C681E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61100AF8-4787-43DB-A685-C42ED7A12504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{350BBA77-1C9F-4D8D-AE32-AE1C180B77B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{E961E4E0-9113-49A0-8EB8-03CB5463E976}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6448" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6492" uniqueCount="617">
   <si>
     <t>날짜</t>
   </si>
@@ -697,6 +697,9 @@
   </si>
   <si>
     <t>DPM644-BK265</t>
+  </si>
+  <si>
+    <t>체크아웃/바오지</t>
   </si>
   <si>
     <t>상품명</t>
@@ -2273,7 +2276,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFDFECA-6A42-4082-92B2-02E22FDF7C51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F85C1F7-AE3C-4883-8BDF-37CED419309C}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2282,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2297,46 +2300,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="R1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="S1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="T1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2344,7 +2347,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2371,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2389,7 +2392,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2406,7 +2409,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2433,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -2451,7 +2454,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2468,7 +2471,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2483,37 +2486,37 @@
         <v>270</v>
       </c>
       <c r="G4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" t="s">
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2530,7 +2533,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2557,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2575,7 +2578,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2592,7 +2595,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2619,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2637,7 +2640,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2654,7 +2657,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2681,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2699,7 +2702,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2716,7 +2719,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2743,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2761,7 +2764,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2778,7 +2781,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2805,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2823,7 +2826,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2840,7 +2843,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2867,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2885,7 +2888,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2902,7 +2905,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2929,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2947,7 +2950,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2961,16 +2964,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2991,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3023,16 +3026,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" t="s">
         <v>250</v>
-      </c>
-      <c r="B13" t="s">
-        <v>251</v>
-      </c>
-      <c r="C13" t="s">
-        <v>248</v>
-      </c>
-      <c r="D13" t="s">
-        <v>249</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3053,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3085,16 +3088,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3115,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3147,16 +3150,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3177,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3209,16 +3212,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3239,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3271,16 +3274,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3301,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3333,16 +3336,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3363,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3395,16 +3398,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3425,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3457,16 +3460,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3487,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3519,16 +3522,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D21" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3549,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3581,16 +3584,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B22" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3611,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3643,16 +3646,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D23" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3673,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3705,16 +3708,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3735,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3767,16 +3770,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3797,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3829,16 +3832,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D26" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3859,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3891,16 +3894,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C27" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3921,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3953,16 +3956,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C28" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D28" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3983,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4015,16 +4018,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D29" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4045,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4077,16 +4080,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C30" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D30" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4107,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4139,16 +4142,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4169,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4201,16 +4204,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C32" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4231,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4263,16 +4266,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>292</v>
+      </c>
+      <c r="B33" t="s">
+        <v>293</v>
+      </c>
+      <c r="C33" t="s">
+        <v>249</v>
+      </c>
+      <c r="D33" t="s">
         <v>291</v>
-      </c>
-      <c r="B33" t="s">
-        <v>292</v>
-      </c>
-      <c r="C33" t="s">
-        <v>248</v>
-      </c>
-      <c r="D33" t="s">
-        <v>290</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4293,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4325,16 +4328,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C34" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4355,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4387,16 +4390,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C35" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D35" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4417,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4449,16 +4452,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D36" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4479,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4511,16 +4514,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D37" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4541,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4573,16 +4576,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D38" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4603,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4635,16 +4638,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C39" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D39" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4665,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4697,16 +4700,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C40" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D40" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4727,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4759,16 +4762,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C41" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D41" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4789,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4821,16 +4824,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C42" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D42" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4851,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4883,16 +4886,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C43" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D43" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4913,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4945,16 +4948,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B44" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C44" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D44" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4975,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5007,16 +5010,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D45" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5037,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5069,16 +5072,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B46" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C46" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D46" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5099,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5131,16 +5134,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B47" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D47" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5161,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5193,16 +5196,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C48" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D48" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5223,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5255,16 +5258,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B49" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D49" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5285,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5317,16 +5320,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B50" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C50" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5347,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5379,16 +5382,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C51" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5409,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5441,16 +5444,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B52" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D52" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5471,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5503,16 +5506,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>333</v>
+      </c>
+      <c r="B53" t="s">
+        <v>334</v>
+      </c>
+      <c r="C53" t="s">
+        <v>249</v>
+      </c>
+      <c r="D53" t="s">
         <v>332</v>
-      </c>
-      <c r="B53" t="s">
-        <v>333</v>
-      </c>
-      <c r="C53" t="s">
-        <v>248</v>
-      </c>
-      <c r="D53" t="s">
-        <v>331</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5533,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5565,16 +5568,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D54" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5595,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5627,16 +5630,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C55" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5657,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5689,16 +5692,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C56" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D56" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5719,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5751,16 +5754,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C57" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D57" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5781,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5813,16 +5816,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B58" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C58" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5843,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5875,16 +5878,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B59" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C59" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D59" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5905,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5937,16 +5940,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B60" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C60" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D60" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5967,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -5999,16 +6002,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C61" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D61" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6029,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6061,16 +6064,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C62" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6091,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6123,16 +6126,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C63" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6153,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6185,16 +6188,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B64" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C64" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6215,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6247,16 +6250,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C65" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D65" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6277,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6309,16 +6312,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B66" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D66" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6339,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6374,7 +6377,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6401,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6419,7 +6422,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6436,7 +6439,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6463,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L68">
         <v>4</v>
@@ -6481,7 +6484,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6498,7 +6501,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6525,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L69">
         <v>9</v>
@@ -6534,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O69">
         <v>9</v>
@@ -6543,7 +6546,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6560,7 +6563,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6587,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6605,7 +6608,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6622,7 +6625,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6649,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6667,7 +6670,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6681,10 +6684,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B72" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6711,7 +6714,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6729,7 +6732,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6746,7 +6749,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6773,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6791,7 +6794,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6808,7 +6811,7 @@
         <v>213</v>
       </c>
       <c r="B74" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6835,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L74">
         <v>1</v>
@@ -6853,7 +6856,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6870,7 +6873,7 @@
         <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6897,7 +6900,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6915,7 +6918,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6929,10 +6932,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B76" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6959,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6977,7 +6980,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6994,7 +6997,7 @@
         <v>184</v>
       </c>
       <c r="B77" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -7021,7 +7024,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -7039,7 +7042,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7053,10 +7056,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B78" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7083,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7101,7 +7104,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7115,10 +7118,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B79" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7145,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7163,7 +7166,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7180,7 +7183,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7207,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7225,7 +7228,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7239,10 +7242,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B81" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7269,7 +7272,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -7287,7 +7290,7 @@
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7301,10 +7304,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B82" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7331,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7349,7 +7352,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7363,10 +7366,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B83" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7393,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7411,7 +7414,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7425,10 +7428,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B84" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7455,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7473,7 +7476,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7487,10 +7490,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B85" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7517,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7535,7 +7538,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7549,10 +7552,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B86" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7579,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -7597,7 +7600,7 @@
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7611,10 +7614,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B87" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7641,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7659,7 +7662,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7676,7 +7679,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7703,7 +7706,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L88">
         <v>2</v>
@@ -7721,7 +7724,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7738,7 +7741,7 @@
         <v>212</v>
       </c>
       <c r="B89" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7765,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L89">
         <v>1</v>
@@ -7783,7 +7786,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7800,7 +7803,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7827,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L90">
         <v>2</v>
@@ -7845,7 +7848,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7859,10 +7862,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B91" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7889,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7907,7 +7910,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7921,10 +7924,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B92" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7951,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7969,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7986,7 +7989,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -8013,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8031,7 +8034,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8045,10 +8048,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B94" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8075,7 +8078,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8093,7 +8096,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8107,10 +8110,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B95" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8137,7 +8140,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8155,7 +8158,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8169,10 +8172,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B96" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8199,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8217,7 +8220,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8231,10 +8234,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B97" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8261,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8279,7 +8282,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8296,7 +8299,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8323,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L98">
         <v>6</v>
@@ -8332,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="N98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O98">
         <v>5</v>
@@ -8341,7 +8344,7 @@
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8358,7 +8361,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8385,7 +8388,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L99">
         <v>2</v>
@@ -8403,7 +8406,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8420,7 +8423,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8447,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8465,7 +8468,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8479,10 +8482,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B101" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8509,7 +8512,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8527,7 +8530,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8541,10 +8544,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B102" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8571,7 +8574,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8589,7 +8592,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8606,7 +8609,7 @@
         <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8633,7 +8636,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L103">
         <v>1</v>
@@ -8651,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8668,7 +8671,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8695,7 +8698,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8713,7 +8716,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8727,10 +8730,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B105" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8757,7 +8760,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8775,7 +8778,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8792,7 +8795,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8819,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -8837,7 +8840,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8851,10 +8854,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B107" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8881,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8899,7 +8902,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8916,7 +8919,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8943,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8961,7 +8964,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8978,7 +8981,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -9005,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -9023,7 +9026,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -9037,10 +9040,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B110" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -9067,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -9085,7 +9088,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -9099,10 +9102,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B111" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -9129,7 +9132,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9147,7 +9150,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9164,7 +9167,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9191,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9209,7 +9212,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9226,7 +9229,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9241,22 +9244,22 @@
         <v>265</v>
       </c>
       <c r="G113">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L113">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M113">
         <v>3</v>
@@ -9265,13 +9268,13 @@
         <v>3</v>
       </c>
       <c r="O113">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P113" t="s">
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9288,7 +9291,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9315,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L114">
         <v>10</v>
@@ -9333,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9350,7 +9353,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9377,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9395,7 +9398,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9412,7 +9415,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9439,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L116">
         <v>5</v>
@@ -9457,7 +9460,7 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9474,7 +9477,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9501,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9519,7 +9522,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9536,7 +9539,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9563,7 +9566,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9581,7 +9584,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9598,7 +9601,7 @@
         <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9625,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L119">
         <v>2</v>
@@ -9643,7 +9646,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9660,7 +9663,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9687,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9705,7 +9708,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9722,7 +9725,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9749,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L121">
         <v>2</v>
@@ -9767,7 +9770,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9784,7 +9787,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9811,7 +9814,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L122">
         <v>5</v>
@@ -9829,7 +9832,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9846,7 +9849,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9873,7 +9876,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L123">
         <v>2</v>
@@ -9891,7 +9894,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9908,7 +9911,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9935,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L124">
         <v>3</v>
@@ -9953,7 +9956,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9970,7 +9973,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -9997,7 +10000,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -10015,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -10032,7 +10035,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -10059,7 +10062,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -10077,7 +10080,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -10094,7 +10097,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -10121,7 +10124,7 @@
         <v>10</v>
       </c>
       <c r="K127" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L127">
         <v>10</v>
@@ -10139,7 +10142,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -10156,7 +10159,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -10183,7 +10186,7 @@
         <v>7</v>
       </c>
       <c r="K128" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L128">
         <v>14</v>
@@ -10201,7 +10204,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -10218,7 +10221,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10245,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L129">
         <v>9</v>
@@ -10263,7 +10266,7 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10280,7 +10283,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10307,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10325,7 +10328,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10342,7 +10345,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10369,7 +10372,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10387,7 +10390,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10404,7 +10407,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10419,37 +10422,37 @@
         <v>235</v>
       </c>
       <c r="G132">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H132">
         <v>0</v>
       </c>
       <c r="I132">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="L132">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M132">
         <v>10</v>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O132">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P132" t="s">
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10466,7 +10469,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10493,7 +10496,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L133">
         <v>11</v>
@@ -10511,7 +10514,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10528,7 +10531,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10543,37 +10546,37 @@
         <v>245</v>
       </c>
       <c r="G134">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L134">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M134">
         <v>6</v>
       </c>
       <c r="N134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O134">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P134" t="s">
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10590,7 +10593,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10617,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10635,7 +10638,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10652,7 +10655,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10679,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10697,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10714,7 +10717,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10741,7 +10744,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L137">
         <v>4</v>
@@ -10759,7 +10762,7 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10776,7 +10779,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10803,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L138">
         <v>4</v>
@@ -10821,7 +10824,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10838,7 +10841,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10865,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L139">
         <v>3</v>
@@ -10883,7 +10886,7 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10900,7 +10903,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10915,37 +10918,37 @@
         <v>250</v>
       </c>
       <c r="G140">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H140">
         <v>0</v>
       </c>
       <c r="I140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M140">
         <v>0</v>
       </c>
       <c r="N140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P140" t="s">
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10962,7 +10965,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10989,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L141">
         <v>5</v>
@@ -11007,7 +11010,7 @@
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -11024,7 +11027,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -11051,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -11069,7 +11072,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -11086,7 +11089,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -11113,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -11131,7 +11134,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -11148,7 +11151,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -11175,7 +11178,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -11193,7 +11196,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -11207,10 +11210,10 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B145" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -11237,7 +11240,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -11255,7 +11258,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -11269,10 +11272,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B146" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -11299,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -11317,7 +11320,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -11334,7 +11337,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11361,7 +11364,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L147">
         <v>2</v>
@@ -11379,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11396,7 +11399,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11423,7 +11426,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L148">
         <v>6</v>
@@ -11441,7 +11444,7 @@
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11458,7 +11461,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11485,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11503,7 +11506,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11520,7 +11523,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11547,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11565,7 +11568,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11582,7 +11585,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11609,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L151">
         <v>2</v>
@@ -11627,7 +11630,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11641,16 +11644,16 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B152" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C152" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D152" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11671,7 +11674,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11703,16 +11706,16 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>491</v>
+      </c>
+      <c r="B153" t="s">
+        <v>492</v>
+      </c>
+      <c r="C153" t="s">
+        <v>249</v>
+      </c>
+      <c r="D153" t="s">
         <v>490</v>
-      </c>
-      <c r="B153" t="s">
-        <v>491</v>
-      </c>
-      <c r="C153" t="s">
-        <v>248</v>
-      </c>
-      <c r="D153" t="s">
-        <v>489</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11733,7 +11736,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11765,16 +11768,16 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B154" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C154" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D154" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11795,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11827,16 +11830,16 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B155" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C155" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D155" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11857,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11889,16 +11892,16 @@
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B156" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C156" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D156" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11919,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11951,16 +11954,16 @@
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B157" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C157" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D157" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11981,7 +11984,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -12013,16 +12016,16 @@
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B158" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C158" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D158" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -12043,7 +12046,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -12075,16 +12078,16 @@
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B159" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C159" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D159" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -12105,7 +12108,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -12137,16 +12140,16 @@
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B160" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C160" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D160" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -12167,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -12199,16 +12202,16 @@
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B161" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C161" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D161" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -12229,7 +12232,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -12261,16 +12264,16 @@
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B162" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C162" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D162" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -12291,7 +12294,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -12323,16 +12326,16 @@
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B163" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C163" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D163" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -12353,7 +12356,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -12385,16 +12388,16 @@
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B164" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C164" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D164" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -12415,7 +12418,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -12447,16 +12450,16 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B165" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C165" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D165" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12477,7 +12480,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12509,16 +12512,16 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B166" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C166" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D166" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12539,7 +12542,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12571,16 +12574,16 @@
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B167" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C167" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D167" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12601,7 +12604,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12633,16 +12636,16 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B168" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C168" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D168" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12663,7 +12666,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12695,16 +12698,16 @@
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B169" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C169" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D169" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12725,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12757,16 +12760,16 @@
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B170" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C170" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D170" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12787,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12819,16 +12822,16 @@
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B171" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C171" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D171" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12849,7 +12852,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12884,7 +12887,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12911,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L172">
         <v>6</v>
@@ -12929,7 +12932,7 @@
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12946,7 +12949,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12973,7 +12976,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L173">
         <v>7</v>
@@ -12991,7 +12994,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -13008,7 +13011,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -13035,7 +13038,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L174">
         <v>5</v>
@@ -13053,7 +13056,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -13070,7 +13073,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -13097,7 +13100,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -13115,7 +13118,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -13132,7 +13135,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -13159,7 +13162,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -13177,7 +13180,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -13194,7 +13197,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -13221,7 +13224,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L177">
         <v>2</v>
@@ -13239,7 +13242,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -13256,7 +13259,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -13283,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -13301,7 +13304,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -13318,7 +13321,7 @@
         <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -13345,7 +13348,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L179">
         <v>2</v>
@@ -13363,7 +13366,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -13380,7 +13383,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -13407,7 +13410,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L180">
         <v>3</v>
@@ -13425,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -13439,10 +13442,10 @@
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B181" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -13469,7 +13472,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -13487,7 +13490,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -13504,7 +13507,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -13531,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L182">
         <v>6</v>
@@ -13549,7 +13552,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13566,7 +13569,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13593,7 +13596,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L183">
         <v>5</v>
@@ -13611,7 +13614,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13628,7 +13631,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13655,7 +13658,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L184">
         <v>2</v>
@@ -13673,7 +13676,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13690,7 +13693,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13717,7 +13720,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L185">
         <v>4</v>
@@ -13735,7 +13738,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13752,7 +13755,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13779,7 +13782,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13797,7 +13800,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13814,7 +13817,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13841,7 +13844,7 @@
         <v>6</v>
       </c>
       <c r="K187" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L187">
         <v>9</v>
@@ -13859,7 +13862,7 @@
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13876,7 +13879,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13903,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L188">
         <v>9</v>
@@ -13921,7 +13924,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13938,7 +13941,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13965,7 +13968,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13983,7 +13986,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -14000,7 +14003,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -14027,7 +14030,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -14045,7 +14048,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14062,7 +14065,7 @@
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -14089,7 +14092,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L191">
         <v>1</v>
@@ -14098,7 +14101,7 @@
         <v>0</v>
       </c>
       <c r="N191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O191">
         <v>1</v>
@@ -14107,7 +14110,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -14124,7 +14127,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -14151,7 +14154,7 @@
         <v>9</v>
       </c>
       <c r="K192" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L192">
         <v>13</v>
@@ -14169,7 +14172,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -14186,7 +14189,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -14213,7 +14216,7 @@
         <v>4</v>
       </c>
       <c r="K193" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L193">
         <v>26</v>
@@ -14222,7 +14225,7 @@
         <v>17</v>
       </c>
       <c r="N193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O193">
         <v>26</v>
@@ -14231,7 +14234,7 @@
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -14248,7 +14251,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -14275,7 +14278,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L194">
         <v>24</v>
@@ -14293,7 +14296,7 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -14310,7 +14313,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -14331,13 +14334,13 @@
         <v>0</v>
       </c>
       <c r="I195">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J195">
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L195">
         <v>12</v>
@@ -14349,13 +14352,13 @@
         <v>1</v>
       </c>
       <c r="O195">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P195" t="s">
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -14372,7 +14375,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -14393,13 +14396,13 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J196">
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L196">
         <v>9</v>
@@ -14408,16 +14411,16 @@
         <v>7</v>
       </c>
       <c r="N196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O196">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P196" t="s">
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -14431,10 +14434,10 @@
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B197" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -14461,7 +14464,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -14479,7 +14482,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -14496,7 +14499,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -14523,7 +14526,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -14541,7 +14544,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -14558,7 +14561,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -14585,7 +14588,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -14603,7 +14606,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -14617,10 +14620,10 @@
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B200" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -14647,7 +14650,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14665,7 +14668,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14682,7 +14685,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14709,7 +14712,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14727,7 +14730,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14741,10 +14744,10 @@
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B202" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14771,7 +14774,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14789,7 +14792,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14806,7 +14809,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14833,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14851,7 +14854,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14868,7 +14871,7 @@
         <v>195</v>
       </c>
       <c r="B204" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14895,7 +14898,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L204">
         <v>2</v>
@@ -14904,7 +14907,7 @@
         <v>1</v>
       </c>
       <c r="N204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O204">
         <v>2</v>
@@ -14913,7 +14916,7 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14930,7 +14933,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14957,7 +14960,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14975,7 +14978,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14989,10 +14992,10 @@
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B206" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -15019,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -15037,7 +15040,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -15054,7 +15057,7 @@
         <v>200</v>
       </c>
       <c r="B207" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -15081,7 +15084,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L207">
         <v>1</v>
@@ -15099,7 +15102,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -15116,7 +15119,7 @@
         <v>197</v>
       </c>
       <c r="B208" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -15143,7 +15146,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L208">
         <v>1</v>
@@ -15152,7 +15155,7 @@
         <v>1</v>
       </c>
       <c r="N208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O208">
         <v>1</v>
@@ -15161,7 +15164,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -15175,10 +15178,10 @@
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B209" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -15205,7 +15208,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -15223,7 +15226,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -15240,7 +15243,7 @@
         <v>203</v>
       </c>
       <c r="B210" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -15267,7 +15270,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L210">
         <v>1</v>
@@ -15285,7 +15288,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -15302,7 +15305,7 @@
         <v>198</v>
       </c>
       <c r="B211" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -15329,7 +15332,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L211">
         <v>2</v>
@@ -15338,7 +15341,7 @@
         <v>2</v>
       </c>
       <c r="N211">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O211">
         <v>2</v>
@@ -15347,7 +15350,7 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -15361,10 +15364,10 @@
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B212" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -15391,7 +15394,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -15409,7 +15412,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -15426,7 +15429,7 @@
         <v>199</v>
       </c>
       <c r="B213" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -15453,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L213">
         <v>2</v>
@@ -15462,7 +15465,7 @@
         <v>2</v>
       </c>
       <c r="N213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O213">
         <v>2</v>
@@ -15471,7 +15474,7 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -15488,7 +15491,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -15515,7 +15518,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L214">
         <v>2</v>
@@ -15533,7 +15536,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15550,7 +15553,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -15577,7 +15580,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L215">
         <v>3</v>
@@ -15586,7 +15589,7 @@
         <v>2</v>
       </c>
       <c r="N215">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O215">
         <v>3</v>
@@ -15595,7 +15598,7 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -15609,10 +15612,10 @@
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B216" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -15639,7 +15642,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -15657,7 +15660,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15674,7 +15677,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -15701,7 +15704,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L217">
         <v>7</v>
@@ -15719,7 +15722,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15736,7 +15739,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -15763,7 +15766,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L218">
         <v>4</v>
@@ -15781,7 +15784,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15798,7 +15801,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15825,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L219">
         <v>5</v>
@@ -15834,7 +15837,7 @@
         <v>3</v>
       </c>
       <c r="N219">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O219">
         <v>5</v>
@@ -15843,7 +15846,7 @@
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15860,7 +15863,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15887,7 +15890,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L220">
         <v>4</v>
@@ -15896,7 +15899,7 @@
         <v>2</v>
       </c>
       <c r="N220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O220">
         <v>4</v>
@@ -15905,7 +15908,7 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15919,10 +15922,10 @@
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B221" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15949,7 +15952,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15967,7 +15970,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15984,7 +15987,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -16011,7 +16014,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -16029,7 +16032,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -16046,7 +16049,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -16073,7 +16076,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L223">
         <v>14</v>
@@ -16091,7 +16094,7 @@
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -16108,7 +16111,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -16135,7 +16138,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -16153,7 +16156,7 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -16170,7 +16173,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -16185,22 +16188,22 @@
         <v>250</v>
       </c>
       <c r="G225">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H225">
         <v>0</v>
       </c>
       <c r="I225">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J225">
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L225">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M225">
         <v>8</v>
@@ -16209,13 +16212,13 @@
         <v>3</v>
       </c>
       <c r="O225">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P225" t="s">
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -16232,7 +16235,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -16259,7 +16262,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -16277,7 +16280,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -16294,7 +16297,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -16321,7 +16324,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L227">
         <v>15</v>
@@ -16330,7 +16333,7 @@
         <v>10</v>
       </c>
       <c r="N227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O227">
         <v>15</v>
@@ -16339,7 +16342,7 @@
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -16356,7 +16359,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -16383,7 +16386,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L228">
         <v>16</v>
@@ -16392,7 +16395,7 @@
         <v>11</v>
       </c>
       <c r="N228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O228">
         <v>16</v>
@@ -16401,7 +16404,7 @@
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -16418,7 +16421,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -16445,7 +16448,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L229">
         <v>15</v>
@@ -16463,7 +16466,7 @@
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -16480,7 +16483,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -16507,7 +16510,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -16525,7 +16528,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -16542,7 +16545,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -16569,7 +16572,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -16587,7 +16590,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -16616,7 +16619,7 @@
         <v>122</v>
       </c>
       <c r="G232">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -16628,19 +16631,19 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L232">
+        <v>9</v>
+      </c>
+      <c r="M232">
+        <v>1</v>
+      </c>
+      <c r="N232">
         <v>7</v>
       </c>
-      <c r="M232">
-        <v>1</v>
-      </c>
-      <c r="N232">
-        <v>5</v>
-      </c>
       <c r="O232">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P232" t="s">
         <v>13</v>
@@ -16669,7 +16672,7 @@
         <v>122</v>
       </c>
       <c r="G233">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -16681,19 +16684,19 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L233">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M233">
         <v>1</v>
       </c>
       <c r="N233">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O233">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P233" t="s">
         <v>13</v>
@@ -16734,7 +16737,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L234">
         <v>1</v>
@@ -16787,7 +16790,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L235">
         <v>1</v>
@@ -16840,7 +16843,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L236">
         <v>3</v>
@@ -16849,7 +16852,7 @@
         <v>0</v>
       </c>
       <c r="N236">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O236">
         <v>3</v>
@@ -16893,7 +16896,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L237">
         <v>3</v>
@@ -16946,7 +16949,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L238">
         <v>2</v>
@@ -16999,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L239">
         <v>2</v>
@@ -17052,7 +17055,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L240">
         <v>2</v>
@@ -17105,7 +17108,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L241">
         <v>3</v>
@@ -17158,7 +17161,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L242">
         <v>2</v>
@@ -17211,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L243">
         <v>2</v>
@@ -17237,10 +17240,10 @@
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B244" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -17264,7 +17267,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L244">
         <v>0</v>
@@ -17305,7 +17308,7 @@
         <v>122</v>
       </c>
       <c r="G245">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -17317,19 +17320,19 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P245" t="s">
         <v>13</v>
@@ -17370,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -17423,7 +17426,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L247">
         <v>2</v>
@@ -17449,10 +17452,10 @@
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B248" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
@@ -17476,7 +17479,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -17529,7 +17532,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L249">
         <v>2</v>
@@ -17582,7 +17585,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L250">
         <v>1</v>
@@ -17608,10 +17611,10 @@
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B251" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
@@ -17635,7 +17638,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -17688,7 +17691,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L252">
         <v>4</v>
@@ -17741,7 +17744,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L253">
         <v>8</v>
@@ -17750,7 +17753,7 @@
         <v>0</v>
       </c>
       <c r="N253">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O253">
         <v>8</v>
@@ -17794,7 +17797,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L254">
         <v>3</v>
@@ -17847,7 +17850,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L255">
         <v>4</v>
@@ -17900,7 +17903,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L256">
         <v>7</v>
@@ -17953,7 +17956,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L257">
         <v>2</v>
@@ -18006,7 +18009,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L258">
         <v>5</v>
@@ -18059,7 +18062,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L259">
         <v>3</v>
@@ -18088,7 +18091,7 @@
         <v>176</v>
       </c>
       <c r="B260" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C260" t="s">
         <v>177</v>
@@ -18112,7 +18115,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L260">
         <v>19</v>
@@ -18121,7 +18124,7 @@
         <v>0</v>
       </c>
       <c r="N260">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="O260">
         <v>19</v>
@@ -18141,7 +18144,7 @@
         <v>201</v>
       </c>
       <c r="B261" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C261" t="s">
         <v>177</v>
@@ -18165,7 +18168,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L261">
         <v>12</v>
@@ -18194,7 +18197,7 @@
         <v>187</v>
       </c>
       <c r="B262" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C262" t="s">
         <v>177</v>
@@ -18218,7 +18221,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L262">
         <v>18</v>
@@ -18227,7 +18230,7 @@
         <v>0</v>
       </c>
       <c r="N262">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="O262">
         <v>18</v>
@@ -18247,7 +18250,7 @@
         <v>190</v>
       </c>
       <c r="B263" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C263" t="s">
         <v>177</v>
@@ -18262,7 +18265,7 @@
         <v>191</v>
       </c>
       <c r="G263">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="I263">
         <v>0</v>
@@ -18271,19 +18274,19 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L263">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M263">
         <v>0</v>
       </c>
       <c r="N263">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O263">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P263" t="s">
         <v>180</v>
@@ -18302,8 +18305,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{120C5B02-1A81-4220-BD62-5564806F5E7C}">
-  <dimension ref="A1:J629"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15246664-CEEF-4123-99C4-956D1571B799}">
+  <dimension ref="A1:J640"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -38432,6 +38435,226 @@
       </c>
       <c r="J629" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="630" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A630" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B630" t="s">
+        <v>96</v>
+      </c>
+      <c r="E630" t="s">
+        <v>53</v>
+      </c>
+      <c r="F630" t="s">
+        <v>94</v>
+      </c>
+      <c r="I630">
+        <v>1</v>
+      </c>
+      <c r="J630" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="631" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A631" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B631" t="s">
+        <v>61</v>
+      </c>
+      <c r="E631" t="s">
+        <v>219</v>
+      </c>
+      <c r="F631" t="s">
+        <v>94</v>
+      </c>
+      <c r="I631">
+        <v>1</v>
+      </c>
+      <c r="J631" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="632" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A632" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B632" t="s">
+        <v>148</v>
+      </c>
+      <c r="E632" t="s">
+        <v>219</v>
+      </c>
+      <c r="F632" t="s">
+        <v>94</v>
+      </c>
+      <c r="I632">
+        <v>1</v>
+      </c>
+      <c r="J632" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="633" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A633" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B633" t="s">
+        <v>104</v>
+      </c>
+      <c r="E633" t="s">
+        <v>130</v>
+      </c>
+      <c r="F633" t="s">
+        <v>94</v>
+      </c>
+      <c r="I633">
+        <v>1</v>
+      </c>
+      <c r="J633" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="634" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A634" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B634" t="s">
+        <v>125</v>
+      </c>
+      <c r="E634" t="s">
+        <v>13</v>
+      </c>
+      <c r="F634" t="s">
+        <v>87</v>
+      </c>
+      <c r="I634">
+        <v>1</v>
+      </c>
+      <c r="J634" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="635" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A635" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B635" t="s">
+        <v>20</v>
+      </c>
+      <c r="E635" t="s">
+        <v>13</v>
+      </c>
+      <c r="F635" t="s">
+        <v>87</v>
+      </c>
+      <c r="I635">
+        <v>1</v>
+      </c>
+      <c r="J635" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="636" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A636" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B636" t="s">
+        <v>115</v>
+      </c>
+      <c r="E636" t="s">
+        <v>100</v>
+      </c>
+      <c r="F636" t="s">
+        <v>94</v>
+      </c>
+      <c r="I636">
+        <v>1</v>
+      </c>
+      <c r="J636" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="637" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A637" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B637" t="s">
+        <v>123</v>
+      </c>
+      <c r="E637" t="s">
+        <v>133</v>
+      </c>
+      <c r="F637" t="s">
+        <v>66</v>
+      </c>
+      <c r="I637">
+        <v>1</v>
+      </c>
+      <c r="J637" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="638" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A638" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B638" t="s">
+        <v>173</v>
+      </c>
+      <c r="E638" t="s">
+        <v>133</v>
+      </c>
+      <c r="F638" t="s">
+        <v>94</v>
+      </c>
+      <c r="I638">
+        <v>1</v>
+      </c>
+      <c r="J638" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="639" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A639" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B639" t="s">
+        <v>125</v>
+      </c>
+      <c r="E639" t="s">
+        <v>133</v>
+      </c>
+      <c r="F639" t="s">
+        <v>94</v>
+      </c>
+      <c r="I639">
+        <v>1</v>
+      </c>
+      <c r="J639" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="640" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A640" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B640" t="s">
+        <v>190</v>
+      </c>
+      <c r="E640" t="s">
+        <v>188</v>
+      </c>
+      <c r="F640" t="s">
+        <v>94</v>
+      </c>
+      <c r="I640">
+        <v>1</v>
+      </c>
+      <c r="J640" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61100AF8-4787-43DB-A685-C42ED7A12504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ED13D8B-1554-47F3-8A77-143E0B09C3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{E961E4E0-9113-49A0-8EB8-03CB5463E976}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{DB096BD8-C3F9-466B-9288-40B14382B998}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6492" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6636" uniqueCount="617">
   <si>
     <t>날짜</t>
   </si>
@@ -702,6 +702,21 @@
     <t>체크아웃/바오지</t>
   </si>
   <si>
+    <t>BJM931-BK280</t>
+  </si>
+  <si>
+    <t>S-10RA-GYGC</t>
+  </si>
+  <si>
+    <t>S-10RA-MAGG</t>
+  </si>
+  <si>
+    <t>S-10HA-GYGC</t>
+  </si>
+  <si>
+    <t>BJM931-GYOR280</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1188,9 +1203,6 @@
     <t>BJM931BK 바오지 남성 러닝화 블랙 275</t>
   </si>
   <si>
-    <t>BJM931-BK280</t>
-  </si>
-  <si>
     <t>BJM931BK 바오지 남성 러닝화 블랙 280</t>
   </si>
   <si>
@@ -1221,9 +1233,6 @@
     <t>BJM931GYOR 바오지 남성 러닝화 그레이오렌지 275</t>
   </si>
   <si>
-    <t>BJM931-GYOR280</t>
-  </si>
-  <si>
     <t>BJM931GYOR 바오지 남성 러닝화 그레이오렌지 280</t>
   </si>
   <si>
@@ -1870,15 +1879,6 @@
   </si>
   <si>
     <t>ECW304WHPK 바오지 여성 러닝화 화이트핑크 255</t>
-  </si>
-  <si>
-    <t>S-10HA-GYGC</t>
-  </si>
-  <si>
-    <t>S-10RA-GYGC</t>
-  </si>
-  <si>
-    <t>S-10RA-MAGG</t>
   </si>
   <si>
     <t>볼트겔 클리어겔 롤형 테이프 1m</t>
@@ -2276,7 +2276,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F85C1F7-AE3C-4883-8BDF-37CED419309C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C1DBD6-F3CA-4E55-A611-25A79AE89B91}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2285,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2300,46 +2300,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="J1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="M1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="N1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="O1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="R1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="S1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="T1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2347,7 +2347,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2392,7 +2392,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -2454,7 +2454,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -2516,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2578,7 +2578,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2595,7 +2595,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2622,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2640,7 +2640,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2657,7 +2657,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2702,7 +2702,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2764,7 +2764,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2781,7 +2781,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2826,7 +2826,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2888,7 +2888,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2950,7 +2950,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2964,16 +2964,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D12" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3026,16 +3026,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B13" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C13" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D13" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3056,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3088,16 +3088,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" t="s">
         <v>254</v>
       </c>
-      <c r="C14" t="s">
-        <v>249</v>
-      </c>
       <c r="D14" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3150,16 +3150,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" t="s">
         <v>255</v>
-      </c>
-      <c r="B15" t="s">
-        <v>256</v>
-      </c>
-      <c r="C15" t="s">
-        <v>249</v>
-      </c>
-      <c r="D15" t="s">
-        <v>250</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3212,16 +3212,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B16" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C16" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D16" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B17" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C17" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D17" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3336,16 +3336,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B18" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D18" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3366,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3398,16 +3398,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B19" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D19" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3460,16 +3460,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B20" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C20" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D20" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3522,16 +3522,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B21" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C21" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D21" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3584,16 +3584,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B22" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C22" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D22" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3614,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3646,16 +3646,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C23" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D23" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3708,16 +3708,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C24" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D24" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3770,16 +3770,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B25" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C25" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D25" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3832,16 +3832,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C26" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D26" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D27" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3956,16 +3956,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C28" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D28" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4018,16 +4018,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C29" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D29" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4048,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4080,16 +4080,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C30" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D30" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4142,16 +4142,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C31" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D31" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4204,16 +4204,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C32" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4266,16 +4266,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C33" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4328,16 +4328,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C34" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D34" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4390,16 +4390,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>301</v>
+      </c>
+      <c r="B35" t="s">
+        <v>302</v>
+      </c>
+      <c r="C35" t="s">
+        <v>254</v>
+      </c>
+      <c r="D35" t="s">
         <v>296</v>
-      </c>
-      <c r="B35" t="s">
-        <v>297</v>
-      </c>
-      <c r="C35" t="s">
-        <v>249</v>
-      </c>
-      <c r="D35" t="s">
-        <v>291</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4452,16 +4452,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C36" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D36" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4514,16 +4514,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C37" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D37" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4576,16 +4576,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C38" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D38" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4638,16 +4638,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B39" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C39" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D39" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4668,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4700,16 +4700,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C40" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D40" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4762,16 +4762,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C41" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D41" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4792,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4824,16 +4824,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C42" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D42" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4854,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4886,16 +4886,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C43" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D43" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4916,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4948,16 +4948,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C44" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D44" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5010,16 +5010,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C45" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D45" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5040,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5072,16 +5072,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C46" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D46" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5134,16 +5134,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B47" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C47" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D47" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5196,16 +5196,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C48" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D48" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5258,16 +5258,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C49" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D49" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5320,16 +5320,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C50" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D50" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5350,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5382,16 +5382,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C51" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D51" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5444,16 +5444,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C52" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D52" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5506,16 +5506,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C53" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D53" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5536,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5568,16 +5568,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C54" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D54" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5630,16 +5630,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>342</v>
+      </c>
+      <c r="B55" t="s">
+        <v>343</v>
+      </c>
+      <c r="C55" t="s">
+        <v>254</v>
+      </c>
+      <c r="D55" t="s">
         <v>337</v>
-      </c>
-      <c r="B55" t="s">
-        <v>338</v>
-      </c>
-      <c r="C55" t="s">
-        <v>249</v>
-      </c>
-      <c r="D55" t="s">
-        <v>332</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5660,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5692,16 +5692,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B56" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C56" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D56" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5722,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5754,16 +5754,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B57" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C57" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D57" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5784,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5816,16 +5816,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B58" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C58" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D58" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5846,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5878,16 +5878,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C59" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D59" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5940,16 +5940,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B60" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C60" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D60" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -6002,16 +6002,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B61" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C61" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D61" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6032,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6064,16 +6064,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C62" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D62" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6126,16 +6126,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B63" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C63" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D63" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6188,16 +6188,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B64" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C64" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6218,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6250,16 +6250,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B65" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C65" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6280,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6312,16 +6312,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C66" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D66" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6342,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6377,7 +6377,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6404,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6422,7 +6422,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6439,7 +6439,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L68">
         <v>4</v>
@@ -6484,7 +6484,7 @@
         <v>16</v>
       </c>
       <c r="Q68" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -6501,7 +6501,7 @@
         <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -6528,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L69">
         <v>9</v>
@@ -6546,7 +6546,7 @@
         <v>16</v>
       </c>
       <c r="Q69" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -6563,7 +6563,7 @@
         <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -6590,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L70">
         <v>2</v>
@@ -6608,7 +6608,7 @@
         <v>16</v>
       </c>
       <c r="Q70" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -6625,7 +6625,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -6652,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L71">
         <v>2</v>
@@ -6670,7 +6670,7 @@
         <v>16</v>
       </c>
       <c r="Q71" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -6684,10 +6684,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B72" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -6714,7 +6714,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -6732,7 +6732,7 @@
         <v>16</v>
       </c>
       <c r="Q72" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>118</v>
       </c>
       <c r="B73" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L73">
         <v>3</v>
@@ -6794,7 +6794,7 @@
         <v>16</v>
       </c>
       <c r="Q73" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>213</v>
       </c>
       <c r="B74" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C74" t="s">
         <v>24</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L74">
         <v>1</v>
@@ -6856,7 +6856,7 @@
         <v>16</v>
       </c>
       <c r="Q74" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -6873,7 +6873,7 @@
         <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C75" t="s">
         <v>24</v>
@@ -6900,7 +6900,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6918,7 +6918,7 @@
         <v>16</v>
       </c>
       <c r="Q75" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B76" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C76" t="s">
         <v>24</v>
@@ -6962,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -6980,7 +6980,7 @@
         <v>16</v>
       </c>
       <c r="Q76" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -6997,7 +6997,7 @@
         <v>184</v>
       </c>
       <c r="B77" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C77" t="s">
         <v>24</v>
@@ -7024,7 +7024,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -7042,7 +7042,7 @@
         <v>16</v>
       </c>
       <c r="Q77" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B78" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C78" t="s">
         <v>24</v>
@@ -7086,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -7104,7 +7104,7 @@
         <v>16</v>
       </c>
       <c r="Q78" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -7118,10 +7118,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B79" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C79" t="s">
         <v>24</v>
@@ -7148,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -7166,7 +7166,7 @@
         <v>16</v>
       </c>
       <c r="Q79" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -7183,7 +7183,7 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C80" t="s">
         <v>24</v>
@@ -7210,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -7228,7 +7228,7 @@
         <v>16</v>
       </c>
       <c r="Q80" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -7242,10 +7242,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>382</v>
+        <v>220</v>
       </c>
       <c r="B81" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
@@ -7260,37 +7260,37 @@
         <v>280</v>
       </c>
       <c r="G81">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H81">
         <v>0</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81">
         <v>0</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" t="s">
         <v>16</v>
       </c>
       <c r="Q81" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -7304,10 +7304,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B82" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C82" t="s">
         <v>24</v>
@@ -7334,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -7352,7 +7352,7 @@
         <v>16</v>
       </c>
       <c r="Q82" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -7366,10 +7366,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B83" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C83" t="s">
         <v>24</v>
@@ -7396,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -7414,7 +7414,7 @@
         <v>16</v>
       </c>
       <c r="Q83" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -7428,10 +7428,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B84" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C84" t="s">
         <v>24</v>
@@ -7458,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -7476,7 +7476,7 @@
         <v>16</v>
       </c>
       <c r="Q84" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -7490,10 +7490,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B85" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C85" t="s">
         <v>24</v>
@@ -7520,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -7538,7 +7538,7 @@
         <v>16</v>
       </c>
       <c r="Q85" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -7552,10 +7552,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>393</v>
+        <v>224</v>
       </c>
       <c r="B86" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C86" t="s">
         <v>24</v>
@@ -7570,37 +7570,37 @@
         <v>280</v>
       </c>
       <c r="G86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H86">
         <v>0</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86">
         <v>0</v>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="s">
         <v>16</v>
       </c>
       <c r="Q86" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -7614,10 +7614,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B87" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C87" t="s">
         <v>24</v>
@@ -7644,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -7662,7 +7662,7 @@
         <v>16</v>
       </c>
       <c r="Q87" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -7679,7 +7679,7 @@
         <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -7706,7 +7706,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L88">
         <v>2</v>
@@ -7724,7 +7724,7 @@
         <v>16</v>
       </c>
       <c r="Q88" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>212</v>
       </c>
       <c r="B89" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -7768,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L89">
         <v>1</v>
@@ -7786,7 +7786,7 @@
         <v>16</v>
       </c>
       <c r="Q89" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -7803,7 +7803,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C90" t="s">
         <v>24</v>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L90">
         <v>2</v>
@@ -7848,7 +7848,7 @@
         <v>16</v>
       </c>
       <c r="Q90" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B91" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -7892,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -7910,7 +7910,7 @@
         <v>16</v>
       </c>
       <c r="Q91" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -7924,10 +7924,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B92" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C92" t="s">
         <v>24</v>
@@ -7954,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="Q92" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -8034,7 +8034,7 @@
         <v>16</v>
       </c>
       <c r="Q93" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -8048,10 +8048,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B94" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -8078,7 +8078,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -8096,7 +8096,7 @@
         <v>16</v>
       </c>
       <c r="Q94" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -8110,10 +8110,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B95" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C95" t="s">
         <v>24</v>
@@ -8140,7 +8140,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -8158,7 +8158,7 @@
         <v>16</v>
       </c>
       <c r="Q95" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -8172,10 +8172,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B96" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C96" t="s">
         <v>24</v>
@@ -8202,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -8220,7 +8220,7 @@
         <v>16</v>
       </c>
       <c r="Q96" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -8234,10 +8234,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B97" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -8264,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -8282,7 +8282,7 @@
         <v>16</v>
       </c>
       <c r="Q97" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -8326,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L98">
         <v>6</v>
@@ -8335,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O98">
         <v>5</v>
@@ -8344,7 +8344,7 @@
         <v>16</v>
       </c>
       <c r="Q98" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -8361,7 +8361,7 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -8388,7 +8388,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L99">
         <v>2</v>
@@ -8406,7 +8406,7 @@
         <v>16</v>
       </c>
       <c r="Q99" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R99">
         <v>0</v>
@@ -8423,7 +8423,7 @@
         <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -8450,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L100">
         <v>3</v>
@@ -8468,7 +8468,7 @@
         <v>16</v>
       </c>
       <c r="Q100" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -8482,10 +8482,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B101" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -8512,7 +8512,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -8530,7 +8530,7 @@
         <v>16</v>
       </c>
       <c r="Q101" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -8544,10 +8544,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B102" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -8574,7 +8574,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -8592,7 +8592,7 @@
         <v>16</v>
       </c>
       <c r="Q102" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -8609,7 +8609,7 @@
         <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C103" t="s">
         <v>24</v>
@@ -8636,7 +8636,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L103">
         <v>1</v>
@@ -8654,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="Q103" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R103">
         <v>0</v>
@@ -8671,7 +8671,7 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -8698,7 +8698,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -8716,7 +8716,7 @@
         <v>16</v>
       </c>
       <c r="Q104" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -8730,10 +8730,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B105" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -8760,7 +8760,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -8778,7 +8778,7 @@
         <v>16</v>
       </c>
       <c r="Q105" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -8795,7 +8795,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -8810,37 +8810,37 @@
         <v>280</v>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106">
         <v>0</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="L106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M106">
         <v>0</v>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" t="s">
         <v>16</v>
       </c>
       <c r="Q106" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -8854,10 +8854,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B107" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -8884,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>16</v>
       </c>
       <c r="Q107" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -8919,7 +8919,7 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -8964,7 +8964,7 @@
         <v>16</v>
       </c>
       <c r="Q108" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -8981,7 +8981,7 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -9026,7 +9026,7 @@
         <v>16</v>
       </c>
       <c r="Q109" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -9040,10 +9040,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B110" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C110" t="s">
         <v>24</v>
@@ -9070,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -9088,7 +9088,7 @@
         <v>16</v>
       </c>
       <c r="Q110" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -9102,10 +9102,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B111" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C111" t="s">
         <v>24</v>
@@ -9132,7 +9132,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -9150,7 +9150,7 @@
         <v>16</v>
       </c>
       <c r="Q111" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="R111">
         <v>0</v>
@@ -9167,7 +9167,7 @@
         <v>52</v>
       </c>
       <c r="B112" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C112" t="s">
         <v>24</v>
@@ -9194,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L112">
         <v>4</v>
@@ -9212,7 +9212,7 @@
         <v>16</v>
       </c>
       <c r="Q112" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -9229,7 +9229,7 @@
         <v>96</v>
       </c>
       <c r="B113" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C113" t="s">
         <v>24</v>
@@ -9256,7 +9256,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L113">
         <v>9</v>
@@ -9274,7 +9274,7 @@
         <v>16</v>
       </c>
       <c r="Q113" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -9291,7 +9291,7 @@
         <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -9318,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L114">
         <v>10</v>
@@ -9327,7 +9327,7 @@
         <v>0</v>
       </c>
       <c r="N114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114">
         <v>10</v>
@@ -9336,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="Q114" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -9353,7 +9353,7 @@
         <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C115" t="s">
         <v>24</v>
@@ -9380,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L115">
         <v>4</v>
@@ -9398,7 +9398,7 @@
         <v>16</v>
       </c>
       <c r="Q115" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -9415,7 +9415,7 @@
         <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C116" t="s">
         <v>24</v>
@@ -9430,7 +9430,7 @@
         <v>280</v>
       </c>
       <c r="G116">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -9442,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L116">
         <v>5</v>
@@ -9460,7 +9460,7 @@
         <v>16</v>
       </c>
       <c r="Q116" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -9477,7 +9477,7 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C117" t="s">
         <v>24</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L117">
         <v>2</v>
@@ -9522,7 +9522,7 @@
         <v>16</v>
       </c>
       <c r="Q117" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -9539,7 +9539,7 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C118" t="s">
         <v>24</v>
@@ -9566,7 +9566,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9584,7 +9584,7 @@
         <v>16</v>
       </c>
       <c r="Q118" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="R118">
         <v>0</v>
@@ -9601,7 +9601,7 @@
         <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C119" t="s">
         <v>24</v>
@@ -9628,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L119">
         <v>2</v>
@@ -9646,7 +9646,7 @@
         <v>16</v>
       </c>
       <c r="Q119" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="R119">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C120" t="s">
         <v>24</v>
@@ -9690,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L120">
         <v>2</v>
@@ -9708,7 +9708,7 @@
         <v>16</v>
       </c>
       <c r="Q120" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="R120">
         <v>0</v>
@@ -9725,7 +9725,7 @@
         <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -9752,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L121">
         <v>2</v>
@@ -9770,7 +9770,7 @@
         <v>16</v>
       </c>
       <c r="Q121" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -9787,7 +9787,7 @@
         <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C122" t="s">
         <v>24</v>
@@ -9814,7 +9814,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L122">
         <v>5</v>
@@ -9832,7 +9832,7 @@
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -9849,7 +9849,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C123" t="s">
         <v>24</v>
@@ -9876,7 +9876,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L123">
         <v>2</v>
@@ -9894,7 +9894,7 @@
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="R123">
         <v>0</v>
@@ -9911,7 +9911,7 @@
         <v>95</v>
       </c>
       <c r="B124" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C124" t="s">
         <v>24</v>
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L124">
         <v>3</v>
@@ -9956,7 +9956,7 @@
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="R124">
         <v>0</v>
@@ -9973,7 +9973,7 @@
         <v>84</v>
       </c>
       <c r="B125" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C125" t="s">
         <v>24</v>
@@ -10000,7 +10000,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -10018,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="Q125" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -10035,7 +10035,7 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C126" t="s">
         <v>24</v>
@@ -10062,7 +10062,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L126">
         <v>4</v>
@@ -10080,7 +10080,7 @@
         <v>16</v>
       </c>
       <c r="Q126" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -10097,7 +10097,7 @@
         <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
@@ -10124,7 +10124,7 @@
         <v>10</v>
       </c>
       <c r="K127" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L127">
         <v>10</v>
@@ -10133,7 +10133,7 @@
         <v>5</v>
       </c>
       <c r="N127">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O127">
         <v>10</v>
@@ -10142,7 +10142,7 @@
         <v>16</v>
       </c>
       <c r="Q127" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -10159,7 +10159,7 @@
         <v>69</v>
       </c>
       <c r="B128" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -10186,7 +10186,7 @@
         <v>7</v>
       </c>
       <c r="K128" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L128">
         <v>14</v>
@@ -10204,7 +10204,7 @@
         <v>16</v>
       </c>
       <c r="Q128" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -10221,7 +10221,7 @@
         <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -10248,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L129">
         <v>9</v>
@@ -10257,7 +10257,7 @@
         <v>6</v>
       </c>
       <c r="N129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O129">
         <v>9</v>
@@ -10266,7 +10266,7 @@
         <v>16</v>
       </c>
       <c r="Q129" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="R129">
         <v>0</v>
@@ -10283,7 +10283,7 @@
         <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -10310,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L130">
         <v>7</v>
@@ -10328,7 +10328,7 @@
         <v>16</v>
       </c>
       <c r="Q130" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>77</v>
       </c>
       <c r="B131" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C131" t="s">
         <v>18</v>
@@ -10372,7 +10372,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -10390,7 +10390,7 @@
         <v>16</v>
       </c>
       <c r="Q131" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="R131">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C132" t="s">
         <v>18</v>
@@ -10434,7 +10434,7 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L132">
         <v>19</v>
@@ -10452,7 +10452,7 @@
         <v>16</v>
       </c>
       <c r="Q132" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -10469,7 +10469,7 @@
         <v>78</v>
       </c>
       <c r="B133" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C133" t="s">
         <v>18</v>
@@ -10496,7 +10496,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L133">
         <v>11</v>
@@ -10514,7 +10514,7 @@
         <v>16</v>
       </c>
       <c r="Q133" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -10531,7 +10531,7 @@
         <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C134" t="s">
         <v>18</v>
@@ -10558,7 +10558,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L134">
         <v>18</v>
@@ -10576,7 +10576,7 @@
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -10593,7 +10593,7 @@
         <v>75</v>
       </c>
       <c r="B135" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C135" t="s">
         <v>18</v>
@@ -10620,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -10638,7 +10638,7 @@
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -10655,7 +10655,7 @@
         <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
@@ -10682,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L136">
         <v>4</v>
@@ -10700,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="R136">
         <v>0</v>
@@ -10717,7 +10717,7 @@
         <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C137" t="s">
         <v>18</v>
@@ -10744,7 +10744,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L137">
         <v>4</v>
@@ -10762,7 +10762,7 @@
         <v>16</v>
       </c>
       <c r="Q137" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -10779,7 +10779,7 @@
         <v>161</v>
       </c>
       <c r="B138" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C138" t="s">
         <v>18</v>
@@ -10806,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L138">
         <v>4</v>
@@ -10824,7 +10824,7 @@
         <v>16</v>
       </c>
       <c r="Q138" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -10841,7 +10841,7 @@
         <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C139" t="s">
         <v>18</v>
@@ -10856,7 +10856,7 @@
         <v>245</v>
       </c>
       <c r="G139">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L139">
         <v>3</v>
@@ -10886,7 +10886,7 @@
         <v>16</v>
       </c>
       <c r="Q139" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="R139">
         <v>0</v>
@@ -10903,7 +10903,7 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -10930,7 +10930,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L140">
         <v>4</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="N140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O140">
         <v>4</v>
@@ -10948,7 +10948,7 @@
         <v>16</v>
       </c>
       <c r="Q140" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -10965,7 +10965,7 @@
         <v>162</v>
       </c>
       <c r="B141" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -10992,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L141">
         <v>5</v>
@@ -11001,7 +11001,7 @@
         <v>0</v>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O141">
         <v>5</v>
@@ -11010,7 +11010,7 @@
         <v>16</v>
       </c>
       <c r="Q141" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -11027,7 +11027,7 @@
         <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -11054,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -11072,7 +11072,7 @@
         <v>16</v>
       </c>
       <c r="Q142" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="R142">
         <v>0</v>
@@ -11089,7 +11089,7 @@
         <v>166</v>
       </c>
       <c r="B143" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L143">
         <v>1</v>
@@ -11134,7 +11134,7 @@
         <v>16</v>
       </c>
       <c r="Q143" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="R143">
         <v>0</v>
@@ -11151,7 +11151,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -11178,7 +11178,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L144">
         <v>2</v>
@@ -11196,7 +11196,7 @@
         <v>16</v>
       </c>
       <c r="Q144" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -11210,10 +11210,10 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B145" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C145" t="s">
         <v>18</v>
@@ -11240,7 +11240,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -11258,7 +11258,7 @@
         <v>16</v>
       </c>
       <c r="Q145" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -11272,10 +11272,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B146" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -11302,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -11320,7 +11320,7 @@
         <v>16</v>
       </c>
       <c r="Q146" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -11337,7 +11337,7 @@
         <v>171</v>
       </c>
       <c r="B147" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -11364,7 +11364,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L147">
         <v>2</v>
@@ -11382,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="Q147" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="R147">
         <v>0</v>
@@ -11399,7 +11399,7 @@
         <v>112</v>
       </c>
       <c r="B148" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -11414,37 +11414,37 @@
         <v>240</v>
       </c>
       <c r="G148">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L148">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M148">
         <v>2</v>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O148">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P148" t="s">
         <v>16</v>
       </c>
       <c r="Q148" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -11461,7 +11461,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C149" t="s">
         <v>18</v>
@@ -11488,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>16</v>
       </c>
       <c r="Q149" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -11523,7 +11523,7 @@
         <v>105</v>
       </c>
       <c r="B150" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
@@ -11538,7 +11538,7 @@
         <v>250</v>
       </c>
       <c r="G150">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -11550,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L150">
         <v>2</v>
@@ -11568,7 +11568,7 @@
         <v>16</v>
       </c>
       <c r="Q150" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="R150">
         <v>0</v>
@@ -11585,7 +11585,7 @@
         <v>116</v>
       </c>
       <c r="B151" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C151" t="s">
         <v>18</v>
@@ -11612,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L151">
         <v>2</v>
@@ -11630,7 +11630,7 @@
         <v>16</v>
       </c>
       <c r="Q151" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -11644,16 +11644,16 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B152" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C152" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D152" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -11674,7 +11674,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -11706,16 +11706,16 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B153" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C153" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D153" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -11736,7 +11736,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -11768,16 +11768,16 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>496</v>
+      </c>
+      <c r="B154" t="s">
+        <v>497</v>
+      </c>
+      <c r="C154" t="s">
+        <v>254</v>
+      </c>
+      <c r="D154" t="s">
         <v>493</v>
-      </c>
-      <c r="B154" t="s">
-        <v>494</v>
-      </c>
-      <c r="C154" t="s">
-        <v>249</v>
-      </c>
-      <c r="D154" t="s">
-        <v>490</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -11798,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -11830,16 +11830,16 @@
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B155" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C155" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D155" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -11860,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -11892,16 +11892,16 @@
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B156" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C156" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D156" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -11922,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -11954,16 +11954,16 @@
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B157" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C157" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D157" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -11984,7 +11984,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -12016,16 +12016,16 @@
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B158" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C158" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D158" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -12046,7 +12046,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -12078,16 +12078,16 @@
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B159" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C159" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D159" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -12108,7 +12108,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -12140,16 +12140,16 @@
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B160" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C160" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D160" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -12202,16 +12202,16 @@
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B161" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C161" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D161" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -12232,7 +12232,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -12264,16 +12264,16 @@
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B162" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C162" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D162" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -12294,7 +12294,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -12326,16 +12326,16 @@
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B163" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C163" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D163" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -12356,7 +12356,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -12388,16 +12388,16 @@
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B164" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C164" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D164" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E164" t="s">
         <v>22</v>
@@ -12418,7 +12418,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L164">
         <v>0</v>
@@ -12450,16 +12450,16 @@
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B165" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C165" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D165" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E165" t="s">
         <v>22</v>
@@ -12480,7 +12480,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -12512,16 +12512,16 @@
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B166" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C166" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D166" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E166" t="s">
         <v>22</v>
@@ -12542,7 +12542,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -12574,16 +12574,16 @@
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B167" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C167" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D167" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E167" t="s">
         <v>22</v>
@@ -12604,7 +12604,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -12636,16 +12636,16 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B168" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C168" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D168" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E168" t="s">
         <v>22</v>
@@ -12666,7 +12666,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -12698,16 +12698,16 @@
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B169" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C169" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D169" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E169" t="s">
         <v>22</v>
@@ -12728,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -12760,16 +12760,16 @@
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B170" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C170" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D170" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E170" t="s">
         <v>22</v>
@@ -12790,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -12822,16 +12822,16 @@
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B171" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C171" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D171" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E171" t="s">
         <v>22</v>
@@ -12852,7 +12852,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -12887,7 +12887,7 @@
         <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C172" t="s">
         <v>24</v>
@@ -12902,37 +12902,37 @@
         <v>235</v>
       </c>
       <c r="G172">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J172">
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L172">
+        <v>7</v>
+      </c>
+      <c r="M172">
+        <v>1</v>
+      </c>
+      <c r="N172">
+        <v>1</v>
+      </c>
+      <c r="O172">
         <v>6</v>
       </c>
-      <c r="M172">
-        <v>1</v>
-      </c>
-      <c r="N172">
-        <v>0</v>
-      </c>
-      <c r="O172">
-        <v>5</v>
-      </c>
       <c r="P172" t="s">
         <v>16</v>
       </c>
       <c r="Q172" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="R172">
         <v>0</v>
@@ -12949,7 +12949,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
@@ -12976,7 +12976,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L173">
         <v>7</v>
@@ -12994,7 +12994,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="R173">
         <v>0</v>
@@ -13011,7 +13011,7 @@
         <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C174" t="s">
         <v>24</v>
@@ -13038,7 +13038,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L174">
         <v>5</v>
@@ -13056,7 +13056,7 @@
         <v>16</v>
       </c>
       <c r="Q174" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="R174">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -13100,7 +13100,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -13118,7 +13118,7 @@
         <v>16</v>
       </c>
       <c r="Q175" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -13135,7 +13135,7 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C176" t="s">
         <v>24</v>
@@ -13162,7 +13162,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -13180,7 +13180,7 @@
         <v>16</v>
       </c>
       <c r="Q176" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -13197,7 +13197,7 @@
         <v>155</v>
       </c>
       <c r="B177" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C177" t="s">
         <v>24</v>
@@ -13224,7 +13224,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L177">
         <v>2</v>
@@ -13242,7 +13242,7 @@
         <v>16</v>
       </c>
       <c r="Q177" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="R177">
         <v>0</v>
@@ -13259,7 +13259,7 @@
         <v>141</v>
       </c>
       <c r="B178" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C178" t="s">
         <v>24</v>
@@ -13286,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L178">
         <v>2</v>
@@ -13304,7 +13304,7 @@
         <v>16</v>
       </c>
       <c r="Q178" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -13321,7 +13321,7 @@
         <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C179" t="s">
         <v>24</v>
@@ -13348,7 +13348,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L179">
         <v>2</v>
@@ -13366,7 +13366,7 @@
         <v>16</v>
       </c>
       <c r="Q179" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="R179">
         <v>0</v>
@@ -13383,7 +13383,7 @@
         <v>110</v>
       </c>
       <c r="B180" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -13410,7 +13410,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L180">
         <v>3</v>
@@ -13428,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="Q180" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -13442,10 +13442,10 @@
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B181" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C181" t="s">
         <v>24</v>
@@ -13472,7 +13472,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -13490,7 +13490,7 @@
         <v>16</v>
       </c>
       <c r="Q181" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="R181">
         <v>0</v>
@@ -13507,7 +13507,7 @@
         <v>27</v>
       </c>
       <c r="B182" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C182" t="s">
         <v>24</v>
@@ -13522,7 +13522,7 @@
         <v>235</v>
       </c>
       <c r="G182">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L182">
         <v>6</v>
@@ -13552,7 +13552,7 @@
         <v>16</v>
       </c>
       <c r="Q182" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="R182">
         <v>0</v>
@@ -13569,7 +13569,7 @@
         <v>28</v>
       </c>
       <c r="B183" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C183" t="s">
         <v>24</v>
@@ -13584,7 +13584,7 @@
         <v>240</v>
       </c>
       <c r="G183">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -13596,7 +13596,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L183">
         <v>5</v>
@@ -13614,7 +13614,7 @@
         <v>16</v>
       </c>
       <c r="Q183" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -13631,7 +13631,7 @@
         <v>157</v>
       </c>
       <c r="B184" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C184" t="s">
         <v>24</v>
@@ -13658,7 +13658,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L184">
         <v>2</v>
@@ -13676,7 +13676,7 @@
         <v>16</v>
       </c>
       <c r="Q184" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="R184">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>108</v>
       </c>
       <c r="B185" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C185" t="s">
         <v>24</v>
@@ -13720,7 +13720,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L185">
         <v>4</v>
@@ -13738,7 +13738,7 @@
         <v>16</v>
       </c>
       <c r="Q185" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="R185">
         <v>0</v>
@@ -13755,7 +13755,7 @@
         <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -13782,7 +13782,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L186">
         <v>2</v>
@@ -13800,7 +13800,7 @@
         <v>16</v>
       </c>
       <c r="Q186" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -13817,7 +13817,7 @@
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C187" t="s">
         <v>24</v>
@@ -13832,22 +13832,22 @@
         <v>235</v>
       </c>
       <c r="G187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187">
         <v>0</v>
       </c>
       <c r="I187">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J187">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K187" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L187">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M187">
         <v>3</v>
@@ -13856,13 +13856,13 @@
         <v>1</v>
       </c>
       <c r="O187">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P187" t="s">
         <v>16</v>
       </c>
       <c r="Q187" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="R187">
         <v>0</v>
@@ -13879,7 +13879,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C188" t="s">
         <v>24</v>
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L188">
         <v>9</v>
@@ -13924,7 +13924,7 @@
         <v>16</v>
       </c>
       <c r="Q188" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="R188">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>42</v>
       </c>
       <c r="B189" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C189" t="s">
         <v>24</v>
@@ -13968,7 +13968,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L189">
         <v>8</v>
@@ -13986,7 +13986,7 @@
         <v>16</v>
       </c>
       <c r="Q189" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="R189">
         <v>0</v>
@@ -14003,7 +14003,7 @@
         <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C190" t="s">
         <v>24</v>
@@ -14030,7 +14030,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L190">
         <v>8</v>
@@ -14048,7 +14048,7 @@
         <v>16</v>
       </c>
       <c r="Q190" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14065,7 +14065,7 @@
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -14092,7 +14092,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L191">
         <v>1</v>
@@ -14110,7 +14110,7 @@
         <v>16</v>
       </c>
       <c r="Q191" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -14127,7 +14127,7 @@
         <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C192" t="s">
         <v>24</v>
@@ -14154,7 +14154,7 @@
         <v>9</v>
       </c>
       <c r="K192" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L192">
         <v>13</v>
@@ -14163,7 +14163,7 @@
         <v>8</v>
       </c>
       <c r="N192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O192">
         <v>11</v>
@@ -14172,7 +14172,7 @@
         <v>16</v>
       </c>
       <c r="Q192" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R192">
         <v>0</v>
@@ -14189,7 +14189,7 @@
         <v>67</v>
       </c>
       <c r="B193" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
@@ -14204,22 +14204,22 @@
         <v>240</v>
       </c>
       <c r="G193">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J193">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K193" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L193">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M193">
         <v>17</v>
@@ -14228,13 +14228,13 @@
         <v>4</v>
       </c>
       <c r="O193">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P193" t="s">
         <v>16</v>
       </c>
       <c r="Q193" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R193">
         <v>0</v>
@@ -14251,7 +14251,7 @@
         <v>44</v>
       </c>
       <c r="B194" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C194" t="s">
         <v>24</v>
@@ -14278,7 +14278,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L194">
         <v>24</v>
@@ -14296,7 +14296,7 @@
         <v>16</v>
       </c>
       <c r="Q194" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R194">
         <v>0</v>
@@ -14313,7 +14313,7 @@
         <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C195" t="s">
         <v>24</v>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L195">
         <v>12</v>
@@ -14358,7 +14358,7 @@
         <v>16</v>
       </c>
       <c r="Q195" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R195">
         <v>0</v>
@@ -14375,7 +14375,7 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C196" t="s">
         <v>24</v>
@@ -14402,7 +14402,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L196">
         <v>9</v>
@@ -14420,7 +14420,7 @@
         <v>16</v>
       </c>
       <c r="Q196" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -14434,10 +14434,10 @@
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B197" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -14464,7 +14464,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -14482,7 +14482,7 @@
         <v>16</v>
       </c>
       <c r="Q197" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R197">
         <v>0</v>
@@ -14499,7 +14499,7 @@
         <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C198" t="s">
         <v>24</v>
@@ -14526,7 +14526,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L198">
         <v>8</v>
@@ -14544,7 +14544,7 @@
         <v>16</v>
       </c>
       <c r="Q198" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -14561,7 +14561,7 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C199" t="s">
         <v>24</v>
@@ -14588,7 +14588,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L199">
         <v>5</v>
@@ -14606,7 +14606,7 @@
         <v>16</v>
       </c>
       <c r="Q199" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R199">
         <v>0</v>
@@ -14620,10 +14620,10 @@
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B200" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C200" t="s">
         <v>24</v>
@@ -14650,7 +14650,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -14668,7 +14668,7 @@
         <v>16</v>
       </c>
       <c r="Q200" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R200">
         <v>0</v>
@@ -14685,7 +14685,7 @@
         <v>83</v>
       </c>
       <c r="B201" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C201" t="s">
         <v>24</v>
@@ -14712,7 +14712,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L201">
         <v>3</v>
@@ -14730,7 +14730,7 @@
         <v>16</v>
       </c>
       <c r="Q201" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14744,10 +14744,10 @@
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B202" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C202" t="s">
         <v>24</v>
@@ -14774,7 +14774,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14792,7 +14792,7 @@
         <v>16</v>
       </c>
       <c r="Q202" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C203" t="s">
         <v>24</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L203">
         <v>2</v>
@@ -14854,7 +14854,7 @@
         <v>16</v>
       </c>
       <c r="Q203" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="R203">
         <v>0</v>
@@ -14871,7 +14871,7 @@
         <v>195</v>
       </c>
       <c r="B204" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C204" t="s">
         <v>24</v>
@@ -14898,7 +14898,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L204">
         <v>2</v>
@@ -14916,7 +14916,7 @@
         <v>16</v>
       </c>
       <c r="Q204" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="R204">
         <v>0</v>
@@ -14933,7 +14933,7 @@
         <v>88</v>
       </c>
       <c r="B205" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C205" t="s">
         <v>24</v>
@@ -14960,7 +14960,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L205">
         <v>1</v>
@@ -14978,7 +14978,7 @@
         <v>16</v>
       </c>
       <c r="Q205" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="R205">
         <v>0</v>
@@ -14992,10 +14992,10 @@
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B206" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C206" t="s">
         <v>24</v>
@@ -15022,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L206">
         <v>0</v>
@@ -15040,7 +15040,7 @@
         <v>16</v>
       </c>
       <c r="Q206" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="R206">
         <v>0</v>
@@ -15057,7 +15057,7 @@
         <v>200</v>
       </c>
       <c r="B207" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C207" t="s">
         <v>24</v>
@@ -15084,7 +15084,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L207">
         <v>1</v>
@@ -15093,7 +15093,7 @@
         <v>1</v>
       </c>
       <c r="N207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O207">
         <v>1</v>
@@ -15102,7 +15102,7 @@
         <v>16</v>
       </c>
       <c r="Q207" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="R207">
         <v>0</v>
@@ -15119,7 +15119,7 @@
         <v>197</v>
       </c>
       <c r="B208" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C208" t="s">
         <v>24</v>
@@ -15146,7 +15146,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L208">
         <v>1</v>
@@ -15164,7 +15164,7 @@
         <v>16</v>
       </c>
       <c r="Q208" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="R208">
         <v>0</v>
@@ -15178,10 +15178,10 @@
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B209" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C209" t="s">
         <v>24</v>
@@ -15208,7 +15208,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L209">
         <v>0</v>
@@ -15226,7 +15226,7 @@
         <v>16</v>
       </c>
       <c r="Q209" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="R209">
         <v>0</v>
@@ -15243,7 +15243,7 @@
         <v>203</v>
       </c>
       <c r="B210" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C210" t="s">
         <v>24</v>
@@ -15270,7 +15270,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L210">
         <v>1</v>
@@ -15288,7 +15288,7 @@
         <v>16</v>
       </c>
       <c r="Q210" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="R210">
         <v>0</v>
@@ -15305,7 +15305,7 @@
         <v>198</v>
       </c>
       <c r="B211" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C211" t="s">
         <v>24</v>
@@ -15332,7 +15332,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L211">
         <v>2</v>
@@ -15350,7 +15350,7 @@
         <v>16</v>
       </c>
       <c r="Q211" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="R211">
         <v>0</v>
@@ -15364,10 +15364,10 @@
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B212" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C212" t="s">
         <v>24</v>
@@ -15394,7 +15394,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -15412,7 +15412,7 @@
         <v>16</v>
       </c>
       <c r="Q212" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="R212">
         <v>0</v>
@@ -15429,7 +15429,7 @@
         <v>199</v>
       </c>
       <c r="B213" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C213" t="s">
         <v>24</v>
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L213">
         <v>2</v>
@@ -15465,7 +15465,7 @@
         <v>2</v>
       </c>
       <c r="N213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O213">
         <v>2</v>
@@ -15474,7 +15474,7 @@
         <v>16</v>
       </c>
       <c r="Q213" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="R213">
         <v>0</v>
@@ -15491,7 +15491,7 @@
         <v>46</v>
       </c>
       <c r="B214" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C214" t="s">
         <v>24</v>
@@ -15518,7 +15518,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L214">
         <v>2</v>
@@ -15536,7 +15536,7 @@
         <v>16</v>
       </c>
       <c r="Q214" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15553,7 +15553,7 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C215" t="s">
         <v>24</v>
@@ -15580,7 +15580,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L215">
         <v>3</v>
@@ -15598,7 +15598,7 @@
         <v>16</v>
       </c>
       <c r="Q215" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="R215">
         <v>0</v>
@@ -15612,10 +15612,10 @@
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B216" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C216" t="s">
         <v>24</v>
@@ -15642,7 +15642,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -15660,7 +15660,7 @@
         <v>16</v>
       </c>
       <c r="Q216" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15677,7 +15677,7 @@
         <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C217" t="s">
         <v>24</v>
@@ -15704,7 +15704,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L217">
         <v>7</v>
@@ -15722,7 +15722,7 @@
         <v>16</v>
       </c>
       <c r="Q217" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>99</v>
       </c>
       <c r="B218" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -15766,7 +15766,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L218">
         <v>4</v>
@@ -15784,7 +15784,7 @@
         <v>16</v>
       </c>
       <c r="Q218" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15801,7 +15801,7 @@
         <v>103</v>
       </c>
       <c r="B219" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C219" t="s">
         <v>24</v>
@@ -15816,22 +15816,22 @@
         <v>245</v>
       </c>
       <c r="G219">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H219">
         <v>0</v>
       </c>
       <c r="I219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J219">
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M219">
         <v>3</v>
@@ -15840,13 +15840,13 @@
         <v>1</v>
       </c>
       <c r="O219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P219" t="s">
         <v>16</v>
       </c>
       <c r="Q219" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15863,7 +15863,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C220" t="s">
         <v>24</v>
@@ -15890,7 +15890,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L220">
         <v>4</v>
@@ -15908,7 +15908,7 @@
         <v>16</v>
       </c>
       <c r="Q220" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15922,10 +15922,10 @@
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B221" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C221" t="s">
         <v>24</v>
@@ -15952,7 +15952,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L221">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>16</v>
       </c>
       <c r="Q221" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="R221">
         <v>0</v>
@@ -15987,7 +15987,7 @@
         <v>79</v>
       </c>
       <c r="B222" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C222" t="s">
         <v>24</v>
@@ -16014,7 +16014,7 @@
         <v>2</v>
       </c>
       <c r="K222" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L222">
         <v>2</v>
@@ -16032,7 +16032,7 @@
         <v>16</v>
       </c>
       <c r="Q222" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="R222">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C223" t="s">
         <v>24</v>
@@ -16076,7 +16076,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L223">
         <v>14</v>
@@ -16085,7 +16085,7 @@
         <v>8</v>
       </c>
       <c r="N223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O223">
         <v>14</v>
@@ -16094,7 +16094,7 @@
         <v>16</v>
       </c>
       <c r="Q223" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="R223">
         <v>0</v>
@@ -16111,7 +16111,7 @@
         <v>48</v>
       </c>
       <c r="B224" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C224" t="s">
         <v>24</v>
@@ -16138,7 +16138,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L224">
         <v>12</v>
@@ -16156,7 +16156,7 @@
         <v>16</v>
       </c>
       <c r="Q224" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="R224">
         <v>0</v>
@@ -16173,7 +16173,7 @@
         <v>115</v>
       </c>
       <c r="B225" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C225" t="s">
         <v>24</v>
@@ -16200,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L225">
         <v>11</v>
@@ -16218,7 +16218,7 @@
         <v>16</v>
       </c>
       <c r="Q225" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -16235,7 +16235,7 @@
         <v>114</v>
       </c>
       <c r="B226" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -16262,7 +16262,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L226">
         <v>3</v>
@@ -16280,7 +16280,7 @@
         <v>16</v>
       </c>
       <c r="Q226" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -16297,7 +16297,7 @@
         <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C227" t="s">
         <v>24</v>
@@ -16324,7 +16324,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L227">
         <v>15</v>
@@ -16342,7 +16342,7 @@
         <v>16</v>
       </c>
       <c r="Q227" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="R227">
         <v>0</v>
@@ -16359,7 +16359,7 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C228" t="s">
         <v>24</v>
@@ -16386,7 +16386,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L228">
         <v>16</v>
@@ -16404,7 +16404,7 @@
         <v>16</v>
       </c>
       <c r="Q228" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="R228">
         <v>0</v>
@@ -16421,7 +16421,7 @@
         <v>50</v>
       </c>
       <c r="B229" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C229" t="s">
         <v>24</v>
@@ -16448,7 +16448,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L229">
         <v>15</v>
@@ -16457,7 +16457,7 @@
         <v>10</v>
       </c>
       <c r="N229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O229">
         <v>14</v>
@@ -16466,7 +16466,7 @@
         <v>16</v>
       </c>
       <c r="Q229" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="R229">
         <v>0</v>
@@ -16483,7 +16483,7 @@
         <v>51</v>
       </c>
       <c r="B230" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C230" t="s">
         <v>24</v>
@@ -16510,7 +16510,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L230">
         <v>6</v>
@@ -16528,7 +16528,7 @@
         <v>16</v>
       </c>
       <c r="Q230" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="R230">
         <v>0</v>
@@ -16545,7 +16545,7 @@
         <v>156</v>
       </c>
       <c r="B231" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C231" t="s">
         <v>24</v>
@@ -16572,7 +16572,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L231">
         <v>1</v>
@@ -16590,7 +16590,7 @@
         <v>16</v>
       </c>
       <c r="Q231" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="R231">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>122</v>
       </c>
       <c r="G232">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -16631,19 +16631,19 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L232">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M232">
         <v>1</v>
       </c>
       <c r="N232">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O232">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P232" t="s">
         <v>13</v>
@@ -16672,7 +16672,7 @@
         <v>122</v>
       </c>
       <c r="G233">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -16684,19 +16684,19 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L233">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M233">
         <v>1</v>
       </c>
       <c r="N233">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O233">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="P233" t="s">
         <v>13</v>
@@ -16725,7 +16725,7 @@
         <v>122</v>
       </c>
       <c r="G234">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -16737,19 +16737,19 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L234">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M234">
         <v>0</v>
       </c>
       <c r="N234">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O234">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P234" t="s">
         <v>13</v>
@@ -16778,7 +16778,7 @@
         <v>122</v>
       </c>
       <c r="G235">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -16790,19 +16790,19 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L235">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M235">
         <v>0</v>
       </c>
       <c r="N235">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O235">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P235" t="s">
         <v>13</v>
@@ -16843,7 +16843,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L236">
         <v>3</v>
@@ -16896,7 +16896,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L237">
         <v>3</v>
@@ -16949,7 +16949,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L238">
         <v>2</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L239">
         <v>2</v>
@@ -17055,7 +17055,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L240">
         <v>2</v>
@@ -17108,7 +17108,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L241">
         <v>3</v>
@@ -17161,7 +17161,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L242">
         <v>2</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L243">
         <v>2</v>
@@ -17240,10 +17240,10 @@
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>610</v>
+        <v>223</v>
       </c>
       <c r="B244" t="s">
-        <v>610</v>
+        <v>223</v>
       </c>
       <c r="C244" t="s">
         <v>120</v>
@@ -17255,7 +17255,7 @@
         <v>122</v>
       </c>
       <c r="G244">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -17267,19 +17267,19 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L244">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M244">
         <v>0</v>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P244" t="s">
         <v>13</v>
@@ -17308,7 +17308,7 @@
         <v>122</v>
       </c>
       <c r="G245">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H245">
         <v>0</v>
@@ -17320,19 +17320,19 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L245">
+        <v>5</v>
+      </c>
+      <c r="M245">
+        <v>1</v>
+      </c>
+      <c r="N245">
         <v>3</v>
       </c>
-      <c r="M245">
-        <v>1</v>
-      </c>
-      <c r="N245">
-        <v>1</v>
-      </c>
       <c r="O245">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P245" t="s">
         <v>13</v>
@@ -17361,7 +17361,7 @@
         <v>122</v>
       </c>
       <c r="G246">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -17373,19 +17373,19 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L246">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M246">
         <v>0</v>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O246">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P246" t="s">
         <v>13</v>
@@ -17414,7 +17414,7 @@
         <v>122</v>
       </c>
       <c r="G247">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H247">
         <v>0</v>
@@ -17426,19 +17426,19 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L247">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O247">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P247" t="s">
         <v>13</v>
@@ -17452,10 +17452,10 @@
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>611</v>
+        <v>221</v>
       </c>
       <c r="B248" t="s">
-        <v>611</v>
+        <v>221</v>
       </c>
       <c r="C248" t="s">
         <v>120</v>
@@ -17467,7 +17467,7 @@
         <v>122</v>
       </c>
       <c r="G248">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -17479,19 +17479,19 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L248">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M248">
         <v>0</v>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P248" t="s">
         <v>13</v>
@@ -17520,7 +17520,7 @@
         <v>122</v>
       </c>
       <c r="G249">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -17532,19 +17532,19 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L249">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M249">
         <v>0</v>
       </c>
       <c r="N249">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O249">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P249" t="s">
         <v>13</v>
@@ -17573,7 +17573,7 @@
         <v>122</v>
       </c>
       <c r="G250">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -17585,19 +17585,19 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L250">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M250">
         <v>1</v>
       </c>
       <c r="N250">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O250">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P250" t="s">
         <v>13</v>
@@ -17611,10 +17611,10 @@
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>612</v>
+        <v>222</v>
       </c>
       <c r="B251" t="s">
-        <v>612</v>
+        <v>222</v>
       </c>
       <c r="C251" t="s">
         <v>120</v>
@@ -17626,7 +17626,7 @@
         <v>122</v>
       </c>
       <c r="G251">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H251">
         <v>0</v>
@@ -17638,19 +17638,19 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L251">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M251">
         <v>0</v>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P251" t="s">
         <v>13</v>
@@ -17691,7 +17691,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L252">
         <v>4</v>
@@ -17744,7 +17744,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L253">
         <v>8</v>
@@ -17797,7 +17797,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L254">
         <v>3</v>
@@ -17850,7 +17850,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L255">
         <v>4</v>
@@ -17891,7 +17891,7 @@
         <v>122</v>
       </c>
       <c r="G256">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -17903,19 +17903,19 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L256">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M256">
         <v>0</v>
       </c>
       <c r="N256">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O256">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P256" t="s">
         <v>13</v>
@@ -17956,7 +17956,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L257">
         <v>2</v>
@@ -17997,7 +17997,7 @@
         <v>122</v>
       </c>
       <c r="G258">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -18009,19 +18009,19 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L258">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M258">
         <v>0</v>
       </c>
       <c r="N258">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O258">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P258" t="s">
         <v>13</v>
@@ -18062,7 +18062,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L259">
         <v>3</v>
@@ -18115,7 +18115,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L260">
         <v>19</v>
@@ -18159,7 +18159,7 @@
         <v>179</v>
       </c>
       <c r="G261">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="I261">
         <v>0</v>
@@ -18168,19 +18168,19 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L261">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M261">
         <v>0</v>
       </c>
       <c r="N261">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O261">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P261" t="s">
         <v>180</v>
@@ -18221,7 +18221,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L262">
         <v>18</v>
@@ -18274,7 +18274,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="L263">
         <v>18</v>
@@ -18305,8 +18305,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15246664-CEEF-4123-99C4-956D1571B799}">
-  <dimension ref="A1:J640"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB57410-7915-4F75-A262-5D598FF1A375}">
+  <dimension ref="A1:J676"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -38655,6 +38655,726 @@
       </c>
       <c r="J640" t="s">
         <v>180</v>
+      </c>
+    </row>
+    <row r="641" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A641" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B641" t="s">
+        <v>201</v>
+      </c>
+      <c r="E641" t="s">
+        <v>168</v>
+      </c>
+      <c r="F641" t="s">
+        <v>94</v>
+      </c>
+      <c r="I641">
+        <v>1</v>
+      </c>
+      <c r="J641" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="642" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A642" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B642" t="s">
+        <v>39</v>
+      </c>
+      <c r="E642" t="s">
+        <v>219</v>
+      </c>
+      <c r="F642" t="s">
+        <v>94</v>
+      </c>
+      <c r="I642">
+        <v>1</v>
+      </c>
+      <c r="J642" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="643" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A643" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B643" t="s">
+        <v>67</v>
+      </c>
+      <c r="E643" t="s">
+        <v>219</v>
+      </c>
+      <c r="F643" t="s">
+        <v>94</v>
+      </c>
+      <c r="I643">
+        <v>1</v>
+      </c>
+      <c r="J643" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="644" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A644" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B644" t="s">
+        <v>57</v>
+      </c>
+      <c r="E644" t="s">
+        <v>219</v>
+      </c>
+      <c r="F644" t="s">
+        <v>94</v>
+      </c>
+      <c r="I644">
+        <v>1</v>
+      </c>
+      <c r="J644" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="645" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A645" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B645" t="s">
+        <v>23</v>
+      </c>
+      <c r="E645" t="s">
+        <v>53</v>
+      </c>
+      <c r="F645" t="s">
+        <v>94</v>
+      </c>
+      <c r="I645">
+        <v>1</v>
+      </c>
+      <c r="J645" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="646" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A646" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B646" t="s">
+        <v>220</v>
+      </c>
+      <c r="E646" t="s">
+        <v>100</v>
+      </c>
+      <c r="F646" t="s">
+        <v>94</v>
+      </c>
+      <c r="I646">
+        <v>1</v>
+      </c>
+      <c r="J646" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="647" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A647" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B647" t="s">
+        <v>221</v>
+      </c>
+      <c r="E647" t="s">
+        <v>188</v>
+      </c>
+      <c r="F647" t="s">
+        <v>94</v>
+      </c>
+      <c r="I647">
+        <v>2</v>
+      </c>
+      <c r="J647" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="648" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A648" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B648" t="s">
+        <v>173</v>
+      </c>
+      <c r="E648" t="s">
+        <v>188</v>
+      </c>
+      <c r="F648" t="s">
+        <v>94</v>
+      </c>
+      <c r="I648">
+        <v>2</v>
+      </c>
+      <c r="J648" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="649" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A649" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B649" t="s">
+        <v>217</v>
+      </c>
+      <c r="E649" t="s">
+        <v>188</v>
+      </c>
+      <c r="F649" t="s">
+        <v>94</v>
+      </c>
+      <c r="I649">
+        <v>2</v>
+      </c>
+      <c r="J649" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="650" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A650" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B650" t="s">
+        <v>202</v>
+      </c>
+      <c r="E650" t="s">
+        <v>188</v>
+      </c>
+      <c r="F650" t="s">
+        <v>94</v>
+      </c>
+      <c r="I650">
+        <v>2</v>
+      </c>
+      <c r="J650" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="651" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A651" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B651" t="s">
+        <v>185</v>
+      </c>
+      <c r="E651" t="s">
+        <v>188</v>
+      </c>
+      <c r="F651" t="s">
+        <v>94</v>
+      </c>
+      <c r="I651">
+        <v>2</v>
+      </c>
+      <c r="J651" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="652" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A652" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B652" t="s">
+        <v>174</v>
+      </c>
+      <c r="E652" t="s">
+        <v>188</v>
+      </c>
+      <c r="F652" t="s">
+        <v>94</v>
+      </c>
+      <c r="I652">
+        <v>2</v>
+      </c>
+      <c r="J652" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="653" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A653" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B653" t="s">
+        <v>125</v>
+      </c>
+      <c r="E653" t="s">
+        <v>188</v>
+      </c>
+      <c r="F653" t="s">
+        <v>94</v>
+      </c>
+      <c r="I653">
+        <v>2</v>
+      </c>
+      <c r="J653" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="654" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A654" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B654" t="s">
+        <v>216</v>
+      </c>
+      <c r="E654" t="s">
+        <v>188</v>
+      </c>
+      <c r="F654" t="s">
+        <v>94</v>
+      </c>
+      <c r="I654">
+        <v>2</v>
+      </c>
+      <c r="J654" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="655" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A655" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B655" t="s">
+        <v>222</v>
+      </c>
+      <c r="E655" t="s">
+        <v>188</v>
+      </c>
+      <c r="F655" t="s">
+        <v>94</v>
+      </c>
+      <c r="I655">
+        <v>2</v>
+      </c>
+      <c r="J655" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="656" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A656" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B656" t="s">
+        <v>223</v>
+      </c>
+      <c r="E656" t="s">
+        <v>188</v>
+      </c>
+      <c r="F656" t="s">
+        <v>94</v>
+      </c>
+      <c r="I656">
+        <v>2</v>
+      </c>
+      <c r="J656" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="657" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A657" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B657" t="s">
+        <v>123</v>
+      </c>
+      <c r="E657" t="s">
+        <v>188</v>
+      </c>
+      <c r="F657" t="s">
+        <v>94</v>
+      </c>
+      <c r="I657">
+        <v>2</v>
+      </c>
+      <c r="J657" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="658" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A658" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B658" t="s">
+        <v>172</v>
+      </c>
+      <c r="E658" t="s">
+        <v>188</v>
+      </c>
+      <c r="F658" t="s">
+        <v>94</v>
+      </c>
+      <c r="I658">
+        <v>2</v>
+      </c>
+      <c r="J658" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="659" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A659" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B659" t="s">
+        <v>221</v>
+      </c>
+      <c r="E659" t="s">
+        <v>188</v>
+      </c>
+      <c r="F659" t="s">
+        <v>94</v>
+      </c>
+      <c r="I659">
+        <v>2</v>
+      </c>
+      <c r="J659" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="660" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A660" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B660" t="s">
+        <v>221</v>
+      </c>
+      <c r="E660" t="s">
+        <v>188</v>
+      </c>
+      <c r="F660" t="s">
+        <v>94</v>
+      </c>
+      <c r="I660">
+        <v>2</v>
+      </c>
+      <c r="J660" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="661" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A661" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B661" t="s">
+        <v>173</v>
+      </c>
+      <c r="E661" t="s">
+        <v>188</v>
+      </c>
+      <c r="F661" t="s">
+        <v>94</v>
+      </c>
+      <c r="I661">
+        <v>2</v>
+      </c>
+      <c r="J661" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="662" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A662" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B662" t="s">
+        <v>173</v>
+      </c>
+      <c r="E662" t="s">
+        <v>188</v>
+      </c>
+      <c r="F662" t="s">
+        <v>94</v>
+      </c>
+      <c r="I662">
+        <v>2</v>
+      </c>
+      <c r="J662" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="663" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A663" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B663" t="s">
+        <v>173</v>
+      </c>
+      <c r="E663" t="s">
+        <v>188</v>
+      </c>
+      <c r="F663" t="s">
+        <v>94</v>
+      </c>
+      <c r="I663">
+        <v>2</v>
+      </c>
+      <c r="J663" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="664" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A664" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B664" t="s">
+        <v>173</v>
+      </c>
+      <c r="E664" t="s">
+        <v>188</v>
+      </c>
+      <c r="F664" t="s">
+        <v>94</v>
+      </c>
+      <c r="I664">
+        <v>2</v>
+      </c>
+      <c r="J664" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="665" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A665" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B665" t="s">
+        <v>202</v>
+      </c>
+      <c r="E665" t="s">
+        <v>188</v>
+      </c>
+      <c r="F665" t="s">
+        <v>94</v>
+      </c>
+      <c r="I665">
+        <v>2</v>
+      </c>
+      <c r="J665" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="666" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A666" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B666" t="s">
+        <v>202</v>
+      </c>
+      <c r="E666" t="s">
+        <v>188</v>
+      </c>
+      <c r="F666" t="s">
+        <v>94</v>
+      </c>
+      <c r="I666">
+        <v>2</v>
+      </c>
+      <c r="J666" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="667" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A667" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B667" t="s">
+        <v>217</v>
+      </c>
+      <c r="E667" t="s">
+        <v>188</v>
+      </c>
+      <c r="F667" t="s">
+        <v>94</v>
+      </c>
+      <c r="I667">
+        <v>2</v>
+      </c>
+      <c r="J667" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="668" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A668" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B668" t="s">
+        <v>217</v>
+      </c>
+      <c r="E668" t="s">
+        <v>188</v>
+      </c>
+      <c r="F668" t="s">
+        <v>94</v>
+      </c>
+      <c r="I668">
+        <v>2</v>
+      </c>
+      <c r="J668" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="669" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A669" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B669" t="s">
+        <v>173</v>
+      </c>
+      <c r="E669" t="s">
+        <v>133</v>
+      </c>
+      <c r="F669" t="s">
+        <v>94</v>
+      </c>
+      <c r="I669">
+        <v>1</v>
+      </c>
+      <c r="J669" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="670" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A670" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B670" t="s">
+        <v>139</v>
+      </c>
+      <c r="E670" t="s">
+        <v>133</v>
+      </c>
+      <c r="F670" t="s">
+        <v>94</v>
+      </c>
+      <c r="I670">
+        <v>1</v>
+      </c>
+      <c r="J670" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="671" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A671" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B671" t="s">
+        <v>137</v>
+      </c>
+      <c r="E671" t="s">
+        <v>133</v>
+      </c>
+      <c r="F671" t="s">
+        <v>94</v>
+      </c>
+      <c r="I671">
+        <v>1</v>
+      </c>
+      <c r="J671" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="672" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A672" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B672" t="s">
+        <v>174</v>
+      </c>
+      <c r="E672" t="s">
+        <v>133</v>
+      </c>
+      <c r="F672" t="s">
+        <v>66</v>
+      </c>
+      <c r="I672">
+        <v>1</v>
+      </c>
+      <c r="J672" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="673" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A673" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B673" t="s">
+        <v>224</v>
+      </c>
+      <c r="E673" t="s">
+        <v>53</v>
+      </c>
+      <c r="F673" t="s">
+        <v>94</v>
+      </c>
+      <c r="I673">
+        <v>1</v>
+      </c>
+      <c r="J673" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="674" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A674" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B674" t="s">
+        <v>125</v>
+      </c>
+      <c r="E674" t="s">
+        <v>207</v>
+      </c>
+      <c r="F674" t="s">
+        <v>94</v>
+      </c>
+      <c r="I674">
+        <v>1</v>
+      </c>
+      <c r="J674" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="675" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A675" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B675" t="s">
+        <v>103</v>
+      </c>
+      <c r="E675" t="s">
+        <v>100</v>
+      </c>
+      <c r="F675" t="s">
+        <v>94</v>
+      </c>
+      <c r="I675">
+        <v>1</v>
+      </c>
+      <c r="J675" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="676" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A676" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B676" t="s">
+        <v>112</v>
+      </c>
+      <c r="E676" t="s">
+        <v>100</v>
+      </c>
+      <c r="F676" t="s">
+        <v>94</v>
+      </c>
+      <c r="I676">
+        <v>1</v>
+      </c>
+      <c r="J676" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ED13D8B-1554-47F3-8A77-143E0B09C3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8A06417-F9D6-41F5-8BDB-2BFAF890F3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{DB096BD8-C3F9-466B-9288-40B14382B998}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F71C5E45-BA1A-4D57-8B28-3EA6077F2E69}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6636" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="617">
   <si>
     <t>날짜</t>
   </si>
@@ -2276,7 +2276,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C1DBD6-F3CA-4E55-A611-25A79AE89B91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF5402B9-669B-4632-B108-77DDC2781047}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -16672,7 +16672,7 @@
         <v>122</v>
       </c>
       <c r="G233">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -16687,16 +16687,16 @@
         <v>240</v>
       </c>
       <c r="L233">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M233">
         <v>1</v>
       </c>
       <c r="N233">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O233">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="P233" t="s">
         <v>13</v>
@@ -16725,7 +16725,7 @@
         <v>122</v>
       </c>
       <c r="G234">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -16740,16 +16740,16 @@
         <v>240</v>
       </c>
       <c r="L234">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M234">
         <v>0</v>
       </c>
       <c r="N234">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O234">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P234" t="s">
         <v>13</v>
@@ -16778,7 +16778,7 @@
         <v>122</v>
       </c>
       <c r="G235">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -16793,16 +16793,16 @@
         <v>240</v>
       </c>
       <c r="L235">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M235">
         <v>0</v>
       </c>
       <c r="N235">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O235">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P235" t="s">
         <v>13</v>
@@ -17467,7 +17467,7 @@
         <v>122</v>
       </c>
       <c r="G248">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -17482,16 +17482,16 @@
         <v>240</v>
       </c>
       <c r="L248">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M248">
         <v>0</v>
       </c>
       <c r="N248">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O248">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P248" t="s">
         <v>13</v>
@@ -18305,8 +18305,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB57410-7915-4F75-A262-5D598FF1A375}">
-  <dimension ref="A1:J676"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03A9F8B-D1DD-47B7-B4F6-645F524889CF}">
+  <dimension ref="A1:J666"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -39022,16 +39022,16 @@
         <v>46241</v>
       </c>
       <c r="B659" t="s">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="E659" t="s">
-        <v>188</v>
+        <v>133</v>
       </c>
       <c r="F659" t="s">
         <v>94</v>
       </c>
       <c r="I659">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J659" t="s">
         <v>13</v>
@@ -39042,16 +39042,16 @@
         <v>46241</v>
       </c>
       <c r="B660" t="s">
-        <v>221</v>
+        <v>139</v>
       </c>
       <c r="E660" t="s">
-        <v>188</v>
+        <v>133</v>
       </c>
       <c r="F660" t="s">
         <v>94</v>
       </c>
       <c r="I660">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J660" t="s">
         <v>13</v>
@@ -39062,16 +39062,16 @@
         <v>46241</v>
       </c>
       <c r="B661" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="E661" t="s">
-        <v>188</v>
+        <v>133</v>
       </c>
       <c r="F661" t="s">
         <v>94</v>
       </c>
       <c r="I661">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J661" t="s">
         <v>13</v>
@@ -39082,16 +39082,16 @@
         <v>46241</v>
       </c>
       <c r="B662" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E662" t="s">
-        <v>188</v>
+        <v>133</v>
       </c>
       <c r="F662" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="I662">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J662" t="s">
         <v>13</v>
@@ -39102,19 +39102,19 @@
         <v>46241</v>
       </c>
       <c r="B663" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="E663" t="s">
-        <v>188</v>
+        <v>53</v>
       </c>
       <c r="F663" t="s">
         <v>94</v>
       </c>
       <c r="I663">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J663" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="664" spans="1:10" x14ac:dyDescent="0.3">
@@ -39122,16 +39122,16 @@
         <v>46241</v>
       </c>
       <c r="B664" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="E664" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="F664" t="s">
         <v>94</v>
       </c>
       <c r="I664">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J664" t="s">
         <v>13</v>
@@ -39142,19 +39142,19 @@
         <v>46241</v>
       </c>
       <c r="B665" t="s">
-        <v>202</v>
+        <v>103</v>
       </c>
       <c r="E665" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="F665" t="s">
         <v>94</v>
       </c>
       <c r="I665">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J665" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="666" spans="1:10" x14ac:dyDescent="0.3">
@@ -39162,218 +39162,18 @@
         <v>46241</v>
       </c>
       <c r="B666" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="E666" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="F666" t="s">
         <v>94</v>
       </c>
       <c r="I666">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J666" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="667" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A667" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B667" t="s">
-        <v>217</v>
-      </c>
-      <c r="E667" t="s">
-        <v>188</v>
-      </c>
-      <c r="F667" t="s">
-        <v>94</v>
-      </c>
-      <c r="I667">
-        <v>2</v>
-      </c>
-      <c r="J667" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="668" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A668" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B668" t="s">
-        <v>217</v>
-      </c>
-      <c r="E668" t="s">
-        <v>188</v>
-      </c>
-      <c r="F668" t="s">
-        <v>94</v>
-      </c>
-      <c r="I668">
-        <v>2</v>
-      </c>
-      <c r="J668" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="669" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A669" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B669" t="s">
-        <v>173</v>
-      </c>
-      <c r="E669" t="s">
-        <v>133</v>
-      </c>
-      <c r="F669" t="s">
-        <v>94</v>
-      </c>
-      <c r="I669">
-        <v>1</v>
-      </c>
-      <c r="J669" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="670" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A670" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B670" t="s">
-        <v>139</v>
-      </c>
-      <c r="E670" t="s">
-        <v>133</v>
-      </c>
-      <c r="F670" t="s">
-        <v>94</v>
-      </c>
-      <c r="I670">
-        <v>1</v>
-      </c>
-      <c r="J670" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="671" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A671" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B671" t="s">
-        <v>137</v>
-      </c>
-      <c r="E671" t="s">
-        <v>133</v>
-      </c>
-      <c r="F671" t="s">
-        <v>94</v>
-      </c>
-      <c r="I671">
-        <v>1</v>
-      </c>
-      <c r="J671" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="672" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A672" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B672" t="s">
-        <v>174</v>
-      </c>
-      <c r="E672" t="s">
-        <v>133</v>
-      </c>
-      <c r="F672" t="s">
-        <v>66</v>
-      </c>
-      <c r="I672">
-        <v>1</v>
-      </c>
-      <c r="J672" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="673" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A673" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B673" t="s">
-        <v>224</v>
-      </c>
-      <c r="E673" t="s">
-        <v>53</v>
-      </c>
-      <c r="F673" t="s">
-        <v>94</v>
-      </c>
-      <c r="I673">
-        <v>1</v>
-      </c>
-      <c r="J673" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="674" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A674" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B674" t="s">
-        <v>125</v>
-      </c>
-      <c r="E674" t="s">
-        <v>207</v>
-      </c>
-      <c r="F674" t="s">
-        <v>94</v>
-      </c>
-      <c r="I674">
-        <v>1</v>
-      </c>
-      <c r="J674" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="675" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A675" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B675" t="s">
-        <v>103</v>
-      </c>
-      <c r="E675" t="s">
-        <v>100</v>
-      </c>
-      <c r="F675" t="s">
-        <v>94</v>
-      </c>
-      <c r="I675">
-        <v>1</v>
-      </c>
-      <c r="J675" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="676" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A676" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B676" t="s">
-        <v>112</v>
-      </c>
-      <c r="E676" t="s">
-        <v>100</v>
-      </c>
-      <c r="F676" t="s">
-        <v>94</v>
-      </c>
-      <c r="I676">
-        <v>1</v>
-      </c>
-      <c r="J676" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data_general.xlsx
+++ b/data_general.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idoogen\Desktop\바오지_웹배포\baoji-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8A06417-F9D6-41F5-8BDB-2BFAF890F3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C21285B-9EF8-4B6F-88BD-22D211459EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F71C5E45-BA1A-4D57-8B28-3EA6077F2E69}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{3CC8B3D9-C0A9-4D42-A1A4-867612927143}"/>
   </bookViews>
   <sheets>
     <sheet name="재고현황" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6856" uniqueCount="617">
   <si>
     <t>날짜</t>
   </si>
@@ -717,6 +717,9 @@
     <t>BJM931-GYOR280</t>
   </si>
   <si>
+    <t>ECW304-BK255</t>
+  </si>
+  <si>
     <t>상품명</t>
   </si>
   <si>
@@ -1837,9 +1840,6 @@
   </si>
   <si>
     <t>ECW304BK 바오지 여성 러닝화 블랙 250</t>
-  </si>
-  <si>
-    <t>ECW304-BK255</t>
   </si>
   <si>
     <t>ECW304BK 바오지 여성 러닝화 블랙 255</t>
@@ -2276,7 +2276,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF5402B9-669B-4632-B108-77DDC2781047}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53F1BE4-E949-483E-988F-12924FC2F5B1}">
   <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2285,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2300,46 +2300,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P1" t="s">
         <v>9</v>
       </c>
       <c r="Q1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="R1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -2347,7 +2347,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -2362,37 +2362,37 @@
         <v>260</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P2" t="s">
         <v>16</v>
       </c>
       <c r="Q2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -2454,7 +2454,7 @@
         <v>16</v>
       </c>
       <c r="Q3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -2516,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="Q4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2578,7 +2578,7 @@
         <v>16</v>
       </c>
       <c r="Q5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -2595,7 +2595,7 @@
         <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2622,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -2640,7 +2640,7 @@
         <v>16</v>
       </c>
       <c r="Q6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2657,7 +2657,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -2702,7 +2702,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L8">
         <v>2</v>
@@ -2764,7 +2764,7 @@
         <v>16</v>
       </c>
       <c r="Q8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2781,7 +2781,7 @@
         <v>152</v>
       </c>
       <c r="B9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L9">
         <v>4</v>
@@ -2826,7 +2826,7 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -2888,7 +2888,7 @@
         <v>16</v>
       </c>
       <c r="Q10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -2950,7 +2950,7 @@
         <v>16</v>
       </c>
       <c r="Q11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2964,16 +2964,16 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3026,16 +3026,16 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" t="s">
+        <v>258</v>
+      </c>
+      <c r="C13" t="s">
+        <v>255</v>
+      </c>
+      <c r="D13" t="s">
         <v>256</v>
-      </c>
-      <c r="B13" t="s">
-        <v>257</v>
-      </c>
-      <c r="C13" t="s">
-        <v>254</v>
-      </c>
-      <c r="D13" t="s">
-        <v>255</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3056,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3088,16 +3088,16 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3150,16 +3150,16 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3212,16 +3212,16 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3336,16 +3336,16 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3366,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3398,16 +3398,16 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -3460,16 +3460,16 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -3522,16 +3522,16 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B21" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3584,16 +3584,16 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3614,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3646,16 +3646,16 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3708,16 +3708,16 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3770,16 +3770,16 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -3832,16 +3832,16 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3956,16 +3956,16 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C28" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D28" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4018,16 +4018,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -4048,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4080,16 +4080,16 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4142,16 +4142,16 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4204,16 +4204,16 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4266,16 +4266,16 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>298</v>
+      </c>
+      <c r="B33" t="s">
+        <v>299</v>
+      </c>
+      <c r="C33" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" t="s">
         <v>297</v>
-      </c>
-      <c r="B33" t="s">
-        <v>298</v>
-      </c>
-      <c r="C33" t="s">
-        <v>254</v>
-      </c>
-      <c r="D33" t="s">
-        <v>296</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4328,16 +4328,16 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -4390,16 +4390,16 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -4452,16 +4452,16 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -4514,16 +4514,16 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4576,16 +4576,16 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D38" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -4638,16 +4638,16 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D39" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4668,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -4700,16 +4700,16 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D40" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -4762,16 +4762,16 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D41" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4792,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -4824,16 +4824,16 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C42" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D42" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4854,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -4886,16 +4886,16 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D43" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4916,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -4948,16 +4948,16 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C44" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D44" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -5010,16 +5010,16 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C45" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D45" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -5040,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -5072,16 +5072,16 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D46" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -5134,16 +5134,16 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D47" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -5196,16 +5196,16 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B48" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C48" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D48" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -5258,16 +5258,16 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C49" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D49" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -5320,16 +5320,16 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C50" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D50" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -5350,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -5382,16 +5382,16 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C51" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D51" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -5444,16 +5444,16 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C52" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D52" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -5506,16 +5506,16 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>339</v>
+      </c>
+      <c r="B53" t="s">
+        <v>340</v>
+      </c>
+      <c r="C53" t="s">
+        <v>255</v>
+      </c>
+      <c r="D53" t="s">
         <v>338</v>
-      </c>
-      <c r="B53" t="s">
-        <v>339</v>
-      </c>
-      <c r="C53" t="s">
-        <v>254</v>
-      </c>
-      <c r="D53" t="s">
-        <v>337</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -5536,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -5568,16 +5568,16 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D54" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -5630,16 +5630,16 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B55" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D55" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5660,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -5692,16 +5692,16 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B56" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D56" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5722,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -5754,16 +5754,16 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B57" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C57" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D57" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5784,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -5816,16 +5816,16 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C58" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D58" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5846,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -5878,16 +5878,16 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B59" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C59" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D59" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -5940,16 +5940,16 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B60" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C60" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D60" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -6002,16 +6002,16 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B61" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C61" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D61" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -6032,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -6064,16 +6064,16 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B62" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C62" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D62" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -6126,16 +6126,16 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B63" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -6188,16 +6188,16 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B64" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C64" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D64" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -6218,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -6250,16 +6250,16 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C65" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D65" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -6280,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -6312,16 +6312,16 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B66" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C66" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D66" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -6342,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -6377,7 +6377,7 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -6404,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L67">
         <v>4</v>
@@ -6422,7 +6422,7 @@
         <v>16</v>
       </c>
       <c r="Q67" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -6439,7 +6439,7 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L68">
         <v>4</